--- a/database/controller_excel/Resguardo_Alejandro_Cancino_Arguello.xlsx
+++ b/database/controller_excel/Resguardo_Alejandro_Cancino_Arguello.xlsx
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>23/04/2025</t>
+    <t>24/04/2025</t>
   </si>
   <si>
     <t>Nombre:</t>

--- a/database/controller_excel/Resguardo_Alejandro_Cancino_Arguello.xlsx
+++ b/database/controller_excel/Resguardo_Alejandro_Cancino_Arguello.xlsx
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>24/04/2025</t>
+    <t>28/04/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -86,6 +86,450 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>XPS 13 9315</t>
+  </si>
+  <si>
+    <t>29502T3</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00154</t>
+  </si>
+  <si>
+    <t>Desktop</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>Elite Desk 800 G1</t>
+  </si>
+  <si>
+    <t>MXL5071Z2Q</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00027</t>
+  </si>
+  <si>
+    <t>EliteDesk 800G1</t>
+  </si>
+  <si>
+    <t>MXL4503CFF</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00110</t>
+  </si>
+  <si>
+    <t>CALL MANAGER NUEVO</t>
+  </si>
+  <si>
+    <t>CISCO</t>
+  </si>
+  <si>
+    <t>UCS C220M3BE</t>
+  </si>
+  <si>
+    <t>220M3222</t>
+  </si>
+  <si>
+    <t>SERVIDOR 19</t>
+  </si>
+  <si>
+    <t>POWEREDGE R710</t>
+  </si>
+  <si>
+    <t>BRNFSL1</t>
+  </si>
+  <si>
+    <t>SERVIDOR 18</t>
+  </si>
+  <si>
+    <t>POWEREDGE R720</t>
+  </si>
+  <si>
+    <t>B3X7RV1</t>
+  </si>
+  <si>
+    <t>SAN</t>
+  </si>
+  <si>
+    <t>POWERVAULT MD3200i</t>
+  </si>
+  <si>
+    <t>48DT7V1</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>UNIDAD DE CINTAS 19</t>
+  </si>
+  <si>
+    <t>POWER VAULT 114 X</t>
+  </si>
+  <si>
+    <t>YN106813H628</t>
+  </si>
+  <si>
+    <t>SERVIDOR 27</t>
+  </si>
+  <si>
+    <t>POWEREDGE 2950</t>
+  </si>
+  <si>
+    <t>DPBP6K1</t>
+  </si>
+  <si>
+    <t>SERVIDOR 29</t>
+  </si>
+  <si>
+    <t>POWEREDGE R320</t>
+  </si>
+  <si>
+    <t>D64MW12</t>
+  </si>
+  <si>
+    <t>UNIDAD DE CINTAS</t>
+  </si>
+  <si>
+    <t>POWER VAULT 124 T</t>
+  </si>
+  <si>
+    <t>8DDB6K1</t>
+  </si>
+  <si>
+    <t>Switch Linksys Cisco SD216</t>
+  </si>
+  <si>
+    <t>SD216</t>
+  </si>
+  <si>
+    <t>S/N</t>
+  </si>
+  <si>
+    <t>NVR</t>
+  </si>
+  <si>
+    <t>HIKVISION</t>
+  </si>
+  <si>
+    <t>DS-7616NI-K2/16P</t>
+  </si>
+  <si>
+    <t>L48074542</t>
+  </si>
+  <si>
+    <t>DVR HIKVISION</t>
+  </si>
+  <si>
+    <t>DS-7716NI-I4/16P</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>3D Optical</t>
+  </si>
+  <si>
+    <t>Switch 8 Puertos</t>
+  </si>
+  <si>
+    <t>Planet</t>
+  </si>
+  <si>
+    <t>GSD-804P</t>
+  </si>
+  <si>
+    <t>A350106300034</t>
+  </si>
+  <si>
+    <t>Access PRO</t>
+  </si>
+  <si>
+    <t>AP233</t>
+  </si>
+  <si>
+    <t>AP234</t>
+  </si>
+  <si>
+    <t>Switch</t>
+  </si>
+  <si>
+    <t>Cisco</t>
+  </si>
+  <si>
+    <t>CATALYST 2960-X SERIES</t>
+  </si>
+  <si>
+    <t>FCW1906B1MY</t>
+  </si>
+  <si>
+    <t>FCW1906B1LJ</t>
+  </si>
+  <si>
+    <t>FCW1906B1MM</t>
+  </si>
+  <si>
+    <t>CATALYST 2960-X SERIES POE+</t>
+  </si>
+  <si>
+    <t>FOC1710Y1FV</t>
+  </si>
+  <si>
+    <t>CATALYST 3560</t>
+  </si>
+  <si>
+    <t>CAT0948R334</t>
+  </si>
+  <si>
+    <t>F0C1503Z3QP</t>
+  </si>
+  <si>
+    <t>F0C1514X0EZ</t>
+  </si>
+  <si>
+    <t>FOC1903S1ME</t>
+  </si>
+  <si>
+    <t>Catalyst 3750X-24T-E</t>
+  </si>
+  <si>
+    <t>FD01816Z3AU</t>
+  </si>
+  <si>
+    <t>FIREWALL</t>
+  </si>
+  <si>
+    <t>FORTINET</t>
+  </si>
+  <si>
+    <t>FG100D3G14827870</t>
+  </si>
+  <si>
+    <t>FG100D3G14827806 MASTER</t>
+  </si>
+  <si>
+    <t>FG100D3G14827806</t>
+  </si>
+  <si>
+    <t>FG100D3G14827870 SLAVE</t>
+  </si>
+  <si>
+    <t>CALL MANAGER</t>
+  </si>
+  <si>
+    <t>FTX1328AHLG</t>
+  </si>
+  <si>
+    <t>ROUTER</t>
+  </si>
+  <si>
+    <t>CISCO 1900 SERIES</t>
+  </si>
+  <si>
+    <t>CFTX1614857Q</t>
+  </si>
+  <si>
+    <t>FTX174386AU</t>
+  </si>
+  <si>
+    <t>UPS</t>
+  </si>
+  <si>
+    <t>APC</t>
+  </si>
+  <si>
+    <t>APC Galaxy 3500</t>
+  </si>
+  <si>
+    <t>G35TF30KB4F</t>
+  </si>
+  <si>
+    <t>ACCESSPOINT</t>
+  </si>
+  <si>
+    <t>221E</t>
+  </si>
+  <si>
+    <t>FP221ETF22083298</t>
+  </si>
+  <si>
+    <t>FP221ETF22083291</t>
+  </si>
+  <si>
+    <t>FP221ETF22083300</t>
+  </si>
+  <si>
+    <t>FP221ETF22083299</t>
+  </si>
+  <si>
+    <t>Amplificador celular</t>
+  </si>
+  <si>
+    <t>EPCOM</t>
+  </si>
+  <si>
+    <t>G08W27160502</t>
+  </si>
+  <si>
+    <t>Camara Fija</t>
+  </si>
+  <si>
+    <t>DS-2CD2432F-I</t>
+  </si>
+  <si>
+    <t>I20140922CCWR480540694</t>
+  </si>
+  <si>
+    <t>DS-2CD1043G0-I</t>
+  </si>
+  <si>
+    <t>I20220824AAWRK47327687</t>
+  </si>
+  <si>
+    <t>Camara PTZ</t>
+  </si>
+  <si>
+    <t>DS-2DE4215IW-DE</t>
+  </si>
+  <si>
+    <t>DE20190506CCWRD16875921W</t>
+  </si>
+  <si>
+    <t>DS-2CD2232-I5</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802490</t>
+  </si>
+  <si>
+    <t>I20200824AAWRK47327674</t>
+  </si>
+  <si>
+    <t>DS-2DE7174-A</t>
+  </si>
+  <si>
+    <t>A20150122CCWR500502005</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802472</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802475</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802494</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802491</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802480</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802497</t>
+  </si>
+  <si>
+    <t>DS-2CD2422FWD-IW</t>
+  </si>
+  <si>
+    <t>IW20170808AAWR808998451</t>
+  </si>
+  <si>
+    <t>I20140922CCWR480540755</t>
+  </si>
+  <si>
+    <t>I20140922CCWR480540785</t>
+  </si>
+  <si>
+    <t>DS-2CD2T42WD-I5</t>
+  </si>
+  <si>
+    <t>I520160810BBWR633078836</t>
+  </si>
+  <si>
+    <t>I520160810BBWR633078735</t>
+  </si>
+  <si>
+    <t>I520160810BBWR633078506</t>
+  </si>
+  <si>
+    <t>A20150122CCWR500502035</t>
+  </si>
+  <si>
+    <t>KOBLENZ</t>
+  </si>
+  <si>
+    <t>4816 R</t>
+  </si>
+  <si>
+    <t>16-09-17766</t>
+  </si>
+  <si>
+    <t>Lector Biometrico</t>
+  </si>
+  <si>
+    <t>BioEntry W2</t>
+  </si>
+  <si>
+    <t>BEW2-0DP</t>
+  </si>
+  <si>
+    <t>Equipo de Videoconferencia</t>
+  </si>
+  <si>
+    <t>Chromebox</t>
+  </si>
+  <si>
+    <t>Asus</t>
+  </si>
+  <si>
+    <t>H6MSCX001323</t>
+  </si>
+  <si>
+    <t>Camara Videoconferencia</t>
+  </si>
+  <si>
+    <t>Logitech</t>
+  </si>
+  <si>
+    <t>1742LZ106AB8</t>
+  </si>
+  <si>
+    <t>Conectores Videoconferencia</t>
+  </si>
+  <si>
+    <t>Conectores</t>
+  </si>
+  <si>
+    <t>Estrella Bocinas Videoconferencia</t>
+  </si>
+  <si>
+    <t>886-000056</t>
+  </si>
+  <si>
+    <t>Estrella</t>
+  </si>
+  <si>
+    <t>Cisco UC Phone CP-8831</t>
+  </si>
+  <si>
+    <t>FCH19052AQZ</t>
+  </si>
+  <si>
+    <t>Telefono</t>
+  </si>
+  <si>
+    <t>FCH19052DJ7</t>
+  </si>
+  <si>
     <t>Camara Intrinsicamente segura</t>
   </si>
   <si>
@@ -95,12 +539,129 @@
     <t>XP7700</t>
   </si>
   <si>
+    <t>Bocina</t>
+  </si>
+  <si>
+    <t>Jabra</t>
+  </si>
+  <si>
+    <t>PHS001U</t>
+  </si>
+  <si>
+    <t>Pantalla TV</t>
+  </si>
+  <si>
+    <t>VISIO</t>
+  </si>
+  <si>
+    <t>E700I-B3</t>
+  </si>
+  <si>
+    <t>LFTRRGCQ4100300</t>
+  </si>
+  <si>
+    <t>LFTRRGCQ4000557</t>
+  </si>
+  <si>
+    <t>Equipo GEFEN</t>
+  </si>
+  <si>
+    <t>GEFEN</t>
+  </si>
+  <si>
+    <t>EXT-WHD-1080P-SRR</t>
+  </si>
+  <si>
+    <t>AX1508000071</t>
+  </si>
+  <si>
+    <t>GEFEN TOOL BOX</t>
+  </si>
+  <si>
+    <t>Epcom titanium</t>
+  </si>
+  <si>
+    <t>SKG18093503</t>
+  </si>
+  <si>
+    <t>Amplificador para Difusion</t>
+  </si>
+  <si>
+    <t>STEREN</t>
+  </si>
+  <si>
+    <t>Amplificador de Audio</t>
+  </si>
+  <si>
+    <t>Bocinas para Plafon</t>
+  </si>
+  <si>
+    <t>Bocinas</t>
+  </si>
+  <si>
+    <t>Video Proyector</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>U2722DE</t>
+  </si>
+  <si>
+    <t>93QBBH3</t>
+  </si>
+  <si>
+    <t>G3QBBH3</t>
+  </si>
+  <si>
+    <t>Doking Station</t>
+  </si>
+  <si>
+    <t>K20A</t>
+  </si>
+  <si>
+    <t>HP19XS3</t>
+  </si>
+  <si>
+    <t>Cargador de Doking</t>
+  </si>
+  <si>
+    <t>HA180MP180</t>
+  </si>
+  <si>
+    <t>CN-03XYY8-CH200-17G-0BTJ-A04</t>
+  </si>
+  <si>
+    <t>Teclado</t>
+  </si>
+  <si>
+    <t>K235</t>
+  </si>
+  <si>
+    <t>2212MR022028</t>
+  </si>
+  <si>
+    <t>M170</t>
+  </si>
+  <si>
+    <t>2206LZXB9VF8</t>
+  </si>
+  <si>
+    <t>Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPS </t>
+  </si>
+  <si>
+    <t>5216 R</t>
+  </si>
+  <si>
+    <t>24-07-57975</t>
+  </si>
+  <si>
     <t>SWITCH SAN 1</t>
   </si>
   <si>
-    <t>DELL</t>
-  </si>
-  <si>
     <t>POWERCONNECT 6224</t>
   </si>
   <si>
@@ -113,477 +674,6 @@
     <t>J50KTS1</t>
   </si>
   <si>
-    <t>CALL MANAGER NUEVO</t>
-  </si>
-  <si>
-    <t>CISCO</t>
-  </si>
-  <si>
-    <t>UCS C220M3BE</t>
-  </si>
-  <si>
-    <t>220M3222</t>
-  </si>
-  <si>
-    <t>SERVIDOR 19</t>
-  </si>
-  <si>
-    <t>POWEREDGE R710</t>
-  </si>
-  <si>
-    <t>BRNFSL1</t>
-  </si>
-  <si>
-    <t>SERVIDOR 18</t>
-  </si>
-  <si>
-    <t>POWEREDGE R720</t>
-  </si>
-  <si>
-    <t>B3X7RV1</t>
-  </si>
-  <si>
-    <t>SAN</t>
-  </si>
-  <si>
-    <t>POWERVAULT MD3200i</t>
-  </si>
-  <si>
-    <t>48DT7V1</t>
-  </si>
-  <si>
-    <t>Monitor</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>UNIDAD DE CINTAS 19</t>
-  </si>
-  <si>
-    <t>POWER VAULT 114 X</t>
-  </si>
-  <si>
-    <t>YN106813H628</t>
-  </si>
-  <si>
-    <t>SERVIDOR 27</t>
-  </si>
-  <si>
-    <t>POWEREDGE 2950</t>
-  </si>
-  <si>
-    <t>DPBP6K1</t>
-  </si>
-  <si>
-    <t>SERVIDOR 29</t>
-  </si>
-  <si>
-    <t>POWEREDGE R320</t>
-  </si>
-  <si>
-    <t>D64MW12</t>
-  </si>
-  <si>
-    <t>UNIDAD DE CINTAS</t>
-  </si>
-  <si>
-    <t>POWER VAULT 124 T</t>
-  </si>
-  <si>
-    <t>8DDB6K1</t>
-  </si>
-  <si>
-    <t>Switch Linksys Cisco SD216</t>
-  </si>
-  <si>
-    <t>SD216</t>
-  </si>
-  <si>
-    <t>S/N</t>
-  </si>
-  <si>
-    <t>NVR</t>
-  </si>
-  <si>
-    <t>HIKVISION</t>
-  </si>
-  <si>
-    <t>DS-7616NI-K2/16P</t>
-  </si>
-  <si>
-    <t>L48074542</t>
-  </si>
-  <si>
-    <t>DVR HIKVISION</t>
-  </si>
-  <si>
-    <t>DS-7716NI-I4/16P</t>
-  </si>
-  <si>
-    <t>Mouse</t>
-  </si>
-  <si>
-    <t>3D Optical</t>
-  </si>
-  <si>
-    <t>Switch 8 Puertos</t>
-  </si>
-  <si>
-    <t>Planet</t>
-  </si>
-  <si>
-    <t>GSD-804P</t>
-  </si>
-  <si>
-    <t>A350106300034</t>
-  </si>
-  <si>
-    <t>Access PRO</t>
-  </si>
-  <si>
-    <t>AP233</t>
-  </si>
-  <si>
-    <t>AP234</t>
-  </si>
-  <si>
-    <t>Switch</t>
-  </si>
-  <si>
-    <t>Cisco</t>
-  </si>
-  <si>
-    <t>CATALYST 2960-X SERIES</t>
-  </si>
-  <si>
-    <t>FCW1906B1MY</t>
-  </si>
-  <si>
-    <t>FCW1906B1LJ</t>
-  </si>
-  <si>
-    <t>FCW1906B1MM</t>
-  </si>
-  <si>
-    <t>CATALYST 2960-X SERIES POE+</t>
-  </si>
-  <si>
-    <t>FOC1710Y1FV</t>
-  </si>
-  <si>
-    <t>CATALYST 3560</t>
-  </si>
-  <si>
-    <t>CAT0948R334</t>
-  </si>
-  <si>
-    <t>F0C1503Z3QP</t>
-  </si>
-  <si>
-    <t>F0C1514X0EZ</t>
-  </si>
-  <si>
-    <t>FOC1903S1ME</t>
-  </si>
-  <si>
-    <t>Catalyst 3750X-24T-E</t>
-  </si>
-  <si>
-    <t>FD01816Z3AU</t>
-  </si>
-  <si>
-    <t>FIREWALL</t>
-  </si>
-  <si>
-    <t>FORTINET</t>
-  </si>
-  <si>
-    <t>FG100D3G14827870</t>
-  </si>
-  <si>
-    <t>FG100D3G14827806 MASTER</t>
-  </si>
-  <si>
-    <t>FG100D3G14827806</t>
-  </si>
-  <si>
-    <t>FG100D3G14827870 SLAVE</t>
-  </si>
-  <si>
-    <t>CALL MANAGER</t>
-  </si>
-  <si>
-    <t>FTX1328AHLG</t>
-  </si>
-  <si>
-    <t>ROUTER</t>
-  </si>
-  <si>
-    <t>CISCO 1900 SERIES</t>
-  </si>
-  <si>
-    <t>CFTX1614857Q</t>
-  </si>
-  <si>
-    <t>FTX174386AU</t>
-  </si>
-  <si>
-    <t>UPS</t>
-  </si>
-  <si>
-    <t>APC</t>
-  </si>
-  <si>
-    <t>APC Galaxy 3500</t>
-  </si>
-  <si>
-    <t>G35TF30KB4F</t>
-  </si>
-  <si>
-    <t>ACCESSPOINT</t>
-  </si>
-  <si>
-    <t>221E</t>
-  </si>
-  <si>
-    <t>FP221ETF22083298</t>
-  </si>
-  <si>
-    <t>FP221ETF22083291</t>
-  </si>
-  <si>
-    <t>FP221ETF22083300</t>
-  </si>
-  <si>
-    <t>FP221ETF22083299</t>
-  </si>
-  <si>
-    <t>Amplificador celular</t>
-  </si>
-  <si>
-    <t>EPCOM</t>
-  </si>
-  <si>
-    <t>G08W27160502</t>
-  </si>
-  <si>
-    <t>Camara Fija</t>
-  </si>
-  <si>
-    <t>DS-2CD2432F-I</t>
-  </si>
-  <si>
-    <t>I20140922CCWR480540694</t>
-  </si>
-  <si>
-    <t>DS-2CD1043G0-I</t>
-  </si>
-  <si>
-    <t>I20220824AAWRK47327687</t>
-  </si>
-  <si>
-    <t>Camara PTZ</t>
-  </si>
-  <si>
-    <t>DS-2DE4215IW-DE</t>
-  </si>
-  <si>
-    <t>DE20190506CCWRD16875921W</t>
-  </si>
-  <si>
-    <t>DS-2CD2232-I5</t>
-  </si>
-  <si>
-    <t>I520150207CCWR502802490</t>
-  </si>
-  <si>
-    <t>I20200824AAWRK47327674</t>
-  </si>
-  <si>
-    <t>DS-2DE7174-A</t>
-  </si>
-  <si>
-    <t>A20150122CCWR500502005</t>
-  </si>
-  <si>
-    <t>I520150207CCWR502802472</t>
-  </si>
-  <si>
-    <t>I520150207CCWR502802475</t>
-  </si>
-  <si>
-    <t>I520150207CCWR502802494</t>
-  </si>
-  <si>
-    <t>I520150207CCWR502802491</t>
-  </si>
-  <si>
-    <t>I520150207CCWR502802480</t>
-  </si>
-  <si>
-    <t>I520150207CCWR502802497</t>
-  </si>
-  <si>
-    <t>DS-2CD2422FWD-IW</t>
-  </si>
-  <si>
-    <t>IW20170808AAWR808998451</t>
-  </si>
-  <si>
-    <t>I20140922CCWR480540755</t>
-  </si>
-  <si>
-    <t>I20140922CCWR480540785</t>
-  </si>
-  <si>
-    <t>DS-2CD2T42WD-I5</t>
-  </si>
-  <si>
-    <t>I520160810BBWR633078836</t>
-  </si>
-  <si>
-    <t>I520160810BBWR633078735</t>
-  </si>
-  <si>
-    <t>I520160810BBWR633078506</t>
-  </si>
-  <si>
-    <t>A20150122CCWR500502035</t>
-  </si>
-  <si>
-    <t>KOBLENZ</t>
-  </si>
-  <si>
-    <t>4816 R</t>
-  </si>
-  <si>
-    <t>16-09-17766</t>
-  </si>
-  <si>
-    <t>Lector Biometrico</t>
-  </si>
-  <si>
-    <t>BioEntry W2</t>
-  </si>
-  <si>
-    <t>BEW2-0DP</t>
-  </si>
-  <si>
-    <t>Equipo de Videoconferencia</t>
-  </si>
-  <si>
-    <t>Chromebox</t>
-  </si>
-  <si>
-    <t>Asus</t>
-  </si>
-  <si>
-    <t>H6MSCX001323</t>
-  </si>
-  <si>
-    <t>Camara Videoconferencia</t>
-  </si>
-  <si>
-    <t>Logitech</t>
-  </si>
-  <si>
-    <t>1742LZ106AB8</t>
-  </si>
-  <si>
-    <t>Conectores Videoconferencia</t>
-  </si>
-  <si>
-    <t>Conectores</t>
-  </si>
-  <si>
-    <t>Estrella Bocinas Videoconferencia</t>
-  </si>
-  <si>
-    <t>886-000056</t>
-  </si>
-  <si>
-    <t>Estrella</t>
-  </si>
-  <si>
-    <t>Cisco UC Phone CP-8831</t>
-  </si>
-  <si>
-    <t>FCH19052AQZ</t>
-  </si>
-  <si>
-    <t>Telefono</t>
-  </si>
-  <si>
-    <t>FCH19052DJ7</t>
-  </si>
-  <si>
-    <t>Bocina</t>
-  </si>
-  <si>
-    <t>Jabra</t>
-  </si>
-  <si>
-    <t>PHS001U</t>
-  </si>
-  <si>
-    <t>Pantalla TV</t>
-  </si>
-  <si>
-    <t>VISIO</t>
-  </si>
-  <si>
-    <t>E700I-B3</t>
-  </si>
-  <si>
-    <t>LFTRRGCQ4100300</t>
-  </si>
-  <si>
-    <t>LFTRRGCQ4000557</t>
-  </si>
-  <si>
-    <t>Equipo GEFEN</t>
-  </si>
-  <si>
-    <t>GEFEN</t>
-  </si>
-  <si>
-    <t>EXT-WHD-1080P-SRR</t>
-  </si>
-  <si>
-    <t>AX1508000071</t>
-  </si>
-  <si>
-    <t>GEFEN TOOL BOX</t>
-  </si>
-  <si>
-    <t>Epcom titanium</t>
-  </si>
-  <si>
-    <t>SKG18093503</t>
-  </si>
-  <si>
-    <t>Amplificador para Difusion</t>
-  </si>
-  <si>
-    <t>STEREN</t>
-  </si>
-  <si>
-    <t>Amplificador de Audio</t>
-  </si>
-  <si>
-    <t>Bocinas para Plafon</t>
-  </si>
-  <si>
-    <t>Bocinas</t>
-  </si>
-  <si>
-    <t>Video Proyector</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Cargador Laptop</t>
   </si>
   <si>
@@ -591,96 +681,6 @@
   </si>
   <si>
     <t>CN-05M5GT1-CH200-279-048G-A00</t>
-  </si>
-  <si>
-    <t>U2722DE</t>
-  </si>
-  <si>
-    <t>93QBBH3</t>
-  </si>
-  <si>
-    <t>G3QBBH3</t>
-  </si>
-  <si>
-    <t>Doking Station</t>
-  </si>
-  <si>
-    <t>K20A</t>
-  </si>
-  <si>
-    <t>HP19XS3</t>
-  </si>
-  <si>
-    <t>Cargador de Doking</t>
-  </si>
-  <si>
-    <t>HA180MP180</t>
-  </si>
-  <si>
-    <t>CN-03XYY8-CH200-17G-0BTJ-A04</t>
-  </si>
-  <si>
-    <t>Teclado</t>
-  </si>
-  <si>
-    <t>K235</t>
-  </si>
-  <si>
-    <t>2212MR022028</t>
-  </si>
-  <si>
-    <t>M170</t>
-  </si>
-  <si>
-    <t>2206LZXB9VF8</t>
-  </si>
-  <si>
-    <t>Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UPS </t>
-  </si>
-  <si>
-    <t>5216 R</t>
-  </si>
-  <si>
-    <t>24-07-57975</t>
-  </si>
-  <si>
-    <t>Desktop</t>
-  </si>
-  <si>
-    <t>HP</t>
-  </si>
-  <si>
-    <t>Elite Desk 800 G1</t>
-  </si>
-  <si>
-    <t>MXL5071Z2Q</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00027</t>
-  </si>
-  <si>
-    <t>EliteDesk 800G1</t>
-  </si>
-  <si>
-    <t>MXL4503CFF</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00110</t>
-  </si>
-  <si>
-    <t>Laptop</t>
-  </si>
-  <si>
-    <t>XPS 13 9315</t>
-  </si>
-  <si>
-    <t>29502T3</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00154</t>
   </si>
   <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
@@ -1538,46 +1538,38 @@
         <v>24</v>
       </c>
       <c r="E19" s="38"/>
-      <c r="F19" s="38">
-        <v>14187000333707</v>
+      <c r="F19" s="38" t="s">
+        <v>25</v>
       </c>
       <c r="G19" s="38"/>
       <c r="H19" s="38"/>
       <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="15">
-      <c r="A20" s="38">
-        <v>2</v>
-      </c>
-      <c r="B20" s="38" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="38" t="s">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
     </row>
     <row r="21" spans="1:10" customHeight="1" ht="15">
       <c r="A21" s="38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B21" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="38" t="s">
         <v>29</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21" s="38" t="s">
-        <v>27</v>
       </c>
       <c r="E21" s="38"/>
       <c r="F21" s="38" t="s">
@@ -1588,84 +1580,68 @@
       <c r="I21" s="38"/>
     </row>
     <row r="22" spans="1:10" customHeight="1" ht="15">
-      <c r="A22" s="38">
-        <v>4</v>
-      </c>
-      <c r="B22" s="38" t="s">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
     </row>
     <row r="23" spans="1:10" customHeight="1" ht="15">
       <c r="A23" s="38">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E23" s="38"/>
       <c r="F23" s="38" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G23" s="38"/>
       <c r="H23" s="38"/>
       <c r="I23" s="38"/>
     </row>
     <row r="24" spans="1:10" customHeight="1" ht="15">
-      <c r="A24" s="38">
-        <v>6</v>
-      </c>
-      <c r="B24" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
+      <c r="A24" s="22"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
     </row>
     <row r="25" spans="1:10" customHeight="1" ht="15">
       <c r="A25" s="38">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E25" s="38"/>
       <c r="F25" s="38" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
@@ -1673,20 +1649,20 @@
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="15">
       <c r="A26" s="38">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E26" s="38"/>
       <c r="F26" s="38" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G26" s="38"/>
       <c r="H26" s="38"/>
@@ -1694,20 +1670,20 @@
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="15">
       <c r="A27" s="38">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D27" s="38" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E27" s="38"/>
       <c r="F27" s="38" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G27" s="38"/>
       <c r="H27" s="38"/>
@@ -1715,20 +1691,20 @@
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
       <c r="A28" s="38">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E28" s="38"/>
       <c r="F28" s="38" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G28" s="38"/>
       <c r="H28" s="38"/>
@@ -1736,20 +1712,20 @@
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="15">
       <c r="A29" s="38">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E29" s="38"/>
       <c r="F29" s="38" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G29" s="38"/>
       <c r="H29" s="38"/>
@@ -1757,20 +1733,20 @@
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
       <c r="A30" s="38">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E30" s="38"/>
       <c r="F30" s="38" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G30" s="38"/>
       <c r="H30" s="38"/>
@@ -1778,20 +1754,20 @@
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="15">
       <c r="A31" s="38">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D31" s="38" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E31" s="38"/>
       <c r="F31" s="38" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G31" s="38"/>
       <c r="H31" s="38"/>
@@ -1799,20 +1775,20 @@
     </row>
     <row r="32" spans="1:10" customHeight="1" ht="15">
       <c r="A32" s="38">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="D32" s="38" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E32" s="38"/>
       <c r="F32" s="38" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G32" s="38"/>
       <c r="H32" s="38"/>
@@ -1820,20 +1796,20 @@
     </row>
     <row r="33" spans="1:10" customHeight="1" ht="15">
       <c r="A33" s="38">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C33" s="38" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="D33" s="38" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E33" s="38"/>
-      <c r="F33" s="38">
-        <v>647235228</v>
+      <c r="F33" s="38" t="s">
+        <v>61</v>
       </c>
       <c r="G33" s="38"/>
       <c r="H33" s="38"/>
@@ -1841,20 +1817,20 @@
     </row>
     <row r="34" spans="1:10" customHeight="1" ht="15">
       <c r="A34" s="38">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="D34" s="38" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E34" s="38"/>
       <c r="F34" s="38" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G34" s="38"/>
       <c r="H34" s="38"/>
@@ -1862,20 +1838,20 @@
     </row>
     <row r="35" spans="1:10" customHeight="1" ht="15">
       <c r="A35" s="38">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B35" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" s="38" t="s">
         <v>67</v>
-      </c>
-      <c r="C35" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="D35" s="38" t="s">
-        <v>60</v>
       </c>
       <c r="E35" s="38"/>
       <c r="F35" s="38" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G35" s="38"/>
       <c r="H35" s="38"/>
@@ -1883,20 +1859,20 @@
     </row>
     <row r="36" spans="1:10" customHeight="1" ht="15">
       <c r="A36" s="38">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B36" s="38" t="s">
         <v>69</v>
       </c>
       <c r="C36" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="D36" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="D36" s="38" t="s">
-        <v>71</v>
-      </c>
       <c r="E36" s="38"/>
-      <c r="F36" s="38" t="s">
-        <v>72</v>
+      <c r="F36" s="38">
+        <v>647235228</v>
       </c>
       <c r="G36" s="38"/>
       <c r="H36" s="38"/>
@@ -1904,20 +1880,20 @@
     </row>
     <row r="37" spans="1:10" customHeight="1" ht="15">
       <c r="A37" s="38">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C37" s="38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D37" s="38" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E37" s="38"/>
       <c r="F37" s="38" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="G37" s="38"/>
       <c r="H37" s="38"/>
@@ -1925,20 +1901,20 @@
     </row>
     <row r="38" spans="1:10" customHeight="1" ht="15">
       <c r="A38" s="38">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E38" s="38"/>
       <c r="F38" s="38" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="G38" s="38"/>
       <c r="H38" s="38"/>
@@ -1946,20 +1922,20 @@
     </row>
     <row r="39" spans="1:10" customHeight="1" ht="15">
       <c r="A39" s="38">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E39" s="38"/>
       <c r="F39" s="38" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G39" s="38"/>
       <c r="H39" s="38"/>
@@ -1967,20 +1943,20 @@
     </row>
     <row r="40" spans="1:10" customHeight="1" ht="15">
       <c r="A40" s="38">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C40" s="38" t="s">
         <v>77</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E40" s="38"/>
       <c r="F40" s="38" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G40" s="38"/>
       <c r="H40" s="38"/>
@@ -1988,20 +1964,20 @@
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
       <c r="A41" s="38">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C41" s="38" t="s">
         <v>77</v>
       </c>
       <c r="D41" s="38" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E41" s="38"/>
       <c r="F41" s="38" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G41" s="38"/>
       <c r="H41" s="38"/>
@@ -2009,13 +1985,13 @@
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
       <c r="A42" s="38">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C42" s="38" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D42" s="38" t="s">
         <v>82</v>
@@ -2030,20 +2006,20 @@
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="38">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G43" s="38"/>
       <c r="H43" s="38"/>
@@ -2051,20 +2027,20 @@
     </row>
     <row r="44" spans="1:10" customHeight="1" ht="15">
       <c r="A44" s="38">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C44" s="38" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D44" s="38" t="s">
         <v>82</v>
       </c>
       <c r="E44" s="38"/>
       <c r="F44" s="38" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G44" s="38"/>
       <c r="H44" s="38"/>
@@ -2072,16 +2048,16 @@
     </row>
     <row r="45" spans="1:10" customHeight="1" ht="15">
       <c r="A45" s="38">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E45" s="38"/>
       <c r="F45" s="38" t="s">
@@ -2093,20 +2069,20 @@
     </row>
     <row r="46" spans="1:10" customHeight="1" ht="15">
       <c r="A46" s="38">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="E46" s="38"/>
       <c r="F46" s="38" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G46" s="38"/>
       <c r="H46" s="38"/>
@@ -2114,16 +2090,16 @@
     </row>
     <row r="47" spans="1:10" customHeight="1" ht="15">
       <c r="A47" s="38">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B47" s="38" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C47" s="38" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E47" s="38"/>
       <c r="F47" s="38" t="s">
@@ -2135,20 +2111,20 @@
     </row>
     <row r="48" spans="1:10" customHeight="1" ht="15">
       <c r="A48" s="38">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B48" s="38" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C48" s="38" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D48" s="38" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E48" s="38"/>
       <c r="F48" s="38" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G48" s="38"/>
       <c r="H48" s="38"/>
@@ -2156,20 +2132,20 @@
     </row>
     <row r="49" spans="1:10" customHeight="1" ht="15">
       <c r="A49" s="38">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B49" s="38" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C49" s="38" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="E49" s="38"/>
       <c r="F49" s="38" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G49" s="38"/>
       <c r="H49" s="38"/>
@@ -2177,18 +2153,20 @@
     </row>
     <row r="50" spans="1:10" customHeight="1" ht="15">
       <c r="A50" s="38">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B50" s="38" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="C50" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D50" s="38"/>
+        <v>81</v>
+      </c>
+      <c r="D50" s="38" t="s">
+        <v>93</v>
+      </c>
       <c r="E50" s="38"/>
       <c r="F50" s="38" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G50" s="38"/>
       <c r="H50" s="38"/>
@@ -2196,20 +2174,20 @@
     </row>
     <row r="51" spans="1:10" customHeight="1" ht="15">
       <c r="A51" s="38">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B51" s="38" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C51" s="38" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="D51" s="38" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E51" s="38"/>
       <c r="F51" s="38" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G51" s="38"/>
       <c r="H51" s="38"/>
@@ -2217,20 +2195,20 @@
     </row>
     <row r="52" spans="1:10" customHeight="1" ht="15">
       <c r="A52" s="38">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B52" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="C52" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="D52" s="38" t="s">
         <v>99</v>
-      </c>
-      <c r="C52" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D52" s="38" t="s">
-        <v>100</v>
       </c>
       <c r="E52" s="38"/>
       <c r="F52" s="38" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G52" s="38"/>
       <c r="H52" s="38"/>
@@ -2238,20 +2216,18 @@
     </row>
     <row r="53" spans="1:10" customHeight="1" ht="15">
       <c r="A53" s="38">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B53" s="38" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C53" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="D53" s="38" t="s">
-        <v>105</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="D53" s="38"/>
       <c r="E53" s="38"/>
       <c r="F53" s="38" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G53" s="38"/>
       <c r="H53" s="38"/>
@@ -2259,20 +2235,20 @@
     </row>
     <row r="54" spans="1:10" customHeight="1" ht="15">
       <c r="A54" s="38">
+        <v>33</v>
+      </c>
+      <c r="B54" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="C54" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="B54" s="38" t="s">
-        <v>107</v>
-      </c>
-      <c r="C54" s="38" t="s">
-        <v>92</v>
-      </c>
       <c r="D54" s="38" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E54" s="38"/>
       <c r="F54" s="38" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G54" s="38"/>
       <c r="H54" s="38"/>
@@ -2280,20 +2256,20 @@
     </row>
     <row r="55" spans="1:10" customHeight="1" ht="15">
       <c r="A55" s="38">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B55" s="38" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C55" s="38" t="s">
-        <v>92</v>
+        <v>36</v>
       </c>
       <c r="D55" s="38" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E55" s="38"/>
       <c r="F55" s="38" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G55" s="38"/>
       <c r="H55" s="38"/>
@@ -2301,20 +2277,20 @@
     </row>
     <row r="56" spans="1:10" customHeight="1" ht="15">
       <c r="A56" s="38">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B56" s="38" t="s">
         <v>107</v>
       </c>
       <c r="C56" s="38" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="D56" s="38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E56" s="38"/>
       <c r="F56" s="38" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G56" s="38"/>
       <c r="H56" s="38"/>
@@ -2322,20 +2298,20 @@
     </row>
     <row r="57" spans="1:10" customHeight="1" ht="15">
       <c r="A57" s="38">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B57" s="38" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C57" s="38" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D57" s="38" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E57" s="38"/>
       <c r="F57" s="38" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G57" s="38"/>
       <c r="H57" s="38"/>
@@ -2343,20 +2319,20 @@
     </row>
     <row r="58" spans="1:10" customHeight="1" ht="15">
       <c r="A58" s="38">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B58" s="38" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C58" s="38" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="D58" s="38" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E58" s="38"/>
       <c r="F58" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G58" s="38"/>
       <c r="H58" s="38"/>
@@ -2364,20 +2340,20 @@
     </row>
     <row r="59" spans="1:10" customHeight="1" ht="15">
       <c r="A59" s="38">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B59" s="38" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C59" s="38" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="D59" s="38" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E59" s="38"/>
       <c r="F59" s="38" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G59" s="38"/>
       <c r="H59" s="38"/>
@@ -2385,20 +2361,20 @@
     </row>
     <row r="60" spans="1:10" customHeight="1" ht="15">
       <c r="A60" s="38">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B60" s="38" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C60" s="38" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="D60" s="38" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="E60" s="38"/>
       <c r="F60" s="38" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G60" s="38"/>
       <c r="H60" s="38"/>
@@ -2406,20 +2382,20 @@
     </row>
     <row r="61" spans="1:10" customHeight="1" ht="15">
       <c r="A61" s="38">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B61" s="38" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C61" s="38" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="D61" s="38" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E61" s="38"/>
       <c r="F61" s="38" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G61" s="38"/>
       <c r="H61" s="38"/>
@@ -2427,20 +2403,20 @@
     </row>
     <row r="62" spans="1:10" customHeight="1" ht="15">
       <c r="A62" s="38">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B62" s="38" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C62" s="38" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D62" s="38" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E62" s="38"/>
       <c r="F62" s="38" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G62" s="38"/>
       <c r="H62" s="38"/>
@@ -2448,20 +2424,20 @@
     </row>
     <row r="63" spans="1:10" customHeight="1" ht="15">
       <c r="A63" s="38">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B63" s="38" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C63" s="38" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D63" s="38" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E63" s="38"/>
       <c r="F63" s="38" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G63" s="38"/>
       <c r="H63" s="38"/>
@@ -2469,20 +2445,20 @@
     </row>
     <row r="64" spans="1:10" customHeight="1" ht="15">
       <c r="A64" s="38">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B64" s="38" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C64" s="38" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D64" s="38" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E64" s="38"/>
       <c r="F64" s="38" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G64" s="38"/>
       <c r="H64" s="38"/>
@@ -2490,16 +2466,16 @@
     </row>
     <row r="65" spans="1:10" customHeight="1" ht="15">
       <c r="A65" s="38">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B65" s="38" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C65" s="38" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D65" s="38" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E65" s="38"/>
       <c r="F65" s="38" t="s">
@@ -2511,16 +2487,16 @@
     </row>
     <row r="66" spans="1:10" customHeight="1" ht="15">
       <c r="A66" s="38">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B66" s="38" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C66" s="38" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D66" s="38" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E66" s="38"/>
       <c r="F66" s="38" t="s">
@@ -2532,20 +2508,20 @@
     </row>
     <row r="67" spans="1:10" customHeight="1" ht="15">
       <c r="A67" s="38">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B67" s="38" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="C67" s="38" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D67" s="38" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E67" s="38"/>
       <c r="F67" s="38" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G67" s="38"/>
       <c r="H67" s="38"/>
@@ -2553,20 +2529,20 @@
     </row>
     <row r="68" spans="1:10" customHeight="1" ht="15">
       <c r="A68" s="38">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B68" s="38" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C68" s="38" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D68" s="38" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E68" s="38"/>
       <c r="F68" s="38" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G68" s="38"/>
       <c r="H68" s="38"/>
@@ -2574,20 +2550,20 @@
     </row>
     <row r="69" spans="1:10" customHeight="1" ht="15">
       <c r="A69" s="38">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B69" s="38" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C69" s="38" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D69" s="38" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E69" s="38"/>
       <c r="F69" s="38" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G69" s="38"/>
       <c r="H69" s="38"/>
@@ -2595,20 +2571,20 @@
     </row>
     <row r="70" spans="1:10" customHeight="1" ht="15">
       <c r="A70" s="38">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B70" s="38" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C70" s="38" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D70" s="38" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E70" s="38"/>
       <c r="F70" s="38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G70" s="38"/>
       <c r="H70" s="38"/>
@@ -2616,16 +2592,16 @@
     </row>
     <row r="71" spans="1:10" customHeight="1" ht="15">
       <c r="A71" s="38">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B71" s="38" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C71" s="38" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D71" s="38" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E71" s="38"/>
       <c r="F71" s="38" t="s">
@@ -2637,16 +2613,16 @@
     </row>
     <row r="72" spans="1:10" customHeight="1" ht="15">
       <c r="A72" s="38">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B72" s="38" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C72" s="38" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D72" s="38" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E72" s="38"/>
       <c r="F72" s="38" t="s">
@@ -2658,16 +2634,16 @@
     </row>
     <row r="73" spans="1:10" customHeight="1" ht="15">
       <c r="A73" s="38">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B73" s="38" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C73" s="38" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D73" s="38" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E73" s="38"/>
       <c r="F73" s="38" t="s">
@@ -2679,13 +2655,13 @@
     </row>
     <row r="74" spans="1:10" customHeight="1" ht="15">
       <c r="A74" s="38">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B74" s="38" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C74" s="38" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D74" s="38" t="s">
         <v>139</v>
@@ -2700,16 +2676,16 @@
     </row>
     <row r="75" spans="1:10" customHeight="1" ht="15">
       <c r="A75" s="38">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B75" s="38" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C75" s="38" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D75" s="38" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="E75" s="38"/>
       <c r="F75" s="38" t="s">
@@ -2721,16 +2697,16 @@
     </row>
     <row r="76" spans="1:10" customHeight="1" ht="15">
       <c r="A76" s="38">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B76" s="38" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C76" s="38" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D76" s="38" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="E76" s="38"/>
       <c r="F76" s="38" t="s">
@@ -2742,20 +2718,20 @@
     </row>
     <row r="77" spans="1:10" customHeight="1" ht="15">
       <c r="A77" s="38">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B77" s="38" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C77" s="38" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D77" s="38" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="E77" s="38"/>
       <c r="F77" s="38" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G77" s="38"/>
       <c r="H77" s="38"/>
@@ -2763,20 +2739,20 @@
     </row>
     <row r="78" spans="1:10" customHeight="1" ht="15">
       <c r="A78" s="38">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B78" s="38" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="C78" s="38" t="s">
-        <v>144</v>
+        <v>66</v>
       </c>
       <c r="D78" s="38" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E78" s="38"/>
       <c r="F78" s="38" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G78" s="38"/>
       <c r="H78" s="38"/>
@@ -2784,20 +2760,20 @@
     </row>
     <row r="79" spans="1:10" customHeight="1" ht="15">
       <c r="A79" s="38">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B79" s="38" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="C79" s="38" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="D79" s="38" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E79" s="38"/>
-      <c r="F79" s="38">
-        <v>544161389</v>
+      <c r="F79" s="38" t="s">
+        <v>146</v>
       </c>
       <c r="G79" s="38"/>
       <c r="H79" s="38"/>
@@ -2805,20 +2781,20 @@
     </row>
     <row r="80" spans="1:10" customHeight="1" ht="15">
       <c r="A80" s="38">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B80" s="38" t="s">
+        <v>125</v>
+      </c>
+      <c r="C80" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="D80" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="E80" s="38"/>
+      <c r="F80" s="38" t="s">
         <v>147</v>
-      </c>
-      <c r="C80" s="38" t="s">
-        <v>148</v>
-      </c>
-      <c r="D80" s="38" t="s">
-        <v>149</v>
-      </c>
-      <c r="E80" s="38"/>
-      <c r="F80" s="38">
-        <v>544161388</v>
       </c>
       <c r="G80" s="38"/>
       <c r="H80" s="38"/>
@@ -2826,20 +2802,20 @@
     </row>
     <row r="81" spans="1:10" customHeight="1" ht="15">
       <c r="A81" s="38">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B81" s="38" t="s">
-        <v>150</v>
+        <v>107</v>
       </c>
       <c r="C81" s="38" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D81" s="38" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E81" s="38"/>
       <c r="F81" s="38" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G81" s="38"/>
       <c r="H81" s="38"/>
@@ -2847,20 +2823,20 @@
     </row>
     <row r="82" spans="1:10" customHeight="1" ht="15">
       <c r="A82" s="38">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B82" s="38" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C82" s="38" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D82" s="38" t="s">
-        <v>60</v>
+        <v>153</v>
       </c>
       <c r="E82" s="38"/>
-      <c r="F82" s="38" t="s">
-        <v>156</v>
+      <c r="F82" s="38">
+        <v>544161389</v>
       </c>
       <c r="G82" s="38"/>
       <c r="H82" s="38"/>
@@ -2868,20 +2844,20 @@
     </row>
     <row r="83" spans="1:10" customHeight="1" ht="15">
       <c r="A83" s="38">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B83" s="38" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C83" s="38" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D83" s="38" t="s">
-        <v>60</v>
+        <v>153</v>
       </c>
       <c r="E83" s="38"/>
-      <c r="F83" s="38" t="s">
-        <v>60</v>
+      <c r="F83" s="38">
+        <v>544161388</v>
       </c>
       <c r="G83" s="38"/>
       <c r="H83" s="38"/>
@@ -2889,20 +2865,20 @@
     </row>
     <row r="84" spans="1:10" customHeight="1" ht="15">
       <c r="A84" s="38">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B84" s="38" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C84" s="38" t="s">
         <v>155</v>
       </c>
       <c r="D84" s="38" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E84" s="38"/>
       <c r="F84" s="38" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G84" s="38"/>
       <c r="H84" s="38"/>
@@ -2910,20 +2886,20 @@
     </row>
     <row r="85" spans="1:10" customHeight="1" ht="15">
       <c r="A85" s="38">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B85" s="38" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C85" s="38" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
       <c r="D85" s="38" t="s">
-        <v>162</v>
+        <v>64</v>
       </c>
       <c r="E85" s="38"/>
       <c r="F85" s="38" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G85" s="38"/>
       <c r="H85" s="38"/>
@@ -2931,20 +2907,20 @@
     </row>
     <row r="86" spans="1:10" customHeight="1" ht="15">
       <c r="A86" s="38">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B86" s="38" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C86" s="38" t="s">
-        <v>77</v>
+        <v>162</v>
       </c>
       <c r="D86" s="38" t="s">
-        <v>162</v>
+        <v>64</v>
       </c>
       <c r="E86" s="38"/>
       <c r="F86" s="38" t="s">
-        <v>165</v>
+        <v>64</v>
       </c>
       <c r="G86" s="38"/>
       <c r="H86" s="38"/>
@@ -2952,20 +2928,20 @@
     </row>
     <row r="87" spans="1:10" customHeight="1" ht="15">
       <c r="A87" s="38">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B87" s="38" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C87" s="38" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="D87" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E87" s="38"/>
-      <c r="F87" s="38">
-        <v>29016514</v>
+      <c r="F87" s="38" t="s">
+        <v>160</v>
       </c>
       <c r="G87" s="38"/>
       <c r="H87" s="38"/>
@@ -2973,20 +2949,20 @@
     </row>
     <row r="88" spans="1:10" customHeight="1" ht="15">
       <c r="A88" s="38">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B88" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="C88" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="D88" s="38" t="s">
         <v>166</v>
       </c>
-      <c r="C88" s="38" t="s">
+      <c r="E88" s="38"/>
+      <c r="F88" s="38" t="s">
         <v>167</v>
-      </c>
-      <c r="D88" s="38" t="s">
-        <v>168</v>
-      </c>
-      <c r="E88" s="38"/>
-      <c r="F88" s="38">
-        <v>29016400</v>
       </c>
       <c r="G88" s="38"/>
       <c r="H88" s="38"/>
@@ -2994,20 +2970,20 @@
     </row>
     <row r="89" spans="1:10" customHeight="1" ht="15">
       <c r="A89" s="38">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B89" s="38" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C89" s="38" t="s">
-        <v>170</v>
+        <v>81</v>
       </c>
       <c r="D89" s="38" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E89" s="38"/>
       <c r="F89" s="38" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G89" s="38"/>
       <c r="H89" s="38"/>
@@ -3015,20 +2991,20 @@
     </row>
     <row r="90" spans="1:10" customHeight="1" ht="15">
       <c r="A90" s="38">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B90" s="38" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C90" s="38" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D90" s="38" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E90" s="38"/>
-      <c r="F90" s="38" t="s">
-        <v>173</v>
+      <c r="F90" s="38">
+        <v>14187000333707</v>
       </c>
       <c r="G90" s="38"/>
       <c r="H90" s="38"/>
@@ -3036,20 +3012,20 @@
     </row>
     <row r="91" spans="1:10" customHeight="1" ht="15">
       <c r="A91" s="38">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B91" s="38" t="s">
+        <v>173</v>
+      </c>
+      <c r="C91" s="38" t="s">
         <v>174</v>
       </c>
-      <c r="C91" s="38" t="s">
+      <c r="D91" s="38" t="s">
         <v>175</v>
       </c>
-      <c r="D91" s="38" t="s">
-        <v>176</v>
-      </c>
       <c r="E91" s="38"/>
-      <c r="F91" s="38" t="s">
-        <v>177</v>
+      <c r="F91" s="38">
+        <v>29016400</v>
       </c>
       <c r="G91" s="38"/>
       <c r="H91" s="38"/>
@@ -3057,20 +3033,20 @@
     </row>
     <row r="92" spans="1:10" customHeight="1" ht="15">
       <c r="A92" s="38">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B92" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="C92" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="D92" s="38" t="s">
         <v>178</v>
-      </c>
-      <c r="C92" s="38" t="s">
-        <v>178</v>
-      </c>
-      <c r="D92" s="38" t="s">
-        <v>60</v>
       </c>
       <c r="E92" s="38"/>
       <c r="F92" s="38" t="s">
-        <v>60</v>
+        <v>179</v>
       </c>
       <c r="G92" s="38"/>
       <c r="H92" s="38"/>
@@ -3078,16 +3054,16 @@
     </row>
     <row r="93" spans="1:10" customHeight="1" ht="15">
       <c r="A93" s="38">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B93" s="38" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C93" s="38" t="s">
-        <v>114</v>
+        <v>177</v>
       </c>
       <c r="D93" s="38" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E93" s="38"/>
       <c r="F93" s="38" t="s">
@@ -3099,20 +3075,20 @@
     </row>
     <row r="94" spans="1:10" customHeight="1" ht="15">
       <c r="A94" s="38">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B94" s="38" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C94" s="38" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D94" s="38" t="s">
-        <v>60</v>
+        <v>183</v>
       </c>
       <c r="E94" s="38"/>
       <c r="F94" s="38" t="s">
-        <v>60</v>
+        <v>184</v>
       </c>
       <c r="G94" s="38"/>
       <c r="H94" s="38"/>
@@ -3120,58 +3096,62 @@
     </row>
     <row r="95" spans="1:10" customHeight="1" ht="15">
       <c r="A95" s="38">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B95" s="38" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C95" s="38" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D95" s="38" t="s">
-        <v>183</v>
+        <v>64</v>
       </c>
       <c r="E95" s="38"/>
-      <c r="F95" s="38"/>
+      <c r="F95" s="38" t="s">
+        <v>64</v>
+      </c>
       <c r="G95" s="38"/>
       <c r="H95" s="38"/>
       <c r="I95" s="38"/>
     </row>
     <row r="96" spans="1:10" customHeight="1" ht="15">
       <c r="A96" s="38">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B96" s="38" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C96" s="38" t="s">
-        <v>182</v>
+        <v>118</v>
       </c>
       <c r="D96" s="38" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E96" s="38"/>
-      <c r="F96" s="38"/>
+      <c r="F96" s="38" t="s">
+        <v>187</v>
+      </c>
       <c r="G96" s="38"/>
       <c r="H96" s="38"/>
       <c r="I96" s="38"/>
     </row>
     <row r="97" spans="1:10" customHeight="1" ht="15">
       <c r="A97" s="38">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B97" s="38" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C97" s="38" t="s">
-        <v>26</v>
+        <v>185</v>
       </c>
       <c r="D97" s="38" t="s">
-        <v>187</v>
+        <v>64</v>
       </c>
       <c r="E97" s="38"/>
       <c r="F97" s="38" t="s">
-        <v>187</v>
+        <v>64</v>
       </c>
       <c r="G97" s="38"/>
       <c r="H97" s="38"/>
@@ -3179,62 +3159,58 @@
     </row>
     <row r="98" spans="1:10" customHeight="1" ht="15">
       <c r="A98" s="38">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B98" s="38" t="s">
         <v>188</v>
       </c>
       <c r="C98" s="38" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="D98" s="38" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E98" s="38"/>
-      <c r="F98" s="38" t="s">
-        <v>190</v>
-      </c>
+      <c r="F98" s="38"/>
       <c r="G98" s="38"/>
       <c r="H98" s="38"/>
       <c r="I98" s="38"/>
     </row>
     <row r="99" spans="1:10" customHeight="1" ht="15">
       <c r="A99" s="38">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B99" s="38" t="s">
-        <v>44</v>
+        <v>191</v>
       </c>
       <c r="C99" s="38" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="D99" s="38" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E99" s="38"/>
-      <c r="F99" s="38" t="s">
-        <v>192</v>
-      </c>
+      <c r="F99" s="38"/>
       <c r="G99" s="38"/>
       <c r="H99" s="38"/>
       <c r="I99" s="38"/>
     </row>
     <row r="100" spans="1:10" customHeight="1" ht="15">
       <c r="A100" s="38">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B100" s="38" t="s">
-        <v>44</v>
+        <v>193</v>
       </c>
       <c r="C100" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D100" s="38" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E100" s="38"/>
       <c r="F100" s="38" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G100" s="38"/>
       <c r="H100" s="38"/>
@@ -3242,20 +3218,20 @@
     </row>
     <row r="101" spans="1:10" customHeight="1" ht="15">
       <c r="A101" s="38">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B101" s="38" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="C101" s="38" t="s">
-        <v>26</v>
+        <v>174</v>
       </c>
       <c r="D101" s="38" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="E101" s="38"/>
-      <c r="F101" s="38" t="s">
-        <v>196</v>
+      <c r="F101" s="38">
+        <v>29016514</v>
       </c>
       <c r="G101" s="38"/>
       <c r="H101" s="38"/>
@@ -3263,20 +3239,20 @@
     </row>
     <row r="102" spans="1:10" customHeight="1" ht="15">
       <c r="A102" s="38">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B102" s="38" t="s">
-        <v>197</v>
+        <v>48</v>
       </c>
       <c r="C102" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D102" s="38" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E102" s="38"/>
       <c r="F102" s="38" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G102" s="38"/>
       <c r="H102" s="38"/>
@@ -3284,20 +3260,20 @@
     </row>
     <row r="103" spans="1:10" customHeight="1" ht="15">
       <c r="A103" s="38">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B103" s="38" t="s">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="C103" s="38" t="s">
-        <v>155</v>
+        <v>23</v>
       </c>
       <c r="D103" s="38" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="E103" s="38"/>
       <c r="F103" s="38" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="G103" s="38"/>
       <c r="H103" s="38"/>
@@ -3305,20 +3281,20 @@
     </row>
     <row r="104" spans="1:10" customHeight="1" ht="15">
       <c r="A104" s="38">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B104" s="38" t="s">
-        <v>67</v>
+        <v>198</v>
       </c>
       <c r="C104" s="38" t="s">
-        <v>155</v>
+        <v>23</v>
       </c>
       <c r="D104" s="38" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E104" s="38"/>
       <c r="F104" s="38" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G104" s="38"/>
       <c r="H104" s="38"/>
@@ -3326,20 +3302,20 @@
     </row>
     <row r="105" spans="1:10" customHeight="1" ht="15">
       <c r="A105" s="38">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B105" s="38" t="s">
-        <v>67</v>
+        <v>201</v>
       </c>
       <c r="C105" s="38" t="s">
-        <v>205</v>
-      </c>
-      <c r="D105" s="38">
-        <v>1929</v>
+        <v>23</v>
+      </c>
+      <c r="D105" s="38" t="s">
+        <v>202</v>
       </c>
       <c r="E105" s="38"/>
-      <c r="F105" s="38">
-        <v>730316922522</v>
+      <c r="F105" s="38" t="s">
+        <v>203</v>
       </c>
       <c r="G105" s="38"/>
       <c r="H105" s="38"/>
@@ -3347,20 +3323,20 @@
     </row>
     <row r="106" spans="1:10" customHeight="1" ht="15">
       <c r="A106" s="38">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B106" s="38" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C106" s="38" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="D106" s="38" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E106" s="38"/>
       <c r="F106" s="38" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G106" s="38"/>
       <c r="H106" s="38"/>
@@ -3368,105 +3344,129 @@
     </row>
     <row r="107" spans="1:10" customHeight="1" ht="15">
       <c r="A107" s="38">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B107" s="38" t="s">
-        <v>209</v>
+        <v>71</v>
       </c>
       <c r="C107" s="38" t="s">
-        <v>210</v>
+        <v>159</v>
       </c>
       <c r="D107" s="38" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E107" s="38"/>
       <c r="F107" s="38" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="G107" s="38"/>
       <c r="H107" s="38"/>
       <c r="I107" s="38"/>
     </row>
     <row r="108" spans="1:10" customHeight="1" ht="15">
-      <c r="A108" s="22"/>
-      <c r="B108" s="22"/>
-      <c r="C108" s="22"/>
-      <c r="D108" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="E108" s="22"/>
-      <c r="F108" s="22"/>
-      <c r="G108" s="22"/>
-      <c r="H108" s="22"/>
-      <c r="I108" s="22"/>
+      <c r="A108" s="38">
+        <v>87</v>
+      </c>
+      <c r="B108" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="C108" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="D108" s="38">
+        <v>1929</v>
+      </c>
+      <c r="E108" s="38"/>
+      <c r="F108" s="38">
+        <v>730316922522</v>
+      </c>
+      <c r="G108" s="38"/>
+      <c r="H108" s="38"/>
+      <c r="I108" s="38"/>
     </row>
     <row r="109" spans="1:10" customHeight="1" ht="15">
       <c r="A109" s="38">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B109" s="38" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C109" s="38" t="s">
-        <v>210</v>
+        <v>148</v>
       </c>
       <c r="D109" s="38" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E109" s="38"/>
       <c r="F109" s="38" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G109" s="38"/>
       <c r="H109" s="38"/>
       <c r="I109" s="38"/>
     </row>
     <row r="110" spans="1:10" customHeight="1" ht="15">
-      <c r="A110" s="22"/>
-      <c r="B110" s="22"/>
-      <c r="C110" s="22"/>
-      <c r="D110" s="22" t="s">
-        <v>216</v>
-      </c>
-      <c r="E110" s="22"/>
-      <c r="F110" s="22"/>
-      <c r="G110" s="22"/>
-      <c r="H110" s="22"/>
-      <c r="I110" s="22"/>
+      <c r="A110" s="38">
+        <v>89</v>
+      </c>
+      <c r="B110" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="C110" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D110" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="E110" s="38"/>
+      <c r="F110" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="G110" s="38"/>
+      <c r="H110" s="38"/>
+      <c r="I110" s="38"/>
     </row>
     <row r="111" spans="1:10" customHeight="1" ht="15">
       <c r="A111" s="38">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B111" s="38" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C111" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D111" s="38" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E111" s="38"/>
       <c r="F111" s="38" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G111" s="38"/>
       <c r="H111" s="38"/>
       <c r="I111" s="38"/>
     </row>
     <row r="112" spans="1:10" customHeight="1" ht="15">
-      <c r="A112" s="22"/>
-      <c r="B112" s="22"/>
-      <c r="C112" s="22"/>
-      <c r="D112" s="22" t="s">
+      <c r="A112" s="38">
+        <v>91</v>
+      </c>
+      <c r="B112" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="C112" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D112" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="E112" s="38"/>
+      <c r="F112" s="38" t="s">
         <v>220</v>
       </c>
-      <c r="E112" s="22"/>
-      <c r="F112" s="22"/>
-      <c r="G112" s="22"/>
-      <c r="H112" s="22"/>
-      <c r="I112" s="22"/>
+      <c r="G112" s="38"/>
+      <c r="H112" s="38"/>
+      <c r="I112" s="38"/>
     </row>
     <row r="113" spans="1:10" customHeight="1" ht="15">
       <c r="A113" s="16"/>

--- a/database/controller_excel/Resguardo_Alejandro_Cancino_Arguello.xlsx
+++ b/database/controller_excel/Resguardo_Alejandro_Cancino_Arguello.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="175">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>28/04/2025</t>
+    <t>30/04/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -86,43 +86,31 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
-    <t>Laptop</t>
+    <t>Camara Intrinsicamente segura</t>
+  </si>
+  <si>
+    <t>SONIM</t>
+  </si>
+  <si>
+    <t>XP7700</t>
+  </si>
+  <si>
+    <t>SWITCH SAN 1</t>
   </si>
   <si>
     <t>DELL</t>
   </si>
   <si>
-    <t>XPS 13 9315</t>
-  </si>
-  <si>
-    <t>29502T3</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00154</t>
-  </si>
-  <si>
-    <t>Desktop</t>
-  </si>
-  <si>
-    <t>HP</t>
-  </si>
-  <si>
-    <t>Elite Desk 800 G1</t>
-  </si>
-  <si>
-    <t>MXL5071Z2Q</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00027</t>
-  </si>
-  <si>
-    <t>EliteDesk 800G1</t>
-  </si>
-  <si>
-    <t>MXL4503CFF</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00110</t>
+    <t>POWERCONNECT 6224</t>
+  </si>
+  <si>
+    <t>D50KTS1</t>
+  </si>
+  <si>
+    <t>SWITCH SAN 2</t>
+  </si>
+  <si>
+    <t>J50KTS1</t>
   </si>
   <si>
     <t>CALL MANAGER NUEVO</t>
@@ -212,9 +200,6 @@
     <t>SD216</t>
   </si>
   <si>
-    <t>S/N</t>
-  </si>
-  <si>
     <t>NVR</t>
   </si>
   <si>
@@ -528,159 +513,6 @@
   </si>
   <si>
     <t>FCH19052DJ7</t>
-  </si>
-  <si>
-    <t>Camara Intrinsicamente segura</t>
-  </si>
-  <si>
-    <t>SONIM</t>
-  </si>
-  <si>
-    <t>XP7700</t>
-  </si>
-  <si>
-    <t>Bocina</t>
-  </si>
-  <si>
-    <t>Jabra</t>
-  </si>
-  <si>
-    <t>PHS001U</t>
-  </si>
-  <si>
-    <t>Pantalla TV</t>
-  </si>
-  <si>
-    <t>VISIO</t>
-  </si>
-  <si>
-    <t>E700I-B3</t>
-  </si>
-  <si>
-    <t>LFTRRGCQ4100300</t>
-  </si>
-  <si>
-    <t>LFTRRGCQ4000557</t>
-  </si>
-  <si>
-    <t>Equipo GEFEN</t>
-  </si>
-  <si>
-    <t>GEFEN</t>
-  </si>
-  <si>
-    <t>EXT-WHD-1080P-SRR</t>
-  </si>
-  <si>
-    <t>AX1508000071</t>
-  </si>
-  <si>
-    <t>GEFEN TOOL BOX</t>
-  </si>
-  <si>
-    <t>Epcom titanium</t>
-  </si>
-  <si>
-    <t>SKG18093503</t>
-  </si>
-  <si>
-    <t>Amplificador para Difusion</t>
-  </si>
-  <si>
-    <t>STEREN</t>
-  </si>
-  <si>
-    <t>Amplificador de Audio</t>
-  </si>
-  <si>
-    <t>Bocinas para Plafon</t>
-  </si>
-  <si>
-    <t>Bocinas</t>
-  </si>
-  <si>
-    <t>Video Proyector</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>U2722DE</t>
-  </si>
-  <si>
-    <t>93QBBH3</t>
-  </si>
-  <si>
-    <t>G3QBBH3</t>
-  </si>
-  <si>
-    <t>Doking Station</t>
-  </si>
-  <si>
-    <t>K20A</t>
-  </si>
-  <si>
-    <t>HP19XS3</t>
-  </si>
-  <si>
-    <t>Cargador de Doking</t>
-  </si>
-  <si>
-    <t>HA180MP180</t>
-  </si>
-  <si>
-    <t>CN-03XYY8-CH200-17G-0BTJ-A04</t>
-  </si>
-  <si>
-    <t>Teclado</t>
-  </si>
-  <si>
-    <t>K235</t>
-  </si>
-  <si>
-    <t>2212MR022028</t>
-  </si>
-  <si>
-    <t>M170</t>
-  </si>
-  <si>
-    <t>2206LZXB9VF8</t>
-  </si>
-  <si>
-    <t>Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UPS </t>
-  </si>
-  <si>
-    <t>5216 R</t>
-  </si>
-  <si>
-    <t>24-07-57975</t>
-  </si>
-  <si>
-    <t>SWITCH SAN 1</t>
-  </si>
-  <si>
-    <t>POWERCONNECT 6224</t>
-  </si>
-  <si>
-    <t>D50KTS1</t>
-  </si>
-  <si>
-    <t>SWITCH SAN 2</t>
-  </si>
-  <si>
-    <t>J50KTS1</t>
-  </si>
-  <si>
-    <t>Cargador Laptop</t>
-  </si>
-  <si>
-    <t>HA45SNM210</t>
-  </si>
-  <si>
-    <t>CN-05M5GT1-CH200-279-048G-A00</t>
   </si>
   <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
@@ -1538,38 +1370,46 @@
         <v>24</v>
       </c>
       <c r="E19" s="38"/>
-      <c r="F19" s="38" t="s">
-        <v>25</v>
+      <c r="F19" s="38">
+        <v>14187000333707</v>
       </c>
       <c r="G19" s="38"/>
       <c r="H19" s="38"/>
       <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="15">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22" t="s">
+      <c r="A20" s="38">
+        <v>2</v>
+      </c>
+      <c r="B20" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
+      <c r="D20" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
     </row>
     <row r="21" spans="1:10" customHeight="1" ht="15">
       <c r="A21" s="38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B21" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="38" t="s">
         <v>27</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="38" t="s">
-        <v>29</v>
       </c>
       <c r="E21" s="38"/>
       <c r="F21" s="38" t="s">
@@ -1580,68 +1420,84 @@
       <c r="I21" s="38"/>
     </row>
     <row r="22" spans="1:10" customHeight="1" ht="15">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22" t="s">
+      <c r="A22" s="38">
+        <v>4</v>
+      </c>
+      <c r="B22" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
+      <c r="C22" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
     </row>
     <row r="23" spans="1:10" customHeight="1" ht="15">
       <c r="A23" s="38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E23" s="38"/>
       <c r="F23" s="38" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G23" s="38"/>
       <c r="H23" s="38"/>
       <c r="I23" s="38"/>
     </row>
     <row r="24" spans="1:10" customHeight="1" ht="15">
-      <c r="A24" s="22"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
+      <c r="A24" s="38">
+        <v>6</v>
+      </c>
+      <c r="B24" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
     </row>
     <row r="25" spans="1:10" customHeight="1" ht="15">
       <c r="A25" s="38">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E25" s="38"/>
       <c r="F25" s="38" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
@@ -1649,20 +1505,20 @@
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="15">
       <c r="A26" s="38">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E26" s="38"/>
       <c r="F26" s="38" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G26" s="38"/>
       <c r="H26" s="38"/>
@@ -1670,20 +1526,20 @@
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="15">
       <c r="A27" s="38">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D27" s="38" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E27" s="38"/>
       <c r="F27" s="38" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G27" s="38"/>
       <c r="H27" s="38"/>
@@ -1691,20 +1547,20 @@
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
       <c r="A28" s="38">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E28" s="38"/>
       <c r="F28" s="38" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G28" s="38"/>
       <c r="H28" s="38"/>
@@ -1712,20 +1568,20 @@
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="15">
       <c r="A29" s="38">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E29" s="38"/>
       <c r="F29" s="38" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G29" s="38"/>
       <c r="H29" s="38"/>
@@ -1733,20 +1589,20 @@
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
       <c r="A30" s="38">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E30" s="38"/>
       <c r="F30" s="38" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G30" s="38"/>
       <c r="H30" s="38"/>
@@ -1754,20 +1610,20 @@
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="15">
       <c r="A31" s="38">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D31" s="38" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E31" s="38"/>
       <c r="F31" s="38" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G31" s="38"/>
       <c r="H31" s="38"/>
@@ -1775,20 +1631,20 @@
     </row>
     <row r="32" spans="1:10" customHeight="1" ht="15">
       <c r="A32" s="38">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="D32" s="38" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E32" s="38"/>
       <c r="F32" s="38" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G32" s="38"/>
       <c r="H32" s="38"/>
@@ -1796,20 +1652,20 @@
     </row>
     <row r="33" spans="1:10" customHeight="1" ht="15">
       <c r="A33" s="38">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C33" s="38" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="D33" s="38" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E33" s="38"/>
-      <c r="F33" s="38" t="s">
-        <v>61</v>
+      <c r="F33" s="38">
+        <v>647235228</v>
       </c>
       <c r="G33" s="38"/>
       <c r="H33" s="38"/>
@@ -1817,20 +1673,20 @@
     </row>
     <row r="34" spans="1:10" customHeight="1" ht="15">
       <c r="A34" s="38">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="D34" s="38" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E34" s="38"/>
       <c r="F34" s="38" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="G34" s="38"/>
       <c r="H34" s="38"/>
@@ -1838,20 +1694,20 @@
     </row>
     <row r="35" spans="1:10" customHeight="1" ht="15">
       <c r="A35" s="38">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C35" s="38" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D35" s="38" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="E35" s="38"/>
       <c r="F35" s="38" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="G35" s="38"/>
       <c r="H35" s="38"/>
@@ -1859,20 +1715,20 @@
     </row>
     <row r="36" spans="1:10" customHeight="1" ht="15">
       <c r="A36" s="38">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B36" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" s="38" t="s">
         <v>69</v>
-      </c>
-      <c r="C36" s="38" t="s">
-        <v>66</v>
       </c>
       <c r="D36" s="38" t="s">
         <v>70</v>
       </c>
       <c r="E36" s="38"/>
-      <c r="F36" s="38">
-        <v>647235228</v>
+      <c r="F36" s="38" t="s">
+        <v>71</v>
       </c>
       <c r="G36" s="38"/>
       <c r="H36" s="38"/>
@@ -1880,20 +1736,20 @@
     </row>
     <row r="37" spans="1:10" customHeight="1" ht="15">
       <c r="A37" s="38">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C37" s="38" t="s">
         <v>72</v>
       </c>
       <c r="D37" s="38" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E37" s="38"/>
       <c r="F37" s="38" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="G37" s="38"/>
       <c r="H37" s="38"/>
@@ -1901,20 +1757,20 @@
     </row>
     <row r="38" spans="1:10" customHeight="1" ht="15">
       <c r="A38" s="38">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C38" s="38" t="s">
         <v>72</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E38" s="38"/>
       <c r="F38" s="38" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G38" s="38"/>
       <c r="H38" s="38"/>
@@ -1922,20 +1778,20 @@
     </row>
     <row r="39" spans="1:10" customHeight="1" ht="15">
       <c r="A39" s="38">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E39" s="38"/>
       <c r="F39" s="38" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G39" s="38"/>
       <c r="H39" s="38"/>
@@ -1943,20 +1799,20 @@
     </row>
     <row r="40" spans="1:10" customHeight="1" ht="15">
       <c r="A40" s="38">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B40" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="C40" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="D40" s="38" t="s">
         <v>77</v>
-      </c>
-      <c r="C40" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="D40" s="38" t="s">
-        <v>64</v>
       </c>
       <c r="E40" s="38"/>
       <c r="F40" s="38" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G40" s="38"/>
       <c r="H40" s="38"/>
@@ -1964,20 +1820,20 @@
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
       <c r="A41" s="38">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B41" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="C41" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="D41" s="38" t="s">
         <v>77</v>
-      </c>
-      <c r="C41" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="D41" s="38" t="s">
-        <v>64</v>
       </c>
       <c r="E41" s="38"/>
       <c r="F41" s="38" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G41" s="38"/>
       <c r="H41" s="38"/>
@@ -1985,20 +1841,20 @@
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
       <c r="A42" s="38">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C42" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="D42" s="38" t="s">
         <v>81</v>
-      </c>
-      <c r="D42" s="38" t="s">
-        <v>82</v>
       </c>
       <c r="E42" s="38"/>
       <c r="F42" s="38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G42" s="38"/>
       <c r="H42" s="38"/>
@@ -2006,16 +1862,16 @@
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="38">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38" t="s">
@@ -2027,16 +1883,16 @@
     </row>
     <row r="44" spans="1:10" customHeight="1" ht="15">
       <c r="A44" s="38">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C44" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="D44" s="38" t="s">
         <v>81</v>
-      </c>
-      <c r="D44" s="38" t="s">
-        <v>82</v>
       </c>
       <c r="E44" s="38"/>
       <c r="F44" s="38" t="s">
@@ -2048,20 +1904,20 @@
     </row>
     <row r="45" spans="1:10" customHeight="1" ht="15">
       <c r="A45" s="38">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E45" s="38"/>
       <c r="F45" s="38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G45" s="38"/>
       <c r="H45" s="38"/>
@@ -2069,20 +1925,20 @@
     </row>
     <row r="46" spans="1:10" customHeight="1" ht="15">
       <c r="A46" s="38">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="E46" s="38"/>
       <c r="F46" s="38" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G46" s="38"/>
       <c r="H46" s="38"/>
@@ -2090,20 +1946,20 @@
     </row>
     <row r="47" spans="1:10" customHeight="1" ht="15">
       <c r="A47" s="38">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B47" s="38" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C47" s="38" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E47" s="38"/>
       <c r="F47" s="38" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G47" s="38"/>
       <c r="H47" s="38"/>
@@ -2111,20 +1967,20 @@
     </row>
     <row r="48" spans="1:10" customHeight="1" ht="15">
       <c r="A48" s="38">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B48" s="38" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C48" s="38" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D48" s="38" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E48" s="38"/>
       <c r="F48" s="38" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G48" s="38"/>
       <c r="H48" s="38"/>
@@ -2132,20 +1988,20 @@
     </row>
     <row r="49" spans="1:10" customHeight="1" ht="15">
       <c r="A49" s="38">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B49" s="38" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C49" s="38" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="E49" s="38"/>
       <c r="F49" s="38" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G49" s="38"/>
       <c r="H49" s="38"/>
@@ -2153,20 +2009,18 @@
     </row>
     <row r="50" spans="1:10" customHeight="1" ht="15">
       <c r="A50" s="38">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B50" s="38" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="C50" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="D50" s="38" t="s">
-        <v>93</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="D50" s="38"/>
       <c r="E50" s="38"/>
       <c r="F50" s="38" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G50" s="38"/>
       <c r="H50" s="38"/>
@@ -2174,20 +2028,20 @@
     </row>
     <row r="51" spans="1:10" customHeight="1" ht="15">
       <c r="A51" s="38">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B51" s="38" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C51" s="38" t="s">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="D51" s="38" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E51" s="38"/>
       <c r="F51" s="38" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G51" s="38"/>
       <c r="H51" s="38"/>
@@ -2195,20 +2049,20 @@
     </row>
     <row r="52" spans="1:10" customHeight="1" ht="15">
       <c r="A52" s="38">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B52" s="38" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C52" s="38" t="s">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="D52" s="38" t="s">
         <v>99</v>
       </c>
       <c r="E52" s="38"/>
       <c r="F52" s="38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G52" s="38"/>
       <c r="H52" s="38"/>
@@ -2216,18 +2070,20 @@
     </row>
     <row r="53" spans="1:10" customHeight="1" ht="15">
       <c r="A53" s="38">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B53" s="38" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C53" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="D53" s="38"/>
+        <v>103</v>
+      </c>
+      <c r="D53" s="38" t="s">
+        <v>104</v>
+      </c>
       <c r="E53" s="38"/>
       <c r="F53" s="38" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G53" s="38"/>
       <c r="H53" s="38"/>
@@ -2235,20 +2091,20 @@
     </row>
     <row r="54" spans="1:10" customHeight="1" ht="15">
       <c r="A54" s="38">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B54" s="38" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C54" s="38" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="D54" s="38" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E54" s="38"/>
       <c r="F54" s="38" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G54" s="38"/>
       <c r="H54" s="38"/>
@@ -2256,20 +2112,20 @@
     </row>
     <row r="55" spans="1:10" customHeight="1" ht="15">
       <c r="A55" s="38">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B55" s="38" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C55" s="38" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="D55" s="38" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E55" s="38"/>
       <c r="F55" s="38" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G55" s="38"/>
       <c r="H55" s="38"/>
@@ -2277,16 +2133,16 @@
     </row>
     <row r="56" spans="1:10" customHeight="1" ht="15">
       <c r="A56" s="38">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B56" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="C56" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="D56" s="38" t="s">
         <v>107</v>
-      </c>
-      <c r="C56" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="D56" s="38" t="s">
-        <v>109</v>
       </c>
       <c r="E56" s="38"/>
       <c r="F56" s="38" t="s">
@@ -2298,20 +2154,20 @@
     </row>
     <row r="57" spans="1:10" customHeight="1" ht="15">
       <c r="A57" s="38">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B57" s="38" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C57" s="38" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D57" s="38" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E57" s="38"/>
       <c r="F57" s="38" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G57" s="38"/>
       <c r="H57" s="38"/>
@@ -2319,16 +2175,16 @@
     </row>
     <row r="58" spans="1:10" customHeight="1" ht="15">
       <c r="A58" s="38">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B58" s="38" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C58" s="38" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="D58" s="38" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E58" s="38"/>
       <c r="F58" s="38" t="s">
@@ -2340,20 +2196,20 @@
     </row>
     <row r="59" spans="1:10" customHeight="1" ht="15">
       <c r="A59" s="38">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B59" s="38" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C59" s="38" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="D59" s="38" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E59" s="38"/>
       <c r="F59" s="38" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G59" s="38"/>
       <c r="H59" s="38"/>
@@ -2361,20 +2217,20 @@
     </row>
     <row r="60" spans="1:10" customHeight="1" ht="15">
       <c r="A60" s="38">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B60" s="38" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C60" s="38" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="D60" s="38" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E60" s="38"/>
       <c r="F60" s="38" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G60" s="38"/>
       <c r="H60" s="38"/>
@@ -2382,20 +2238,20 @@
     </row>
     <row r="61" spans="1:10" customHeight="1" ht="15">
       <c r="A61" s="38">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B61" s="38" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C61" s="38" t="s">
-        <v>118</v>
+        <v>61</v>
       </c>
       <c r="D61" s="38" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E61" s="38"/>
       <c r="F61" s="38" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G61" s="38"/>
       <c r="H61" s="38"/>
@@ -2403,20 +2259,20 @@
     </row>
     <row r="62" spans="1:10" customHeight="1" ht="15">
       <c r="A62" s="38">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B62" s="38" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C62" s="38" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D62" s="38" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E62" s="38"/>
       <c r="F62" s="38" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G62" s="38"/>
       <c r="H62" s="38"/>
@@ -2424,20 +2280,20 @@
     </row>
     <row r="63" spans="1:10" customHeight="1" ht="15">
       <c r="A63" s="38">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B63" s="38" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C63" s="38" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D63" s="38" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E63" s="38"/>
       <c r="F63" s="38" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G63" s="38"/>
       <c r="H63" s="38"/>
@@ -2445,13 +2301,13 @@
     </row>
     <row r="64" spans="1:10" customHeight="1" ht="15">
       <c r="A64" s="38">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B64" s="38" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C64" s="38" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D64" s="38" t="s">
         <v>126</v>
@@ -2466,20 +2322,20 @@
     </row>
     <row r="65" spans="1:10" customHeight="1" ht="15">
       <c r="A65" s="38">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B65" s="38" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C65" s="38" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D65" s="38" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E65" s="38"/>
       <c r="F65" s="38" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G65" s="38"/>
       <c r="H65" s="38"/>
@@ -2487,20 +2343,20 @@
     </row>
     <row r="66" spans="1:10" customHeight="1" ht="15">
       <c r="A66" s="38">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B66" s="38" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C66" s="38" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D66" s="38" t="s">
         <v>123</v>
       </c>
       <c r="E66" s="38"/>
       <c r="F66" s="38" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G66" s="38"/>
       <c r="H66" s="38"/>
@@ -2508,20 +2364,20 @@
     </row>
     <row r="67" spans="1:10" customHeight="1" ht="15">
       <c r="A67" s="38">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B67" s="38" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C67" s="38" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D67" s="38" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E67" s="38"/>
       <c r="F67" s="38" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G67" s="38"/>
       <c r="H67" s="38"/>
@@ -2529,20 +2385,20 @@
     </row>
     <row r="68" spans="1:10" customHeight="1" ht="15">
       <c r="A68" s="38">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B68" s="38" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C68" s="38" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D68" s="38" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E68" s="38"/>
       <c r="F68" s="38" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G68" s="38"/>
       <c r="H68" s="38"/>
@@ -2550,20 +2406,20 @@
     </row>
     <row r="69" spans="1:10" customHeight="1" ht="15">
       <c r="A69" s="38">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B69" s="38" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C69" s="38" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D69" s="38" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E69" s="38"/>
       <c r="F69" s="38" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G69" s="38"/>
       <c r="H69" s="38"/>
@@ -2571,20 +2427,20 @@
     </row>
     <row r="70" spans="1:10" customHeight="1" ht="15">
       <c r="A70" s="38">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B70" s="38" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C70" s="38" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D70" s="38" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E70" s="38"/>
       <c r="F70" s="38" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G70" s="38"/>
       <c r="H70" s="38"/>
@@ -2592,20 +2448,20 @@
     </row>
     <row r="71" spans="1:10" customHeight="1" ht="15">
       <c r="A71" s="38">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B71" s="38" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C71" s="38" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D71" s="38" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E71" s="38"/>
       <c r="F71" s="38" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G71" s="38"/>
       <c r="H71" s="38"/>
@@ -2613,20 +2469,20 @@
     </row>
     <row r="72" spans="1:10" customHeight="1" ht="15">
       <c r="A72" s="38">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B72" s="38" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C72" s="38" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D72" s="38" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="E72" s="38"/>
       <c r="F72" s="38" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G72" s="38"/>
       <c r="H72" s="38"/>
@@ -2634,20 +2490,20 @@
     </row>
     <row r="73" spans="1:10" customHeight="1" ht="15">
       <c r="A73" s="38">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B73" s="38" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C73" s="38" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D73" s="38" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="E73" s="38"/>
       <c r="F73" s="38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G73" s="38"/>
       <c r="H73" s="38"/>
@@ -2655,20 +2511,20 @@
     </row>
     <row r="74" spans="1:10" customHeight="1" ht="15">
       <c r="A74" s="38">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B74" s="38" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C74" s="38" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D74" s="38" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E74" s="38"/>
       <c r="F74" s="38" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G74" s="38"/>
       <c r="H74" s="38"/>
@@ -2676,20 +2532,20 @@
     </row>
     <row r="75" spans="1:10" customHeight="1" ht="15">
       <c r="A75" s="38">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B75" s="38" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C75" s="38" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D75" s="38" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="E75" s="38"/>
       <c r="F75" s="38" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G75" s="38"/>
       <c r="H75" s="38"/>
@@ -2697,20 +2553,20 @@
     </row>
     <row r="76" spans="1:10" customHeight="1" ht="15">
       <c r="A76" s="38">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B76" s="38" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C76" s="38" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D76" s="38" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="E76" s="38"/>
       <c r="F76" s="38" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G76" s="38"/>
       <c r="H76" s="38"/>
@@ -2718,20 +2574,20 @@
     </row>
     <row r="77" spans="1:10" customHeight="1" ht="15">
       <c r="A77" s="38">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B77" s="38" t="s">
         <v>120</v>
       </c>
       <c r="C77" s="38" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D77" s="38" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="E77" s="38"/>
       <c r="F77" s="38" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G77" s="38"/>
       <c r="H77" s="38"/>
@@ -2739,16 +2595,16 @@
     </row>
     <row r="78" spans="1:10" customHeight="1" ht="15">
       <c r="A78" s="38">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B78" s="38" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="C78" s="38" t="s">
-        <v>66</v>
+        <v>143</v>
       </c>
       <c r="D78" s="38" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E78" s="38"/>
       <c r="F78" s="38" t="s">
@@ -2760,20 +2616,20 @@
     </row>
     <row r="79" spans="1:10" customHeight="1" ht="15">
       <c r="A79" s="38">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B79" s="38" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="C79" s="38" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="D79" s="38" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E79" s="38"/>
-      <c r="F79" s="38" t="s">
-        <v>146</v>
+      <c r="F79" s="38">
+        <v>544161389</v>
       </c>
       <c r="G79" s="38"/>
       <c r="H79" s="38"/>
@@ -2781,20 +2637,20 @@
     </row>
     <row r="80" spans="1:10" customHeight="1" ht="15">
       <c r="A80" s="38">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B80" s="38" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="C80" s="38" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="D80" s="38" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="E80" s="38"/>
-      <c r="F80" s="38" t="s">
-        <v>147</v>
+      <c r="F80" s="38">
+        <v>544161388</v>
       </c>
       <c r="G80" s="38"/>
       <c r="H80" s="38"/>
@@ -2802,20 +2658,20 @@
     </row>
     <row r="81" spans="1:10" customHeight="1" ht="15">
       <c r="A81" s="38">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B81" s="38" t="s">
-        <v>107</v>
+        <v>149</v>
       </c>
       <c r="C81" s="38" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D81" s="38" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E81" s="38"/>
       <c r="F81" s="38" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G81" s="38"/>
       <c r="H81" s="38"/>
@@ -2823,20 +2679,20 @@
     </row>
     <row r="82" spans="1:10" customHeight="1" ht="15">
       <c r="A82" s="38">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B82" s="38" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C82" s="38" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D82" s="38" t="s">
-        <v>153</v>
+        <v>45</v>
       </c>
       <c r="E82" s="38"/>
-      <c r="F82" s="38">
-        <v>544161389</v>
+      <c r="F82" s="38" t="s">
+        <v>155</v>
       </c>
       <c r="G82" s="38"/>
       <c r="H82" s="38"/>
@@ -2844,20 +2700,20 @@
     </row>
     <row r="83" spans="1:10" customHeight="1" ht="15">
       <c r="A83" s="38">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B83" s="38" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C83" s="38" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D83" s="38" t="s">
-        <v>153</v>
+        <v>45</v>
       </c>
       <c r="E83" s="38"/>
-      <c r="F83" s="38">
-        <v>544161388</v>
+      <c r="F83" s="38" t="s">
+        <v>45</v>
       </c>
       <c r="G83" s="38"/>
       <c r="H83" s="38"/>
@@ -2865,20 +2721,20 @@
     </row>
     <row r="84" spans="1:10" customHeight="1" ht="15">
       <c r="A84" s="38">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B84" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="C84" s="38" t="s">
         <v>154</v>
       </c>
-      <c r="C84" s="38" t="s">
-        <v>155</v>
-      </c>
       <c r="D84" s="38" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E84" s="38"/>
       <c r="F84" s="38" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G84" s="38"/>
       <c r="H84" s="38"/>
@@ -2886,20 +2742,20 @@
     </row>
     <row r="85" spans="1:10" customHeight="1" ht="15">
       <c r="A85" s="38">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B85" s="38" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C85" s="38" t="s">
-        <v>159</v>
+        <v>76</v>
       </c>
       <c r="D85" s="38" t="s">
-        <v>64</v>
+        <v>161</v>
       </c>
       <c r="E85" s="38"/>
       <c r="F85" s="38" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G85" s="38"/>
       <c r="H85" s="38"/>
@@ -2907,839 +2763,297 @@
     </row>
     <row r="86" spans="1:10" customHeight="1" ht="15">
       <c r="A86" s="38">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B86" s="38" t="s">
+        <v>163</v>
+      </c>
+      <c r="C86" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="D86" s="38" t="s">
         <v>161</v>
-      </c>
-      <c r="C86" s="38" t="s">
-        <v>162</v>
-      </c>
-      <c r="D86" s="38" t="s">
-        <v>64</v>
       </c>
       <c r="E86" s="38"/>
       <c r="F86" s="38" t="s">
-        <v>64</v>
+        <v>164</v>
       </c>
       <c r="G86" s="38"/>
       <c r="H86" s="38"/>
       <c r="I86" s="38"/>
     </row>
     <row r="87" spans="1:10" customHeight="1" ht="15">
-      <c r="A87" s="38">
-        <v>66</v>
-      </c>
-      <c r="B87" s="38" t="s">
-        <v>163</v>
-      </c>
-      <c r="C87" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="D87" s="38" t="s">
-        <v>164</v>
-      </c>
-      <c r="E87" s="38"/>
-      <c r="F87" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="G87" s="38"/>
-      <c r="H87" s="38"/>
-      <c r="I87" s="38"/>
+      <c r="A87" s="16"/>
+      <c r="B87" s="16"/>
+      <c r="C87" s="16"/>
+      <c r="D87" s="16"/>
+      <c r="E87" s="16"/>
+      <c r="F87" s="23"/>
+      <c r="G87" s="23"/>
+      <c r="H87" s="24"/>
+      <c r="I87" s="24"/>
     </row>
     <row r="88" spans="1:10" customHeight="1" ht="15">
-      <c r="A88" s="38">
-        <v>67</v>
-      </c>
-      <c r="B88" s="38" t="s">
+      <c r="A88" s="25"/>
+      <c r="B88" s="25"/>
+      <c r="C88" s="25"/>
+      <c r="D88" s="25"/>
+      <c r="E88" s="25"/>
+      <c r="F88" s="25"/>
+      <c r="G88" s="25"/>
+      <c r="H88" s="25"/>
+      <c r="I88" s="25"/>
+    </row>
+    <row r="89" spans="1:10" customHeight="1" ht="15">
+      <c r="A89" s="26" t="s">
         <v>165</v>
       </c>
-      <c r="C88" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="D88" s="38" t="s">
+      <c r="B89" s="26"/>
+      <c r="C89" s="26"/>
+      <c r="D89" s="26"/>
+      <c r="E89" s="26"/>
+      <c r="F89" s="26"/>
+      <c r="G89" s="26"/>
+      <c r="H89" s="26"/>
+      <c r="I89" s="26"/>
+    </row>
+    <row r="90" spans="1:10" customHeight="1" ht="15">
+      <c r="A90" s="27"/>
+      <c r="B90" s="27"/>
+      <c r="C90" s="27"/>
+      <c r="D90" s="27"/>
+      <c r="E90" s="27"/>
+      <c r="F90" s="27"/>
+      <c r="G90" s="27"/>
+      <c r="H90" s="27"/>
+      <c r="I90" s="27"/>
+    </row>
+    <row r="91" spans="1:10" customHeight="1" ht="15">
+      <c r="A91" s="28" t="s">
         <v>166</v>
       </c>
-      <c r="E88" s="38"/>
-      <c r="F88" s="38" t="s">
+      <c r="B91" s="28"/>
+      <c r="C91" s="28"/>
+      <c r="D91" s="28"/>
+      <c r="E91" s="28"/>
+      <c r="F91" s="28"/>
+      <c r="G91" s="28"/>
+      <c r="H91" s="28"/>
+      <c r="I91" s="28"/>
+    </row>
+    <row r="92" spans="1:10" customHeight="1" ht="15">
+      <c r="A92" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="G88" s="38"/>
-      <c r="H88" s="38"/>
-      <c r="I88" s="38"/>
-    </row>
-    <row r="89" spans="1:10" customHeight="1" ht="15">
-      <c r="A89" s="38">
-        <v>68</v>
-      </c>
-      <c r="B89" s="38" t="s">
+      <c r="B92" s="28"/>
+      <c r="C92" s="28"/>
+      <c r="D92" s="28"/>
+      <c r="E92" s="28"/>
+      <c r="F92" s="28"/>
+      <c r="G92" s="28"/>
+      <c r="H92" s="28"/>
+      <c r="I92" s="28"/>
+    </row>
+    <row r="93" spans="1:10" customHeight="1" ht="15">
+      <c r="A93" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="C89" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="D89" s="38" t="s">
-        <v>166</v>
-      </c>
-      <c r="E89" s="38"/>
-      <c r="F89" s="38" t="s">
+      <c r="B93" s="28"/>
+      <c r="C93" s="28"/>
+      <c r="D93" s="28"/>
+      <c r="E93" s="28"/>
+      <c r="F93" s="28"/>
+      <c r="G93" s="28"/>
+      <c r="H93" s="28"/>
+      <c r="I93" s="28"/>
+    </row>
+    <row r="94" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A94" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="G89" s="38"/>
-      <c r="H89" s="38"/>
-      <c r="I89" s="38"/>
-    </row>
-    <row r="90" spans="1:10" customHeight="1" ht="15">
-      <c r="A90" s="38">
-        <v>69</v>
-      </c>
-      <c r="B90" s="38" t="s">
+      <c r="B94" s="29"/>
+      <c r="C94" s="29"/>
+      <c r="D94" s="29"/>
+      <c r="E94" s="29"/>
+      <c r="F94" s="29"/>
+      <c r="G94" s="29"/>
+      <c r="H94" s="29"/>
+      <c r="I94" s="29"/>
+      <c r="J94" s="2"/>
+    </row>
+    <row r="95" spans="1:10" customHeight="1" ht="27">
+      <c r="A95" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="C90" s="38" t="s">
+      <c r="B95" s="28"/>
+      <c r="C95" s="28"/>
+      <c r="D95" s="28"/>
+      <c r="E95" s="28"/>
+      <c r="F95" s="28"/>
+      <c r="G95" s="28"/>
+      <c r="H95" s="28"/>
+      <c r="I95" s="28"/>
+    </row>
+    <row r="96" spans="1:10" customHeight="1" ht="15">
+      <c r="A96" s="30"/>
+      <c r="B96" s="30"/>
+      <c r="C96" s="30"/>
+      <c r="D96" s="30"/>
+      <c r="E96" s="30"/>
+      <c r="F96" s="30"/>
+      <c r="G96" s="30"/>
+      <c r="H96" s="30"/>
+      <c r="I96" s="30"/>
+    </row>
+    <row r="97" spans="1:10" customHeight="1" ht="39">
+      <c r="A97" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="D90" s="38" t="s">
+      <c r="B97" s="31"/>
+      <c r="C97" s="31"/>
+      <c r="D97" s="31"/>
+      <c r="E97" s="31"/>
+      <c r="F97" s="31"/>
+      <c r="G97" s="31"/>
+      <c r="H97" s="31"/>
+      <c r="I97" s="31"/>
+    </row>
+    <row r="98" spans="1:10" customHeight="1" ht="15">
+      <c r="A98" s="32"/>
+      <c r="B98" s="32"/>
+      <c r="C98" s="32"/>
+      <c r="D98" s="32"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="33"/>
+      <c r="H98" s="33"/>
+      <c r="I98" s="33"/>
+    </row>
+    <row r="99" spans="1:10" customHeight="1" ht="15">
+      <c r="A99" s="2"/>
+      <c r="B99" s="32"/>
+      <c r="C99" s="32"/>
+      <c r="D99" s="32"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="33"/>
+      <c r="I99" s="33"/>
+    </row>
+    <row r="100" spans="1:10" customHeight="1" ht="15">
+      <c r="A100" s="32"/>
+      <c r="B100" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="E90" s="38"/>
-      <c r="F90" s="38">
-        <v>14187000333707</v>
-      </c>
-      <c r="G90" s="38"/>
-      <c r="H90" s="38"/>
-      <c r="I90" s="38"/>
-    </row>
-    <row r="91" spans="1:10" customHeight="1" ht="15">
-      <c r="A91" s="38">
-        <v>70</v>
-      </c>
-      <c r="B91" s="38" t="s">
+      <c r="C100" s="34"/>
+      <c r="D100" s="34"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="35" t="s">
         <v>173</v>
       </c>
-      <c r="C91" s="38" t="s">
+      <c r="H100" s="35"/>
+      <c r="I100" s="35"/>
+    </row>
+    <row r="101" spans="1:10" customHeight="1" ht="15">
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="D91" s="38" t="s">
-        <v>175</v>
-      </c>
-      <c r="E91" s="38"/>
-      <c r="F91" s="38">
-        <v>29016400</v>
-      </c>
-      <c r="G91" s="38"/>
-      <c r="H91" s="38"/>
-      <c r="I91" s="38"/>
-    </row>
-    <row r="92" spans="1:10" customHeight="1" ht="15">
-      <c r="A92" s="38">
-        <v>71</v>
-      </c>
-      <c r="B92" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="C92" s="38" t="s">
-        <v>177</v>
-      </c>
-      <c r="D92" s="38" t="s">
-        <v>178</v>
-      </c>
-      <c r="E92" s="38"/>
-      <c r="F92" s="38" t="s">
-        <v>179</v>
-      </c>
-      <c r="G92" s="38"/>
-      <c r="H92" s="38"/>
-      <c r="I92" s="38"/>
-    </row>
-    <row r="93" spans="1:10" customHeight="1" ht="15">
-      <c r="A93" s="38">
-        <v>72</v>
-      </c>
-      <c r="B93" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="C93" s="38" t="s">
-        <v>177</v>
-      </c>
-      <c r="D93" s="38" t="s">
-        <v>178</v>
-      </c>
-      <c r="E93" s="38"/>
-      <c r="F93" s="38" t="s">
-        <v>180</v>
-      </c>
-      <c r="G93" s="38"/>
-      <c r="H93" s="38"/>
-      <c r="I93" s="38"/>
-    </row>
-    <row r="94" spans="1:10" customHeight="1" ht="15">
-      <c r="A94" s="38">
-        <v>73</v>
-      </c>
-      <c r="B94" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="C94" s="38" t="s">
-        <v>182</v>
-      </c>
-      <c r="D94" s="38" t="s">
-        <v>183</v>
-      </c>
-      <c r="E94" s="38"/>
-      <c r="F94" s="38" t="s">
-        <v>184</v>
-      </c>
-      <c r="G94" s="38"/>
-      <c r="H94" s="38"/>
-      <c r="I94" s="38"/>
-    </row>
-    <row r="95" spans="1:10" customHeight="1" ht="15">
-      <c r="A95" s="38">
-        <v>74</v>
-      </c>
-      <c r="B95" s="38" t="s">
-        <v>185</v>
-      </c>
-      <c r="C95" s="38" t="s">
-        <v>185</v>
-      </c>
-      <c r="D95" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="E95" s="38"/>
-      <c r="F95" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="G95" s="38"/>
-      <c r="H95" s="38"/>
-      <c r="I95" s="38"/>
-    </row>
-    <row r="96" spans="1:10" customHeight="1" ht="15">
-      <c r="A96" s="38">
-        <v>75</v>
-      </c>
-      <c r="B96" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="C96" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="D96" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="E96" s="38"/>
-      <c r="F96" s="38" t="s">
-        <v>187</v>
-      </c>
-      <c r="G96" s="38"/>
-      <c r="H96" s="38"/>
-      <c r="I96" s="38"/>
-    </row>
-    <row r="97" spans="1:10" customHeight="1" ht="15">
-      <c r="A97" s="38">
-        <v>76</v>
-      </c>
-      <c r="B97" s="38" t="s">
-        <v>185</v>
-      </c>
-      <c r="C97" s="38" t="s">
-        <v>185</v>
-      </c>
-      <c r="D97" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="E97" s="38"/>
-      <c r="F97" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="G97" s="38"/>
-      <c r="H97" s="38"/>
-      <c r="I97" s="38"/>
-    </row>
-    <row r="98" spans="1:10" customHeight="1" ht="15">
-      <c r="A98" s="38">
-        <v>77</v>
-      </c>
-      <c r="B98" s="38" t="s">
-        <v>188</v>
-      </c>
-      <c r="C98" s="38" t="s">
-        <v>189</v>
-      </c>
-      <c r="D98" s="38" t="s">
-        <v>190</v>
-      </c>
-      <c r="E98" s="38"/>
-      <c r="F98" s="38"/>
-      <c r="G98" s="38"/>
-      <c r="H98" s="38"/>
-      <c r="I98" s="38"/>
-    </row>
-    <row r="99" spans="1:10" customHeight="1" ht="15">
-      <c r="A99" s="38">
-        <v>78</v>
-      </c>
-      <c r="B99" s="38" t="s">
-        <v>191</v>
-      </c>
-      <c r="C99" s="38" t="s">
-        <v>189</v>
-      </c>
-      <c r="D99" s="38" t="s">
-        <v>192</v>
-      </c>
-      <c r="E99" s="38"/>
-      <c r="F99" s="38"/>
-      <c r="G99" s="38"/>
-      <c r="H99" s="38"/>
-      <c r="I99" s="38"/>
-    </row>
-    <row r="100" spans="1:10" customHeight="1" ht="15">
-      <c r="A100" s="38">
-        <v>79</v>
-      </c>
-      <c r="B100" s="38" t="s">
-        <v>193</v>
-      </c>
-      <c r="C100" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D100" s="38" t="s">
-        <v>194</v>
-      </c>
-      <c r="E100" s="38"/>
-      <c r="F100" s="38" t="s">
-        <v>194</v>
-      </c>
-      <c r="G100" s="38"/>
-      <c r="H100" s="38"/>
-      <c r="I100" s="38"/>
-    </row>
-    <row r="101" spans="1:10" customHeight="1" ht="15">
-      <c r="A101" s="38">
-        <v>80</v>
-      </c>
-      <c r="B101" s="38" t="s">
-        <v>173</v>
-      </c>
-      <c r="C101" s="38" t="s">
-        <v>174</v>
-      </c>
-      <c r="D101" s="38" t="s">
-        <v>175</v>
-      </c>
-      <c r="E101" s="38"/>
-      <c r="F101" s="38">
-        <v>29016514</v>
-      </c>
-      <c r="G101" s="38"/>
-      <c r="H101" s="38"/>
-      <c r="I101" s="38"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
+      <c r="I101" s="2"/>
     </row>
     <row r="102" spans="1:10" customHeight="1" ht="15">
-      <c r="A102" s="38">
-        <v>81</v>
-      </c>
-      <c r="B102" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="C102" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D102" s="38" t="s">
-        <v>195</v>
-      </c>
-      <c r="E102" s="38"/>
-      <c r="F102" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="G102" s="38"/>
-      <c r="H102" s="38"/>
-      <c r="I102" s="38"/>
+      <c r="A102" s="2"/>
+      <c r="B102" s="37"/>
+      <c r="C102" s="37"/>
+      <c r="D102" s="37"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="37"/>
+      <c r="H102" s="37"/>
+      <c r="I102" s="37"/>
     </row>
     <row r="103" spans="1:10" customHeight="1" ht="15">
-      <c r="A103" s="38">
-        <v>82</v>
-      </c>
-      <c r="B103" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="C103" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D103" s="38" t="s">
-        <v>195</v>
-      </c>
-      <c r="E103" s="38"/>
-      <c r="F103" s="38" t="s">
-        <v>197</v>
-      </c>
-      <c r="G103" s="38"/>
-      <c r="H103" s="38"/>
-      <c r="I103" s="38"/>
+      <c r="A103" s="2"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2"/>
+      <c r="I103" s="2"/>
     </row>
     <row r="104" spans="1:10" customHeight="1" ht="15">
-      <c r="A104" s="38">
-        <v>83</v>
-      </c>
-      <c r="B104" s="38" t="s">
-        <v>198</v>
-      </c>
-      <c r="C104" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D104" s="38" t="s">
-        <v>199</v>
-      </c>
-      <c r="E104" s="38"/>
-      <c r="F104" s="38" t="s">
-        <v>200</v>
-      </c>
-      <c r="G104" s="38"/>
-      <c r="H104" s="38"/>
-      <c r="I104" s="38"/>
-    </row>
-    <row r="105" spans="1:10" customHeight="1" ht="15">
-      <c r="A105" s="38">
-        <v>84</v>
-      </c>
-      <c r="B105" s="38" t="s">
-        <v>201</v>
-      </c>
-      <c r="C105" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D105" s="38" t="s">
-        <v>202</v>
-      </c>
-      <c r="E105" s="38"/>
-      <c r="F105" s="38" t="s">
-        <v>203</v>
-      </c>
-      <c r="G105" s="38"/>
-      <c r="H105" s="38"/>
-      <c r="I105" s="38"/>
-    </row>
-    <row r="106" spans="1:10" customHeight="1" ht="15">
-      <c r="A106" s="38">
-        <v>85</v>
-      </c>
-      <c r="B106" s="38" t="s">
-        <v>204</v>
-      </c>
-      <c r="C106" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="D106" s="38" t="s">
-        <v>205</v>
-      </c>
-      <c r="E106" s="38"/>
-      <c r="F106" s="38" t="s">
-        <v>206</v>
-      </c>
-      <c r="G106" s="38"/>
-      <c r="H106" s="38"/>
-      <c r="I106" s="38"/>
-    </row>
-    <row r="107" spans="1:10" customHeight="1" ht="15">
-      <c r="A107" s="38">
-        <v>86</v>
-      </c>
-      <c r="B107" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="C107" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="D107" s="38" t="s">
-        <v>207</v>
-      </c>
-      <c r="E107" s="38"/>
-      <c r="F107" s="38" t="s">
-        <v>208</v>
-      </c>
-      <c r="G107" s="38"/>
-      <c r="H107" s="38"/>
-      <c r="I107" s="38"/>
-    </row>
-    <row r="108" spans="1:10" customHeight="1" ht="15">
-      <c r="A108" s="38">
-        <v>87</v>
-      </c>
-      <c r="B108" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="C108" s="38" t="s">
-        <v>209</v>
-      </c>
-      <c r="D108" s="38">
-        <v>1929</v>
-      </c>
-      <c r="E108" s="38"/>
-      <c r="F108" s="38">
-        <v>730316922522</v>
-      </c>
-      <c r="G108" s="38"/>
-      <c r="H108" s="38"/>
-      <c r="I108" s="38"/>
-    </row>
-    <row r="109" spans="1:10" customHeight="1" ht="15">
-      <c r="A109" s="38">
-        <v>88</v>
-      </c>
-      <c r="B109" s="38" t="s">
-        <v>210</v>
-      </c>
-      <c r="C109" s="38" t="s">
-        <v>148</v>
-      </c>
-      <c r="D109" s="38" t="s">
-        <v>211</v>
-      </c>
-      <c r="E109" s="38"/>
-      <c r="F109" s="38" t="s">
-        <v>212</v>
-      </c>
-      <c r="G109" s="38"/>
-      <c r="H109" s="38"/>
-      <c r="I109" s="38"/>
-    </row>
-    <row r="110" spans="1:10" customHeight="1" ht="15">
-      <c r="A110" s="38">
-        <v>89</v>
-      </c>
-      <c r="B110" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="C110" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D110" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="E110" s="38"/>
-      <c r="F110" s="38" t="s">
-        <v>215</v>
-      </c>
-      <c r="G110" s="38"/>
-      <c r="H110" s="38"/>
-      <c r="I110" s="38"/>
-    </row>
-    <row r="111" spans="1:10" customHeight="1" ht="15">
-      <c r="A111" s="38">
-        <v>90</v>
-      </c>
-      <c r="B111" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="C111" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D111" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="E111" s="38"/>
-      <c r="F111" s="38" t="s">
-        <v>217</v>
-      </c>
-      <c r="G111" s="38"/>
-      <c r="H111" s="38"/>
-      <c r="I111" s="38"/>
-    </row>
-    <row r="112" spans="1:10" customHeight="1" ht="15">
-      <c r="A112" s="38">
-        <v>91</v>
-      </c>
-      <c r="B112" s="38" t="s">
-        <v>218</v>
-      </c>
-      <c r="C112" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D112" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="E112" s="38"/>
-      <c r="F112" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="G112" s="38"/>
-      <c r="H112" s="38"/>
-      <c r="I112" s="38"/>
-    </row>
-    <row r="113" spans="1:10" customHeight="1" ht="15">
-      <c r="A113" s="16"/>
-      <c r="B113" s="16"/>
-      <c r="C113" s="16"/>
-      <c r="D113" s="16"/>
-      <c r="E113" s="16"/>
-      <c r="F113" s="23"/>
-      <c r="G113" s="23"/>
-      <c r="H113" s="24"/>
-      <c r="I113" s="24"/>
-    </row>
-    <row r="114" spans="1:10" customHeight="1" ht="15">
-      <c r="A114" s="25"/>
-      <c r="B114" s="25"/>
-      <c r="C114" s="25"/>
-      <c r="D114" s="25"/>
-      <c r="E114" s="25"/>
-      <c r="F114" s="25"/>
-      <c r="G114" s="25"/>
-      <c r="H114" s="25"/>
-      <c r="I114" s="25"/>
-    </row>
-    <row r="115" spans="1:10" customHeight="1" ht="15">
-      <c r="A115" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="B115" s="26"/>
-      <c r="C115" s="26"/>
-      <c r="D115" s="26"/>
-      <c r="E115" s="26"/>
-      <c r="F115" s="26"/>
-      <c r="G115" s="26"/>
-      <c r="H115" s="26"/>
-      <c r="I115" s="26"/>
-    </row>
-    <row r="116" spans="1:10" customHeight="1" ht="15">
-      <c r="A116" s="27"/>
-      <c r="B116" s="27"/>
-      <c r="C116" s="27"/>
-      <c r="D116" s="27"/>
-      <c r="E116" s="27"/>
-      <c r="F116" s="27"/>
-      <c r="G116" s="27"/>
-      <c r="H116" s="27"/>
-      <c r="I116" s="27"/>
-    </row>
-    <row r="117" spans="1:10" customHeight="1" ht="15">
-      <c r="A117" s="28" t="s">
-        <v>222</v>
-      </c>
-      <c r="B117" s="28"/>
-      <c r="C117" s="28"/>
-      <c r="D117" s="28"/>
-      <c r="E117" s="28"/>
-      <c r="F117" s="28"/>
-      <c r="G117" s="28"/>
-      <c r="H117" s="28"/>
-      <c r="I117" s="28"/>
-    </row>
-    <row r="118" spans="1:10" customHeight="1" ht="15">
-      <c r="A118" s="28" t="s">
-        <v>223</v>
-      </c>
-      <c r="B118" s="28"/>
-      <c r="C118" s="28"/>
-      <c r="D118" s="28"/>
-      <c r="E118" s="28"/>
-      <c r="F118" s="28"/>
-      <c r="G118" s="28"/>
-      <c r="H118" s="28"/>
-      <c r="I118" s="28"/>
-    </row>
-    <row r="119" spans="1:10" customHeight="1" ht="15">
-      <c r="A119" s="28" t="s">
-        <v>224</v>
-      </c>
-      <c r="B119" s="28"/>
-      <c r="C119" s="28"/>
-      <c r="D119" s="28"/>
-      <c r="E119" s="28"/>
-      <c r="F119" s="28"/>
-      <c r="G119" s="28"/>
-      <c r="H119" s="28"/>
-      <c r="I119" s="28"/>
-    </row>
-    <row r="120" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A120" s="29" t="s">
-        <v>225</v>
-      </c>
-      <c r="B120" s="29"/>
-      <c r="C120" s="29"/>
-      <c r="D120" s="29"/>
-      <c r="E120" s="29"/>
-      <c r="F120" s="29"/>
-      <c r="G120" s="29"/>
-      <c r="H120" s="29"/>
-      <c r="I120" s="29"/>
-      <c r="J120" s="2"/>
-    </row>
-    <row r="121" spans="1:10" customHeight="1" ht="27">
-      <c r="A121" s="28" t="s">
-        <v>226</v>
-      </c>
-      <c r="B121" s="28"/>
-      <c r="C121" s="28"/>
-      <c r="D121" s="28"/>
-      <c r="E121" s="28"/>
-      <c r="F121" s="28"/>
-      <c r="G121" s="28"/>
-      <c r="H121" s="28"/>
-      <c r="I121" s="28"/>
-    </row>
-    <row r="122" spans="1:10" customHeight="1" ht="15">
-      <c r="A122" s="30"/>
-      <c r="B122" s="30"/>
-      <c r="C122" s="30"/>
-      <c r="D122" s="30"/>
-      <c r="E122" s="30"/>
-      <c r="F122" s="30"/>
-      <c r="G122" s="30"/>
-      <c r="H122" s="30"/>
-      <c r="I122" s="30"/>
-    </row>
-    <row r="123" spans="1:10" customHeight="1" ht="39">
-      <c r="A123" s="31" t="s">
-        <v>227</v>
-      </c>
-      <c r="B123" s="31"/>
-      <c r="C123" s="31"/>
-      <c r="D123" s="31"/>
-      <c r="E123" s="31"/>
-      <c r="F123" s="31"/>
-      <c r="G123" s="31"/>
-      <c r="H123" s="31"/>
-      <c r="I123" s="31"/>
-    </row>
-    <row r="124" spans="1:10" customHeight="1" ht="15">
-      <c r="A124" s="32"/>
-      <c r="B124" s="32"/>
-      <c r="C124" s="32"/>
-      <c r="D124" s="32"/>
-      <c r="E124" s="2"/>
-      <c r="F124" s="2"/>
-      <c r="G124" s="33"/>
-      <c r="H124" s="33"/>
-      <c r="I124" s="33"/>
-    </row>
-    <row r="125" spans="1:10" customHeight="1" ht="15">
-      <c r="A125" s="2"/>
-      <c r="B125" s="32"/>
-      <c r="C125" s="32"/>
-      <c r="D125" s="32"/>
-      <c r="E125" s="2"/>
-      <c r="F125" s="2"/>
-      <c r="G125" s="2"/>
-      <c r="H125" s="33"/>
-      <c r="I125" s="33"/>
-    </row>
-    <row r="126" spans="1:10" customHeight="1" ht="15">
-      <c r="A126" s="32"/>
-      <c r="B126" s="34" t="s">
-        <v>228</v>
-      </c>
-      <c r="C126" s="34"/>
-      <c r="D126" s="34"/>
-      <c r="E126" s="2"/>
-      <c r="F126" s="2"/>
-      <c r="G126" s="35" t="s">
-        <v>229</v>
-      </c>
-      <c r="H126" s="35"/>
-      <c r="I126" s="35"/>
-    </row>
-    <row r="127" spans="1:10" customHeight="1" ht="15">
-      <c r="A127" s="2"/>
-      <c r="B127" s="2"/>
-      <c r="C127" s="2"/>
-      <c r="D127" s="36" t="s">
-        <v>230</v>
-      </c>
-      <c r="E127" s="2"/>
-      <c r="F127" s="2"/>
-      <c r="G127" s="2"/>
-      <c r="H127" s="2"/>
-      <c r="I127" s="2"/>
-    </row>
-    <row r="128" spans="1:10" customHeight="1" ht="15">
-      <c r="A128" s="2"/>
-      <c r="B128" s="37"/>
-      <c r="C128" s="37"/>
-      <c r="D128" s="37"/>
-      <c r="E128" s="2"/>
-      <c r="F128" s="2"/>
-      <c r="G128" s="37"/>
-      <c r="H128" s="37"/>
-      <c r="I128" s="37"/>
-    </row>
-    <row r="129" spans="1:10" customHeight="1" ht="15">
-      <c r="A129" s="2"/>
-      <c r="B129" s="2"/>
-      <c r="C129" s="2"/>
-      <c r="D129" s="2"/>
-      <c r="E129" s="2"/>
-      <c r="F129" s="2"/>
-      <c r="G129" s="2"/>
-      <c r="H129" s="2"/>
-      <c r="I129" s="2"/>
-    </row>
-    <row r="130" spans="1:10" customHeight="1" ht="15">
-      <c r="A130" s="2"/>
-      <c r="B130" s="34" t="s">
+      <c r="A104" s="2"/>
+      <c r="B104" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="C130" s="34"/>
-      <c r="D130" s="34"/>
-      <c r="E130" s="2"/>
-      <c r="F130" s="2"/>
-      <c r="G130" s="34" t="str">
+      <c r="C104" s="34"/>
+      <c r="D104" s="34"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="34" t="str">
         <f>C10</f>
         <v>Alejandro Cancino Arguello</v>
       </c>
-      <c r="H130" s="34"/>
-      <c r="I130" s="34"/>
-    </row>
-    <row r="131" spans="1:10" customHeight="1" ht="15">
-      <c r="A131" s="2"/>
-      <c r="B131" s="34" t="s">
+      <c r="H104" s="34"/>
+      <c r="I104" s="34"/>
+    </row>
+    <row r="105" spans="1:10" customHeight="1" ht="15">
+      <c r="A105" s="2"/>
+      <c r="B105" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="C131" s="34"/>
-      <c r="D131" s="34"/>
-      <c r="E131" s="2"/>
-      <c r="F131" s="2"/>
-      <c r="G131" s="34" t="str">
+      <c r="C105" s="34"/>
+      <c r="D105" s="34"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="34" t="str">
         <f>C12</f>
         <v>Supervisor TI</v>
       </c>
-      <c r="H131" s="34"/>
-      <c r="I131" s="34"/>
-    </row>
-    <row r="132" spans="1:10" customHeight="1" ht="15">
-      <c r="A132" s="2"/>
-      <c r="B132" s="2"/>
-      <c r="C132" s="2"/>
-      <c r="D132" s="2"/>
-      <c r="E132" s="2"/>
-      <c r="F132" s="2"/>
-      <c r="G132" s="32"/>
-      <c r="H132" s="32"/>
-      <c r="I132" s="32"/>
-    </row>
-    <row r="133" spans="1:10" customHeight="1" ht="15">
-      <c r="A133" s="2"/>
-      <c r="B133" s="2"/>
-      <c r="C133" s="2"/>
-      <c r="D133" s="2"/>
-      <c r="E133" s="2"/>
-      <c r="F133" s="2"/>
-      <c r="G133" s="2"/>
-      <c r="H133" s="2"/>
-      <c r="I133" s="2"/>
-    </row>
-    <row r="134" spans="1:10" customHeight="1" ht="15">
-      <c r="A134" s="32"/>
-      <c r="B134" s="32"/>
-      <c r="C134" s="32"/>
-      <c r="D134" s="32"/>
-      <c r="E134" s="2"/>
-      <c r="F134" s="2"/>
-      <c r="G134" s="2"/>
-      <c r="H134" s="2"/>
-      <c r="I134" s="2"/>
+      <c r="H105" s="34"/>
+      <c r="I105" s="34"/>
+    </row>
+    <row r="106" spans="1:10" customHeight="1" ht="15">
+      <c r="A106" s="2"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="32"/>
+      <c r="H106" s="32"/>
+      <c r="I106" s="32"/>
+    </row>
+    <row r="107" spans="1:10" customHeight="1" ht="15">
+      <c r="A107" s="2"/>
+      <c r="B107" s="2"/>
+      <c r="C107" s="2"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
+      <c r="H107" s="2"/>
+      <c r="I107" s="2"/>
+    </row>
+    <row r="108" spans="1:10" customHeight="1" ht="15">
+      <c r="A108" s="32"/>
+      <c r="B108" s="32"/>
+      <c r="C108" s="32"/>
+      <c r="D108" s="32"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="2"/>
+      <c r="G108" s="2"/>
+      <c r="H108" s="2"/>
+      <c r="I108" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -3758,23 +3072,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D113:E113"/>
-    <mergeCell ref="F113:G113"/>
-    <mergeCell ref="H113:I113"/>
-    <mergeCell ref="A115:I115"/>
-    <mergeCell ref="A117:I117"/>
-    <mergeCell ref="A118:I118"/>
-    <mergeCell ref="A119:I119"/>
-    <mergeCell ref="A120:I120"/>
-    <mergeCell ref="A121:I121"/>
-    <mergeCell ref="A122:I122"/>
-    <mergeCell ref="A123:I123"/>
-    <mergeCell ref="B126:D126"/>
-    <mergeCell ref="G126:I126"/>
-    <mergeCell ref="B130:D130"/>
-    <mergeCell ref="G130:I130"/>
-    <mergeCell ref="B131:D131"/>
-    <mergeCell ref="G131:I131"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="A89:I89"/>
+    <mergeCell ref="A91:I91"/>
+    <mergeCell ref="A92:I92"/>
+    <mergeCell ref="A93:I93"/>
+    <mergeCell ref="A94:I94"/>
+    <mergeCell ref="A95:I95"/>
+    <mergeCell ref="A96:I96"/>
+    <mergeCell ref="A97:I97"/>
+    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="G100:I100"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="G104:I104"/>
+    <mergeCell ref="B105:D105"/>
+    <mergeCell ref="G105:I105"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -3979,85 +3293,7 @@
     <mergeCell ref="D86:E86"/>
     <mergeCell ref="F86:G86"/>
     <mergeCell ref="H86:I86"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="D88:E88"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="D89:E89"/>
-    <mergeCell ref="F89:G89"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="F90:G90"/>
-    <mergeCell ref="H90:I90"/>
-    <mergeCell ref="D91:E91"/>
-    <mergeCell ref="F91:G91"/>
-    <mergeCell ref="H91:I91"/>
-    <mergeCell ref="D92:E92"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="H92:I92"/>
-    <mergeCell ref="D93:E93"/>
-    <mergeCell ref="F93:G93"/>
-    <mergeCell ref="H93:I93"/>
-    <mergeCell ref="D94:E94"/>
-    <mergeCell ref="F94:G94"/>
-    <mergeCell ref="H94:I94"/>
-    <mergeCell ref="D95:E95"/>
-    <mergeCell ref="F95:G95"/>
-    <mergeCell ref="H95:I95"/>
-    <mergeCell ref="D96:E96"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="H96:I96"/>
-    <mergeCell ref="D97:E97"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="H97:I97"/>
-    <mergeCell ref="D98:E98"/>
-    <mergeCell ref="F98:G98"/>
-    <mergeCell ref="H98:I98"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:G99"/>
-    <mergeCell ref="H99:I99"/>
-    <mergeCell ref="D100:E100"/>
-    <mergeCell ref="F100:G100"/>
-    <mergeCell ref="H100:I100"/>
-    <mergeCell ref="D101:E101"/>
-    <mergeCell ref="F101:G101"/>
-    <mergeCell ref="H101:I101"/>
-    <mergeCell ref="D102:E102"/>
-    <mergeCell ref="F102:G102"/>
-    <mergeCell ref="H102:I102"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="F103:G103"/>
-    <mergeCell ref="H103:I103"/>
-    <mergeCell ref="D104:E104"/>
-    <mergeCell ref="F104:G104"/>
-    <mergeCell ref="H104:I104"/>
-    <mergeCell ref="D105:E105"/>
-    <mergeCell ref="F105:G105"/>
-    <mergeCell ref="H105:I105"/>
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="F106:G106"/>
-    <mergeCell ref="H106:I106"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="F107:G107"/>
-    <mergeCell ref="H107:I107"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="F108:G108"/>
-    <mergeCell ref="H108:I108"/>
-    <mergeCell ref="D109:E109"/>
-    <mergeCell ref="F109:G109"/>
-    <mergeCell ref="H109:I109"/>
-    <mergeCell ref="D110:E110"/>
-    <mergeCell ref="F110:G110"/>
-    <mergeCell ref="H110:I110"/>
-    <mergeCell ref="D111:E111"/>
-    <mergeCell ref="F111:G111"/>
-    <mergeCell ref="H111:I111"/>
-    <mergeCell ref="D112:E112"/>
-    <mergeCell ref="F112:G112"/>
-    <mergeCell ref="H112:I112"/>
-    <mergeCell ref="H19:I112"/>
+    <mergeCell ref="H19:I86"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Alejandro_Cancino_Arguello.xlsx
+++ b/database/controller_excel/Resguardo_Alejandro_Cancino_Arguello.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="187">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>30/04/2025</t>
+    <t>04/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -50,7 +50,7 @@
     <t>Área:</t>
   </si>
   <si>
-    <t>Supervisor TI</t>
+    <t>Coordinador de TI</t>
   </si>
   <si>
     <t>Región:</t>
@@ -86,6 +86,27 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
+    <t>Unidad DVD</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>GP60NB50</t>
+  </si>
+  <si>
+    <t>CNH4306278</t>
+  </si>
+  <si>
+    <t>Diadema</t>
+  </si>
+  <si>
+    <t>108DB1</t>
+  </si>
+  <si>
+    <t>2032CW</t>
+  </si>
+  <si>
     <t>Camara Intrinsicamente segura</t>
   </si>
   <si>
@@ -248,9 +269,6 @@
     <t>Switch</t>
   </si>
   <si>
-    <t>Cisco</t>
-  </si>
-  <si>
     <t>CATALYST 2960-X SERIES</t>
   </si>
   <si>
@@ -515,6 +533,18 @@
     <t>FCH19052DJ7</t>
   </si>
   <si>
+    <t>Audifonos</t>
+  </si>
+  <si>
+    <t>Samsung</t>
+  </si>
+  <si>
+    <t>GIUHIUIÑGYI</t>
+  </si>
+  <si>
+    <t>5494UVTUFT</t>
+  </si>
+  <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
   </si>
   <si>
@@ -543,6 +573,12 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Abraham Palayot Sanchez</t>
+  </si>
+  <si>
+    <t>Coordinador de Información Financiera</t>
   </si>
 </sst>
 </file>
@@ -1370,8 +1406,8 @@
         <v>24</v>
       </c>
       <c r="E19" s="38"/>
-      <c r="F19" s="38">
-        <v>14187000333707</v>
+      <c r="F19" s="38" t="s">
+        <v>25</v>
       </c>
       <c r="G19" s="38"/>
       <c r="H19" s="38"/>
@@ -1382,10 +1418,10 @@
         <v>2</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D20" s="38" t="s">
         <v>27</v>
@@ -1406,14 +1442,14 @@
         <v>29</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D21" s="38" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E21" s="38"/>
-      <c r="F21" s="38" t="s">
-        <v>30</v>
+      <c r="F21" s="38">
+        <v>14187000333707</v>
       </c>
       <c r="G21" s="38"/>
       <c r="H21" s="38"/>
@@ -1424,17 +1460,17 @@
         <v>4</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E22" s="38"/>
       <c r="F22" s="38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G22" s="38"/>
       <c r="H22" s="38"/>
@@ -1445,13 +1481,13 @@
         <v>5</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E23" s="38"/>
       <c r="F23" s="38" t="s">
@@ -1469,14 +1505,14 @@
         <v>38</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E24" s="38"/>
       <c r="F24" s="38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G24" s="38"/>
       <c r="H24" s="38"/>
@@ -1487,17 +1523,17 @@
         <v>7</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E25" s="38"/>
       <c r="F25" s="38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
@@ -1508,17 +1544,17 @@
         <v>8</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E26" s="38"/>
       <c r="F26" s="38" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G26" s="38"/>
       <c r="H26" s="38"/>
@@ -1529,17 +1565,17 @@
         <v>9</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D27" s="38" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E27" s="38"/>
       <c r="F27" s="38" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G27" s="38"/>
       <c r="H27" s="38"/>
@@ -1550,17 +1586,17 @@
         <v>10</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E28" s="38"/>
       <c r="F28" s="38" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G28" s="38"/>
       <c r="H28" s="38"/>
@@ -1571,17 +1607,17 @@
         <v>11</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E29" s="38"/>
       <c r="F29" s="38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G29" s="38"/>
       <c r="H29" s="38"/>
@@ -1592,17 +1628,17 @@
         <v>12</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E30" s="38"/>
       <c r="F30" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G30" s="38"/>
       <c r="H30" s="38"/>
@@ -1613,17 +1649,17 @@
         <v>13</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D31" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E31" s="38"/>
       <c r="F31" s="38" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="G31" s="38"/>
       <c r="H31" s="38"/>
@@ -1634,17 +1670,17 @@
         <v>14</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="D32" s="38" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E32" s="38"/>
       <c r="F32" s="38" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G32" s="38"/>
       <c r="H32" s="38"/>
@@ -1655,17 +1691,17 @@
         <v>15</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C33" s="38" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D33" s="38" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E33" s="38"/>
-      <c r="F33" s="38">
-        <v>647235228</v>
+      <c r="F33" s="38" t="s">
+        <v>52</v>
       </c>
       <c r="G33" s="38"/>
       <c r="H33" s="38"/>
@@ -1676,17 +1712,17 @@
         <v>16</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D34" s="38" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="E34" s="38"/>
       <c r="F34" s="38" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="G34" s="38"/>
       <c r="H34" s="38"/>
@@ -1697,17 +1733,17 @@
         <v>17</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C35" s="38" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D35" s="38" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="E35" s="38"/>
-      <c r="F35" s="38" t="s">
-        <v>45</v>
+      <c r="F35" s="38">
+        <v>647235228</v>
       </c>
       <c r="G35" s="38"/>
       <c r="H35" s="38"/>
@@ -1718,17 +1754,17 @@
         <v>18</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C36" s="38" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D36" s="38" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E36" s="38"/>
       <c r="F36" s="38" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="G36" s="38"/>
       <c r="H36" s="38"/>
@@ -1739,17 +1775,17 @@
         <v>19</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C37" s="38" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D37" s="38" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E37" s="38"/>
       <c r="F37" s="38" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="G37" s="38"/>
       <c r="H37" s="38"/>
@@ -1760,17 +1796,17 @@
         <v>20</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="E38" s="38"/>
       <c r="F38" s="38" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G38" s="38"/>
       <c r="H38" s="38"/>
@@ -1781,17 +1817,17 @@
         <v>21</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="E39" s="38"/>
       <c r="F39" s="38" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G39" s="38"/>
       <c r="H39" s="38"/>
@@ -1802,17 +1838,17 @@
         <v>22</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="E40" s="38"/>
       <c r="F40" s="38" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G40" s="38"/>
       <c r="H40" s="38"/>
@@ -1823,17 +1859,17 @@
         <v>23</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C41" s="38" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="D41" s="38" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E41" s="38"/>
       <c r="F41" s="38" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G41" s="38"/>
       <c r="H41" s="38"/>
@@ -1844,17 +1880,17 @@
         <v>24</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C42" s="38" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="D42" s="38" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E42" s="38"/>
       <c r="F42" s="38" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G42" s="38"/>
       <c r="H42" s="38"/>
@@ -1865,17 +1901,17 @@
         <v>25</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="D43" s="38" t="s">
         <v>83</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G43" s="38"/>
       <c r="H43" s="38"/>
@@ -1886,17 +1922,17 @@
         <v>26</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C44" s="38" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="D44" s="38" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E44" s="38"/>
       <c r="F44" s="38" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G44" s="38"/>
       <c r="H44" s="38"/>
@@ -1907,17 +1943,17 @@
         <v>27</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="E45" s="38"/>
       <c r="F45" s="38" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G45" s="38"/>
       <c r="H45" s="38"/>
@@ -1928,17 +1964,17 @@
         <v>28</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E46" s="38"/>
       <c r="F46" s="38" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G46" s="38"/>
       <c r="H46" s="38"/>
@@ -1949,17 +1985,17 @@
         <v>29</v>
       </c>
       <c r="B47" s="38" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C47" s="38" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E47" s="38"/>
       <c r="F47" s="38" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G47" s="38"/>
       <c r="H47" s="38"/>
@@ -1970,13 +2006,13 @@
         <v>30</v>
       </c>
       <c r="B48" s="38" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C48" s="38" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="D48" s="38" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="E48" s="38"/>
       <c r="F48" s="38" t="s">
@@ -1991,10 +2027,10 @@
         <v>31</v>
       </c>
       <c r="B49" s="38" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C49" s="38" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="D49" s="38" t="s">
         <v>94</v>
@@ -2015,12 +2051,14 @@
         <v>96</v>
       </c>
       <c r="C50" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D50" s="38"/>
+        <v>97</v>
+      </c>
+      <c r="D50" s="38" t="s">
+        <v>98</v>
+      </c>
       <c r="E50" s="38"/>
       <c r="F50" s="38" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G50" s="38"/>
       <c r="H50" s="38"/>
@@ -2031,17 +2069,17 @@
         <v>33</v>
       </c>
       <c r="B51" s="38" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C51" s="38" t="s">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="D51" s="38" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E51" s="38"/>
       <c r="F51" s="38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G51" s="38"/>
       <c r="H51" s="38"/>
@@ -2052,17 +2090,15 @@
         <v>34</v>
       </c>
       <c r="B52" s="38" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C52" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D52" s="38" t="s">
-        <v>99</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="D52" s="38"/>
       <c r="E52" s="38"/>
       <c r="F52" s="38" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G52" s="38"/>
       <c r="H52" s="38"/>
@@ -2073,17 +2109,17 @@
         <v>35</v>
       </c>
       <c r="B53" s="38" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C53" s="38" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="D53" s="38" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E53" s="38"/>
       <c r="F53" s="38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G53" s="38"/>
       <c r="H53" s="38"/>
@@ -2094,17 +2130,17 @@
         <v>36</v>
       </c>
       <c r="B54" s="38" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C54" s="38" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="D54" s="38" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E54" s="38"/>
       <c r="F54" s="38" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G54" s="38"/>
       <c r="H54" s="38"/>
@@ -2115,17 +2151,17 @@
         <v>37</v>
       </c>
       <c r="B55" s="38" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C55" s="38" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="D55" s="38" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E55" s="38"/>
       <c r="F55" s="38" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G55" s="38"/>
       <c r="H55" s="38"/>
@@ -2136,17 +2172,17 @@
         <v>38</v>
       </c>
       <c r="B56" s="38" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C56" s="38" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D56" s="38" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E56" s="38"/>
       <c r="F56" s="38" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G56" s="38"/>
       <c r="H56" s="38"/>
@@ -2157,17 +2193,17 @@
         <v>39</v>
       </c>
       <c r="B57" s="38" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C57" s="38" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D57" s="38" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E57" s="38"/>
       <c r="F57" s="38" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G57" s="38"/>
       <c r="H57" s="38"/>
@@ -2181,14 +2217,14 @@
         <v>112</v>
       </c>
       <c r="C58" s="38" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="D58" s="38" t="s">
         <v>113</v>
       </c>
       <c r="E58" s="38"/>
       <c r="F58" s="38" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G58" s="38"/>
       <c r="H58" s="38"/>
@@ -2199,13 +2235,13 @@
         <v>41</v>
       </c>
       <c r="B59" s="38" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C59" s="38" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D59" s="38" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E59" s="38"/>
       <c r="F59" s="38" t="s">
@@ -2220,17 +2256,17 @@
         <v>42</v>
       </c>
       <c r="B60" s="38" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C60" s="38" t="s">
-        <v>61</v>
+        <v>119</v>
       </c>
       <c r="D60" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E60" s="38"/>
       <c r="F60" s="38" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G60" s="38"/>
       <c r="H60" s="38"/>
@@ -2241,17 +2277,17 @@
         <v>43</v>
       </c>
       <c r="B61" s="38" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C61" s="38" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D61" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E61" s="38"/>
       <c r="F61" s="38" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G61" s="38"/>
       <c r="H61" s="38"/>
@@ -2262,17 +2298,17 @@
         <v>44</v>
       </c>
       <c r="B62" s="38" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C62" s="38" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D62" s="38" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E62" s="38"/>
       <c r="F62" s="38" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G62" s="38"/>
       <c r="H62" s="38"/>
@@ -2283,17 +2319,17 @@
         <v>45</v>
       </c>
       <c r="B63" s="38" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="C63" s="38" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D63" s="38" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="E63" s="38"/>
       <c r="F63" s="38" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G63" s="38"/>
       <c r="H63" s="38"/>
@@ -2304,17 +2340,17 @@
         <v>46</v>
       </c>
       <c r="B64" s="38" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C64" s="38" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D64" s="38" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E64" s="38"/>
       <c r="F64" s="38" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G64" s="38"/>
       <c r="H64" s="38"/>
@@ -2325,17 +2361,17 @@
         <v>47</v>
       </c>
       <c r="B65" s="38" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C65" s="38" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D65" s="38" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E65" s="38"/>
       <c r="F65" s="38" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G65" s="38"/>
       <c r="H65" s="38"/>
@@ -2346,17 +2382,17 @@
         <v>48</v>
       </c>
       <c r="B66" s="38" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="C66" s="38" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D66" s="38" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="E66" s="38"/>
       <c r="F66" s="38" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G66" s="38"/>
       <c r="H66" s="38"/>
@@ -2367,17 +2403,17 @@
         <v>49</v>
       </c>
       <c r="B67" s="38" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C67" s="38" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D67" s="38" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E67" s="38"/>
       <c r="F67" s="38" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G67" s="38"/>
       <c r="H67" s="38"/>
@@ -2388,17 +2424,17 @@
         <v>50</v>
       </c>
       <c r="B68" s="38" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C68" s="38" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D68" s="38" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E68" s="38"/>
       <c r="F68" s="38" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G68" s="38"/>
       <c r="H68" s="38"/>
@@ -2409,17 +2445,17 @@
         <v>51</v>
       </c>
       <c r="B69" s="38" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C69" s="38" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D69" s="38" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E69" s="38"/>
       <c r="F69" s="38" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G69" s="38"/>
       <c r="H69" s="38"/>
@@ -2430,17 +2466,17 @@
         <v>52</v>
       </c>
       <c r="B70" s="38" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C70" s="38" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D70" s="38" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E70" s="38"/>
       <c r="F70" s="38" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G70" s="38"/>
       <c r="H70" s="38"/>
@@ -2451,17 +2487,17 @@
         <v>53</v>
       </c>
       <c r="B71" s="38" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C71" s="38" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D71" s="38" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E71" s="38"/>
       <c r="F71" s="38" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G71" s="38"/>
       <c r="H71" s="38"/>
@@ -2472,17 +2508,17 @@
         <v>54</v>
       </c>
       <c r="B72" s="38" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C72" s="38" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D72" s="38" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="E72" s="38"/>
       <c r="F72" s="38" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G72" s="38"/>
       <c r="H72" s="38"/>
@@ -2493,17 +2529,17 @@
         <v>55</v>
       </c>
       <c r="B73" s="38" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C73" s="38" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D73" s="38" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="E73" s="38"/>
       <c r="F73" s="38" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G73" s="38"/>
       <c r="H73" s="38"/>
@@ -2514,17 +2550,17 @@
         <v>56</v>
       </c>
       <c r="B74" s="38" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C74" s="38" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D74" s="38" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="E74" s="38"/>
       <c r="F74" s="38" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G74" s="38"/>
       <c r="H74" s="38"/>
@@ -2535,17 +2571,17 @@
         <v>57</v>
       </c>
       <c r="B75" s="38" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C75" s="38" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D75" s="38" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="E75" s="38"/>
       <c r="F75" s="38" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G75" s="38"/>
       <c r="H75" s="38"/>
@@ -2556,17 +2592,17 @@
         <v>58</v>
       </c>
       <c r="B76" s="38" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C76" s="38" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D76" s="38" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E76" s="38"/>
       <c r="F76" s="38" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G76" s="38"/>
       <c r="H76" s="38"/>
@@ -2577,17 +2613,17 @@
         <v>59</v>
       </c>
       <c r="B77" s="38" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C77" s="38" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D77" s="38" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="E77" s="38"/>
       <c r="F77" s="38" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G77" s="38"/>
       <c r="H77" s="38"/>
@@ -2598,17 +2634,17 @@
         <v>60</v>
       </c>
       <c r="B78" s="38" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C78" s="38" t="s">
-        <v>143</v>
+        <v>68</v>
       </c>
       <c r="D78" s="38" t="s">
         <v>144</v>
       </c>
       <c r="E78" s="38"/>
       <c r="F78" s="38" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G78" s="38"/>
       <c r="H78" s="38"/>
@@ -2619,17 +2655,17 @@
         <v>61</v>
       </c>
       <c r="B79" s="38" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="C79" s="38" t="s">
-        <v>147</v>
+        <v>68</v>
       </c>
       <c r="D79" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="E79" s="38"/>
+      <c r="F79" s="38" t="s">
         <v>148</v>
-      </c>
-      <c r="E79" s="38"/>
-      <c r="F79" s="38">
-        <v>544161389</v>
       </c>
       <c r="G79" s="38"/>
       <c r="H79" s="38"/>
@@ -2640,17 +2676,17 @@
         <v>62</v>
       </c>
       <c r="B80" s="38" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="C80" s="38" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D80" s="38" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E80" s="38"/>
-      <c r="F80" s="38">
-        <v>544161388</v>
+      <c r="F80" s="38" t="s">
+        <v>151</v>
       </c>
       <c r="G80" s="38"/>
       <c r="H80" s="38"/>
@@ -2661,17 +2697,17 @@
         <v>63</v>
       </c>
       <c r="B81" s="38" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C81" s="38" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D81" s="38" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E81" s="38"/>
-      <c r="F81" s="38" t="s">
-        <v>152</v>
+      <c r="F81" s="38">
+        <v>544161389</v>
       </c>
       <c r="G81" s="38"/>
       <c r="H81" s="38"/>
@@ -2682,17 +2718,17 @@
         <v>64</v>
       </c>
       <c r="B82" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="C82" s="38" t="s">
         <v>153</v>
       </c>
-      <c r="C82" s="38" t="s">
+      <c r="D82" s="38" t="s">
         <v>154</v>
       </c>
-      <c r="D82" s="38" t="s">
-        <v>45</v>
-      </c>
       <c r="E82" s="38"/>
-      <c r="F82" s="38" t="s">
-        <v>155</v>
+      <c r="F82" s="38">
+        <v>544161388</v>
       </c>
       <c r="G82" s="38"/>
       <c r="H82" s="38"/>
@@ -2703,17 +2739,17 @@
         <v>65</v>
       </c>
       <c r="B83" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="C83" s="38" t="s">
         <v>156</v>
       </c>
-      <c r="C83" s="38" t="s">
+      <c r="D83" s="38" t="s">
         <v>157</v>
-      </c>
-      <c r="D83" s="38" t="s">
-        <v>45</v>
       </c>
       <c r="E83" s="38"/>
       <c r="F83" s="38" t="s">
-        <v>45</v>
+        <v>158</v>
       </c>
       <c r="G83" s="38"/>
       <c r="H83" s="38"/>
@@ -2724,17 +2760,17 @@
         <v>66</v>
       </c>
       <c r="B84" s="38" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C84" s="38" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D84" s="38" t="s">
-        <v>159</v>
+        <v>52</v>
       </c>
       <c r="E84" s="38"/>
       <c r="F84" s="38" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="G84" s="38"/>
       <c r="H84" s="38"/>
@@ -2745,17 +2781,17 @@
         <v>67</v>
       </c>
       <c r="B85" s="38" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C85" s="38" t="s">
-        <v>76</v>
+        <v>163</v>
       </c>
       <c r="D85" s="38" t="s">
-        <v>161</v>
+        <v>52</v>
       </c>
       <c r="E85" s="38"/>
       <c r="F85" s="38" t="s">
-        <v>162</v>
+        <v>52</v>
       </c>
       <c r="G85" s="38"/>
       <c r="H85" s="38"/>
@@ -2766,124 +2802,147 @@
         <v>68</v>
       </c>
       <c r="B86" s="38" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C86" s="38" t="s">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="D86" s="38" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E86" s="38"/>
       <c r="F86" s="38" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G86" s="38"/>
       <c r="H86" s="38"/>
       <c r="I86" s="38"/>
     </row>
     <row r="87" spans="1:10" customHeight="1" ht="15">
-      <c r="A87" s="16"/>
-      <c r="B87" s="16"/>
-      <c r="C87" s="16"/>
-      <c r="D87" s="16"/>
-      <c r="E87" s="16"/>
-      <c r="F87" s="23"/>
-      <c r="G87" s="23"/>
-      <c r="H87" s="24"/>
-      <c r="I87" s="24"/>
+      <c r="A87" s="38">
+        <v>69</v>
+      </c>
+      <c r="B87" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="C87" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="D87" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="E87" s="38"/>
+      <c r="F87" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="G87" s="38"/>
+      <c r="H87" s="38"/>
+      <c r="I87" s="38"/>
     </row>
     <row r="88" spans="1:10" customHeight="1" ht="15">
-      <c r="A88" s="25"/>
-      <c r="B88" s="25"/>
-      <c r="C88" s="25"/>
-      <c r="D88" s="25"/>
-      <c r="E88" s="25"/>
-      <c r="F88" s="25"/>
-      <c r="G88" s="25"/>
-      <c r="H88" s="25"/>
-      <c r="I88" s="25"/>
+      <c r="A88" s="38">
+        <v>70</v>
+      </c>
+      <c r="B88" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="C88" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="D88" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="E88" s="38"/>
+      <c r="F88" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="G88" s="38"/>
+      <c r="H88" s="38"/>
+      <c r="I88" s="38"/>
     </row>
     <row r="89" spans="1:10" customHeight="1" ht="15">
-      <c r="A89" s="26" t="s">
-        <v>165</v>
-      </c>
-      <c r="B89" s="26"/>
-      <c r="C89" s="26"/>
-      <c r="D89" s="26"/>
-      <c r="E89" s="26"/>
-      <c r="F89" s="26"/>
-      <c r="G89" s="26"/>
-      <c r="H89" s="26"/>
-      <c r="I89" s="26"/>
+      <c r="A89" s="38">
+        <v>71</v>
+      </c>
+      <c r="B89" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="C89" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="D89" s="38" t="s">
+        <v>173</v>
+      </c>
+      <c r="E89" s="38"/>
+      <c r="F89" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="G89" s="38"/>
+      <c r="H89" s="38"/>
+      <c r="I89" s="38"/>
     </row>
     <row r="90" spans="1:10" customHeight="1" ht="15">
-      <c r="A90" s="27"/>
-      <c r="B90" s="27"/>
-      <c r="C90" s="27"/>
-      <c r="D90" s="27"/>
-      <c r="E90" s="27"/>
-      <c r="F90" s="27"/>
-      <c r="G90" s="27"/>
-      <c r="H90" s="27"/>
-      <c r="I90" s="27"/>
+      <c r="A90" s="16"/>
+      <c r="B90" s="16"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="16"/>
+      <c r="E90" s="16"/>
+      <c r="F90" s="23"/>
+      <c r="G90" s="23"/>
+      <c r="H90" s="24"/>
+      <c r="I90" s="24"/>
     </row>
     <row r="91" spans="1:10" customHeight="1" ht="15">
-      <c r="A91" s="28" t="s">
-        <v>166</v>
-      </c>
-      <c r="B91" s="28"/>
-      <c r="C91" s="28"/>
-      <c r="D91" s="28"/>
-      <c r="E91" s="28"/>
-      <c r="F91" s="28"/>
-      <c r="G91" s="28"/>
-      <c r="H91" s="28"/>
-      <c r="I91" s="28"/>
+      <c r="A91" s="25"/>
+      <c r="B91" s="25"/>
+      <c r="C91" s="25"/>
+      <c r="D91" s="25"/>
+      <c r="E91" s="25"/>
+      <c r="F91" s="25"/>
+      <c r="G91" s="25"/>
+      <c r="H91" s="25"/>
+      <c r="I91" s="25"/>
     </row>
     <row r="92" spans="1:10" customHeight="1" ht="15">
-      <c r="A92" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="B92" s="28"/>
-      <c r="C92" s="28"/>
-      <c r="D92" s="28"/>
-      <c r="E92" s="28"/>
-      <c r="F92" s="28"/>
-      <c r="G92" s="28"/>
-      <c r="H92" s="28"/>
-      <c r="I92" s="28"/>
+      <c r="A92" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="B92" s="26"/>
+      <c r="C92" s="26"/>
+      <c r="D92" s="26"/>
+      <c r="E92" s="26"/>
+      <c r="F92" s="26"/>
+      <c r="G92" s="26"/>
+      <c r="H92" s="26"/>
+      <c r="I92" s="26"/>
     </row>
     <row r="93" spans="1:10" customHeight="1" ht="15">
-      <c r="A93" s="28" t="s">
-        <v>168</v>
-      </c>
-      <c r="B93" s="28"/>
-      <c r="C93" s="28"/>
-      <c r="D93" s="28"/>
-      <c r="E93" s="28"/>
-      <c r="F93" s="28"/>
-      <c r="G93" s="28"/>
-      <c r="H93" s="28"/>
-      <c r="I93" s="28"/>
-    </row>
-    <row r="94" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A94" s="29" t="s">
-        <v>169</v>
-      </c>
-      <c r="B94" s="29"/>
-      <c r="C94" s="29"/>
-      <c r="D94" s="29"/>
-      <c r="E94" s="29"/>
-      <c r="F94" s="29"/>
-      <c r="G94" s="29"/>
-      <c r="H94" s="29"/>
-      <c r="I94" s="29"/>
-      <c r="J94" s="2"/>
-    </row>
-    <row r="95" spans="1:10" customHeight="1" ht="27">
+      <c r="A93" s="27"/>
+      <c r="B93" s="27"/>
+      <c r="C93" s="27"/>
+      <c r="D93" s="27"/>
+      <c r="E93" s="27"/>
+      <c r="F93" s="27"/>
+      <c r="G93" s="27"/>
+      <c r="H93" s="27"/>
+      <c r="I93" s="27"/>
+    </row>
+    <row r="94" spans="1:10" customHeight="1" ht="15">
+      <c r="A94" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="B94" s="28"/>
+      <c r="C94" s="28"/>
+      <c r="D94" s="28"/>
+      <c r="E94" s="28"/>
+      <c r="F94" s="28"/>
+      <c r="G94" s="28"/>
+      <c r="H94" s="28"/>
+      <c r="I94" s="28"/>
+    </row>
+    <row r="95" spans="1:10" customHeight="1" ht="15">
       <c r="A95" s="28" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="B95" s="28"/>
       <c r="C95" s="28"/>
@@ -2895,132 +2954,129 @@
       <c r="I95" s="28"/>
     </row>
     <row r="96" spans="1:10" customHeight="1" ht="15">
-      <c r="A96" s="30"/>
-      <c r="B96" s="30"/>
-      <c r="C96" s="30"/>
-      <c r="D96" s="30"/>
-      <c r="E96" s="30"/>
-      <c r="F96" s="30"/>
-      <c r="G96" s="30"/>
-      <c r="H96" s="30"/>
-      <c r="I96" s="30"/>
-    </row>
-    <row r="97" spans="1:10" customHeight="1" ht="39">
-      <c r="A97" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="B97" s="31"/>
-      <c r="C97" s="31"/>
-      <c r="D97" s="31"/>
-      <c r="E97" s="31"/>
-      <c r="F97" s="31"/>
-      <c r="G97" s="31"/>
-      <c r="H97" s="31"/>
-      <c r="I97" s="31"/>
-    </row>
-    <row r="98" spans="1:10" customHeight="1" ht="15">
-      <c r="A98" s="32"/>
-      <c r="B98" s="32"/>
-      <c r="C98" s="32"/>
-      <c r="D98" s="32"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="33"/>
-      <c r="H98" s="33"/>
-      <c r="I98" s="33"/>
+      <c r="A96" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="B96" s="28"/>
+      <c r="C96" s="28"/>
+      <c r="D96" s="28"/>
+      <c r="E96" s="28"/>
+      <c r="F96" s="28"/>
+      <c r="G96" s="28"/>
+      <c r="H96" s="28"/>
+      <c r="I96" s="28"/>
+    </row>
+    <row r="97" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A97" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="B97" s="29"/>
+      <c r="C97" s="29"/>
+      <c r="D97" s="29"/>
+      <c r="E97" s="29"/>
+      <c r="F97" s="29"/>
+      <c r="G97" s="29"/>
+      <c r="H97" s="29"/>
+      <c r="I97" s="29"/>
+      <c r="J97" s="2"/>
+    </row>
+    <row r="98" spans="1:10" customHeight="1" ht="27">
+      <c r="A98" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="B98" s="28"/>
+      <c r="C98" s="28"/>
+      <c r="D98" s="28"/>
+      <c r="E98" s="28"/>
+      <c r="F98" s="28"/>
+      <c r="G98" s="28"/>
+      <c r="H98" s="28"/>
+      <c r="I98" s="28"/>
     </row>
     <row r="99" spans="1:10" customHeight="1" ht="15">
-      <c r="A99" s="2"/>
-      <c r="B99" s="32"/>
-      <c r="C99" s="32"/>
-      <c r="D99" s="32"/>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-      <c r="H99" s="33"/>
-      <c r="I99" s="33"/>
-    </row>
-    <row r="100" spans="1:10" customHeight="1" ht="15">
-      <c r="A100" s="32"/>
-      <c r="B100" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="C100" s="34"/>
-      <c r="D100" s="34"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="H100" s="35"/>
-      <c r="I100" s="35"/>
+      <c r="A99" s="30"/>
+      <c r="B99" s="30"/>
+      <c r="C99" s="30"/>
+      <c r="D99" s="30"/>
+      <c r="E99" s="30"/>
+      <c r="F99" s="30"/>
+      <c r="G99" s="30"/>
+      <c r="H99" s="30"/>
+      <c r="I99" s="30"/>
+    </row>
+    <row r="100" spans="1:10" customHeight="1" ht="39">
+      <c r="A100" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="B100" s="31"/>
+      <c r="C100" s="31"/>
+      <c r="D100" s="31"/>
+      <c r="E100" s="31"/>
+      <c r="F100" s="31"/>
+      <c r="G100" s="31"/>
+      <c r="H100" s="31"/>
+      <c r="I100" s="31"/>
     </row>
     <row r="101" spans="1:10" customHeight="1" ht="15">
-      <c r="A101" s="2"/>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="36" t="s">
-        <v>174</v>
-      </c>
+      <c r="A101" s="32"/>
+      <c r="B101" s="32"/>
+      <c r="C101" s="32"/>
+      <c r="D101" s="32"/>
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-      <c r="H101" s="2"/>
-      <c r="I101" s="2"/>
+      <c r="G101" s="33"/>
+      <c r="H101" s="33"/>
+      <c r="I101" s="33"/>
     </row>
     <row r="102" spans="1:10" customHeight="1" ht="15">
       <c r="A102" s="2"/>
-      <c r="B102" s="37"/>
-      <c r="C102" s="37"/>
-      <c r="D102" s="37"/>
+      <c r="B102" s="32"/>
+      <c r="C102" s="32"/>
+      <c r="D102" s="32"/>
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
-      <c r="G102" s="37"/>
-      <c r="H102" s="37"/>
-      <c r="I102" s="37"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="33"/>
+      <c r="I102" s="33"/>
     </row>
     <row r="103" spans="1:10" customHeight="1" ht="15">
-      <c r="A103" s="2"/>
-      <c r="B103" s="2"/>
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
+      <c r="A103" s="32"/>
+      <c r="B103" s="34" t="s">
+        <v>182</v>
+      </c>
+      <c r="C103" s="34"/>
+      <c r="D103" s="34"/>
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
-      <c r="G103" s="2"/>
-      <c r="H103" s="2"/>
-      <c r="I103" s="2"/>
+      <c r="G103" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="H103" s="35"/>
+      <c r="I103" s="35"/>
     </row>
     <row r="104" spans="1:10" customHeight="1" ht="15">
       <c r="A104" s="2"/>
-      <c r="B104" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="C104" s="34"/>
-      <c r="D104" s="34"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="36" t="s">
+        <v>184</v>
+      </c>
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
-      <c r="G104" s="34" t="str">
-        <f>C10</f>
-        <v>Alejandro Cancino Arguello</v>
-      </c>
-      <c r="H104" s="34"/>
-      <c r="I104" s="34"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
+      <c r="I104" s="2"/>
     </row>
     <row r="105" spans="1:10" customHeight="1" ht="15">
       <c r="A105" s="2"/>
-      <c r="B105" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C105" s="34"/>
-      <c r="D105" s="34"/>
+      <c r="B105" s="37"/>
+      <c r="C105" s="37"/>
+      <c r="D105" s="37"/>
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
-      <c r="G105" s="34" t="str">
-        <f>C12</f>
-        <v>Supervisor TI</v>
-      </c>
-      <c r="H105" s="34"/>
-      <c r="I105" s="34"/>
+      <c r="G105" s="37"/>
+      <c r="H105" s="37"/>
+      <c r="I105" s="37"/>
     </row>
     <row r="106" spans="1:10" customHeight="1" ht="15">
       <c r="A106" s="2"/>
@@ -3029,31 +3085,74 @@
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
-      <c r="G106" s="32"/>
-      <c r="H106" s="32"/>
-      <c r="I106" s="32"/>
+      <c r="G106" s="2"/>
+      <c r="H106" s="2"/>
+      <c r="I106" s="2"/>
     </row>
     <row r="107" spans="1:10" customHeight="1" ht="15">
       <c r="A107" s="2"/>
-      <c r="B107" s="2"/>
-      <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
+      <c r="B107" s="34" t="s">
+        <v>185</v>
+      </c>
+      <c r="C107" s="34"/>
+      <c r="D107" s="34"/>
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
-      <c r="G107" s="2"/>
-      <c r="H107" s="2"/>
-      <c r="I107" s="2"/>
+      <c r="G107" s="34" t="str">
+        <f>C10</f>
+        <v>Alejandro Cancino Arguello</v>
+      </c>
+      <c r="H107" s="34"/>
+      <c r="I107" s="34"/>
     </row>
     <row r="108" spans="1:10" customHeight="1" ht="15">
-      <c r="A108" s="32"/>
-      <c r="B108" s="32"/>
-      <c r="C108" s="32"/>
-      <c r="D108" s="32"/>
+      <c r="A108" s="2"/>
+      <c r="B108" s="34" t="s">
+        <v>186</v>
+      </c>
+      <c r="C108" s="34"/>
+      <c r="D108" s="34"/>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
-      <c r="G108" s="2"/>
-      <c r="H108" s="2"/>
-      <c r="I108" s="2"/>
+      <c r="G108" s="34" t="str">
+        <f>C12</f>
+        <v>Coordinador de TI</v>
+      </c>
+      <c r="H108" s="34"/>
+      <c r="I108" s="34"/>
+    </row>
+    <row r="109" spans="1:10" customHeight="1" ht="15">
+      <c r="A109" s="2"/>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="2"/>
+      <c r="F109" s="2"/>
+      <c r="G109" s="32"/>
+      <c r="H109" s="32"/>
+      <c r="I109" s="32"/>
+    </row>
+    <row r="110" spans="1:10" customHeight="1" ht="15">
+      <c r="A110" s="2"/>
+      <c r="B110" s="2"/>
+      <c r="C110" s="2"/>
+      <c r="D110" s="2"/>
+      <c r="E110" s="2"/>
+      <c r="F110" s="2"/>
+      <c r="G110" s="2"/>
+      <c r="H110" s="2"/>
+      <c r="I110" s="2"/>
+    </row>
+    <row r="111" spans="1:10" customHeight="1" ht="15">
+      <c r="A111" s="32"/>
+      <c r="B111" s="32"/>
+      <c r="C111" s="32"/>
+      <c r="D111" s="32"/>
+      <c r="E111" s="2"/>
+      <c r="F111" s="2"/>
+      <c r="G111" s="2"/>
+      <c r="H111" s="2"/>
+      <c r="I111" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -3072,23 +3171,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="A89:I89"/>
-    <mergeCell ref="A91:I91"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="H90:I90"/>
     <mergeCell ref="A92:I92"/>
-    <mergeCell ref="A93:I93"/>
     <mergeCell ref="A94:I94"/>
     <mergeCell ref="A95:I95"/>
     <mergeCell ref="A96:I96"/>
     <mergeCell ref="A97:I97"/>
-    <mergeCell ref="B100:D100"/>
-    <mergeCell ref="G100:I100"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="G104:I104"/>
-    <mergeCell ref="B105:D105"/>
-    <mergeCell ref="G105:I105"/>
+    <mergeCell ref="A98:I98"/>
+    <mergeCell ref="A99:I99"/>
+    <mergeCell ref="A100:I100"/>
+    <mergeCell ref="B103:D103"/>
+    <mergeCell ref="G103:I103"/>
+    <mergeCell ref="B107:D107"/>
+    <mergeCell ref="G107:I107"/>
+    <mergeCell ref="B108:D108"/>
+    <mergeCell ref="G108:I108"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -3293,7 +3392,16 @@
     <mergeCell ref="D86:E86"/>
     <mergeCell ref="F86:G86"/>
     <mergeCell ref="H86:I86"/>
-    <mergeCell ref="H19:I86"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="D88:E88"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="D89:E89"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="H19:I89"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Alejandro_Cancino_Arguello.xlsx
+++ b/database/controller_excel/Resguardo_Alejandro_Cancino_Arguello.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="200">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>04/06/2025</t>
+    <t>11/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -86,21 +86,36 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
-    <t>Unidad DVD</t>
+    <t>Cargador de Laptop</t>
+  </si>
+  <si>
+    <t>Tesla</t>
+  </si>
+  <si>
+    <t>LA65NM190</t>
+  </si>
+  <si>
+    <t>CN-0VT148-LOC00-18C-3AF4-A02</t>
+  </si>
+  <si>
+    <t>Docking Station</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>WD19S</t>
+  </si>
+  <si>
+    <t>F9WQSB3</t>
+  </si>
+  <si>
+    <t>Diadema</t>
   </si>
   <si>
     <t>HP</t>
   </si>
   <si>
-    <t>GP60NB50</t>
-  </si>
-  <si>
-    <t>CNH4306278</t>
-  </si>
-  <si>
-    <t>Diadema</t>
-  </si>
-  <si>
     <t>108DB1</t>
   </si>
   <si>
@@ -119,9 +134,6 @@
     <t>SWITCH SAN 1</t>
   </si>
   <si>
-    <t>DELL</t>
-  </si>
-  <si>
     <t>POWERCONNECT 6224</t>
   </si>
   <si>
@@ -545,6 +557,39 @@
     <t>5494UVTUFT</t>
   </si>
   <si>
+    <t>Fijo</t>
+  </si>
+  <si>
+    <t>Kenwood</t>
+  </si>
+  <si>
+    <t>NX-840H-K2</t>
+  </si>
+  <si>
+    <t>B8C10276</t>
+  </si>
+  <si>
+    <t>B8C10300</t>
+  </si>
+  <si>
+    <t>Portátil</t>
+  </si>
+  <si>
+    <t>STEREN</t>
+  </si>
+  <si>
+    <t>RAD-010</t>
+  </si>
+  <si>
+    <t>PO#29980</t>
+  </si>
+  <si>
+    <t>B8C10117</t>
+  </si>
+  <si>
+    <t>B8310394</t>
+  </si>
+  <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
   </si>
   <si>
@@ -573,12 +618,6 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>Abraham Palayot Sanchez</t>
-  </si>
-  <si>
-    <t>Coordinador de Información Financiera</t>
   </si>
 </sst>
 </file>
@@ -1421,14 +1460,14 @@
         <v>26</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D20" s="38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E20" s="38"/>
       <c r="F20" s="38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G20" s="38"/>
       <c r="H20" s="38"/>
@@ -1439,17 +1478,17 @@
         <v>3</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D21" s="38" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E21" s="38"/>
-      <c r="F21" s="38">
-        <v>14187000333707</v>
+      <c r="F21" s="38" t="s">
+        <v>33</v>
       </c>
       <c r="G21" s="38"/>
       <c r="H21" s="38"/>
@@ -1460,17 +1499,17 @@
         <v>4</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E22" s="38"/>
-      <c r="F22" s="38" t="s">
-        <v>35</v>
+      <c r="F22" s="38">
+        <v>14187000333707</v>
       </c>
       <c r="G22" s="38"/>
       <c r="H22" s="38"/>
@@ -1481,17 +1520,17 @@
         <v>5</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E23" s="38"/>
       <c r="F23" s="38" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G23" s="38"/>
       <c r="H23" s="38"/>
@@ -1502,13 +1541,13 @@
         <v>6</v>
       </c>
       <c r="B24" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="38" t="s">
         <v>38</v>
-      </c>
-      <c r="C24" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" s="38" t="s">
-        <v>40</v>
       </c>
       <c r="E24" s="38"/>
       <c r="F24" s="38" t="s">
@@ -1526,14 +1565,14 @@
         <v>42</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E25" s="38"/>
       <c r="F25" s="38" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
@@ -1544,17 +1583,17 @@
         <v>8</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E26" s="38"/>
       <c r="F26" s="38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G26" s="38"/>
       <c r="H26" s="38"/>
@@ -1565,17 +1604,17 @@
         <v>9</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D27" s="38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E27" s="38"/>
       <c r="F27" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G27" s="38"/>
       <c r="H27" s="38"/>
@@ -1586,17 +1625,17 @@
         <v>10</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E28" s="38"/>
       <c r="F28" s="38" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G28" s="38"/>
       <c r="H28" s="38"/>
@@ -1607,17 +1646,17 @@
         <v>11</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E29" s="38"/>
       <c r="F29" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G29" s="38"/>
       <c r="H29" s="38"/>
@@ -1628,17 +1667,17 @@
         <v>12</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E30" s="38"/>
       <c r="F30" s="38" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G30" s="38"/>
       <c r="H30" s="38"/>
@@ -1649,17 +1688,17 @@
         <v>13</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D31" s="38" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E31" s="38"/>
       <c r="F31" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G31" s="38"/>
       <c r="H31" s="38"/>
@@ -1670,17 +1709,17 @@
         <v>14</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D32" s="38" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E32" s="38"/>
       <c r="F32" s="38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G32" s="38"/>
       <c r="H32" s="38"/>
@@ -1691,17 +1730,17 @@
         <v>15</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C33" s="38" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D33" s="38" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E33" s="38"/>
       <c r="F33" s="38" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="G33" s="38"/>
       <c r="H33" s="38"/>
@@ -1712,17 +1751,17 @@
         <v>16</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="D34" s="38" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E34" s="38"/>
       <c r="F34" s="38" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="G34" s="38"/>
       <c r="H34" s="38"/>
@@ -1736,14 +1775,14 @@
         <v>71</v>
       </c>
       <c r="C35" s="38" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D35" s="38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E35" s="38"/>
-      <c r="F35" s="38">
-        <v>647235228</v>
+      <c r="F35" s="38" t="s">
+        <v>74</v>
       </c>
       <c r="G35" s="38"/>
       <c r="H35" s="38"/>
@@ -1754,17 +1793,17 @@
         <v>18</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C36" s="38" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D36" s="38" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="E36" s="38"/>
-      <c r="F36" s="38" t="s">
-        <v>52</v>
+      <c r="F36" s="38">
+        <v>647235228</v>
       </c>
       <c r="G36" s="38"/>
       <c r="H36" s="38"/>
@@ -1775,17 +1814,17 @@
         <v>19</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C37" s="38" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D37" s="38" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E37" s="38"/>
       <c r="F37" s="38" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G37" s="38"/>
       <c r="H37" s="38"/>
@@ -1796,17 +1835,17 @@
         <v>20</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="E38" s="38"/>
       <c r="F38" s="38" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="G38" s="38"/>
       <c r="H38" s="38"/>
@@ -1820,14 +1859,14 @@
         <v>79</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="E39" s="38"/>
       <c r="F39" s="38" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G39" s="38"/>
       <c r="H39" s="38"/>
@@ -1838,17 +1877,17 @@
         <v>22</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E40" s="38"/>
       <c r="F40" s="38" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G40" s="38"/>
       <c r="H40" s="38"/>
@@ -1859,17 +1898,17 @@
         <v>23</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C41" s="38" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="D41" s="38" t="s">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="E41" s="38"/>
       <c r="F41" s="38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G41" s="38"/>
       <c r="H41" s="38"/>
@@ -1880,17 +1919,17 @@
         <v>24</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C42" s="38" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D42" s="38" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E42" s="38"/>
       <c r="F42" s="38" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G42" s="38"/>
       <c r="H42" s="38"/>
@@ -1901,17 +1940,17 @@
         <v>25</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G43" s="38"/>
       <c r="H43" s="38"/>
@@ -1922,17 +1961,17 @@
         <v>26</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C44" s="38" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D44" s="38" t="s">
         <v>87</v>
       </c>
       <c r="E44" s="38"/>
       <c r="F44" s="38" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G44" s="38"/>
       <c r="H44" s="38"/>
@@ -1943,17 +1982,17 @@
         <v>27</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E45" s="38"/>
       <c r="F45" s="38" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G45" s="38"/>
       <c r="H45" s="38"/>
@@ -1964,17 +2003,17 @@
         <v>28</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E46" s="38"/>
       <c r="F46" s="38" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G46" s="38"/>
       <c r="H46" s="38"/>
@@ -1985,17 +2024,17 @@
         <v>29</v>
       </c>
       <c r="B47" s="38" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C47" s="38" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="E47" s="38"/>
       <c r="F47" s="38" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G47" s="38"/>
       <c r="H47" s="38"/>
@@ -2006,17 +2045,17 @@
         <v>30</v>
       </c>
       <c r="B48" s="38" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C48" s="38" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D48" s="38" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E48" s="38"/>
       <c r="F48" s="38" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G48" s="38"/>
       <c r="H48" s="38"/>
@@ -2027,17 +2066,17 @@
         <v>31</v>
       </c>
       <c r="B49" s="38" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C49" s="38" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E49" s="38"/>
       <c r="F49" s="38" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G49" s="38"/>
       <c r="H49" s="38"/>
@@ -2048,10 +2087,10 @@
         <v>32</v>
       </c>
       <c r="B50" s="38" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C50" s="38" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="D50" s="38" t="s">
         <v>98</v>
@@ -2069,17 +2108,17 @@
         <v>33</v>
       </c>
       <c r="B51" s="38" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C51" s="38" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D51" s="38" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E51" s="38"/>
       <c r="F51" s="38" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G51" s="38"/>
       <c r="H51" s="38"/>
@@ -2090,15 +2129,17 @@
         <v>34</v>
       </c>
       <c r="B52" s="38" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C52" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="D52" s="38"/>
+        <v>101</v>
+      </c>
+      <c r="D52" s="38" t="s">
+        <v>104</v>
+      </c>
       <c r="E52" s="38"/>
       <c r="F52" s="38" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G52" s="38"/>
       <c r="H52" s="38"/>
@@ -2109,17 +2150,15 @@
         <v>35</v>
       </c>
       <c r="B53" s="38" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C53" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="D53" s="38" t="s">
-        <v>105</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="D53" s="38"/>
       <c r="E53" s="38"/>
       <c r="F53" s="38" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G53" s="38"/>
       <c r="H53" s="38"/>
@@ -2130,17 +2169,17 @@
         <v>36</v>
       </c>
       <c r="B54" s="38" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C54" s="38" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D54" s="38" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E54" s="38"/>
       <c r="F54" s="38" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G54" s="38"/>
       <c r="H54" s="38"/>
@@ -2154,10 +2193,10 @@
         <v>108</v>
       </c>
       <c r="C55" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="D55" s="38" t="s">
         <v>109</v>
-      </c>
-      <c r="D55" s="38" t="s">
-        <v>110</v>
       </c>
       <c r="E55" s="38"/>
       <c r="F55" s="38" t="s">
@@ -2175,14 +2214,14 @@
         <v>112</v>
       </c>
       <c r="C56" s="38" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="D56" s="38" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E56" s="38"/>
       <c r="F56" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G56" s="38"/>
       <c r="H56" s="38"/>
@@ -2193,17 +2232,17 @@
         <v>39</v>
       </c>
       <c r="B57" s="38" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C57" s="38" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D57" s="38" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E57" s="38"/>
       <c r="F57" s="38" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G57" s="38"/>
       <c r="H57" s="38"/>
@@ -2214,17 +2253,17 @@
         <v>40</v>
       </c>
       <c r="B58" s="38" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C58" s="38" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D58" s="38" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E58" s="38"/>
       <c r="F58" s="38" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G58" s="38"/>
       <c r="H58" s="38"/>
@@ -2235,17 +2274,17 @@
         <v>41</v>
       </c>
       <c r="B59" s="38" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C59" s="38" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D59" s="38" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E59" s="38"/>
       <c r="F59" s="38" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G59" s="38"/>
       <c r="H59" s="38"/>
@@ -2256,17 +2295,17 @@
         <v>42</v>
       </c>
       <c r="B60" s="38" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C60" s="38" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="D60" s="38" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E60" s="38"/>
       <c r="F60" s="38" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G60" s="38"/>
       <c r="H60" s="38"/>
@@ -2277,17 +2316,17 @@
         <v>43</v>
       </c>
       <c r="B61" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C61" s="38" t="s">
-        <v>68</v>
+        <v>123</v>
       </c>
       <c r="D61" s="38" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E61" s="38"/>
       <c r="F61" s="38" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G61" s="38"/>
       <c r="H61" s="38"/>
@@ -2298,17 +2337,17 @@
         <v>44</v>
       </c>
       <c r="B62" s="38" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C62" s="38" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D62" s="38" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E62" s="38"/>
       <c r="F62" s="38" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G62" s="38"/>
       <c r="H62" s="38"/>
@@ -2319,17 +2358,17 @@
         <v>45</v>
       </c>
       <c r="B63" s="38" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C63" s="38" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D63" s="38" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E63" s="38"/>
       <c r="F63" s="38" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G63" s="38"/>
       <c r="H63" s="38"/>
@@ -2340,17 +2379,17 @@
         <v>46</v>
       </c>
       <c r="B64" s="38" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C64" s="38" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D64" s="38" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E64" s="38"/>
       <c r="F64" s="38" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G64" s="38"/>
       <c r="H64" s="38"/>
@@ -2361,17 +2400,17 @@
         <v>47</v>
       </c>
       <c r="B65" s="38" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C65" s="38" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D65" s="38" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="E65" s="38"/>
       <c r="F65" s="38" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G65" s="38"/>
       <c r="H65" s="38"/>
@@ -2382,17 +2421,17 @@
         <v>48</v>
       </c>
       <c r="B66" s="38" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C66" s="38" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D66" s="38" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E66" s="38"/>
       <c r="F66" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G66" s="38"/>
       <c r="H66" s="38"/>
@@ -2403,17 +2442,17 @@
         <v>49</v>
       </c>
       <c r="B67" s="38" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C67" s="38" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D67" s="38" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="E67" s="38"/>
       <c r="F67" s="38" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G67" s="38"/>
       <c r="H67" s="38"/>
@@ -2424,17 +2463,17 @@
         <v>50</v>
       </c>
       <c r="B68" s="38" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C68" s="38" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D68" s="38" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E68" s="38"/>
       <c r="F68" s="38" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G68" s="38"/>
       <c r="H68" s="38"/>
@@ -2445,17 +2484,17 @@
         <v>51</v>
       </c>
       <c r="B69" s="38" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C69" s="38" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D69" s="38" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E69" s="38"/>
       <c r="F69" s="38" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G69" s="38"/>
       <c r="H69" s="38"/>
@@ -2466,17 +2505,17 @@
         <v>52</v>
       </c>
       <c r="B70" s="38" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C70" s="38" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D70" s="38" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E70" s="38"/>
       <c r="F70" s="38" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G70" s="38"/>
       <c r="H70" s="38"/>
@@ -2487,17 +2526,17 @@
         <v>53</v>
       </c>
       <c r="B71" s="38" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C71" s="38" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D71" s="38" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E71" s="38"/>
       <c r="F71" s="38" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G71" s="38"/>
       <c r="H71" s="38"/>
@@ -2508,17 +2547,17 @@
         <v>54</v>
       </c>
       <c r="B72" s="38" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C72" s="38" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D72" s="38" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E72" s="38"/>
       <c r="F72" s="38" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G72" s="38"/>
       <c r="H72" s="38"/>
@@ -2529,17 +2568,17 @@
         <v>55</v>
       </c>
       <c r="B73" s="38" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C73" s="38" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D73" s="38" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="E73" s="38"/>
       <c r="F73" s="38" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G73" s="38"/>
       <c r="H73" s="38"/>
@@ -2550,17 +2589,17 @@
         <v>56</v>
       </c>
       <c r="B74" s="38" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C74" s="38" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D74" s="38" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="E74" s="38"/>
       <c r="F74" s="38" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G74" s="38"/>
       <c r="H74" s="38"/>
@@ -2571,17 +2610,17 @@
         <v>57</v>
       </c>
       <c r="B75" s="38" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C75" s="38" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D75" s="38" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E75" s="38"/>
       <c r="F75" s="38" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G75" s="38"/>
       <c r="H75" s="38"/>
@@ -2592,17 +2631,17 @@
         <v>58</v>
       </c>
       <c r="B76" s="38" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C76" s="38" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D76" s="38" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="E76" s="38"/>
       <c r="F76" s="38" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G76" s="38"/>
       <c r="H76" s="38"/>
@@ -2613,17 +2652,17 @@
         <v>59</v>
       </c>
       <c r="B77" s="38" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C77" s="38" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D77" s="38" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E77" s="38"/>
       <c r="F77" s="38" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G77" s="38"/>
       <c r="H77" s="38"/>
@@ -2634,17 +2673,17 @@
         <v>60</v>
       </c>
       <c r="B78" s="38" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C78" s="38" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D78" s="38" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E78" s="38"/>
       <c r="F78" s="38" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G78" s="38"/>
       <c r="H78" s="38"/>
@@ -2655,17 +2694,17 @@
         <v>61</v>
       </c>
       <c r="B79" s="38" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C79" s="38" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D79" s="38" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="E79" s="38"/>
       <c r="F79" s="38" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G79" s="38"/>
       <c r="H79" s="38"/>
@@ -2676,17 +2715,17 @@
         <v>62</v>
       </c>
       <c r="B80" s="38" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="C80" s="38" t="s">
-        <v>149</v>
+        <v>72</v>
       </c>
       <c r="D80" s="38" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="E80" s="38"/>
       <c r="F80" s="38" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G80" s="38"/>
       <c r="H80" s="38"/>
@@ -2697,7 +2736,7 @@
         <v>63</v>
       </c>
       <c r="B81" s="38" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="C81" s="38" t="s">
         <v>153</v>
@@ -2706,8 +2745,8 @@
         <v>154</v>
       </c>
       <c r="E81" s="38"/>
-      <c r="F81" s="38">
-        <v>544161389</v>
+      <c r="F81" s="38" t="s">
+        <v>155</v>
       </c>
       <c r="G81" s="38"/>
       <c r="H81" s="38"/>
@@ -2718,17 +2757,17 @@
         <v>64</v>
       </c>
       <c r="B82" s="38" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C82" s="38" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D82" s="38" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E82" s="38"/>
       <c r="F82" s="38">
-        <v>544161388</v>
+        <v>544161389</v>
       </c>
       <c r="G82" s="38"/>
       <c r="H82" s="38"/>
@@ -2739,17 +2778,17 @@
         <v>65</v>
       </c>
       <c r="B83" s="38" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C83" s="38" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D83" s="38" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E83" s="38"/>
-      <c r="F83" s="38" t="s">
-        <v>158</v>
+      <c r="F83" s="38">
+        <v>544161388</v>
       </c>
       <c r="G83" s="38"/>
       <c r="H83" s="38"/>
@@ -2766,11 +2805,11 @@
         <v>160</v>
       </c>
       <c r="D84" s="38" t="s">
-        <v>52</v>
+        <v>161</v>
       </c>
       <c r="E84" s="38"/>
       <c r="F84" s="38" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G84" s="38"/>
       <c r="H84" s="38"/>
@@ -2781,17 +2820,17 @@
         <v>67</v>
       </c>
       <c r="B85" s="38" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C85" s="38" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D85" s="38" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E85" s="38"/>
       <c r="F85" s="38" t="s">
-        <v>52</v>
+        <v>165</v>
       </c>
       <c r="G85" s="38"/>
       <c r="H85" s="38"/>
@@ -2802,17 +2841,17 @@
         <v>68</v>
       </c>
       <c r="B86" s="38" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C86" s="38" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D86" s="38" t="s">
-        <v>165</v>
+        <v>56</v>
       </c>
       <c r="E86" s="38"/>
       <c r="F86" s="38" t="s">
-        <v>161</v>
+        <v>56</v>
       </c>
       <c r="G86" s="38"/>
       <c r="H86" s="38"/>
@@ -2823,17 +2862,17 @@
         <v>69</v>
       </c>
       <c r="B87" s="38" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C87" s="38" t="s">
-        <v>39</v>
+        <v>164</v>
       </c>
       <c r="D87" s="38" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E87" s="38"/>
       <c r="F87" s="38" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G87" s="38"/>
       <c r="H87" s="38"/>
@@ -2844,17 +2883,17 @@
         <v>70</v>
       </c>
       <c r="B88" s="38" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C88" s="38" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D88" s="38" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E88" s="38"/>
       <c r="F88" s="38" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G88" s="38"/>
       <c r="H88" s="38"/>
@@ -2865,13 +2904,13 @@
         <v>71</v>
       </c>
       <c r="B89" s="38" t="s">
+        <v>173</v>
+      </c>
+      <c r="C89" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="D89" s="38" t="s">
         <v>171</v>
-      </c>
-      <c r="C89" s="38" t="s">
-        <v>172</v>
-      </c>
-      <c r="D89" s="38" t="s">
-        <v>173</v>
       </c>
       <c r="E89" s="38"/>
       <c r="F89" s="38" t="s">
@@ -2882,261 +2921,311 @@
       <c r="I89" s="38"/>
     </row>
     <row r="90" spans="1:10" customHeight="1" ht="15">
-      <c r="A90" s="16"/>
-      <c r="B90" s="16"/>
-      <c r="C90" s="16"/>
-      <c r="D90" s="16"/>
-      <c r="E90" s="16"/>
-      <c r="F90" s="23"/>
-      <c r="G90" s="23"/>
-      <c r="H90" s="24"/>
-      <c r="I90" s="24"/>
+      <c r="A90" s="38">
+        <v>72</v>
+      </c>
+      <c r="B90" s="38" t="s">
+        <v>175</v>
+      </c>
+      <c r="C90" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="D90" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="E90" s="38"/>
+      <c r="F90" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="G90" s="38"/>
+      <c r="H90" s="38"/>
+      <c r="I90" s="38"/>
     </row>
     <row r="91" spans="1:10" customHeight="1" ht="15">
-      <c r="A91" s="25"/>
-      <c r="B91" s="25"/>
-      <c r="C91" s="25"/>
-      <c r="D91" s="25"/>
-      <c r="E91" s="25"/>
-      <c r="F91" s="25"/>
-      <c r="G91" s="25"/>
-      <c r="H91" s="25"/>
-      <c r="I91" s="25"/>
+      <c r="A91" s="38">
+        <v>73</v>
+      </c>
+      <c r="B91" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="C91" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="D91" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="E91" s="38"/>
+      <c r="F91" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="G91" s="38"/>
+      <c r="H91" s="38"/>
+      <c r="I91" s="38"/>
     </row>
     <row r="92" spans="1:10" customHeight="1" ht="15">
-      <c r="A92" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="B92" s="26"/>
-      <c r="C92" s="26"/>
-      <c r="D92" s="26"/>
-      <c r="E92" s="26"/>
-      <c r="F92" s="26"/>
-      <c r="G92" s="26"/>
-      <c r="H92" s="26"/>
-      <c r="I92" s="26"/>
+      <c r="A92" s="38">
+        <v>74</v>
+      </c>
+      <c r="B92" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="C92" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="D92" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="E92" s="38"/>
+      <c r="F92" s="38" t="s">
+        <v>183</v>
+      </c>
+      <c r="G92" s="38"/>
+      <c r="H92" s="38"/>
+      <c r="I92" s="38"/>
     </row>
     <row r="93" spans="1:10" customHeight="1" ht="15">
-      <c r="A93" s="27"/>
-      <c r="B93" s="27"/>
-      <c r="C93" s="27"/>
-      <c r="D93" s="27"/>
-      <c r="E93" s="27"/>
-      <c r="F93" s="27"/>
-      <c r="G93" s="27"/>
-      <c r="H93" s="27"/>
-      <c r="I93" s="27"/>
+      <c r="A93" s="38">
+        <v>75</v>
+      </c>
+      <c r="B93" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="C93" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="D93" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="E93" s="38"/>
+      <c r="F93" s="38" t="s">
+        <v>187</v>
+      </c>
+      <c r="G93" s="38"/>
+      <c r="H93" s="38"/>
+      <c r="I93" s="38"/>
     </row>
     <row r="94" spans="1:10" customHeight="1" ht="15">
-      <c r="A94" s="28" t="s">
-        <v>176</v>
-      </c>
-      <c r="B94" s="28"/>
-      <c r="C94" s="28"/>
-      <c r="D94" s="28"/>
-      <c r="E94" s="28"/>
-      <c r="F94" s="28"/>
-      <c r="G94" s="28"/>
-      <c r="H94" s="28"/>
-      <c r="I94" s="28"/>
+      <c r="A94" s="38">
+        <v>76</v>
+      </c>
+      <c r="B94" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="C94" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="D94" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="E94" s="38"/>
+      <c r="F94" s="38" t="s">
+        <v>188</v>
+      </c>
+      <c r="G94" s="38"/>
+      <c r="H94" s="38"/>
+      <c r="I94" s="38"/>
     </row>
     <row r="95" spans="1:10" customHeight="1" ht="15">
-      <c r="A95" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="B95" s="28"/>
-      <c r="C95" s="28"/>
-      <c r="D95" s="28"/>
-      <c r="E95" s="28"/>
-      <c r="F95" s="28"/>
-      <c r="G95" s="28"/>
-      <c r="H95" s="28"/>
-      <c r="I95" s="28"/>
+      <c r="A95" s="38">
+        <v>77</v>
+      </c>
+      <c r="B95" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="C95" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="D95" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="E95" s="38"/>
+      <c r="F95" s="38" t="s">
+        <v>189</v>
+      </c>
+      <c r="G95" s="38"/>
+      <c r="H95" s="38"/>
+      <c r="I95" s="38"/>
     </row>
     <row r="96" spans="1:10" customHeight="1" ht="15">
-      <c r="A96" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="B96" s="28"/>
-      <c r="C96" s="28"/>
-      <c r="D96" s="28"/>
-      <c r="E96" s="28"/>
-      <c r="F96" s="28"/>
-      <c r="G96" s="28"/>
-      <c r="H96" s="28"/>
-      <c r="I96" s="28"/>
-    </row>
-    <row r="97" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A97" s="29" t="s">
-        <v>179</v>
-      </c>
-      <c r="B97" s="29"/>
-      <c r="C97" s="29"/>
-      <c r="D97" s="29"/>
-      <c r="E97" s="29"/>
-      <c r="F97" s="29"/>
-      <c r="G97" s="29"/>
-      <c r="H97" s="29"/>
-      <c r="I97" s="29"/>
-      <c r="J97" s="2"/>
-    </row>
-    <row r="98" spans="1:10" customHeight="1" ht="27">
-      <c r="A98" s="28" t="s">
-        <v>180</v>
-      </c>
-      <c r="B98" s="28"/>
-      <c r="C98" s="28"/>
-      <c r="D98" s="28"/>
-      <c r="E98" s="28"/>
-      <c r="F98" s="28"/>
-      <c r="G98" s="28"/>
-      <c r="H98" s="28"/>
-      <c r="I98" s="28"/>
+      <c r="A96" s="16"/>
+      <c r="B96" s="16"/>
+      <c r="C96" s="16"/>
+      <c r="D96" s="16"/>
+      <c r="E96" s="16"/>
+      <c r="F96" s="23"/>
+      <c r="G96" s="23"/>
+      <c r="H96" s="24"/>
+      <c r="I96" s="24"/>
+    </row>
+    <row r="97" spans="1:10" customHeight="1" ht="15">
+      <c r="A97" s="25"/>
+      <c r="B97" s="25"/>
+      <c r="C97" s="25"/>
+      <c r="D97" s="25"/>
+      <c r="E97" s="25"/>
+      <c r="F97" s="25"/>
+      <c r="G97" s="25"/>
+      <c r="H97" s="25"/>
+      <c r="I97" s="25"/>
+    </row>
+    <row r="98" spans="1:10" customHeight="1" ht="15">
+      <c r="A98" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="B98" s="26"/>
+      <c r="C98" s="26"/>
+      <c r="D98" s="26"/>
+      <c r="E98" s="26"/>
+      <c r="F98" s="26"/>
+      <c r="G98" s="26"/>
+      <c r="H98" s="26"/>
+      <c r="I98" s="26"/>
     </row>
     <row r="99" spans="1:10" customHeight="1" ht="15">
-      <c r="A99" s="30"/>
-      <c r="B99" s="30"/>
-      <c r="C99" s="30"/>
-      <c r="D99" s="30"/>
-      <c r="E99" s="30"/>
-      <c r="F99" s="30"/>
-      <c r="G99" s="30"/>
-      <c r="H99" s="30"/>
-      <c r="I99" s="30"/>
-    </row>
-    <row r="100" spans="1:10" customHeight="1" ht="39">
-      <c r="A100" s="31" t="s">
-        <v>181</v>
-      </c>
-      <c r="B100" s="31"/>
-      <c r="C100" s="31"/>
-      <c r="D100" s="31"/>
-      <c r="E100" s="31"/>
-      <c r="F100" s="31"/>
-      <c r="G100" s="31"/>
-      <c r="H100" s="31"/>
-      <c r="I100" s="31"/>
+      <c r="A99" s="27"/>
+      <c r="B99" s="27"/>
+      <c r="C99" s="27"/>
+      <c r="D99" s="27"/>
+      <c r="E99" s="27"/>
+      <c r="F99" s="27"/>
+      <c r="G99" s="27"/>
+      <c r="H99" s="27"/>
+      <c r="I99" s="27"/>
+    </row>
+    <row r="100" spans="1:10" customHeight="1" ht="15">
+      <c r="A100" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="B100" s="28"/>
+      <c r="C100" s="28"/>
+      <c r="D100" s="28"/>
+      <c r="E100" s="28"/>
+      <c r="F100" s="28"/>
+      <c r="G100" s="28"/>
+      <c r="H100" s="28"/>
+      <c r="I100" s="28"/>
     </row>
     <row r="101" spans="1:10" customHeight="1" ht="15">
-      <c r="A101" s="32"/>
-      <c r="B101" s="32"/>
-      <c r="C101" s="32"/>
-      <c r="D101" s="32"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
-      <c r="G101" s="33"/>
-      <c r="H101" s="33"/>
-      <c r="I101" s="33"/>
+      <c r="A101" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="B101" s="28"/>
+      <c r="C101" s="28"/>
+      <c r="D101" s="28"/>
+      <c r="E101" s="28"/>
+      <c r="F101" s="28"/>
+      <c r="G101" s="28"/>
+      <c r="H101" s="28"/>
+      <c r="I101" s="28"/>
     </row>
     <row r="102" spans="1:10" customHeight="1" ht="15">
-      <c r="A102" s="2"/>
-      <c r="B102" s="32"/>
-      <c r="C102" s="32"/>
-      <c r="D102" s="32"/>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-      <c r="H102" s="33"/>
-      <c r="I102" s="33"/>
-    </row>
-    <row r="103" spans="1:10" customHeight="1" ht="15">
-      <c r="A103" s="32"/>
-      <c r="B103" s="34" t="s">
-        <v>182</v>
-      </c>
-      <c r="C103" s="34"/>
-      <c r="D103" s="34"/>
-      <c r="E103" s="2"/>
-      <c r="F103" s="2"/>
-      <c r="G103" s="35" t="s">
-        <v>183</v>
-      </c>
-      <c r="H103" s="35"/>
-      <c r="I103" s="35"/>
-    </row>
-    <row r="104" spans="1:10" customHeight="1" ht="15">
-      <c r="A104" s="2"/>
-      <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
-      <c r="D104" s="36" t="s">
-        <v>184</v>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
-      <c r="H104" s="2"/>
-      <c r="I104" s="2"/>
+      <c r="A102" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="B102" s="28"/>
+      <c r="C102" s="28"/>
+      <c r="D102" s="28"/>
+      <c r="E102" s="28"/>
+      <c r="F102" s="28"/>
+      <c r="G102" s="28"/>
+      <c r="H102" s="28"/>
+      <c r="I102" s="28"/>
+    </row>
+    <row r="103" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A103" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="B103" s="29"/>
+      <c r="C103" s="29"/>
+      <c r="D103" s="29"/>
+      <c r="E103" s="29"/>
+      <c r="F103" s="29"/>
+      <c r="G103" s="29"/>
+      <c r="H103" s="29"/>
+      <c r="I103" s="29"/>
+      <c r="J103" s="2"/>
+    </row>
+    <row r="104" spans="1:10" customHeight="1" ht="27">
+      <c r="A104" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="B104" s="28"/>
+      <c r="C104" s="28"/>
+      <c r="D104" s="28"/>
+      <c r="E104" s="28"/>
+      <c r="F104" s="28"/>
+      <c r="G104" s="28"/>
+      <c r="H104" s="28"/>
+      <c r="I104" s="28"/>
     </row>
     <row r="105" spans="1:10" customHeight="1" ht="15">
-      <c r="A105" s="2"/>
-      <c r="B105" s="37"/>
-      <c r="C105" s="37"/>
-      <c r="D105" s="37"/>
-      <c r="E105" s="2"/>
-      <c r="F105" s="2"/>
-      <c r="G105" s="37"/>
-      <c r="H105" s="37"/>
-      <c r="I105" s="37"/>
-    </row>
-    <row r="106" spans="1:10" customHeight="1" ht="15">
-      <c r="A106" s="2"/>
-      <c r="B106" s="2"/>
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
-      <c r="F106" s="2"/>
-      <c r="G106" s="2"/>
-      <c r="H106" s="2"/>
-      <c r="I106" s="2"/>
+      <c r="A105" s="30"/>
+      <c r="B105" s="30"/>
+      <c r="C105" s="30"/>
+      <c r="D105" s="30"/>
+      <c r="E105" s="30"/>
+      <c r="F105" s="30"/>
+      <c r="G105" s="30"/>
+      <c r="H105" s="30"/>
+      <c r="I105" s="30"/>
+    </row>
+    <row r="106" spans="1:10" customHeight="1" ht="39">
+      <c r="A106" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="B106" s="31"/>
+      <c r="C106" s="31"/>
+      <c r="D106" s="31"/>
+      <c r="E106" s="31"/>
+      <c r="F106" s="31"/>
+      <c r="G106" s="31"/>
+      <c r="H106" s="31"/>
+      <c r="I106" s="31"/>
     </row>
     <row r="107" spans="1:10" customHeight="1" ht="15">
-      <c r="A107" s="2"/>
-      <c r="B107" s="34" t="s">
-        <v>185</v>
-      </c>
-      <c r="C107" s="34"/>
-      <c r="D107" s="34"/>
+      <c r="A107" s="32"/>
+      <c r="B107" s="32"/>
+      <c r="C107" s="32"/>
+      <c r="D107" s="32"/>
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
-      <c r="G107" s="34" t="str">
-        <f>C10</f>
-        <v>Alejandro Cancino Arguello</v>
-      </c>
-      <c r="H107" s="34"/>
-      <c r="I107" s="34"/>
+      <c r="G107" s="33"/>
+      <c r="H107" s="33"/>
+      <c r="I107" s="33"/>
     </row>
     <row r="108" spans="1:10" customHeight="1" ht="15">
       <c r="A108" s="2"/>
-      <c r="B108" s="34" t="s">
-        <v>186</v>
-      </c>
-      <c r="C108" s="34"/>
-      <c r="D108" s="34"/>
+      <c r="B108" s="32"/>
+      <c r="C108" s="32"/>
+      <c r="D108" s="32"/>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
-      <c r="G108" s="34" t="str">
-        <f>C12</f>
-        <v>Coordinador de TI</v>
-      </c>
-      <c r="H108" s="34"/>
-      <c r="I108" s="34"/>
+      <c r="G108" s="2"/>
+      <c r="H108" s="33"/>
+      <c r="I108" s="33"/>
     </row>
     <row r="109" spans="1:10" customHeight="1" ht="15">
-      <c r="A109" s="2"/>
-      <c r="B109" s="2"/>
-      <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
+      <c r="A109" s="32"/>
+      <c r="B109" s="34" t="s">
+        <v>197</v>
+      </c>
+      <c r="C109" s="34"/>
+      <c r="D109" s="34"/>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
-      <c r="G109" s="32"/>
-      <c r="H109" s="32"/>
-      <c r="I109" s="32"/>
+      <c r="G109" s="35" t="s">
+        <v>198</v>
+      </c>
+      <c r="H109" s="35"/>
+      <c r="I109" s="35"/>
     </row>
     <row r="110" spans="1:10" customHeight="1" ht="15">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
-      <c r="D110" s="2"/>
+      <c r="D110" s="36" t="s">
+        <v>199</v>
+      </c>
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
@@ -3144,15 +3233,91 @@
       <c r="I110" s="2"/>
     </row>
     <row r="111" spans="1:10" customHeight="1" ht="15">
-      <c r="A111" s="32"/>
-      <c r="B111" s="32"/>
-      <c r="C111" s="32"/>
-      <c r="D111" s="32"/>
+      <c r="A111" s="2"/>
+      <c r="B111" s="37"/>
+      <c r="C111" s="37"/>
+      <c r="D111" s="37"/>
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
-      <c r="G111" s="2"/>
-      <c r="H111" s="2"/>
-      <c r="I111" s="2"/>
+      <c r="G111" s="37"/>
+      <c r="H111" s="37"/>
+      <c r="I111" s="37"/>
+    </row>
+    <row r="112" spans="1:10" customHeight="1" ht="15">
+      <c r="A112" s="2"/>
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
+      <c r="D112" s="2"/>
+      <c r="E112" s="2"/>
+      <c r="F112" s="2"/>
+      <c r="G112" s="2"/>
+      <c r="H112" s="2"/>
+      <c r="I112" s="2"/>
+    </row>
+    <row r="113" spans="1:10" customHeight="1" ht="15">
+      <c r="A113" s="2"/>
+      <c r="B113" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C113" s="34"/>
+      <c r="D113" s="34"/>
+      <c r="E113" s="2"/>
+      <c r="F113" s="2"/>
+      <c r="G113" s="34" t="str">
+        <f>C10</f>
+        <v>Alejandro Cancino Arguello</v>
+      </c>
+      <c r="H113" s="34"/>
+      <c r="I113" s="34"/>
+    </row>
+    <row r="114" spans="1:10" customHeight="1" ht="15">
+      <c r="A114" s="2"/>
+      <c r="B114" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C114" s="34"/>
+      <c r="D114" s="34"/>
+      <c r="E114" s="2"/>
+      <c r="F114" s="2"/>
+      <c r="G114" s="34" t="str">
+        <f>C12</f>
+        <v>Coordinador de TI</v>
+      </c>
+      <c r="H114" s="34"/>
+      <c r="I114" s="34"/>
+    </row>
+    <row r="115" spans="1:10" customHeight="1" ht="15">
+      <c r="A115" s="2"/>
+      <c r="B115" s="2"/>
+      <c r="C115" s="2"/>
+      <c r="D115" s="2"/>
+      <c r="E115" s="2"/>
+      <c r="F115" s="2"/>
+      <c r="G115" s="32"/>
+      <c r="H115" s="32"/>
+      <c r="I115" s="32"/>
+    </row>
+    <row r="116" spans="1:10" customHeight="1" ht="15">
+      <c r="A116" s="2"/>
+      <c r="B116" s="2"/>
+      <c r="C116" s="2"/>
+      <c r="D116" s="2"/>
+      <c r="E116" s="2"/>
+      <c r="F116" s="2"/>
+      <c r="G116" s="2"/>
+      <c r="H116" s="2"/>
+      <c r="I116" s="2"/>
+    </row>
+    <row r="117" spans="1:10" customHeight="1" ht="15">
+      <c r="A117" s="32"/>
+      <c r="B117" s="32"/>
+      <c r="C117" s="32"/>
+      <c r="D117" s="32"/>
+      <c r="E117" s="2"/>
+      <c r="F117" s="2"/>
+      <c r="G117" s="2"/>
+      <c r="H117" s="2"/>
+      <c r="I117" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -3171,23 +3336,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="F90:G90"/>
-    <mergeCell ref="H90:I90"/>
-    <mergeCell ref="A92:I92"/>
-    <mergeCell ref="A94:I94"/>
-    <mergeCell ref="A95:I95"/>
-    <mergeCell ref="A96:I96"/>
-    <mergeCell ref="A97:I97"/>
+    <mergeCell ref="D96:E96"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="H96:I96"/>
     <mergeCell ref="A98:I98"/>
-    <mergeCell ref="A99:I99"/>
     <mergeCell ref="A100:I100"/>
-    <mergeCell ref="B103:D103"/>
-    <mergeCell ref="G103:I103"/>
-    <mergeCell ref="B107:D107"/>
-    <mergeCell ref="G107:I107"/>
-    <mergeCell ref="B108:D108"/>
-    <mergeCell ref="G108:I108"/>
+    <mergeCell ref="A101:I101"/>
+    <mergeCell ref="A102:I102"/>
+    <mergeCell ref="A103:I103"/>
+    <mergeCell ref="A104:I104"/>
+    <mergeCell ref="A105:I105"/>
+    <mergeCell ref="A106:I106"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="G109:I109"/>
+    <mergeCell ref="B113:D113"/>
+    <mergeCell ref="G113:I113"/>
+    <mergeCell ref="B114:D114"/>
+    <mergeCell ref="G114:I114"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -3401,7 +3566,25 @@
     <mergeCell ref="D89:E89"/>
     <mergeCell ref="F89:G89"/>
     <mergeCell ref="H89:I89"/>
-    <mergeCell ref="H19:I89"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="H90:I90"/>
+    <mergeCell ref="D91:E91"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="H91:I91"/>
+    <mergeCell ref="D92:E92"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="H92:I92"/>
+    <mergeCell ref="D93:E93"/>
+    <mergeCell ref="F93:G93"/>
+    <mergeCell ref="H93:I93"/>
+    <mergeCell ref="D94:E94"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="H94:I94"/>
+    <mergeCell ref="D95:E95"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="H95:I95"/>
+    <mergeCell ref="H19:I95"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Alejandro_Cancino_Arguello.xlsx
+++ b/database/controller_excel/Resguardo_Alejandro_Cancino_Arguello.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="208">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>11/06/2025</t>
+    <t>19/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -56,7 +56,7 @@
     <t>Región:</t>
   </si>
   <si>
-    <t>Sur</t>
+    <t>Norte</t>
   </si>
   <si>
     <t>Ubicación:</t>
@@ -86,30 +86,474 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
-    <t>Cargador de Laptop</t>
-  </si>
-  <si>
-    <t>Tesla</t>
-  </si>
-  <si>
-    <t>LA65NM190</t>
-  </si>
-  <si>
-    <t>CN-0VT148-LOC00-18C-3AF4-A02</t>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>Latitude 5520</t>
+  </si>
+  <si>
+    <t>C3Y9FG3</t>
+  </si>
+  <si>
+    <t>fyfgukghloi</t>
+  </si>
+  <si>
+    <t>DVZ-TP-TI-00027</t>
+  </si>
+  <si>
+    <t>Asus</t>
+  </si>
+  <si>
+    <t>asus3000-1234</t>
+  </si>
+  <si>
+    <t>DVZ-VH-000001</t>
+  </si>
+  <si>
+    <t>Camara Intrinsicamente segura</t>
+  </si>
+  <si>
+    <t>SONIM</t>
+  </si>
+  <si>
+    <t>XP7700</t>
+  </si>
+  <si>
+    <t>SWITCH SAN 1</t>
+  </si>
+  <si>
+    <t>POWERCONNECT 6224</t>
+  </si>
+  <si>
+    <t>D50KTS1</t>
+  </si>
+  <si>
+    <t>SWITCH SAN 2</t>
+  </si>
+  <si>
+    <t>J50KTS1</t>
+  </si>
+  <si>
+    <t>CALL MANAGER NUEVO</t>
+  </si>
+  <si>
+    <t>CISCO</t>
+  </si>
+  <si>
+    <t>UCS C220M3BE</t>
+  </si>
+  <si>
+    <t>220M3222</t>
+  </si>
+  <si>
+    <t>SERVIDOR 19</t>
+  </si>
+  <si>
+    <t>POWEREDGE R710</t>
+  </si>
+  <si>
+    <t>BRNFSL1</t>
+  </si>
+  <si>
+    <t>SERVIDOR 18</t>
+  </si>
+  <si>
+    <t>POWEREDGE R720</t>
+  </si>
+  <si>
+    <t>B3X7RV1</t>
+  </si>
+  <si>
+    <t>SAN</t>
+  </si>
+  <si>
+    <t>POWERVAULT MD3200i</t>
+  </si>
+  <si>
+    <t>48DT7V1</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>UNIDAD DE CINTAS 19</t>
+  </si>
+  <si>
+    <t>POWER VAULT 114 X</t>
+  </si>
+  <si>
+    <t>YN106813H628</t>
+  </si>
+  <si>
+    <t>SERVIDOR 27</t>
+  </si>
+  <si>
+    <t>POWEREDGE 2950</t>
+  </si>
+  <si>
+    <t>DPBP6K1</t>
+  </si>
+  <si>
+    <t>SERVIDOR 29</t>
+  </si>
+  <si>
+    <t>POWEREDGE R320</t>
+  </si>
+  <si>
+    <t>D64MW12</t>
+  </si>
+  <si>
+    <t>UNIDAD DE CINTAS</t>
+  </si>
+  <si>
+    <t>POWER VAULT 124 T</t>
+  </si>
+  <si>
+    <t>8DDB6K1</t>
+  </si>
+  <si>
+    <t>Switch Linksys Cisco SD216</t>
+  </si>
+  <si>
+    <t>SD216</t>
+  </si>
+  <si>
+    <t>NVR</t>
+  </si>
+  <si>
+    <t>HIKVISION</t>
+  </si>
+  <si>
+    <t>DS-7616NI-K2/16P</t>
+  </si>
+  <si>
+    <t>L48074542</t>
+  </si>
+  <si>
+    <t>DVR HIKVISION</t>
+  </si>
+  <si>
+    <t>DS-7716NI-I4/16P</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>3D Optical</t>
+  </si>
+  <si>
+    <t>Switch 8 Puertos</t>
+  </si>
+  <si>
+    <t>Planet</t>
+  </si>
+  <si>
+    <t>GSD-804P</t>
+  </si>
+  <si>
+    <t>A350106300034</t>
+  </si>
+  <si>
+    <t>Access PRO</t>
+  </si>
+  <si>
+    <t>AP233</t>
+  </si>
+  <si>
+    <t>AP234</t>
+  </si>
+  <si>
+    <t>Switch</t>
+  </si>
+  <si>
+    <t>CATALYST 2960-X SERIES</t>
+  </si>
+  <si>
+    <t>FCW1906B1MY</t>
+  </si>
+  <si>
+    <t>FCW1906B1LJ</t>
+  </si>
+  <si>
+    <t>FCW1906B1MM</t>
+  </si>
+  <si>
+    <t>CATALYST 2960-X SERIES POE+</t>
+  </si>
+  <si>
+    <t>FOC1710Y1FV</t>
+  </si>
+  <si>
+    <t>CATALYST 3560</t>
+  </si>
+  <si>
+    <t>CAT0948R334</t>
+  </si>
+  <si>
+    <t>F0C1503Z3QP</t>
+  </si>
+  <si>
+    <t>F0C1514X0EZ</t>
+  </si>
+  <si>
+    <t>FOC1903S1ME</t>
+  </si>
+  <si>
+    <t>Catalyst 3750X-24T-E</t>
+  </si>
+  <si>
+    <t>FD01816Z3AU</t>
+  </si>
+  <si>
+    <t>FIREWALL</t>
+  </si>
+  <si>
+    <t>FORTINET</t>
+  </si>
+  <si>
+    <t>FG100D3G14827870</t>
+  </si>
+  <si>
+    <t>FG100D3G14827806 MASTER</t>
+  </si>
+  <si>
+    <t>FG100D3G14827806</t>
+  </si>
+  <si>
+    <t>FG100D3G14827870 SLAVE</t>
+  </si>
+  <si>
+    <t>CALL MANAGER</t>
+  </si>
+  <si>
+    <t>FTX1328AHLG</t>
+  </si>
+  <si>
+    <t>ROUTER</t>
+  </si>
+  <si>
+    <t>CISCO 1900 SERIES</t>
+  </si>
+  <si>
+    <t>CFTX1614857Q</t>
+  </si>
+  <si>
+    <t>FTX174386AU</t>
+  </si>
+  <si>
+    <t>UPS</t>
+  </si>
+  <si>
+    <t>APC</t>
+  </si>
+  <si>
+    <t>APC Galaxy 3500</t>
+  </si>
+  <si>
+    <t>G35TF30KB4F</t>
+  </si>
+  <si>
+    <t>ACCESSPOINT</t>
+  </si>
+  <si>
+    <t>221E</t>
+  </si>
+  <si>
+    <t>FP221ETF22083298</t>
+  </si>
+  <si>
+    <t>FP221ETF22083291</t>
+  </si>
+  <si>
+    <t>FP221ETF22083300</t>
+  </si>
+  <si>
+    <t>FP221ETF22083299</t>
+  </si>
+  <si>
+    <t>Amplificador celular</t>
+  </si>
+  <si>
+    <t>EPCOM</t>
+  </si>
+  <si>
+    <t>G08W27160502</t>
+  </si>
+  <si>
+    <t>Camara Fija</t>
+  </si>
+  <si>
+    <t>DS-2CD2432F-I</t>
+  </si>
+  <si>
+    <t>I20140922CCWR480540694</t>
+  </si>
+  <si>
+    <t>DS-2CD1043G0-I</t>
+  </si>
+  <si>
+    <t>I20220824AAWRK47327687</t>
+  </si>
+  <si>
+    <t>Camara PTZ</t>
+  </si>
+  <si>
+    <t>DS-2DE4215IW-DE</t>
+  </si>
+  <si>
+    <t>DE20190506CCWRD16875921W</t>
+  </si>
+  <si>
+    <t>DS-2CD2232-I5</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802490</t>
+  </si>
+  <si>
+    <t>I20200824AAWRK47327674</t>
+  </si>
+  <si>
+    <t>DS-2DE7174-A</t>
+  </si>
+  <si>
+    <t>A20150122CCWR500502005</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802472</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802475</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802494</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802491</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802480</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802497</t>
+  </si>
+  <si>
+    <t>DS-2CD2422FWD-IW</t>
+  </si>
+  <si>
+    <t>IW20170808AAWR808998451</t>
+  </si>
+  <si>
+    <t>I20140922CCWR480540755</t>
+  </si>
+  <si>
+    <t>I20140922CCWR480540785</t>
+  </si>
+  <si>
+    <t>DS-2CD2T42WD-I5</t>
+  </si>
+  <si>
+    <t>I520160810BBWR633078836</t>
+  </si>
+  <si>
+    <t>I520160810BBWR633078735</t>
+  </si>
+  <si>
+    <t>I520160810BBWR633078506</t>
+  </si>
+  <si>
+    <t>A20150122CCWR500502035</t>
+  </si>
+  <si>
+    <t>KOBLENZ</t>
+  </si>
+  <si>
+    <t>4816 R</t>
+  </si>
+  <si>
+    <t>16-09-17766</t>
+  </si>
+  <si>
+    <t>Lector Biometrico</t>
+  </si>
+  <si>
+    <t>BioEntry W2</t>
+  </si>
+  <si>
+    <t>BEW2-0DP</t>
+  </si>
+  <si>
+    <t>Equipo de Videoconferencia</t>
+  </si>
+  <si>
+    <t>Chromebox</t>
+  </si>
+  <si>
+    <t>H6MSCX001323</t>
+  </si>
+  <si>
+    <t>Camara Videoconferencia</t>
+  </si>
+  <si>
+    <t>Logitech</t>
+  </si>
+  <si>
+    <t>1742LZ106AB8</t>
+  </si>
+  <si>
+    <t>Conectores Videoconferencia</t>
+  </si>
+  <si>
+    <t>Conectores</t>
+  </si>
+  <si>
+    <t>Estrella Bocinas Videoconferencia</t>
+  </si>
+  <si>
+    <t>886-000056</t>
+  </si>
+  <si>
+    <t>Estrella</t>
+  </si>
+  <si>
+    <t>Cisco UC Phone CP-8831</t>
+  </si>
+  <si>
+    <t>FCH19052AQZ</t>
+  </si>
+  <si>
+    <t>Telefono</t>
+  </si>
+  <si>
+    <t>FCH19052DJ7</t>
   </si>
   <si>
     <t>Docking Station</t>
   </si>
   <si>
-    <t>DELL</t>
-  </si>
-  <si>
     <t>WD19S</t>
   </si>
   <si>
     <t>F9WQSB3</t>
   </si>
   <si>
+    <t>Audifonos</t>
+  </si>
+  <si>
+    <t>Samsung</t>
+  </si>
+  <si>
+    <t>GIUHIUIÑGYI</t>
+  </si>
+  <si>
+    <t>5494UVTUFT</t>
+  </si>
+  <si>
     <t>Diadema</t>
   </si>
   <si>
@@ -122,441 +566,6 @@
     <t>2032CW</t>
   </si>
   <si>
-    <t>Camara Intrinsicamente segura</t>
-  </si>
-  <si>
-    <t>SONIM</t>
-  </si>
-  <si>
-    <t>XP7700</t>
-  </si>
-  <si>
-    <t>SWITCH SAN 1</t>
-  </si>
-  <si>
-    <t>POWERCONNECT 6224</t>
-  </si>
-  <si>
-    <t>D50KTS1</t>
-  </si>
-  <si>
-    <t>SWITCH SAN 2</t>
-  </si>
-  <si>
-    <t>J50KTS1</t>
-  </si>
-  <si>
-    <t>CALL MANAGER NUEVO</t>
-  </si>
-  <si>
-    <t>CISCO</t>
-  </si>
-  <si>
-    <t>UCS C220M3BE</t>
-  </si>
-  <si>
-    <t>220M3222</t>
-  </si>
-  <si>
-    <t>SERVIDOR 19</t>
-  </si>
-  <si>
-    <t>POWEREDGE R710</t>
-  </si>
-  <si>
-    <t>BRNFSL1</t>
-  </si>
-  <si>
-    <t>SERVIDOR 18</t>
-  </si>
-  <si>
-    <t>POWEREDGE R720</t>
-  </si>
-  <si>
-    <t>B3X7RV1</t>
-  </si>
-  <si>
-    <t>SAN</t>
-  </si>
-  <si>
-    <t>POWERVAULT MD3200i</t>
-  </si>
-  <si>
-    <t>48DT7V1</t>
-  </si>
-  <si>
-    <t>Monitor</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>UNIDAD DE CINTAS 19</t>
-  </si>
-  <si>
-    <t>POWER VAULT 114 X</t>
-  </si>
-  <si>
-    <t>YN106813H628</t>
-  </si>
-  <si>
-    <t>SERVIDOR 27</t>
-  </si>
-  <si>
-    <t>POWEREDGE 2950</t>
-  </si>
-  <si>
-    <t>DPBP6K1</t>
-  </si>
-  <si>
-    <t>SERVIDOR 29</t>
-  </si>
-  <si>
-    <t>POWEREDGE R320</t>
-  </si>
-  <si>
-    <t>D64MW12</t>
-  </si>
-  <si>
-    <t>UNIDAD DE CINTAS</t>
-  </si>
-  <si>
-    <t>POWER VAULT 124 T</t>
-  </si>
-  <si>
-    <t>8DDB6K1</t>
-  </si>
-  <si>
-    <t>Switch Linksys Cisco SD216</t>
-  </si>
-  <si>
-    <t>SD216</t>
-  </si>
-  <si>
-    <t>NVR</t>
-  </si>
-  <si>
-    <t>HIKVISION</t>
-  </si>
-  <si>
-    <t>DS-7616NI-K2/16P</t>
-  </si>
-  <si>
-    <t>L48074542</t>
-  </si>
-  <si>
-    <t>DVR HIKVISION</t>
-  </si>
-  <si>
-    <t>DS-7716NI-I4/16P</t>
-  </si>
-  <si>
-    <t>Mouse</t>
-  </si>
-  <si>
-    <t>3D Optical</t>
-  </si>
-  <si>
-    <t>Switch 8 Puertos</t>
-  </si>
-  <si>
-    <t>Planet</t>
-  </si>
-  <si>
-    <t>GSD-804P</t>
-  </si>
-  <si>
-    <t>A350106300034</t>
-  </si>
-  <si>
-    <t>Access PRO</t>
-  </si>
-  <si>
-    <t>AP233</t>
-  </si>
-  <si>
-    <t>AP234</t>
-  </si>
-  <si>
-    <t>Switch</t>
-  </si>
-  <si>
-    <t>CATALYST 2960-X SERIES</t>
-  </si>
-  <si>
-    <t>FCW1906B1MY</t>
-  </si>
-  <si>
-    <t>FCW1906B1LJ</t>
-  </si>
-  <si>
-    <t>FCW1906B1MM</t>
-  </si>
-  <si>
-    <t>CATALYST 2960-X SERIES POE+</t>
-  </si>
-  <si>
-    <t>FOC1710Y1FV</t>
-  </si>
-  <si>
-    <t>CATALYST 3560</t>
-  </si>
-  <si>
-    <t>CAT0948R334</t>
-  </si>
-  <si>
-    <t>F0C1503Z3QP</t>
-  </si>
-  <si>
-    <t>F0C1514X0EZ</t>
-  </si>
-  <si>
-    <t>FOC1903S1ME</t>
-  </si>
-  <si>
-    <t>Catalyst 3750X-24T-E</t>
-  </si>
-  <si>
-    <t>FD01816Z3AU</t>
-  </si>
-  <si>
-    <t>FIREWALL</t>
-  </si>
-  <si>
-    <t>FORTINET</t>
-  </si>
-  <si>
-    <t>FG100D3G14827870</t>
-  </si>
-  <si>
-    <t>FG100D3G14827806 MASTER</t>
-  </si>
-  <si>
-    <t>FG100D3G14827806</t>
-  </si>
-  <si>
-    <t>FG100D3G14827870 SLAVE</t>
-  </si>
-  <si>
-    <t>CALL MANAGER</t>
-  </si>
-  <si>
-    <t>FTX1328AHLG</t>
-  </si>
-  <si>
-    <t>ROUTER</t>
-  </si>
-  <si>
-    <t>CISCO 1900 SERIES</t>
-  </si>
-  <si>
-    <t>CFTX1614857Q</t>
-  </si>
-  <si>
-    <t>FTX174386AU</t>
-  </si>
-  <si>
-    <t>UPS</t>
-  </si>
-  <si>
-    <t>APC</t>
-  </si>
-  <si>
-    <t>APC Galaxy 3500</t>
-  </si>
-  <si>
-    <t>G35TF30KB4F</t>
-  </si>
-  <si>
-    <t>ACCESSPOINT</t>
-  </si>
-  <si>
-    <t>221E</t>
-  </si>
-  <si>
-    <t>FP221ETF22083298</t>
-  </si>
-  <si>
-    <t>FP221ETF22083291</t>
-  </si>
-  <si>
-    <t>FP221ETF22083300</t>
-  </si>
-  <si>
-    <t>FP221ETF22083299</t>
-  </si>
-  <si>
-    <t>Amplificador celular</t>
-  </si>
-  <si>
-    <t>EPCOM</t>
-  </si>
-  <si>
-    <t>G08W27160502</t>
-  </si>
-  <si>
-    <t>Camara Fija</t>
-  </si>
-  <si>
-    <t>DS-2CD2432F-I</t>
-  </si>
-  <si>
-    <t>I20140922CCWR480540694</t>
-  </si>
-  <si>
-    <t>DS-2CD1043G0-I</t>
-  </si>
-  <si>
-    <t>I20220824AAWRK47327687</t>
-  </si>
-  <si>
-    <t>Camara PTZ</t>
-  </si>
-  <si>
-    <t>DS-2DE4215IW-DE</t>
-  </si>
-  <si>
-    <t>DE20190506CCWRD16875921W</t>
-  </si>
-  <si>
-    <t>DS-2CD2232-I5</t>
-  </si>
-  <si>
-    <t>I520150207CCWR502802490</t>
-  </si>
-  <si>
-    <t>I20200824AAWRK47327674</t>
-  </si>
-  <si>
-    <t>DS-2DE7174-A</t>
-  </si>
-  <si>
-    <t>A20150122CCWR500502005</t>
-  </si>
-  <si>
-    <t>I520150207CCWR502802472</t>
-  </si>
-  <si>
-    <t>I520150207CCWR502802475</t>
-  </si>
-  <si>
-    <t>I520150207CCWR502802494</t>
-  </si>
-  <si>
-    <t>I520150207CCWR502802491</t>
-  </si>
-  <si>
-    <t>I520150207CCWR502802480</t>
-  </si>
-  <si>
-    <t>I520150207CCWR502802497</t>
-  </si>
-  <si>
-    <t>DS-2CD2422FWD-IW</t>
-  </si>
-  <si>
-    <t>IW20170808AAWR808998451</t>
-  </si>
-  <si>
-    <t>I20140922CCWR480540755</t>
-  </si>
-  <si>
-    <t>I20140922CCWR480540785</t>
-  </si>
-  <si>
-    <t>DS-2CD2T42WD-I5</t>
-  </si>
-  <si>
-    <t>I520160810BBWR633078836</t>
-  </si>
-  <si>
-    <t>I520160810BBWR633078735</t>
-  </si>
-  <si>
-    <t>I520160810BBWR633078506</t>
-  </si>
-  <si>
-    <t>A20150122CCWR500502035</t>
-  </si>
-  <si>
-    <t>KOBLENZ</t>
-  </si>
-  <si>
-    <t>4816 R</t>
-  </si>
-  <si>
-    <t>16-09-17766</t>
-  </si>
-  <si>
-    <t>Lector Biometrico</t>
-  </si>
-  <si>
-    <t>BioEntry W2</t>
-  </si>
-  <si>
-    <t>BEW2-0DP</t>
-  </si>
-  <si>
-    <t>Equipo de Videoconferencia</t>
-  </si>
-  <si>
-    <t>Chromebox</t>
-  </si>
-  <si>
-    <t>Asus</t>
-  </si>
-  <si>
-    <t>H6MSCX001323</t>
-  </si>
-  <si>
-    <t>Camara Videoconferencia</t>
-  </si>
-  <si>
-    <t>Logitech</t>
-  </si>
-  <si>
-    <t>1742LZ106AB8</t>
-  </si>
-  <si>
-    <t>Conectores Videoconferencia</t>
-  </si>
-  <si>
-    <t>Conectores</t>
-  </si>
-  <si>
-    <t>Estrella Bocinas Videoconferencia</t>
-  </si>
-  <si>
-    <t>886-000056</t>
-  </si>
-  <si>
-    <t>Estrella</t>
-  </si>
-  <si>
-    <t>Cisco UC Phone CP-8831</t>
-  </si>
-  <si>
-    <t>FCH19052AQZ</t>
-  </si>
-  <si>
-    <t>Telefono</t>
-  </si>
-  <si>
-    <t>FCH19052DJ7</t>
-  </si>
-  <si>
-    <t>Audifonos</t>
-  </si>
-  <si>
-    <t>Samsung</t>
-  </si>
-  <si>
-    <t>GIUHIUIÑGYI</t>
-  </si>
-  <si>
-    <t>5494UVTUFT</t>
-  </si>
-  <si>
     <t>Fijo</t>
   </si>
   <si>
@@ -590,6 +599,15 @@
     <t>B8310394</t>
   </si>
   <si>
+    <t xml:space="preserve">Adaptador de Puerto  </t>
+  </si>
+  <si>
+    <t>vybojnkm</t>
+  </si>
+  <si>
+    <t>VTYBUNJMKL</t>
+  </si>
+  <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
   </si>
   <si>
@@ -618,6 +636,12 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Cristobal Soto Escalante</t>
+  </si>
+  <si>
+    <t>Coordinador de Proyectos</t>
   </si>
 </sst>
 </file>
@@ -1449,88 +1473,74 @@
         <v>25</v>
       </c>
       <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
+      <c r="H19" s="38" t="s">
+        <v>26</v>
+      </c>
       <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="15">
-      <c r="A20" s="38">
-        <v>2</v>
-      </c>
-      <c r="B20" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="38" t="s">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
     </row>
     <row r="21" spans="1:10" customHeight="1" ht="15">
       <c r="A21" s="38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D21" s="38" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E21" s="38"/>
-      <c r="F21" s="38" t="s">
-        <v>33</v>
+      <c r="F21" s="38">
+        <v>12346987515</v>
       </c>
       <c r="G21" s="38"/>
       <c r="H21" s="38"/>
       <c r="I21" s="38"/>
     </row>
     <row r="22" spans="1:10" customHeight="1" ht="15">
-      <c r="A22" s="38">
-        <v>4</v>
-      </c>
-      <c r="B22" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38">
-        <v>14187000333707</v>
-      </c>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
     </row>
     <row r="23" spans="1:10" customHeight="1" ht="15">
       <c r="A23" s="38">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E23" s="38"/>
-      <c r="F23" s="38" t="s">
-        <v>39</v>
+      <c r="F23" s="38">
+        <v>14187000333707</v>
       </c>
       <c r="G23" s="38"/>
       <c r="H23" s="38"/>
@@ -1538,20 +1548,20 @@
     </row>
     <row r="24" spans="1:10" customHeight="1" ht="15">
       <c r="A24" s="38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E24" s="38"/>
       <c r="F24" s="38" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G24" s="38"/>
       <c r="H24" s="38"/>
@@ -1559,20 +1569,20 @@
     </row>
     <row r="25" spans="1:10" customHeight="1" ht="15">
       <c r="A25" s="38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E25" s="38"/>
       <c r="F25" s="38" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
@@ -1580,20 +1590,20 @@
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="15">
       <c r="A26" s="38">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E26" s="38"/>
       <c r="F26" s="38" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G26" s="38"/>
       <c r="H26" s="38"/>
@@ -1601,20 +1611,20 @@
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="15">
       <c r="A27" s="38">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D27" s="38" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E27" s="38"/>
       <c r="F27" s="38" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G27" s="38"/>
       <c r="H27" s="38"/>
@@ -1622,20 +1632,20 @@
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
       <c r="A28" s="38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E28" s="38"/>
       <c r="F28" s="38" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G28" s="38"/>
       <c r="H28" s="38"/>
@@ -1643,20 +1653,20 @@
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="15">
       <c r="A29" s="38">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E29" s="38"/>
       <c r="F29" s="38" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G29" s="38"/>
       <c r="H29" s="38"/>
@@ -1664,20 +1674,20 @@
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
       <c r="A30" s="38">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E30" s="38"/>
       <c r="F30" s="38" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G30" s="38"/>
       <c r="H30" s="38"/>
@@ -1685,20 +1695,20 @@
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="15">
       <c r="A31" s="38">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D31" s="38" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E31" s="38"/>
       <c r="F31" s="38" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G31" s="38"/>
       <c r="H31" s="38"/>
@@ -1706,20 +1716,20 @@
     </row>
     <row r="32" spans="1:10" customHeight="1" ht="15">
       <c r="A32" s="38">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D32" s="38" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E32" s="38"/>
       <c r="F32" s="38" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G32" s="38"/>
       <c r="H32" s="38"/>
@@ -1727,20 +1737,20 @@
     </row>
     <row r="33" spans="1:10" customHeight="1" ht="15">
       <c r="A33" s="38">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C33" s="38" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D33" s="38" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E33" s="38"/>
       <c r="F33" s="38" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G33" s="38"/>
       <c r="H33" s="38"/>
@@ -1748,20 +1758,20 @@
     </row>
     <row r="34" spans="1:10" customHeight="1" ht="15">
       <c r="A34" s="38">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D34" s="38" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E34" s="38"/>
       <c r="F34" s="38" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="G34" s="38"/>
       <c r="H34" s="38"/>
@@ -1769,20 +1779,20 @@
     </row>
     <row r="35" spans="1:10" customHeight="1" ht="15">
       <c r="A35" s="38">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C35" s="38" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="D35" s="38" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E35" s="38"/>
       <c r="F35" s="38" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="G35" s="38"/>
       <c r="H35" s="38"/>
@@ -1790,20 +1800,20 @@
     </row>
     <row r="36" spans="1:10" customHeight="1" ht="15">
       <c r="A36" s="38">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C36" s="38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D36" s="38" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E36" s="38"/>
-      <c r="F36" s="38">
-        <v>647235228</v>
+      <c r="F36" s="38" t="s">
+        <v>71</v>
       </c>
       <c r="G36" s="38"/>
       <c r="H36" s="38"/>
@@ -1811,20 +1821,20 @@
     </row>
     <row r="37" spans="1:10" customHeight="1" ht="15">
       <c r="A37" s="38">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C37" s="38" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D37" s="38" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="E37" s="38"/>
-      <c r="F37" s="38" t="s">
-        <v>56</v>
+      <c r="F37" s="38">
+        <v>647235228</v>
       </c>
       <c r="G37" s="38"/>
       <c r="H37" s="38"/>
@@ -1832,20 +1842,20 @@
     </row>
     <row r="38" spans="1:10" customHeight="1" ht="15">
       <c r="A38" s="38">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E38" s="38"/>
       <c r="F38" s="38" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G38" s="38"/>
       <c r="H38" s="38"/>
@@ -1853,20 +1863,20 @@
     </row>
     <row r="39" spans="1:10" customHeight="1" ht="15">
       <c r="A39" s="38">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="E39" s="38"/>
       <c r="F39" s="38" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="G39" s="38"/>
       <c r="H39" s="38"/>
@@ -1874,20 +1884,20 @@
     </row>
     <row r="40" spans="1:10" customHeight="1" ht="15">
       <c r="A40" s="38">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="E40" s="38"/>
       <c r="F40" s="38" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G40" s="38"/>
       <c r="H40" s="38"/>
@@ -1895,20 +1905,20 @@
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
       <c r="A41" s="38">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C41" s="38" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D41" s="38" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E41" s="38"/>
       <c r="F41" s="38" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G41" s="38"/>
       <c r="H41" s="38"/>
@@ -1916,20 +1926,20 @@
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
       <c r="A42" s="38">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C42" s="38" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="D42" s="38" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="E42" s="38"/>
       <c r="F42" s="38" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G42" s="38"/>
       <c r="H42" s="38"/>
@@ -1937,20 +1947,20 @@
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="38">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G43" s="38"/>
       <c r="H43" s="38"/>
@@ -1958,20 +1968,20 @@
     </row>
     <row r="44" spans="1:10" customHeight="1" ht="15">
       <c r="A44" s="38">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C44" s="38" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D44" s="38" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E44" s="38"/>
       <c r="F44" s="38" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G44" s="38"/>
       <c r="H44" s="38"/>
@@ -1979,20 +1989,20 @@
     </row>
     <row r="45" spans="1:10" customHeight="1" ht="15">
       <c r="A45" s="38">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E45" s="38"/>
       <c r="F45" s="38" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="G45" s="38"/>
       <c r="H45" s="38"/>
@@ -2000,20 +2010,20 @@
     </row>
     <row r="46" spans="1:10" customHeight="1" ht="15">
       <c r="A46" s="38">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E46" s="38"/>
       <c r="F46" s="38" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G46" s="38"/>
       <c r="H46" s="38"/>
@@ -2021,20 +2031,20 @@
     </row>
     <row r="47" spans="1:10" customHeight="1" ht="15">
       <c r="A47" s="38">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B47" s="38" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C47" s="38" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E47" s="38"/>
       <c r="F47" s="38" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G47" s="38"/>
       <c r="H47" s="38"/>
@@ -2042,20 +2052,20 @@
     </row>
     <row r="48" spans="1:10" customHeight="1" ht="15">
       <c r="A48" s="38">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B48" s="38" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C48" s="38" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D48" s="38" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E48" s="38"/>
       <c r="F48" s="38" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G48" s="38"/>
       <c r="H48" s="38"/>
@@ -2063,20 +2073,20 @@
     </row>
     <row r="49" spans="1:10" customHeight="1" ht="15">
       <c r="A49" s="38">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B49" s="38" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C49" s="38" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E49" s="38"/>
       <c r="F49" s="38" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G49" s="38"/>
       <c r="H49" s="38"/>
@@ -2084,20 +2094,20 @@
     </row>
     <row r="50" spans="1:10" customHeight="1" ht="15">
       <c r="A50" s="38">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B50" s="38" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C50" s="38" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D50" s="38" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="E50" s="38"/>
       <c r="F50" s="38" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G50" s="38"/>
       <c r="H50" s="38"/>
@@ -2105,20 +2115,20 @@
     </row>
     <row r="51" spans="1:10" customHeight="1" ht="15">
       <c r="A51" s="38">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B51" s="38" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="C51" s="38" t="s">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="D51" s="38" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E51" s="38"/>
       <c r="F51" s="38" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G51" s="38"/>
       <c r="H51" s="38"/>
@@ -2126,20 +2136,20 @@
     </row>
     <row r="52" spans="1:10" customHeight="1" ht="15">
       <c r="A52" s="38">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B52" s="38" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C52" s="38" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D52" s="38" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E52" s="38"/>
       <c r="F52" s="38" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="G52" s="38"/>
       <c r="H52" s="38"/>
@@ -2147,18 +2157,20 @@
     </row>
     <row r="53" spans="1:10" customHeight="1" ht="15">
       <c r="A53" s="38">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B53" s="38" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C53" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="D53" s="38"/>
+        <v>98</v>
+      </c>
+      <c r="D53" s="38" t="s">
+        <v>101</v>
+      </c>
       <c r="E53" s="38"/>
       <c r="F53" s="38" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G53" s="38"/>
       <c r="H53" s="38"/>
@@ -2166,20 +2178,18 @@
     </row>
     <row r="54" spans="1:10" customHeight="1" ht="15">
       <c r="A54" s="38">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B54" s="38" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C54" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="D54" s="38" t="s">
-        <v>109</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="D54" s="38"/>
       <c r="E54" s="38"/>
       <c r="F54" s="38" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="G54" s="38"/>
       <c r="H54" s="38"/>
@@ -2187,20 +2197,20 @@
     </row>
     <row r="55" spans="1:10" customHeight="1" ht="15">
       <c r="A55" s="38">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B55" s="38" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C55" s="38" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D55" s="38" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E55" s="38"/>
       <c r="F55" s="38" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G55" s="38"/>
       <c r="H55" s="38"/>
@@ -2208,20 +2218,20 @@
     </row>
     <row r="56" spans="1:10" customHeight="1" ht="15">
       <c r="A56" s="38">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B56" s="38" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C56" s="38" t="s">
-        <v>113</v>
+        <v>40</v>
       </c>
       <c r="D56" s="38" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E56" s="38"/>
       <c r="F56" s="38" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="G56" s="38"/>
       <c r="H56" s="38"/>
@@ -2229,20 +2239,20 @@
     </row>
     <row r="57" spans="1:10" customHeight="1" ht="15">
       <c r="A57" s="38">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B57" s="38" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C57" s="38" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D57" s="38" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E57" s="38"/>
       <c r="F57" s="38" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G57" s="38"/>
       <c r="H57" s="38"/>
@@ -2250,20 +2260,20 @@
     </row>
     <row r="58" spans="1:10" customHeight="1" ht="15">
       <c r="A58" s="38">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B58" s="38" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C58" s="38" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D58" s="38" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E58" s="38"/>
       <c r="F58" s="38" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G58" s="38"/>
       <c r="H58" s="38"/>
@@ -2271,20 +2281,20 @@
     </row>
     <row r="59" spans="1:10" customHeight="1" ht="15">
       <c r="A59" s="38">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B59" s="38" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C59" s="38" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D59" s="38" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E59" s="38"/>
       <c r="F59" s="38" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G59" s="38"/>
       <c r="H59" s="38"/>
@@ -2292,20 +2302,20 @@
     </row>
     <row r="60" spans="1:10" customHeight="1" ht="15">
       <c r="A60" s="38">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B60" s="38" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C60" s="38" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D60" s="38" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E60" s="38"/>
       <c r="F60" s="38" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G60" s="38"/>
       <c r="H60" s="38"/>
@@ -2313,20 +2323,20 @@
     </row>
     <row r="61" spans="1:10" customHeight="1" ht="15">
       <c r="A61" s="38">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B61" s="38" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C61" s="38" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="D61" s="38" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="E61" s="38"/>
       <c r="F61" s="38" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="G61" s="38"/>
       <c r="H61" s="38"/>
@@ -2334,20 +2344,20 @@
     </row>
     <row r="62" spans="1:10" customHeight="1" ht="15">
       <c r="A62" s="38">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B62" s="38" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C62" s="38" t="s">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="D62" s="38" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E62" s="38"/>
       <c r="F62" s="38" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="G62" s="38"/>
       <c r="H62" s="38"/>
@@ -2355,20 +2365,20 @@
     </row>
     <row r="63" spans="1:10" customHeight="1" ht="15">
       <c r="A63" s="38">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B63" s="38" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C63" s="38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D63" s="38" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E63" s="38"/>
       <c r="F63" s="38" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G63" s="38"/>
       <c r="H63" s="38"/>
@@ -2376,20 +2386,20 @@
     </row>
     <row r="64" spans="1:10" customHeight="1" ht="15">
       <c r="A64" s="38">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B64" s="38" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C64" s="38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D64" s="38" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E64" s="38"/>
       <c r="F64" s="38" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="G64" s="38"/>
       <c r="H64" s="38"/>
@@ -2397,20 +2407,20 @@
     </row>
     <row r="65" spans="1:10" customHeight="1" ht="15">
       <c r="A65" s="38">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B65" s="38" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C65" s="38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D65" s="38" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E65" s="38"/>
       <c r="F65" s="38" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="G65" s="38"/>
       <c r="H65" s="38"/>
@@ -2418,20 +2428,20 @@
     </row>
     <row r="66" spans="1:10" customHeight="1" ht="15">
       <c r="A66" s="38">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B66" s="38" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C66" s="38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D66" s="38" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E66" s="38"/>
       <c r="F66" s="38" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="G66" s="38"/>
       <c r="H66" s="38"/>
@@ -2439,20 +2449,20 @@
     </row>
     <row r="67" spans="1:10" customHeight="1" ht="15">
       <c r="A67" s="38">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B67" s="38" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C67" s="38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D67" s="38" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E67" s="38"/>
       <c r="F67" s="38" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G67" s="38"/>
       <c r="H67" s="38"/>
@@ -2460,20 +2470,20 @@
     </row>
     <row r="68" spans="1:10" customHeight="1" ht="15">
       <c r="A68" s="38">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B68" s="38" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C68" s="38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D68" s="38" t="s">
         <v>133</v>
       </c>
       <c r="E68" s="38"/>
       <c r="F68" s="38" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G68" s="38"/>
       <c r="H68" s="38"/>
@@ -2481,20 +2491,20 @@
     </row>
     <row r="69" spans="1:10" customHeight="1" ht="15">
       <c r="A69" s="38">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B69" s="38" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C69" s="38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D69" s="38" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E69" s="38"/>
       <c r="F69" s="38" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G69" s="38"/>
       <c r="H69" s="38"/>
@@ -2502,20 +2512,20 @@
     </row>
     <row r="70" spans="1:10" customHeight="1" ht="15">
       <c r="A70" s="38">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B70" s="38" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C70" s="38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D70" s="38" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E70" s="38"/>
       <c r="F70" s="38" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G70" s="38"/>
       <c r="H70" s="38"/>
@@ -2523,20 +2533,20 @@
     </row>
     <row r="71" spans="1:10" customHeight="1" ht="15">
       <c r="A71" s="38">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B71" s="38" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C71" s="38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D71" s="38" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E71" s="38"/>
       <c r="F71" s="38" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G71" s="38"/>
       <c r="H71" s="38"/>
@@ -2544,20 +2554,20 @@
     </row>
     <row r="72" spans="1:10" customHeight="1" ht="15">
       <c r="A72" s="38">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B72" s="38" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C72" s="38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D72" s="38" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E72" s="38"/>
       <c r="F72" s="38" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G72" s="38"/>
       <c r="H72" s="38"/>
@@ -2565,20 +2575,20 @@
     </row>
     <row r="73" spans="1:10" customHeight="1" ht="15">
       <c r="A73" s="38">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B73" s="38" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C73" s="38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D73" s="38" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E73" s="38"/>
       <c r="F73" s="38" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G73" s="38"/>
       <c r="H73" s="38"/>
@@ -2586,20 +2596,20 @@
     </row>
     <row r="74" spans="1:10" customHeight="1" ht="15">
       <c r="A74" s="38">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B74" s="38" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C74" s="38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D74" s="38" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="E74" s="38"/>
       <c r="F74" s="38" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G74" s="38"/>
       <c r="H74" s="38"/>
@@ -2607,20 +2617,20 @@
     </row>
     <row r="75" spans="1:10" customHeight="1" ht="15">
       <c r="A75" s="38">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B75" s="38" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C75" s="38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D75" s="38" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="E75" s="38"/>
       <c r="F75" s="38" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G75" s="38"/>
       <c r="H75" s="38"/>
@@ -2628,20 +2638,20 @@
     </row>
     <row r="76" spans="1:10" customHeight="1" ht="15">
       <c r="A76" s="38">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B76" s="38" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C76" s="38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D76" s="38" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E76" s="38"/>
       <c r="F76" s="38" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G76" s="38"/>
       <c r="H76" s="38"/>
@@ -2649,20 +2659,20 @@
     </row>
     <row r="77" spans="1:10" customHeight="1" ht="15">
       <c r="A77" s="38">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B77" s="38" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C77" s="38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D77" s="38" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="E77" s="38"/>
       <c r="F77" s="38" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="G77" s="38"/>
       <c r="H77" s="38"/>
@@ -2670,20 +2680,20 @@
     </row>
     <row r="78" spans="1:10" customHeight="1" ht="15">
       <c r="A78" s="38">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B78" s="38" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C78" s="38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D78" s="38" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E78" s="38"/>
       <c r="F78" s="38" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G78" s="38"/>
       <c r="H78" s="38"/>
@@ -2691,20 +2701,20 @@
     </row>
     <row r="79" spans="1:10" customHeight="1" ht="15">
       <c r="A79" s="38">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B79" s="38" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C79" s="38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D79" s="38" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E79" s="38"/>
       <c r="F79" s="38" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G79" s="38"/>
       <c r="H79" s="38"/>
@@ -2712,20 +2722,20 @@
     </row>
     <row r="80" spans="1:10" customHeight="1" ht="15">
       <c r="A80" s="38">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B80" s="38" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C80" s="38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D80" s="38" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E80" s="38"/>
       <c r="F80" s="38" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="G80" s="38"/>
       <c r="H80" s="38"/>
@@ -2733,20 +2743,20 @@
     </row>
     <row r="81" spans="1:10" customHeight="1" ht="15">
       <c r="A81" s="38">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B81" s="38" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="C81" s="38" t="s">
-        <v>153</v>
+        <v>69</v>
       </c>
       <c r="D81" s="38" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="E81" s="38"/>
       <c r="F81" s="38" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="G81" s="38"/>
       <c r="H81" s="38"/>
@@ -2754,20 +2764,20 @@
     </row>
     <row r="82" spans="1:10" customHeight="1" ht="15">
       <c r="A82" s="38">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B82" s="38" t="s">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="C82" s="38" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D82" s="38" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E82" s="38"/>
-      <c r="F82" s="38">
-        <v>544161389</v>
+      <c r="F82" s="38" t="s">
+        <v>152</v>
       </c>
       <c r="G82" s="38"/>
       <c r="H82" s="38"/>
@@ -2775,20 +2785,20 @@
     </row>
     <row r="83" spans="1:10" customHeight="1" ht="15">
       <c r="A83" s="38">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B83" s="38" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C83" s="38" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D83" s="38" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E83" s="38"/>
       <c r="F83" s="38">
-        <v>544161388</v>
+        <v>544161389</v>
       </c>
       <c r="G83" s="38"/>
       <c r="H83" s="38"/>
@@ -2796,20 +2806,20 @@
     </row>
     <row r="84" spans="1:10" customHeight="1" ht="15">
       <c r="A84" s="38">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B84" s="38" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C84" s="38" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D84" s="38" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E84" s="38"/>
-      <c r="F84" s="38" t="s">
-        <v>162</v>
+      <c r="F84" s="38">
+        <v>544161388</v>
       </c>
       <c r="G84" s="38"/>
       <c r="H84" s="38"/>
@@ -2817,20 +2827,20 @@
     </row>
     <row r="85" spans="1:10" customHeight="1" ht="15">
       <c r="A85" s="38">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B85" s="38" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C85" s="38" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D85" s="38" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="E85" s="38"/>
       <c r="F85" s="38" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G85" s="38"/>
       <c r="H85" s="38"/>
@@ -2838,20 +2848,20 @@
     </row>
     <row r="86" spans="1:10" customHeight="1" ht="15">
       <c r="A86" s="38">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B86" s="38" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C86" s="38" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D86" s="38" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E86" s="38"/>
       <c r="F86" s="38" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="G86" s="38"/>
       <c r="H86" s="38"/>
@@ -2859,20 +2869,20 @@
     </row>
     <row r="87" spans="1:10" customHeight="1" ht="15">
       <c r="A87" s="38">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B87" s="38" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C87" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D87" s="38" t="s">
-        <v>169</v>
+        <v>53</v>
       </c>
       <c r="E87" s="38"/>
       <c r="F87" s="38" t="s">
-        <v>165</v>
+        <v>53</v>
       </c>
       <c r="G87" s="38"/>
       <c r="H87" s="38"/>
@@ -2880,20 +2890,20 @@
     </row>
     <row r="88" spans="1:10" customHeight="1" ht="15">
       <c r="A88" s="38">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B88" s="38" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C88" s="38" t="s">
-        <v>43</v>
+        <v>160</v>
       </c>
       <c r="D88" s="38" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E88" s="38"/>
       <c r="F88" s="38" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="G88" s="38"/>
       <c r="H88" s="38"/>
@@ -2901,20 +2911,20 @@
     </row>
     <row r="89" spans="1:10" customHeight="1" ht="15">
       <c r="A89" s="38">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B89" s="38" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C89" s="38" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D89" s="38" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E89" s="38"/>
       <c r="F89" s="38" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="G89" s="38"/>
       <c r="H89" s="38"/>
@@ -2922,20 +2932,20 @@
     </row>
     <row r="90" spans="1:10" customHeight="1" ht="15">
       <c r="A90" s="38">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B90" s="38" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C90" s="38" t="s">
-        <v>176</v>
+        <v>40</v>
       </c>
       <c r="D90" s="38" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="E90" s="38"/>
       <c r="F90" s="38" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="G90" s="38"/>
       <c r="H90" s="38"/>
@@ -2943,20 +2953,20 @@
     </row>
     <row r="91" spans="1:10" customHeight="1" ht="15">
       <c r="A91" s="38">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B91" s="38" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C91" s="38" t="s">
-        <v>180</v>
+        <v>23</v>
       </c>
       <c r="D91" s="38" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="E91" s="38"/>
       <c r="F91" s="38" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="G91" s="38"/>
       <c r="H91" s="38"/>
@@ -2964,20 +2974,20 @@
     </row>
     <row r="92" spans="1:10" customHeight="1" ht="15">
       <c r="A92" s="38">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B92" s="38" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C92" s="38" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D92" s="38" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E92" s="38"/>
       <c r="F92" s="38" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="G92" s="38"/>
       <c r="H92" s="38"/>
@@ -2985,20 +2995,20 @@
     </row>
     <row r="93" spans="1:10" customHeight="1" ht="15">
       <c r="A93" s="38">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B93" s="38" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C93" s="38" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D93" s="38" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="E93" s="38"/>
       <c r="F93" s="38" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G93" s="38"/>
       <c r="H93" s="38"/>
@@ -3006,20 +3016,20 @@
     </row>
     <row r="94" spans="1:10" customHeight="1" ht="15">
       <c r="A94" s="38">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B94" s="38" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C94" s="38" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D94" s="38" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E94" s="38"/>
       <c r="F94" s="38" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G94" s="38"/>
       <c r="H94" s="38"/>
@@ -3027,127 +3037,158 @@
     </row>
     <row r="95" spans="1:10" customHeight="1" ht="15">
       <c r="A95" s="38">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B95" s="38" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C95" s="38" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D95" s="38" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E95" s="38"/>
       <c r="F95" s="38" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G95" s="38"/>
       <c r="H95" s="38"/>
       <c r="I95" s="38"/>
     </row>
     <row r="96" spans="1:10" customHeight="1" ht="15">
-      <c r="A96" s="16"/>
-      <c r="B96" s="16"/>
-      <c r="C96" s="16"/>
-      <c r="D96" s="16"/>
-      <c r="E96" s="16"/>
-      <c r="F96" s="23"/>
-      <c r="G96" s="23"/>
-      <c r="H96" s="24"/>
-      <c r="I96" s="24"/>
+      <c r="A96" s="38">
+        <v>76</v>
+      </c>
+      <c r="B96" s="38" t="s">
+        <v>187</v>
+      </c>
+      <c r="C96" s="38" t="s">
+        <v>188</v>
+      </c>
+      <c r="D96" s="38" t="s">
+        <v>189</v>
+      </c>
+      <c r="E96" s="38"/>
+      <c r="F96" s="38" t="s">
+        <v>190</v>
+      </c>
+      <c r="G96" s="38"/>
+      <c r="H96" s="38"/>
+      <c r="I96" s="38"/>
     </row>
     <row r="97" spans="1:10" customHeight="1" ht="15">
-      <c r="A97" s="25"/>
-      <c r="B97" s="25"/>
-      <c r="C97" s="25"/>
-      <c r="D97" s="25"/>
-      <c r="E97" s="25"/>
-      <c r="F97" s="25"/>
-      <c r="G97" s="25"/>
-      <c r="H97" s="25"/>
-      <c r="I97" s="25"/>
+      <c r="A97" s="38">
+        <v>77</v>
+      </c>
+      <c r="B97" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="C97" s="38" t="s">
+        <v>183</v>
+      </c>
+      <c r="D97" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="E97" s="38"/>
+      <c r="F97" s="38" t="s">
+        <v>191</v>
+      </c>
+      <c r="G97" s="38"/>
+      <c r="H97" s="38"/>
+      <c r="I97" s="38"/>
     </row>
     <row r="98" spans="1:10" customHeight="1" ht="15">
-      <c r="A98" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="B98" s="26"/>
-      <c r="C98" s="26"/>
-      <c r="D98" s="26"/>
-      <c r="E98" s="26"/>
-      <c r="F98" s="26"/>
-      <c r="G98" s="26"/>
-      <c r="H98" s="26"/>
-      <c r="I98" s="26"/>
+      <c r="A98" s="38">
+        <v>78</v>
+      </c>
+      <c r="B98" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="C98" s="38" t="s">
+        <v>183</v>
+      </c>
+      <c r="D98" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="E98" s="38"/>
+      <c r="F98" s="38" t="s">
+        <v>192</v>
+      </c>
+      <c r="G98" s="38"/>
+      <c r="H98" s="38"/>
+      <c r="I98" s="38"/>
     </row>
     <row r="99" spans="1:10" customHeight="1" ht="15">
-      <c r="A99" s="27"/>
-      <c r="B99" s="27"/>
-      <c r="C99" s="27"/>
-      <c r="D99" s="27"/>
-      <c r="E99" s="27"/>
-      <c r="F99" s="27"/>
-      <c r="G99" s="27"/>
-      <c r="H99" s="27"/>
-      <c r="I99" s="27"/>
+      <c r="A99" s="38">
+        <v>79</v>
+      </c>
+      <c r="B99" s="38" t="s">
+        <v>193</v>
+      </c>
+      <c r="C99" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="D99" s="38" t="s">
+        <v>194</v>
+      </c>
+      <c r="E99" s="38"/>
+      <c r="F99" s="38" t="s">
+        <v>195</v>
+      </c>
+      <c r="G99" s="38"/>
+      <c r="H99" s="38"/>
+      <c r="I99" s="38"/>
     </row>
     <row r="100" spans="1:10" customHeight="1" ht="15">
-      <c r="A100" s="28" t="s">
-        <v>191</v>
-      </c>
-      <c r="B100" s="28"/>
-      <c r="C100" s="28"/>
-      <c r="D100" s="28"/>
-      <c r="E100" s="28"/>
-      <c r="F100" s="28"/>
-      <c r="G100" s="28"/>
-      <c r="H100" s="28"/>
-      <c r="I100" s="28"/>
+      <c r="A100" s="16"/>
+      <c r="B100" s="16"/>
+      <c r="C100" s="16"/>
+      <c r="D100" s="16"/>
+      <c r="E100" s="16"/>
+      <c r="F100" s="23"/>
+      <c r="G100" s="23"/>
+      <c r="H100" s="24"/>
+      <c r="I100" s="24"/>
     </row>
     <row r="101" spans="1:10" customHeight="1" ht="15">
-      <c r="A101" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="B101" s="28"/>
-      <c r="C101" s="28"/>
-      <c r="D101" s="28"/>
-      <c r="E101" s="28"/>
-      <c r="F101" s="28"/>
-      <c r="G101" s="28"/>
-      <c r="H101" s="28"/>
-      <c r="I101" s="28"/>
+      <c r="A101" s="25"/>
+      <c r="B101" s="25"/>
+      <c r="C101" s="25"/>
+      <c r="D101" s="25"/>
+      <c r="E101" s="25"/>
+      <c r="F101" s="25"/>
+      <c r="G101" s="25"/>
+      <c r="H101" s="25"/>
+      <c r="I101" s="25"/>
     </row>
     <row r="102" spans="1:10" customHeight="1" ht="15">
-      <c r="A102" s="28" t="s">
-        <v>193</v>
-      </c>
-      <c r="B102" s="28"/>
-      <c r="C102" s="28"/>
-      <c r="D102" s="28"/>
-      <c r="E102" s="28"/>
-      <c r="F102" s="28"/>
-      <c r="G102" s="28"/>
-      <c r="H102" s="28"/>
-      <c r="I102" s="28"/>
-    </row>
-    <row r="103" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A103" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="B103" s="29"/>
-      <c r="C103" s="29"/>
-      <c r="D103" s="29"/>
-      <c r="E103" s="29"/>
-      <c r="F103" s="29"/>
-      <c r="G103" s="29"/>
-      <c r="H103" s="29"/>
-      <c r="I103" s="29"/>
-      <c r="J103" s="2"/>
-    </row>
-    <row r="104" spans="1:10" customHeight="1" ht="27">
+      <c r="A102" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="B102" s="26"/>
+      <c r="C102" s="26"/>
+      <c r="D102" s="26"/>
+      <c r="E102" s="26"/>
+      <c r="F102" s="26"/>
+      <c r="G102" s="26"/>
+      <c r="H102" s="26"/>
+      <c r="I102" s="26"/>
+    </row>
+    <row r="103" spans="1:10" customHeight="1" ht="15">
+      <c r="A103" s="27"/>
+      <c r="B103" s="27"/>
+      <c r="C103" s="27"/>
+      <c r="D103" s="27"/>
+      <c r="E103" s="27"/>
+      <c r="F103" s="27"/>
+      <c r="G103" s="27"/>
+      <c r="H103" s="27"/>
+      <c r="I103" s="27"/>
+    </row>
+    <row r="104" spans="1:10" customHeight="1" ht="15">
       <c r="A104" s="28" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B104" s="28"/>
       <c r="C104" s="28"/>
@@ -3159,143 +3200,142 @@
       <c r="I104" s="28"/>
     </row>
     <row r="105" spans="1:10" customHeight="1" ht="15">
-      <c r="A105" s="30"/>
-      <c r="B105" s="30"/>
-      <c r="C105" s="30"/>
-      <c r="D105" s="30"/>
-      <c r="E105" s="30"/>
-      <c r="F105" s="30"/>
-      <c r="G105" s="30"/>
-      <c r="H105" s="30"/>
-      <c r="I105" s="30"/>
-    </row>
-    <row r="106" spans="1:10" customHeight="1" ht="39">
-      <c r="A106" s="31" t="s">
-        <v>196</v>
-      </c>
-      <c r="B106" s="31"/>
-      <c r="C106" s="31"/>
-      <c r="D106" s="31"/>
-      <c r="E106" s="31"/>
-      <c r="F106" s="31"/>
-      <c r="G106" s="31"/>
-      <c r="H106" s="31"/>
-      <c r="I106" s="31"/>
-    </row>
-    <row r="107" spans="1:10" customHeight="1" ht="15">
-      <c r="A107" s="32"/>
-      <c r="B107" s="32"/>
-      <c r="C107" s="32"/>
-      <c r="D107" s="32"/>
-      <c r="E107" s="2"/>
-      <c r="F107" s="2"/>
-      <c r="G107" s="33"/>
-      <c r="H107" s="33"/>
-      <c r="I107" s="33"/>
-    </row>
-    <row r="108" spans="1:10" customHeight="1" ht="15">
-      <c r="A108" s="2"/>
-      <c r="B108" s="32"/>
-      <c r="C108" s="32"/>
-      <c r="D108" s="32"/>
-      <c r="E108" s="2"/>
-      <c r="F108" s="2"/>
-      <c r="G108" s="2"/>
-      <c r="H108" s="33"/>
-      <c r="I108" s="33"/>
+      <c r="A105" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="B105" s="28"/>
+      <c r="C105" s="28"/>
+      <c r="D105" s="28"/>
+      <c r="E105" s="28"/>
+      <c r="F105" s="28"/>
+      <c r="G105" s="28"/>
+      <c r="H105" s="28"/>
+      <c r="I105" s="28"/>
+    </row>
+    <row r="106" spans="1:10" customHeight="1" ht="15">
+      <c r="A106" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="B106" s="28"/>
+      <c r="C106" s="28"/>
+      <c r="D106" s="28"/>
+      <c r="E106" s="28"/>
+      <c r="F106" s="28"/>
+      <c r="G106" s="28"/>
+      <c r="H106" s="28"/>
+      <c r="I106" s="28"/>
+    </row>
+    <row r="107" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A107" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="B107" s="29"/>
+      <c r="C107" s="29"/>
+      <c r="D107" s="29"/>
+      <c r="E107" s="29"/>
+      <c r="F107" s="29"/>
+      <c r="G107" s="29"/>
+      <c r="H107" s="29"/>
+      <c r="I107" s="29"/>
+      <c r="J107" s="2"/>
+    </row>
+    <row r="108" spans="1:10" customHeight="1" ht="27">
+      <c r="A108" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="B108" s="28"/>
+      <c r="C108" s="28"/>
+      <c r="D108" s="28"/>
+      <c r="E108" s="28"/>
+      <c r="F108" s="28"/>
+      <c r="G108" s="28"/>
+      <c r="H108" s="28"/>
+      <c r="I108" s="28"/>
     </row>
     <row r="109" spans="1:10" customHeight="1" ht="15">
-      <c r="A109" s="32"/>
-      <c r="B109" s="34" t="s">
-        <v>197</v>
-      </c>
-      <c r="C109" s="34"/>
-      <c r="D109" s="34"/>
-      <c r="E109" s="2"/>
-      <c r="F109" s="2"/>
-      <c r="G109" s="35" t="s">
-        <v>198</v>
-      </c>
-      <c r="H109" s="35"/>
-      <c r="I109" s="35"/>
-    </row>
-    <row r="110" spans="1:10" customHeight="1" ht="15">
-      <c r="A110" s="2"/>
-      <c r="B110" s="2"/>
-      <c r="C110" s="2"/>
-      <c r="D110" s="36" t="s">
-        <v>199</v>
-      </c>
-      <c r="E110" s="2"/>
-      <c r="F110" s="2"/>
-      <c r="G110" s="2"/>
-      <c r="H110" s="2"/>
-      <c r="I110" s="2"/>
+      <c r="A109" s="30"/>
+      <c r="B109" s="30"/>
+      <c r="C109" s="30"/>
+      <c r="D109" s="30"/>
+      <c r="E109" s="30"/>
+      <c r="F109" s="30"/>
+      <c r="G109" s="30"/>
+      <c r="H109" s="30"/>
+      <c r="I109" s="30"/>
+    </row>
+    <row r="110" spans="1:10" customHeight="1" ht="39">
+      <c r="A110" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="B110" s="31"/>
+      <c r="C110" s="31"/>
+      <c r="D110" s="31"/>
+      <c r="E110" s="31"/>
+      <c r="F110" s="31"/>
+      <c r="G110" s="31"/>
+      <c r="H110" s="31"/>
+      <c r="I110" s="31"/>
     </row>
     <row r="111" spans="1:10" customHeight="1" ht="15">
-      <c r="A111" s="2"/>
-      <c r="B111" s="37"/>
-      <c r="C111" s="37"/>
-      <c r="D111" s="37"/>
+      <c r="A111" s="32"/>
+      <c r="B111" s="32"/>
+      <c r="C111" s="32"/>
+      <c r="D111" s="32"/>
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
-      <c r="G111" s="37"/>
-      <c r="H111" s="37"/>
-      <c r="I111" s="37"/>
+      <c r="G111" s="33"/>
+      <c r="H111" s="33"/>
+      <c r="I111" s="33"/>
     </row>
     <row r="112" spans="1:10" customHeight="1" ht="15">
       <c r="A112" s="2"/>
-      <c r="B112" s="2"/>
-      <c r="C112" s="2"/>
-      <c r="D112" s="2"/>
+      <c r="B112" s="32"/>
+      <c r="C112" s="32"/>
+      <c r="D112" s="32"/>
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
-      <c r="H112" s="2"/>
-      <c r="I112" s="2"/>
+      <c r="H112" s="33"/>
+      <c r="I112" s="33"/>
     </row>
     <row r="113" spans="1:10" customHeight="1" ht="15">
-      <c r="A113" s="2"/>
+      <c r="A113" s="32"/>
       <c r="B113" s="34" t="s">
-        <v>8</v>
+        <v>203</v>
       </c>
       <c r="C113" s="34"/>
       <c r="D113" s="34"/>
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
-      <c r="G113" s="34" t="str">
-        <f>C10</f>
-        <v>Alejandro Cancino Arguello</v>
-      </c>
-      <c r="H113" s="34"/>
-      <c r="I113" s="34"/>
+      <c r="G113" s="35" t="s">
+        <v>204</v>
+      </c>
+      <c r="H113" s="35"/>
+      <c r="I113" s="35"/>
     </row>
     <row r="114" spans="1:10" customHeight="1" ht="15">
       <c r="A114" s="2"/>
-      <c r="B114" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C114" s="34"/>
-      <c r="D114" s="34"/>
+      <c r="B114" s="2"/>
+      <c r="C114" s="2"/>
+      <c r="D114" s="36" t="s">
+        <v>205</v>
+      </c>
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
-      <c r="G114" s="34" t="str">
-        <f>C12</f>
-        <v>Coordinador de TI</v>
-      </c>
-      <c r="H114" s="34"/>
-      <c r="I114" s="34"/>
+      <c r="G114" s="2"/>
+      <c r="H114" s="2"/>
+      <c r="I114" s="2"/>
     </row>
     <row r="115" spans="1:10" customHeight="1" ht="15">
       <c r="A115" s="2"/>
-      <c r="B115" s="2"/>
-      <c r="C115" s="2"/>
-      <c r="D115" s="2"/>
+      <c r="B115" s="37"/>
+      <c r="C115" s="37"/>
+      <c r="D115" s="37"/>
       <c r="E115" s="2"/>
       <c r="F115" s="2"/>
-      <c r="G115" s="32"/>
-      <c r="H115" s="32"/>
-      <c r="I115" s="32"/>
+      <c r="G115" s="37"/>
+      <c r="H115" s="37"/>
+      <c r="I115" s="37"/>
     </row>
     <row r="116" spans="1:10" customHeight="1" ht="15">
       <c r="A116" s="2"/>
@@ -3309,15 +3349,69 @@
       <c r="I116" s="2"/>
     </row>
     <row r="117" spans="1:10" customHeight="1" ht="15">
-      <c r="A117" s="32"/>
-      <c r="B117" s="32"/>
-      <c r="C117" s="32"/>
-      <c r="D117" s="32"/>
+      <c r="A117" s="2"/>
+      <c r="B117" s="34" t="s">
+        <v>206</v>
+      </c>
+      <c r="C117" s="34"/>
+      <c r="D117" s="34"/>
       <c r="E117" s="2"/>
       <c r="F117" s="2"/>
-      <c r="G117" s="2"/>
-      <c r="H117" s="2"/>
-      <c r="I117" s="2"/>
+      <c r="G117" s="34" t="str">
+        <f>C10</f>
+        <v>Alejandro Cancino Arguello</v>
+      </c>
+      <c r="H117" s="34"/>
+      <c r="I117" s="34"/>
+    </row>
+    <row r="118" spans="1:10" customHeight="1" ht="15">
+      <c r="A118" s="2"/>
+      <c r="B118" s="34" t="s">
+        <v>207</v>
+      </c>
+      <c r="C118" s="34"/>
+      <c r="D118" s="34"/>
+      <c r="E118" s="2"/>
+      <c r="F118" s="2"/>
+      <c r="G118" s="34" t="str">
+        <f>C12</f>
+        <v>Coordinador de TI</v>
+      </c>
+      <c r="H118" s="34"/>
+      <c r="I118" s="34"/>
+    </row>
+    <row r="119" spans="1:10" customHeight="1" ht="15">
+      <c r="A119" s="2"/>
+      <c r="B119" s="2"/>
+      <c r="C119" s="2"/>
+      <c r="D119" s="2"/>
+      <c r="E119" s="2"/>
+      <c r="F119" s="2"/>
+      <c r="G119" s="32"/>
+      <c r="H119" s="32"/>
+      <c r="I119" s="32"/>
+    </row>
+    <row r="120" spans="1:10" customHeight="1" ht="15">
+      <c r="A120" s="2"/>
+      <c r="B120" s="2"/>
+      <c r="C120" s="2"/>
+      <c r="D120" s="2"/>
+      <c r="E120" s="2"/>
+      <c r="F120" s="2"/>
+      <c r="G120" s="2"/>
+      <c r="H120" s="2"/>
+      <c r="I120" s="2"/>
+    </row>
+    <row r="121" spans="1:10" customHeight="1" ht="15">
+      <c r="A121" s="32"/>
+      <c r="B121" s="32"/>
+      <c r="C121" s="32"/>
+      <c r="D121" s="32"/>
+      <c r="E121" s="2"/>
+      <c r="F121" s="2"/>
+      <c r="G121" s="2"/>
+      <c r="H121" s="2"/>
+      <c r="I121" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -3336,23 +3430,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D96:E96"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="H96:I96"/>
-    <mergeCell ref="A98:I98"/>
-    <mergeCell ref="A100:I100"/>
-    <mergeCell ref="A101:I101"/>
+    <mergeCell ref="D100:E100"/>
+    <mergeCell ref="F100:G100"/>
+    <mergeCell ref="H100:I100"/>
     <mergeCell ref="A102:I102"/>
-    <mergeCell ref="A103:I103"/>
     <mergeCell ref="A104:I104"/>
     <mergeCell ref="A105:I105"/>
     <mergeCell ref="A106:I106"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="G109:I109"/>
+    <mergeCell ref="A107:I107"/>
+    <mergeCell ref="A108:I108"/>
+    <mergeCell ref="A109:I109"/>
+    <mergeCell ref="A110:I110"/>
     <mergeCell ref="B113:D113"/>
     <mergeCell ref="G113:I113"/>
-    <mergeCell ref="B114:D114"/>
-    <mergeCell ref="G114:I114"/>
+    <mergeCell ref="B117:D117"/>
+    <mergeCell ref="G117:I117"/>
+    <mergeCell ref="B118:D118"/>
+    <mergeCell ref="G118:I118"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -3584,7 +3678,19 @@
     <mergeCell ref="D95:E95"/>
     <mergeCell ref="F95:G95"/>
     <mergeCell ref="H95:I95"/>
-    <mergeCell ref="H19:I95"/>
+    <mergeCell ref="D96:E96"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="H96:I96"/>
+    <mergeCell ref="D97:E97"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="H97:I97"/>
+    <mergeCell ref="D98:E98"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="H98:I98"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:G99"/>
+    <mergeCell ref="H99:I99"/>
+    <mergeCell ref="H19:I99"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Alejandro_Cancino_Arguello.xlsx
+++ b/database/controller_excel/Resguardo_Alejandro_Cancino_Arguello.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="185">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,589 +41,535 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>25/06/2025</t>
+    <t>01/07/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
+    <t>Región:</t>
+  </si>
+  <si>
+    <t>Norte</t>
+  </si>
+  <si>
+    <t>Ubicación:</t>
+  </si>
+  <si>
+    <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
+  </si>
+  <si>
+    <t>ITEM</t>
+  </si>
+  <si>
+    <t>TIPO</t>
+  </si>
+  <si>
+    <t>MARCA</t>
+  </si>
+  <si>
+    <t>MODELO</t>
+  </si>
+  <si>
+    <t>NUMERO DE SERIE</t>
+  </si>
+  <si>
+    <t>OBSERVACIONES</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>Latitude 5520</t>
+  </si>
+  <si>
+    <t>C3Y9FG3</t>
+  </si>
+  <si>
+    <t>DVZ-TP-TI-00027</t>
+  </si>
+  <si>
+    <t>Diadema</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>108DB1</t>
+  </si>
+  <si>
+    <t>2032CW</t>
+  </si>
+  <si>
+    <t>Camara Intrinsicamente segura</t>
+  </si>
+  <si>
+    <t>SONIM</t>
+  </si>
+  <si>
+    <t>XP7700</t>
+  </si>
+  <si>
+    <t>SWITCH SAN 1</t>
+  </si>
+  <si>
+    <t>POWERCONNECT 6224</t>
+  </si>
+  <si>
+    <t>D50KTS1</t>
+  </si>
+  <si>
+    <t>SWITCH SAN 2</t>
+  </si>
+  <si>
+    <t>J50KTS1</t>
+  </si>
+  <si>
+    <t>CALL MANAGER NUEVO</t>
+  </si>
+  <si>
+    <t>CISCO</t>
+  </si>
+  <si>
+    <t>UCS C220M3BE</t>
+  </si>
+  <si>
+    <t>220M3222</t>
+  </si>
+  <si>
+    <t>SERVIDOR 19</t>
+  </si>
+  <si>
+    <t>POWEREDGE R710</t>
+  </si>
+  <si>
+    <t>BRNFSL1</t>
+  </si>
+  <si>
+    <t>SERVIDOR 18</t>
+  </si>
+  <si>
+    <t>POWEREDGE R720</t>
+  </si>
+  <si>
+    <t>B3X7RV1</t>
+  </si>
+  <si>
+    <t>SAN</t>
+  </si>
+  <si>
+    <t>POWERVAULT MD3200i</t>
+  </si>
+  <si>
+    <t>48DT7V1</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>UNIDAD DE CINTAS 19</t>
+  </si>
+  <si>
+    <t>POWER VAULT 114 X</t>
+  </si>
+  <si>
+    <t>YN106813H628</t>
+  </si>
+  <si>
+    <t>SERVIDOR 27</t>
+  </si>
+  <si>
+    <t>POWEREDGE 2950</t>
+  </si>
+  <si>
+    <t>DPBP6K1</t>
+  </si>
+  <si>
+    <t>SERVIDOR 29</t>
+  </si>
+  <si>
+    <t>POWEREDGE R320</t>
+  </si>
+  <si>
+    <t>D64MW12</t>
+  </si>
+  <si>
+    <t>UNIDAD DE CINTAS</t>
+  </si>
+  <si>
+    <t>POWER VAULT 124 T</t>
+  </si>
+  <si>
+    <t>8DDB6K1</t>
+  </si>
+  <si>
+    <t>Switch Linksys Cisco SD216</t>
+  </si>
+  <si>
+    <t>SD216</t>
+  </si>
+  <si>
+    <t>NVR</t>
+  </si>
+  <si>
+    <t>HIKVISION</t>
+  </si>
+  <si>
+    <t>DS-7616NI-K2/16P</t>
+  </si>
+  <si>
+    <t>L48074542</t>
+  </si>
+  <si>
+    <t>DVR HIKVISION</t>
+  </si>
+  <si>
+    <t>DS-7716NI-I4/16P</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>3D Optical</t>
+  </si>
+  <si>
+    <t>Switch 8 Puertos</t>
+  </si>
+  <si>
+    <t>Planet</t>
+  </si>
+  <si>
+    <t>GSD-804P</t>
+  </si>
+  <si>
+    <t>A350106300034</t>
+  </si>
+  <si>
+    <t>Access PRO</t>
+  </si>
+  <si>
+    <t>AP233</t>
+  </si>
+  <si>
+    <t>AP234</t>
+  </si>
+  <si>
+    <t>Switch</t>
+  </si>
+  <si>
+    <t>CATALYST 2960-X SERIES</t>
+  </si>
+  <si>
+    <t>FCW1906B1MY</t>
+  </si>
+  <si>
+    <t>FCW1906B1LJ</t>
+  </si>
+  <si>
+    <t>FCW1906B1MM</t>
+  </si>
+  <si>
+    <t>CATALYST 2960-X SERIES POE+</t>
+  </si>
+  <si>
+    <t>FOC1710Y1FV</t>
+  </si>
+  <si>
+    <t>CATALYST 3560</t>
+  </si>
+  <si>
+    <t>CAT0948R334</t>
+  </si>
+  <si>
+    <t>F0C1503Z3QP</t>
+  </si>
+  <si>
+    <t>F0C1514X0EZ</t>
+  </si>
+  <si>
+    <t>FOC1903S1ME</t>
+  </si>
+  <si>
+    <t>Catalyst 3750X-24T-E</t>
+  </si>
+  <si>
+    <t>FD01816Z3AU</t>
+  </si>
+  <si>
+    <t>FIREWALL</t>
+  </si>
+  <si>
+    <t>FORTINET</t>
+  </si>
+  <si>
+    <t>FG100D3G14827870</t>
+  </si>
+  <si>
+    <t>FG100D3G14827806 MASTER</t>
+  </si>
+  <si>
+    <t>FG100D3G14827806</t>
+  </si>
+  <si>
+    <t>FG100D3G14827870 SLAVE</t>
+  </si>
+  <si>
+    <t>CALL MANAGER</t>
+  </si>
+  <si>
+    <t>FTX1328AHLG</t>
+  </si>
+  <si>
+    <t>ROUTER</t>
+  </si>
+  <si>
+    <t>CISCO 1900 SERIES</t>
+  </si>
+  <si>
+    <t>CFTX1614857Q</t>
+  </si>
+  <si>
+    <t>FTX174386AU</t>
+  </si>
+  <si>
+    <t>UPS</t>
+  </si>
+  <si>
+    <t>APC</t>
+  </si>
+  <si>
+    <t>APC Galaxy 3500</t>
+  </si>
+  <si>
+    <t>G35TF30KB4F</t>
+  </si>
+  <si>
+    <t>ACCESSPOINT</t>
+  </si>
+  <si>
+    <t>221E</t>
+  </si>
+  <si>
+    <t>FP221ETF22083298</t>
+  </si>
+  <si>
+    <t>FP221ETF22083291</t>
+  </si>
+  <si>
+    <t>FP221ETF22083300</t>
+  </si>
+  <si>
+    <t>FP221ETF22083299</t>
+  </si>
+  <si>
+    <t>Amplificador celular</t>
+  </si>
+  <si>
+    <t>EPCOM</t>
+  </si>
+  <si>
+    <t>G08W27160502</t>
+  </si>
+  <si>
+    <t>Camara Fija</t>
+  </si>
+  <si>
+    <t>DS-2CD2432F-I</t>
+  </si>
+  <si>
+    <t>I20140922CCWR480540694</t>
+  </si>
+  <si>
+    <t>DS-2CD1043G0-I</t>
+  </si>
+  <si>
+    <t>I20220824AAWRK47327687</t>
+  </si>
+  <si>
+    <t>Camara PTZ</t>
+  </si>
+  <si>
+    <t>DS-2DE4215IW-DE</t>
+  </si>
+  <si>
+    <t>DE20190506CCWRD16875921W</t>
+  </si>
+  <si>
+    <t>DS-2CD2232-I5</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802490</t>
+  </si>
+  <si>
+    <t>I20200824AAWRK47327674</t>
+  </si>
+  <si>
+    <t>DS-2DE7174-A</t>
+  </si>
+  <si>
+    <t>A20150122CCWR500502005</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802472</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802475</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802494</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802491</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802480</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802497</t>
+  </si>
+  <si>
+    <t>Docking Station</t>
+  </si>
+  <si>
+    <t>WD19S</t>
+  </si>
+  <si>
+    <t>F9WQSB3</t>
+  </si>
+  <si>
+    <t>I20140922CCWR480540755</t>
+  </si>
+  <si>
+    <t>I20140922CCWR480540785</t>
+  </si>
+  <si>
+    <t>DS-2CD2T42WD-I5</t>
+  </si>
+  <si>
+    <t>I520160810BBWR633078836</t>
+  </si>
+  <si>
+    <t>I520160810BBWR633078735</t>
+  </si>
+  <si>
+    <t>I520160810BBWR633078506</t>
+  </si>
+  <si>
+    <t>A20150122CCWR500502035</t>
+  </si>
+  <si>
+    <t>KOBLENZ</t>
+  </si>
+  <si>
+    <t>4816 R</t>
+  </si>
+  <si>
+    <t>16-09-17766</t>
+  </si>
+  <si>
+    <t>DS-2CD2422FWD-IW</t>
+  </si>
+  <si>
+    <t>IW20170808AAWR808998451</t>
+  </si>
+  <si>
+    <t>Lector Biometrico</t>
+  </si>
+  <si>
+    <t>BioEntry W2</t>
+  </si>
+  <si>
+    <t>BEW2-0DP</t>
+  </si>
+  <si>
+    <t>Equipo de Videoconferencia</t>
+  </si>
+  <si>
+    <t>Chromebox</t>
+  </si>
+  <si>
+    <t>Asus</t>
+  </si>
+  <si>
+    <t>H6MSCX001323</t>
+  </si>
+  <si>
+    <t>Camara Videoconferencia</t>
+  </si>
+  <si>
+    <t>Logitech</t>
+  </si>
+  <si>
+    <t>1742LZ106AB8</t>
+  </si>
+  <si>
+    <t>Conectores Videoconferencia</t>
+  </si>
+  <si>
+    <t>Conectores</t>
+  </si>
+  <si>
+    <t>Estrella Bocinas Videoconferencia</t>
+  </si>
+  <si>
+    <t>886-000056</t>
+  </si>
+  <si>
+    <t>Estrella</t>
+  </si>
+  <si>
+    <t>Cisco UC Phone CP-8831</t>
+  </si>
+  <si>
+    <t>FCH19052AQZ</t>
+  </si>
+  <si>
+    <t>Telefono</t>
+  </si>
+  <si>
+    <t>FCH19052DJ7</t>
+  </si>
+  <si>
+    <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
+  </si>
+  <si>
+    <t>1. El uso correcto del equipo asignado.</t>
+  </si>
+  <si>
+    <t>2. Permitir realizar la auditoría y mantenimiento programado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Reportar cualquier anomalía al área de TI. </t>
+  </si>
+  <si>
+    <t>4. Hago constar que el equipo de cómputo es intransferible y esta estríctamente prohibido dejarlo en lugares de exposición de riesgo, daño y/o extravío.</t>
+  </si>
+  <si>
+    <t>5. Comunicar en caso de robo o extravío al área de TI.</t>
+  </si>
+  <si>
+    <t>Acepto que he comprendido claramente las responsabilidades que tengo con los equipos de trabajo que la empresa me ha otorgado y que el uso es exclusivamente laboral.</t>
+  </si>
+  <si>
+    <t>ENTREGA:</t>
+  </si>
+  <si>
+    <t>ACEPTA Y RECIBE:</t>
+  </si>
+  <si>
+    <t>Cristobal Soto Escalante</t>
+  </si>
+  <si>
+    <t>Coordinador de Proyectos</t>
+  </si>
+  <si>
     <t>Coordinador de TI</t>
-  </si>
-  <si>
-    <t>Región:</t>
-  </si>
-  <si>
-    <t>Norte</t>
-  </si>
-  <si>
-    <t>Ubicación:</t>
-  </si>
-  <si>
-    <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
-  </si>
-  <si>
-    <t>ITEM</t>
-  </si>
-  <si>
-    <t>TIPO</t>
-  </si>
-  <si>
-    <t>MARCA</t>
-  </si>
-  <si>
-    <t>MODELO</t>
-  </si>
-  <si>
-    <t>NUMERO DE SERIE</t>
-  </si>
-  <si>
-    <t>OBSERVACIONES</t>
-  </si>
-  <si>
-    <t>Laptop</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>Latitude 5520</t>
-  </si>
-  <si>
-    <t>C3Y9FG3</t>
-  </si>
-  <si>
-    <t>DVZ-TP-TI-00027</t>
-  </si>
-  <si>
-    <t>Diadema</t>
-  </si>
-  <si>
-    <t>HP</t>
-  </si>
-  <si>
-    <t>108DB1</t>
-  </si>
-  <si>
-    <t>2032CW</t>
-  </si>
-  <si>
-    <t>Camara Intrinsicamente segura</t>
-  </si>
-  <si>
-    <t>SONIM</t>
-  </si>
-  <si>
-    <t>XP7700</t>
-  </si>
-  <si>
-    <t>SWITCH SAN 1</t>
-  </si>
-  <si>
-    <t>POWERCONNECT 6224</t>
-  </si>
-  <si>
-    <t>D50KTS1</t>
-  </si>
-  <si>
-    <t>SWITCH SAN 2</t>
-  </si>
-  <si>
-    <t>J50KTS1</t>
-  </si>
-  <si>
-    <t>CALL MANAGER NUEVO</t>
-  </si>
-  <si>
-    <t>CISCO</t>
-  </si>
-  <si>
-    <t>UCS C220M3BE</t>
-  </si>
-  <si>
-    <t>220M3222</t>
-  </si>
-  <si>
-    <t>SERVIDOR 19</t>
-  </si>
-  <si>
-    <t>POWEREDGE R710</t>
-  </si>
-  <si>
-    <t>BRNFSL1</t>
-  </si>
-  <si>
-    <t>SERVIDOR 18</t>
-  </si>
-  <si>
-    <t>POWEREDGE R720</t>
-  </si>
-  <si>
-    <t>B3X7RV1</t>
-  </si>
-  <si>
-    <t>SAN</t>
-  </si>
-  <si>
-    <t>POWERVAULT MD3200i</t>
-  </si>
-  <si>
-    <t>48DT7V1</t>
-  </si>
-  <si>
-    <t>Monitor</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>UNIDAD DE CINTAS 19</t>
-  </si>
-  <si>
-    <t>POWER VAULT 114 X</t>
-  </si>
-  <si>
-    <t>YN106813H628</t>
-  </si>
-  <si>
-    <t>SERVIDOR 27</t>
-  </si>
-  <si>
-    <t>POWEREDGE 2950</t>
-  </si>
-  <si>
-    <t>DPBP6K1</t>
-  </si>
-  <si>
-    <t>SERVIDOR 29</t>
-  </si>
-  <si>
-    <t>POWEREDGE R320</t>
-  </si>
-  <si>
-    <t>D64MW12</t>
-  </si>
-  <si>
-    <t>UNIDAD DE CINTAS</t>
-  </si>
-  <si>
-    <t>POWER VAULT 124 T</t>
-  </si>
-  <si>
-    <t>8DDB6K1</t>
-  </si>
-  <si>
-    <t>Switch Linksys Cisco SD216</t>
-  </si>
-  <si>
-    <t>SD216</t>
-  </si>
-  <si>
-    <t>NVR</t>
-  </si>
-  <si>
-    <t>HIKVISION</t>
-  </si>
-  <si>
-    <t>DS-7616NI-K2/16P</t>
-  </si>
-  <si>
-    <t>L48074542</t>
-  </si>
-  <si>
-    <t>DVR HIKVISION</t>
-  </si>
-  <si>
-    <t>DS-7716NI-I4/16P</t>
-  </si>
-  <si>
-    <t>Mouse</t>
-  </si>
-  <si>
-    <t>3D Optical</t>
-  </si>
-  <si>
-    <t>Switch 8 Puertos</t>
-  </si>
-  <si>
-    <t>Planet</t>
-  </si>
-  <si>
-    <t>GSD-804P</t>
-  </si>
-  <si>
-    <t>A350106300034</t>
-  </si>
-  <si>
-    <t>Access PRO</t>
-  </si>
-  <si>
-    <t>AP233</t>
-  </si>
-  <si>
-    <t>AP234</t>
-  </si>
-  <si>
-    <t>Switch</t>
-  </si>
-  <si>
-    <t>CATALYST 2960-X SERIES</t>
-  </si>
-  <si>
-    <t>FCW1906B1MY</t>
-  </si>
-  <si>
-    <t>FCW1906B1LJ</t>
-  </si>
-  <si>
-    <t>FCW1906B1MM</t>
-  </si>
-  <si>
-    <t>CATALYST 2960-X SERIES POE+</t>
-  </si>
-  <si>
-    <t>FOC1710Y1FV</t>
-  </si>
-  <si>
-    <t>CATALYST 3560</t>
-  </si>
-  <si>
-    <t>CAT0948R334</t>
-  </si>
-  <si>
-    <t>F0C1503Z3QP</t>
-  </si>
-  <si>
-    <t>F0C1514X0EZ</t>
-  </si>
-  <si>
-    <t>FOC1903S1ME</t>
-  </si>
-  <si>
-    <t>Catalyst 3750X-24T-E</t>
-  </si>
-  <si>
-    <t>FD01816Z3AU</t>
-  </si>
-  <si>
-    <t>FIREWALL</t>
-  </si>
-  <si>
-    <t>FORTINET</t>
-  </si>
-  <si>
-    <t>FG100D3G14827870</t>
-  </si>
-  <si>
-    <t>FG100D3G14827806 MASTER</t>
-  </si>
-  <si>
-    <t>FG100D3G14827806</t>
-  </si>
-  <si>
-    <t>FG100D3G14827870 SLAVE</t>
-  </si>
-  <si>
-    <t>CALL MANAGER</t>
-  </si>
-  <si>
-    <t>FTX1328AHLG</t>
-  </si>
-  <si>
-    <t>ROUTER</t>
-  </si>
-  <si>
-    <t>CISCO 1900 SERIES</t>
-  </si>
-  <si>
-    <t>CFTX1614857Q</t>
-  </si>
-  <si>
-    <t>FTX174386AU</t>
-  </si>
-  <si>
-    <t>UPS</t>
-  </si>
-  <si>
-    <t>APC</t>
-  </si>
-  <si>
-    <t>APC Galaxy 3500</t>
-  </si>
-  <si>
-    <t>G35TF30KB4F</t>
-  </si>
-  <si>
-    <t>ACCESSPOINT</t>
-  </si>
-  <si>
-    <t>221E</t>
-  </si>
-  <si>
-    <t>FP221ETF22083298</t>
-  </si>
-  <si>
-    <t>FP221ETF22083291</t>
-  </si>
-  <si>
-    <t>FP221ETF22083300</t>
-  </si>
-  <si>
-    <t>FP221ETF22083299</t>
-  </si>
-  <si>
-    <t>Amplificador celular</t>
-  </si>
-  <si>
-    <t>EPCOM</t>
-  </si>
-  <si>
-    <t>G08W27160502</t>
-  </si>
-  <si>
-    <t>Camara Fija</t>
-  </si>
-  <si>
-    <t>DS-2CD2432F-I</t>
-  </si>
-  <si>
-    <t>I20140922CCWR480540694</t>
-  </si>
-  <si>
-    <t>DS-2CD1043G0-I</t>
-  </si>
-  <si>
-    <t>I20220824AAWRK47327687</t>
-  </si>
-  <si>
-    <t>Camara PTZ</t>
-  </si>
-  <si>
-    <t>DS-2DE4215IW-DE</t>
-  </si>
-  <si>
-    <t>DE20190506CCWRD16875921W</t>
-  </si>
-  <si>
-    <t>DS-2CD2232-I5</t>
-  </si>
-  <si>
-    <t>I520150207CCWR502802490</t>
-  </si>
-  <si>
-    <t>I20200824AAWRK47327674</t>
-  </si>
-  <si>
-    <t>DS-2DE7174-A</t>
-  </si>
-  <si>
-    <t>A20150122CCWR500502005</t>
-  </si>
-  <si>
-    <t>I520150207CCWR502802472</t>
-  </si>
-  <si>
-    <t>I520150207CCWR502802475</t>
-  </si>
-  <si>
-    <t>I520150207CCWR502802494</t>
-  </si>
-  <si>
-    <t>I520150207CCWR502802491</t>
-  </si>
-  <si>
-    <t>I520150207CCWR502802480</t>
-  </si>
-  <si>
-    <t>I520150207CCWR502802497</t>
-  </si>
-  <si>
-    <t>DS-2CD2422FWD-IW</t>
-  </si>
-  <si>
-    <t>IW20170808AAWR808998451</t>
-  </si>
-  <si>
-    <t>I20140922CCWR480540755</t>
-  </si>
-  <si>
-    <t>I20140922CCWR480540785</t>
-  </si>
-  <si>
-    <t>DS-2CD2T42WD-I5</t>
-  </si>
-  <si>
-    <t>I520160810BBWR633078836</t>
-  </si>
-  <si>
-    <t>I520160810BBWR633078735</t>
-  </si>
-  <si>
-    <t>I520160810BBWR633078506</t>
-  </si>
-  <si>
-    <t>A20150122CCWR500502035</t>
-  </si>
-  <si>
-    <t>KOBLENZ</t>
-  </si>
-  <si>
-    <t>4816 R</t>
-  </si>
-  <si>
-    <t>16-09-17766</t>
-  </si>
-  <si>
-    <t>Lector Biometrico</t>
-  </si>
-  <si>
-    <t>BioEntry W2</t>
-  </si>
-  <si>
-    <t>BEW2-0DP</t>
-  </si>
-  <si>
-    <t>Equipo de Videoconferencia</t>
-  </si>
-  <si>
-    <t>Chromebox</t>
-  </si>
-  <si>
-    <t>Asus</t>
-  </si>
-  <si>
-    <t>H6MSCX001323</t>
-  </si>
-  <si>
-    <t>Camara Videoconferencia</t>
-  </si>
-  <si>
-    <t>Logitech</t>
-  </si>
-  <si>
-    <t>1742LZ106AB8</t>
-  </si>
-  <si>
-    <t>Conectores Videoconferencia</t>
-  </si>
-  <si>
-    <t>Conectores</t>
-  </si>
-  <si>
-    <t>Estrella Bocinas Videoconferencia</t>
-  </si>
-  <si>
-    <t>886-000056</t>
-  </si>
-  <si>
-    <t>Estrella</t>
-  </si>
-  <si>
-    <t>Cisco UC Phone CP-8831</t>
-  </si>
-  <si>
-    <t>FCH19052AQZ</t>
-  </si>
-  <si>
-    <t>Telefono</t>
-  </si>
-  <si>
-    <t>FCH19052DJ7</t>
-  </si>
-  <si>
-    <t>Docking Station</t>
-  </si>
-  <si>
-    <t>WD19S</t>
-  </si>
-  <si>
-    <t>F9WQSB3</t>
-  </si>
-  <si>
-    <t>Audifonos</t>
-  </si>
-  <si>
-    <t>Samsung</t>
-  </si>
-  <si>
-    <t>GIUHIUIÑGYI</t>
-  </si>
-  <si>
-    <t>5494UVTUFT</t>
-  </si>
-  <si>
-    <t>Fijo</t>
-  </si>
-  <si>
-    <t>Kenwood</t>
-  </si>
-  <si>
-    <t>NX-840H-K2</t>
-  </si>
-  <si>
-    <t>B8C10276</t>
-  </si>
-  <si>
-    <t>B8C10300</t>
-  </si>
-  <si>
-    <t>Portátil</t>
-  </si>
-  <si>
-    <t>STEREN</t>
-  </si>
-  <si>
-    <t>RAD-010</t>
-  </si>
-  <si>
-    <t>PO#29980</t>
-  </si>
-  <si>
-    <t>B8C10117</t>
-  </si>
-  <si>
-    <t>B8310394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adaptador de Puerto  </t>
-  </si>
-  <si>
-    <t>vybojnkm</t>
-  </si>
-  <si>
-    <t>VTYBUNJMKL</t>
-  </si>
-  <si>
-    <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
-  </si>
-  <si>
-    <t>1. El uso correcto del equipo asignado.</t>
-  </si>
-  <si>
-    <t>2. Permitir realizar la auditoría y mantenimiento programado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Reportar cualquier anomalía al área de TI. </t>
-  </si>
-  <si>
-    <t>4. Hago constar que el equipo de cómputo es intransferible y esta estríctamente prohibido dejarlo en lugares de exposición de riesgo, daño y/o extravío.</t>
-  </si>
-  <si>
-    <t>5. Comunicar en caso de robo o extravío al área de TI.</t>
-  </si>
-  <si>
-    <t>Acepto que he comprendido claramente las responsabilidades que tengo con los equipos de trabajo que la empresa me ha otorgado y que el uso es exclusivamente laboral.</t>
-  </si>
-  <si>
-    <t>ENTREGA:</t>
-  </si>
-  <si>
-    <t>ACEPTA Y RECIBE:</t>
-  </si>
-  <si>
-    <t>Cristobal Soto Escalante</t>
-  </si>
-  <si>
-    <t>Coordinador de Proyectos</t>
   </si>
 </sst>
 </file>
@@ -771,6 +717,32 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -839,32 +811,6 @@
       </left>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -953,41 +899,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="0" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="12" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="13" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="3" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="4" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -997,15 +913,45 @@
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
     <xf xfId="0" fontId="4" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="5" numFmtId="0" fillId="3" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="7" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="12" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="13" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="4" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
@@ -1290,7 +1236,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K118"/>
+  <dimension ref="A1:K111"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="12.5546875" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="true" style="0"/>
@@ -1307,73 +1253,73 @@
     <row r="1" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="2" spans="1:11" customHeight="1" ht="15.75">
       <c r="A2" s="1"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="27" t="s">
+      <c r="B2" s="41"/>
+      <c r="C2" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="33" t="s">
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="34"/>
+      <c r="J2" s="40"/>
     </row>
     <row r="3" spans="1:11" customHeight="1" ht="15.75">
       <c r="A3" s="1"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="33" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="34"/>
+      <c r="J3" s="40"/>
     </row>
     <row r="4" spans="1:11" customHeight="1" ht="15.75">
       <c r="A4" s="1"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="33" t="s">
+      <c r="B4" s="42"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="34"/>
+      <c r="J4" s="40"/>
     </row>
     <row r="5" spans="1:11" customHeight="1" ht="15.75">
       <c r="A5" s="1"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="27" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="35"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="49"/>
     </row>
     <row r="6" spans="1:11" customHeight="1" ht="9.75">
       <c r="A6" s="1"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="36"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="50"/>
     </row>
     <row r="7" spans="1:11" customHeight="1" ht="15.75">
       <c r="H7" s="2"/>
@@ -1385,14 +1331,14 @@
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
       <c r="I8" s="2" t="s">
         <v>7</v>
       </c>
@@ -1416,19 +1362,21 @@
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="11">
+        <v>12</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="I10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" s="6"/>
+      <c r="J10" s="6">
+        <v>95</v>
+      </c>
     </row>
     <row r="11" spans="1:11" customHeight="1" ht="15.75">
       <c r="G11" s="12"/>
@@ -1436,40 +1384,40 @@
     <row r="12" spans="1:11" customHeight="1" ht="15.75">
       <c r="A12" s="13"/>
       <c r="B12" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
+        <v>13</v>
+      </c>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
     </row>
     <row r="13" spans="1:11" customHeight="1" ht="15.75">
       <c r="A13" s="13"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
     </row>
     <row r="14" spans="1:11" customHeight="1" ht="15.75">
       <c r="A14" s="13"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
     </row>
     <row r="15" spans="1:11" customHeight="1" ht="15.75">
       <c r="A15" s="14"/>
@@ -1485,26 +1433,26 @@
     <row r="16" spans="1:11" customHeight="1" ht="15.75">
       <c r="A16" s="15"/>
       <c r="B16" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="D16" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="E16" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="39" t="s">
+      <c r="F16" s="40"/>
+      <c r="G16" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="34"/>
-      <c r="G16" s="39" t="s">
+      <c r="H16" s="40"/>
+      <c r="I16" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="34"/>
-      <c r="I16" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" s="34"/>
+      <c r="J16" s="40"/>
       <c r="K16" s="17"/>
     </row>
     <row r="17" spans="1:11">
@@ -1513,17 +1461,17 @@
         <v>1</v>
       </c>
       <c r="C17" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="53" t="s">
+      <c r="E17" s="53" t="s">
         <v>22</v>
-      </c>
-      <c r="E17" s="53" t="s">
-        <v>23</v>
       </c>
       <c r="F17" s="53"/>
       <c r="G17" s="53" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H17" s="53"/>
       <c r="I17" s="53"/>
@@ -1536,7 +1484,7 @@
       <c r="C18" s="53"/>
       <c r="D18" s="53"/>
       <c r="E18" s="51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F18" s="53"/>
       <c r="G18" s="53"/>
@@ -1551,17 +1499,17 @@
         <v>2</v>
       </c>
       <c r="C19" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="53" t="s">
+      <c r="E19" s="53" t="s">
         <v>27</v>
-      </c>
-      <c r="E19" s="53" t="s">
-        <v>28</v>
       </c>
       <c r="F19" s="53"/>
       <c r="G19" s="53" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H19" s="53"/>
       <c r="I19" s="53"/>
@@ -1574,13 +1522,13 @@
         <v>3</v>
       </c>
       <c r="C20" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="53" t="s">
+      <c r="E20" s="53" t="s">
         <v>31</v>
-      </c>
-      <c r="E20" s="53" t="s">
-        <v>32</v>
       </c>
       <c r="F20" s="53"/>
       <c r="G20" s="53">
@@ -1597,17 +1545,17 @@
         <v>4</v>
       </c>
       <c r="C21" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="53" t="s">
         <v>33</v>
-      </c>
-      <c r="D21" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="53" t="s">
-        <v>34</v>
       </c>
       <c r="F21" s="53"/>
       <c r="G21" s="53" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H21" s="53"/>
       <c r="I21" s="53"/>
@@ -1620,17 +1568,17 @@
         <v>5</v>
       </c>
       <c r="C22" s="53" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D22" s="53" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E22" s="53" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F22" s="53"/>
       <c r="G22" s="53" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H22" s="53"/>
       <c r="I22" s="53"/>
@@ -1643,17 +1591,17 @@
         <v>6</v>
       </c>
       <c r="C23" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="53" t="s">
+      <c r="E23" s="53" t="s">
         <v>39</v>
-      </c>
-      <c r="E23" s="53" t="s">
-        <v>40</v>
       </c>
       <c r="F23" s="53"/>
       <c r="G23" s="53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H23" s="53"/>
       <c r="I23" s="53"/>
@@ -1666,17 +1614,17 @@
         <v>7</v>
       </c>
       <c r="C24" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="53" t="s">
         <v>42</v>
-      </c>
-      <c r="D24" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" s="53" t="s">
-        <v>43</v>
       </c>
       <c r="F24" s="53"/>
       <c r="G24" s="53" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H24" s="53"/>
       <c r="I24" s="53"/>
@@ -1689,17 +1637,17 @@
         <v>8</v>
       </c>
       <c r="C25" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="53" t="s">
         <v>45</v>
-      </c>
-      <c r="D25" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="E25" s="53" t="s">
-        <v>46</v>
       </c>
       <c r="F25" s="53"/>
       <c r="G25" s="53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H25" s="53"/>
       <c r="I25" s="53"/>
@@ -1712,17 +1660,17 @@
         <v>9</v>
       </c>
       <c r="C26" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="53" t="s">
         <v>48</v>
-      </c>
-      <c r="D26" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="E26" s="53" t="s">
-        <v>49</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="53" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H26" s="53"/>
       <c r="I26" s="53"/>
@@ -1735,17 +1683,17 @@
         <v>10</v>
       </c>
       <c r="C27" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="53" t="s">
         <v>51</v>
-      </c>
-      <c r="D27" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="E27" s="53" t="s">
-        <v>52</v>
       </c>
       <c r="F27" s="53"/>
       <c r="G27" s="53" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H27" s="53"/>
       <c r="I27" s="53"/>
@@ -1758,17 +1706,17 @@
         <v>11</v>
       </c>
       <c r="C28" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="53" t="s">
         <v>53</v>
-      </c>
-      <c r="D28" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="E28" s="53" t="s">
-        <v>54</v>
       </c>
       <c r="F28" s="53"/>
       <c r="G28" s="53" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H28" s="53"/>
       <c r="I28" s="53"/>
@@ -1781,17 +1729,17 @@
         <v>12</v>
       </c>
       <c r="C29" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="53" t="s">
         <v>56</v>
-      </c>
-      <c r="D29" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="E29" s="53" t="s">
-        <v>57</v>
       </c>
       <c r="F29" s="53"/>
       <c r="G29" s="53" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H29" s="53"/>
       <c r="I29" s="53"/>
@@ -1804,17 +1752,17 @@
         <v>13</v>
       </c>
       <c r="C30" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="53" t="s">
         <v>59</v>
-      </c>
-      <c r="D30" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="E30" s="53" t="s">
-        <v>60</v>
       </c>
       <c r="F30" s="53"/>
       <c r="G30" s="53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H30" s="53"/>
       <c r="I30" s="53"/>
@@ -1827,17 +1775,17 @@
         <v>14</v>
       </c>
       <c r="C31" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="53" t="s">
         <v>62</v>
-      </c>
-      <c r="D31" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="E31" s="53" t="s">
-        <v>63</v>
       </c>
       <c r="F31" s="53"/>
       <c r="G31" s="53" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H31" s="53"/>
       <c r="I31" s="53"/>
@@ -1850,17 +1798,17 @@
         <v>15</v>
       </c>
       <c r="C32" s="53" t="s">
+        <v>64</v>
+      </c>
+      <c r="D32" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="E32" s="53" t="s">
         <v>65</v>
-      </c>
-      <c r="D32" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="E32" s="53" t="s">
-        <v>66</v>
       </c>
       <c r="F32" s="53"/>
       <c r="G32" s="53" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H32" s="53"/>
       <c r="I32" s="53"/>
@@ -1873,17 +1821,17 @@
         <v>16</v>
       </c>
       <c r="C33" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="D33" s="53" t="s">
+      <c r="E33" s="53" t="s">
         <v>68</v>
-      </c>
-      <c r="E33" s="53" t="s">
-        <v>69</v>
       </c>
       <c r="F33" s="53"/>
       <c r="G33" s="53" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H33" s="53"/>
       <c r="I33" s="53"/>
@@ -1896,13 +1844,13 @@
         <v>17</v>
       </c>
       <c r="C34" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="E34" s="53" t="s">
         <v>71</v>
-      </c>
-      <c r="D34" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="E34" s="53" t="s">
-        <v>72</v>
       </c>
       <c r="F34" s="53"/>
       <c r="G34" s="53">
@@ -1919,17 +1867,17 @@
         <v>18</v>
       </c>
       <c r="C35" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" s="53" t="s">
         <v>73</v>
       </c>
-      <c r="D35" s="53" t="s">
-        <v>74</v>
-      </c>
       <c r="E35" s="53" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F35" s="53"/>
       <c r="G35" s="53" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H35" s="53"/>
       <c r="I35" s="53"/>
@@ -1942,17 +1890,17 @@
         <v>19</v>
       </c>
       <c r="C36" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" s="53" t="s">
         <v>73</v>
       </c>
-      <c r="D36" s="53" t="s">
-        <v>74</v>
-      </c>
       <c r="E36" s="53" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F36" s="53"/>
       <c r="G36" s="53" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H36" s="53"/>
       <c r="I36" s="53"/>
@@ -1965,17 +1913,17 @@
         <v>20</v>
       </c>
       <c r="C37" s="53" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="D37" s="53" t="s">
+      <c r="E37" s="53" t="s">
         <v>76</v>
-      </c>
-      <c r="E37" s="53" t="s">
-        <v>77</v>
       </c>
       <c r="F37" s="53"/>
       <c r="G37" s="53" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H37" s="53"/>
       <c r="I37" s="53"/>
@@ -1988,17 +1936,17 @@
         <v>21</v>
       </c>
       <c r="C38" s="53" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D38" s="53" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E38" s="53" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F38" s="53"/>
       <c r="G38" s="53" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H38" s="53"/>
       <c r="I38" s="53"/>
@@ -2011,17 +1959,17 @@
         <v>22</v>
       </c>
       <c r="C39" s="53" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D39" s="53" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E39" s="53" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F39" s="53"/>
       <c r="G39" s="53" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H39" s="53"/>
       <c r="I39" s="53"/>
@@ -2034,17 +1982,17 @@
         <v>23</v>
       </c>
       <c r="C40" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="D40" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="E40" s="53" t="s">
         <v>82</v>
-      </c>
-      <c r="D40" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="E40" s="53" t="s">
-        <v>83</v>
       </c>
       <c r="F40" s="53"/>
       <c r="G40" s="53" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H40" s="53"/>
       <c r="I40" s="53"/>
@@ -2057,17 +2005,17 @@
         <v>24</v>
       </c>
       <c r="C41" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="D41" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="E41" s="53" t="s">
         <v>82</v>
-      </c>
-      <c r="D41" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="E41" s="53" t="s">
-        <v>83</v>
       </c>
       <c r="F41" s="53"/>
       <c r="G41" s="53" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H41" s="53"/>
       <c r="I41" s="53"/>
@@ -2080,17 +2028,17 @@
         <v>25</v>
       </c>
       <c r="C42" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="D42" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="E42" s="53" t="s">
         <v>82</v>
-      </c>
-      <c r="D42" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="E42" s="53" t="s">
-        <v>83</v>
       </c>
       <c r="F42" s="53"/>
       <c r="G42" s="53" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H42" s="53"/>
       <c r="I42" s="53"/>
@@ -2103,17 +2051,17 @@
         <v>26</v>
       </c>
       <c r="C43" s="53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D43" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E43" s="53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F43" s="53"/>
       <c r="G43" s="53" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H43" s="53"/>
       <c r="I43" s="53"/>
@@ -2126,17 +2074,17 @@
         <v>27</v>
       </c>
       <c r="C44" s="53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D44" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E44" s="53" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F44" s="53"/>
       <c r="G44" s="53" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H44" s="53"/>
       <c r="I44" s="53"/>
@@ -2149,17 +2097,17 @@
         <v>28</v>
       </c>
       <c r="C45" s="53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D45" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E45" s="53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F45" s="53"/>
       <c r="G45" s="53" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H45" s="53"/>
       <c r="I45" s="53"/>
@@ -2172,17 +2120,17 @@
         <v>29</v>
       </c>
       <c r="C46" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="D46" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="E46" s="53" t="s">
         <v>82</v>
-      </c>
-      <c r="D46" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="E46" s="53" t="s">
-        <v>83</v>
       </c>
       <c r="F46" s="53"/>
       <c r="G46" s="53" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H46" s="53"/>
       <c r="I46" s="53"/>
@@ -2195,17 +2143,17 @@
         <v>30</v>
       </c>
       <c r="C47" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="D47" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="E47" s="53" t="s">
         <v>82</v>
-      </c>
-      <c r="D47" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="E47" s="53" t="s">
-        <v>83</v>
       </c>
       <c r="F47" s="53"/>
       <c r="G47" s="53" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H47" s="53"/>
       <c r="I47" s="53"/>
@@ -2218,17 +2166,17 @@
         <v>31</v>
       </c>
       <c r="C48" s="53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D48" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E48" s="53" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F48" s="53"/>
       <c r="G48" s="53" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H48" s="53"/>
       <c r="I48" s="53"/>
@@ -2241,17 +2189,17 @@
         <v>32</v>
       </c>
       <c r="C49" s="53" t="s">
+        <v>95</v>
+      </c>
+      <c r="D49" s="53" t="s">
         <v>96</v>
       </c>
-      <c r="D49" s="53" t="s">
+      <c r="E49" s="53" t="s">
         <v>97</v>
-      </c>
-      <c r="E49" s="53" t="s">
-        <v>98</v>
       </c>
       <c r="F49" s="53"/>
       <c r="G49" s="53" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H49" s="53"/>
       <c r="I49" s="53"/>
@@ -2264,17 +2212,17 @@
         <v>33</v>
       </c>
       <c r="C50" s="53" t="s">
+        <v>95</v>
+      </c>
+      <c r="D50" s="53" t="s">
         <v>96</v>
       </c>
-      <c r="D50" s="53" t="s">
-        <v>97</v>
-      </c>
       <c r="E50" s="53" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F50" s="53"/>
       <c r="G50" s="53" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H50" s="53"/>
       <c r="I50" s="53"/>
@@ -2287,15 +2235,15 @@
         <v>34</v>
       </c>
       <c r="C51" s="53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D51" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E51" s="53"/>
       <c r="F51" s="53"/>
       <c r="G51" s="53" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H51" s="53"/>
       <c r="I51" s="53"/>
@@ -2308,17 +2256,17 @@
         <v>35</v>
       </c>
       <c r="C52" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="D52" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="E52" s="53" t="s">
         <v>104</v>
-      </c>
-      <c r="D52" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="E52" s="53" t="s">
-        <v>105</v>
       </c>
       <c r="F52" s="53"/>
       <c r="G52" s="53" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H52" s="53"/>
       <c r="I52" s="53"/>
@@ -2331,17 +2279,17 @@
         <v>36</v>
       </c>
       <c r="C53" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="D53" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="E53" s="53" t="s">
         <v>104</v>
-      </c>
-      <c r="D53" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="E53" s="53" t="s">
-        <v>105</v>
       </c>
       <c r="F53" s="53"/>
       <c r="G53" s="53" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H53" s="53"/>
       <c r="I53" s="53"/>
@@ -2354,17 +2302,17 @@
         <v>37</v>
       </c>
       <c r="C54" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="D54" s="53" t="s">
         <v>108</v>
       </c>
-      <c r="D54" s="53" t="s">
+      <c r="E54" s="53" t="s">
         <v>109</v>
-      </c>
-      <c r="E54" s="53" t="s">
-        <v>110</v>
       </c>
       <c r="F54" s="53"/>
       <c r="G54" s="53" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H54" s="53"/>
       <c r="I54" s="53"/>
@@ -2377,17 +2325,17 @@
         <v>38</v>
       </c>
       <c r="C55" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="D55" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="E55" s="53" t="s">
         <v>112</v>
-      </c>
-      <c r="D55" s="53" t="s">
-        <v>97</v>
-      </c>
-      <c r="E55" s="53" t="s">
-        <v>113</v>
       </c>
       <c r="F55" s="53"/>
       <c r="G55" s="53" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H55" s="53"/>
       <c r="I55" s="53"/>
@@ -2400,17 +2348,17 @@
         <v>39</v>
       </c>
       <c r="C56" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="D56" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="E56" s="53" t="s">
         <v>112</v>
-      </c>
-      <c r="D56" s="53" t="s">
-        <v>97</v>
-      </c>
-      <c r="E56" s="53" t="s">
-        <v>113</v>
       </c>
       <c r="F56" s="53"/>
       <c r="G56" s="53" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H56" s="53"/>
       <c r="I56" s="53"/>
@@ -2423,17 +2371,17 @@
         <v>40</v>
       </c>
       <c r="C57" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="D57" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="E57" s="53" t="s">
         <v>112</v>
-      </c>
-      <c r="D57" s="53" t="s">
-        <v>97</v>
-      </c>
-      <c r="E57" s="53" t="s">
-        <v>113</v>
       </c>
       <c r="F57" s="53"/>
       <c r="G57" s="53" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H57" s="53"/>
       <c r="I57" s="53"/>
@@ -2446,17 +2394,17 @@
         <v>41</v>
       </c>
       <c r="C58" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="D58" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="E58" s="53" t="s">
         <v>112</v>
-      </c>
-      <c r="D58" s="53" t="s">
-        <v>97</v>
-      </c>
-      <c r="E58" s="53" t="s">
-        <v>113</v>
       </c>
       <c r="F58" s="53"/>
       <c r="G58" s="53" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H58" s="53"/>
       <c r="I58" s="53"/>
@@ -2469,17 +2417,17 @@
         <v>42</v>
       </c>
       <c r="C59" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="D59" s="53" t="s">
         <v>118</v>
       </c>
-      <c r="D59" s="53" t="s">
-        <v>119</v>
-      </c>
       <c r="E59" s="53" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F59" s="53"/>
       <c r="G59" s="53" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H59" s="53"/>
       <c r="I59" s="53"/>
@@ -2492,17 +2440,17 @@
         <v>43</v>
       </c>
       <c r="C60" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="D60" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="E60" s="53" t="s">
         <v>121</v>
-      </c>
-      <c r="D60" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="E60" s="53" t="s">
-        <v>122</v>
       </c>
       <c r="F60" s="53"/>
       <c r="G60" s="53" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H60" s="53"/>
       <c r="I60" s="53"/>
@@ -2515,17 +2463,17 @@
         <v>44</v>
       </c>
       <c r="C61" s="53" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D61" s="53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E61" s="53" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F61" s="53"/>
       <c r="G61" s="53" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H61" s="53"/>
       <c r="I61" s="53"/>
@@ -2538,17 +2486,17 @@
         <v>45</v>
       </c>
       <c r="C62" s="53" t="s">
+        <v>125</v>
+      </c>
+      <c r="D62" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="E62" s="53" t="s">
         <v>126</v>
-      </c>
-      <c r="D62" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="E62" s="53" t="s">
-        <v>127</v>
       </c>
       <c r="F62" s="53"/>
       <c r="G62" s="53" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H62" s="53"/>
       <c r="I62" s="53"/>
@@ -2561,17 +2509,17 @@
         <v>46</v>
       </c>
       <c r="C63" s="53" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D63" s="53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E63" s="53" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F63" s="53"/>
       <c r="G63" s="53" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H63" s="53"/>
       <c r="I63" s="53"/>
@@ -2584,17 +2532,17 @@
         <v>47</v>
       </c>
       <c r="C64" s="53" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D64" s="53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E64" s="53" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F64" s="53"/>
       <c r="G64" s="53" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H64" s="53"/>
       <c r="I64" s="53"/>
@@ -2607,17 +2555,17 @@
         <v>48</v>
       </c>
       <c r="C65" s="53" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D65" s="53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E65" s="53" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F65" s="53"/>
       <c r="G65" s="53" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H65" s="53"/>
       <c r="I65" s="53"/>
@@ -2630,17 +2578,17 @@
         <v>49</v>
       </c>
       <c r="C66" s="53" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D66" s="53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E66" s="53" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F66" s="53"/>
       <c r="G66" s="53" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H66" s="53"/>
       <c r="I66" s="53"/>
@@ -2653,17 +2601,17 @@
         <v>50</v>
       </c>
       <c r="C67" s="53" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D67" s="53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E67" s="53" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F67" s="53"/>
       <c r="G67" s="53" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H67" s="53"/>
       <c r="I67" s="53"/>
@@ -2676,17 +2624,17 @@
         <v>51</v>
       </c>
       <c r="C68" s="53" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D68" s="53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E68" s="53" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F68" s="53"/>
       <c r="G68" s="53" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H68" s="53"/>
       <c r="I68" s="53"/>
@@ -2699,17 +2647,17 @@
         <v>52</v>
       </c>
       <c r="C69" s="53" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D69" s="53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E69" s="53" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F69" s="53"/>
       <c r="G69" s="53" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H69" s="53"/>
       <c r="I69" s="53"/>
@@ -2722,17 +2670,17 @@
         <v>53</v>
       </c>
       <c r="C70" s="53" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D70" s="53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E70" s="53" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F70" s="53"/>
       <c r="G70" s="53" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H70" s="53"/>
       <c r="I70" s="53"/>
@@ -2745,17 +2693,17 @@
         <v>54</v>
       </c>
       <c r="C71" s="53" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D71" s="53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E71" s="53" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F71" s="53"/>
       <c r="G71" s="53" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H71" s="53"/>
       <c r="I71" s="53"/>
@@ -2768,10 +2716,10 @@
         <v>55</v>
       </c>
       <c r="C72" s="53" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="D72" s="53" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="E72" s="53" t="s">
         <v>140</v>
@@ -2791,13 +2739,13 @@
         <v>56</v>
       </c>
       <c r="C73" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="D73" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="E73" s="53" t="s">
         <v>121</v>
-      </c>
-      <c r="D73" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="E73" s="53" t="s">
-        <v>122</v>
       </c>
       <c r="F73" s="53"/>
       <c r="G73" s="53" t="s">
@@ -2814,13 +2762,13 @@
         <v>57</v>
       </c>
       <c r="C74" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="D74" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="E74" s="53" t="s">
         <v>121</v>
-      </c>
-      <c r="D74" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="E74" s="53" t="s">
-        <v>122</v>
       </c>
       <c r="F74" s="53"/>
       <c r="G74" s="53" t="s">
@@ -2837,10 +2785,10 @@
         <v>58</v>
       </c>
       <c r="C75" s="53" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D75" s="53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E75" s="53" t="s">
         <v>144</v>
@@ -2860,10 +2808,10 @@
         <v>59</v>
       </c>
       <c r="C76" s="53" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D76" s="53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E76" s="53" t="s">
         <v>144</v>
@@ -2883,10 +2831,10 @@
         <v>60</v>
       </c>
       <c r="C77" s="53" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D77" s="53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E77" s="53" t="s">
         <v>144</v>
@@ -2906,13 +2854,13 @@
         <v>61</v>
       </c>
       <c r="C78" s="53" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D78" s="53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E78" s="53" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F78" s="53"/>
       <c r="G78" s="53" t="s">
@@ -2929,7 +2877,7 @@
         <v>62</v>
       </c>
       <c r="C79" s="53" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D79" s="53" t="s">
         <v>149</v>
@@ -2952,17 +2900,17 @@
         <v>63</v>
       </c>
       <c r="C80" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="D80" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="E80" s="53" t="s">
         <v>152</v>
       </c>
-      <c r="D80" s="53" t="s">
+      <c r="F80" s="53"/>
+      <c r="G80" s="53" t="s">
         <v>153</v>
-      </c>
-      <c r="E80" s="53" t="s">
-        <v>154</v>
-      </c>
-      <c r="F80" s="53"/>
-      <c r="G80" s="53">
-        <v>544161389</v>
       </c>
       <c r="H80" s="53"/>
       <c r="I80" s="53"/>
@@ -2975,13 +2923,13 @@
         <v>64</v>
       </c>
       <c r="C81" s="53" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D81" s="53" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E81" s="53" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F81" s="53"/>
       <c r="G81" s="53">
@@ -2998,17 +2946,17 @@
         <v>65</v>
       </c>
       <c r="C82" s="53" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D82" s="53" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E82" s="53" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F82" s="53"/>
       <c r="G82" s="53" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H82" s="53"/>
       <c r="I82" s="53"/>
@@ -3021,17 +2969,17 @@
         <v>66</v>
       </c>
       <c r="C83" s="53" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D83" s="53" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E83" s="53" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F83" s="53"/>
       <c r="G83" s="53" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H83" s="53"/>
       <c r="I83" s="53"/>
@@ -3044,17 +2992,17 @@
         <v>67</v>
       </c>
       <c r="C84" s="53" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D84" s="53" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E84" s="53" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F84" s="53"/>
       <c r="G84" s="53" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H84" s="53"/>
       <c r="I84" s="53"/>
@@ -3067,17 +3015,17 @@
         <v>68</v>
       </c>
       <c r="C85" s="53" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D85" s="53" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E85" s="53" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F85" s="53"/>
       <c r="G85" s="53" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H85" s="53"/>
       <c r="I85" s="53"/>
@@ -3090,17 +3038,17 @@
         <v>69</v>
       </c>
       <c r="C86" s="53" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D86" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E86" s="53" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F86" s="53"/>
       <c r="G86" s="53" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H86" s="53"/>
       <c r="I86" s="53"/>
@@ -3113,17 +3061,17 @@
         <v>70</v>
       </c>
       <c r="C87" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="D87" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="E87" s="53" t="s">
         <v>169</v>
-      </c>
-      <c r="D87" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="E87" s="53" t="s">
-        <v>167</v>
       </c>
       <c r="F87" s="53"/>
       <c r="G87" s="53" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H87" s="53"/>
       <c r="I87" s="53"/>
@@ -3136,455 +3084,293 @@
         <v>71</v>
       </c>
       <c r="C88" s="53" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="D88" s="53" t="s">
-        <v>22</v>
+        <v>155</v>
       </c>
       <c r="E88" s="53" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="F88" s="53"/>
-      <c r="G88" s="53" t="s">
-        <v>173</v>
+      <c r="G88" s="53">
+        <v>544161389</v>
       </c>
       <c r="H88" s="53"/>
       <c r="I88" s="53"/>
       <c r="J88" s="53"/>
       <c r="K88" s="17"/>
     </row>
-    <row r="89" spans="1:11">
-      <c r="A89" s="52"/>
-      <c r="B89" s="53">
-        <v>72</v>
-      </c>
-      <c r="C89" s="53" t="s">
+    <row r="89" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A89" s="18"/>
+      <c r="B89" s="24"/>
+      <c r="C89" s="24"/>
+      <c r="D89" s="24"/>
+      <c r="E89" s="35"/>
+      <c r="F89" s="31"/>
+      <c r="G89" s="35"/>
+      <c r="H89" s="31"/>
+      <c r="I89" s="35"/>
+      <c r="J89" s="31"/>
+    </row>
+    <row r="90" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A90" s="18"/>
+      <c r="B90" s="24"/>
+      <c r="C90" s="24"/>
+      <c r="D90" s="24"/>
+      <c r="E90" s="30"/>
+      <c r="F90" s="31"/>
+      <c r="G90" s="32"/>
+      <c r="H90" s="31"/>
+      <c r="I90" s="32"/>
+      <c r="J90" s="31"/>
+    </row>
+    <row r="91" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A91" s="13"/>
+      <c r="B91" s="13"/>
+      <c r="C91" s="13"/>
+      <c r="D91" s="13"/>
+      <c r="E91" s="13"/>
+      <c r="F91" s="13"/>
+      <c r="G91" s="13"/>
+      <c r="H91" s="13"/>
+      <c r="I91" s="13"/>
+      <c r="J91" s="13"/>
+    </row>
+    <row r="92" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A92" s="19"/>
+      <c r="B92" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="C92" s="26"/>
+      <c r="D92" s="26"/>
+      <c r="E92" s="26"/>
+      <c r="F92" s="26"/>
+      <c r="G92" s="26"/>
+      <c r="H92" s="26"/>
+      <c r="I92" s="26"/>
+      <c r="J92" s="26"/>
+    </row>
+    <row r="93" spans="1:11" customHeight="1" ht="9">
+      <c r="A93" s="20"/>
+      <c r="B93" s="20"/>
+      <c r="C93" s="20"/>
+      <c r="D93" s="20"/>
+      <c r="E93" s="20"/>
+      <c r="F93" s="20"/>
+      <c r="G93" s="20"/>
+      <c r="H93" s="20"/>
+      <c r="I93" s="20"/>
+      <c r="J93" s="20"/>
+    </row>
+    <row r="94" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A94" s="20"/>
+      <c r="B94" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="D89" s="53" t="s">
+      <c r="C94" s="26"/>
+      <c r="D94" s="26"/>
+      <c r="E94" s="26"/>
+      <c r="F94" s="26"/>
+      <c r="G94" s="26"/>
+      <c r="H94" s="26"/>
+      <c r="I94" s="26"/>
+      <c r="J94" s="26"/>
+    </row>
+    <row r="95" spans="1:11" customHeight="1" ht="15">
+      <c r="A95" s="20"/>
+      <c r="B95" s="27" t="s">
         <v>175</v>
       </c>
-      <c r="E89" s="53" t="s">
+      <c r="C95" s="26"/>
+      <c r="D95" s="26"/>
+      <c r="E95" s="26"/>
+      <c r="F95" s="26"/>
+      <c r="G95" s="26"/>
+      <c r="H95" s="26"/>
+      <c r="I95" s="26"/>
+      <c r="J95" s="26"/>
+    </row>
+    <row r="96" spans="1:11" customHeight="1" ht="15">
+      <c r="A96" s="20"/>
+      <c r="B96" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="F89" s="53"/>
-      <c r="G89" s="53" t="s">
+      <c r="C96" s="26"/>
+      <c r="D96" s="26"/>
+      <c r="E96" s="26"/>
+      <c r="F96" s="26"/>
+      <c r="G96" s="26"/>
+      <c r="H96" s="26"/>
+      <c r="I96" s="26"/>
+      <c r="J96" s="26"/>
+    </row>
+    <row r="97" spans="1:11" customHeight="1" ht="15">
+      <c r="A97" s="20"/>
+      <c r="B97" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="H89" s="53"/>
-      <c r="I89" s="53"/>
-      <c r="J89" s="53"/>
-      <c r="K89" s="17"/>
-    </row>
-    <row r="90" spans="1:11">
-      <c r="A90" s="52"/>
-      <c r="B90" s="53">
-        <v>73</v>
-      </c>
-      <c r="C90" s="53" t="s">
+      <c r="C97" s="26"/>
+      <c r="D97" s="26"/>
+      <c r="E97" s="26"/>
+      <c r="F97" s="26"/>
+      <c r="G97" s="26"/>
+      <c r="H97" s="26"/>
+      <c r="I97" s="26"/>
+      <c r="J97" s="26"/>
+    </row>
+    <row r="98" spans="1:11" customHeight="1" ht="15">
+      <c r="A98" s="20"/>
+      <c r="B98" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="D90" s="53" t="s">
+      <c r="C98" s="26"/>
+      <c r="D98" s="26"/>
+      <c r="E98" s="26"/>
+      <c r="F98" s="26"/>
+      <c r="G98" s="26"/>
+      <c r="H98" s="26"/>
+      <c r="I98" s="26"/>
+      <c r="J98" s="26"/>
+    </row>
+    <row r="99" spans="1:11" customHeight="1" ht="12">
+      <c r="A99" s="21"/>
+      <c r="B99" s="28"/>
+      <c r="C99" s="26"/>
+      <c r="D99" s="26"/>
+      <c r="E99" s="26"/>
+      <c r="F99" s="26"/>
+      <c r="G99" s="26"/>
+      <c r="H99" s="26"/>
+      <c r="I99" s="26"/>
+      <c r="J99" s="26"/>
+    </row>
+    <row r="100" spans="1:11" customHeight="1" ht="27.75">
+      <c r="A100" s="17"/>
+      <c r="B100" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="E90" s="53" t="s">
+      <c r="C100" s="26"/>
+      <c r="D100" s="26"/>
+      <c r="E100" s="26"/>
+      <c r="F100" s="26"/>
+      <c r="G100" s="26"/>
+      <c r="H100" s="26"/>
+      <c r="I100" s="26"/>
+      <c r="J100" s="26"/>
+    </row>
+    <row r="101" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A101" s="22"/>
+      <c r="B101" s="22"/>
+      <c r="C101" s="22"/>
+      <c r="D101" s="22"/>
+      <c r="E101" s="22"/>
+      <c r="H101" s="15"/>
+      <c r="I101" s="15"/>
+      <c r="J101" s="15"/>
+    </row>
+    <row r="102" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C102" s="22"/>
+      <c r="D102" s="22"/>
+      <c r="E102" s="22"/>
+      <c r="I102" s="15"/>
+      <c r="J102" s="15"/>
+    </row>
+    <row r="103" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A103" s="22"/>
+      <c r="B103" s="22"/>
+      <c r="C103" s="25" t="s">
         <v>180</v>
       </c>
-      <c r="F90" s="53"/>
-      <c r="G90" s="53" t="s">
+      <c r="D103" s="26"/>
+      <c r="E103" s="26"/>
+      <c r="H103" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="H90" s="53"/>
-      <c r="I90" s="53"/>
-      <c r="J90" s="53"/>
-      <c r="K90" s="17"/>
-    </row>
-    <row r="91" spans="1:11">
-      <c r="A91" s="52"/>
-      <c r="B91" s="53">
-        <v>74</v>
-      </c>
-      <c r="C91" s="53" t="s">
-        <v>178</v>
-      </c>
-      <c r="D91" s="53" t="s">
-        <v>179</v>
-      </c>
-      <c r="E91" s="53" t="s">
-        <v>180</v>
-      </c>
-      <c r="F91" s="53"/>
-      <c r="G91" s="53" t="s">
+      <c r="I103" s="26"/>
+      <c r="J103" s="26"/>
+    </row>
+    <row r="104" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="105" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C105" s="23"/>
+      <c r="D105" s="23"/>
+      <c r="E105" s="23"/>
+      <c r="H105" s="23"/>
+      <c r="I105" s="23"/>
+      <c r="J105" s="23"/>
+    </row>
+    <row r="106" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="107" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C107" s="25" t="s">
         <v>182</v>
       </c>
-      <c r="H91" s="53"/>
-      <c r="I91" s="53"/>
-      <c r="J91" s="53"/>
-      <c r="K91" s="17"/>
-    </row>
-    <row r="92" spans="1:11">
-      <c r="A92" s="52"/>
-      <c r="B92" s="53">
-        <v>75</v>
-      </c>
-      <c r="C92" s="53" t="s">
-        <v>183</v>
-      </c>
-      <c r="D92" s="53" t="s">
-        <v>184</v>
-      </c>
-      <c r="E92" s="53" t="s">
-        <v>185</v>
-      </c>
-      <c r="F92" s="53"/>
-      <c r="G92" s="53" t="s">
-        <v>186</v>
-      </c>
-      <c r="H92" s="53"/>
-      <c r="I92" s="53"/>
-      <c r="J92" s="53"/>
-      <c r="K92" s="17"/>
-    </row>
-    <row r="93" spans="1:11">
-      <c r="A93" s="52"/>
-      <c r="B93" s="53">
-        <v>76</v>
-      </c>
-      <c r="C93" s="53" t="s">
-        <v>178</v>
-      </c>
-      <c r="D93" s="53" t="s">
-        <v>179</v>
-      </c>
-      <c r="E93" s="53" t="s">
-        <v>180</v>
-      </c>
-      <c r="F93" s="53"/>
-      <c r="G93" s="53" t="s">
-        <v>187</v>
-      </c>
-      <c r="H93" s="53"/>
-      <c r="I93" s="53"/>
-      <c r="J93" s="53"/>
-      <c r="K93" s="17"/>
-    </row>
-    <row r="94" spans="1:11">
-      <c r="A94" s="52"/>
-      <c r="B94" s="53">
-        <v>77</v>
-      </c>
-      <c r="C94" s="53" t="s">
-        <v>178</v>
-      </c>
-      <c r="D94" s="53" t="s">
-        <v>179</v>
-      </c>
-      <c r="E94" s="53" t="s">
-        <v>180</v>
-      </c>
-      <c r="F94" s="53"/>
-      <c r="G94" s="53" t="s">
-        <v>188</v>
-      </c>
-      <c r="H94" s="53"/>
-      <c r="I94" s="53"/>
-      <c r="J94" s="53"/>
-      <c r="K94" s="17"/>
-    </row>
-    <row r="95" spans="1:11">
-      <c r="A95" s="52"/>
-      <c r="B95" s="53">
-        <v>78</v>
-      </c>
-      <c r="C95" s="53" t="s">
-        <v>189</v>
-      </c>
-      <c r="D95" s="53" t="s">
-        <v>160</v>
-      </c>
-      <c r="E95" s="53" t="s">
-        <v>190</v>
-      </c>
-      <c r="F95" s="53"/>
-      <c r="G95" s="53" t="s">
-        <v>191</v>
-      </c>
-      <c r="H95" s="53"/>
-      <c r="I95" s="53"/>
-      <c r="J95" s="53"/>
-      <c r="K95" s="17"/>
-    </row>
-    <row r="96" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A96" s="18"/>
-      <c r="B96" s="46"/>
-      <c r="C96" s="46"/>
-      <c r="D96" s="46"/>
-      <c r="E96" s="47"/>
-      <c r="F96" s="48"/>
-      <c r="G96" s="47"/>
-      <c r="H96" s="48"/>
-      <c r="I96" s="47"/>
-      <c r="J96" s="48"/>
-    </row>
-    <row r="97" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A97" s="18"/>
-      <c r="B97" s="46"/>
-      <c r="C97" s="46"/>
-      <c r="D97" s="46"/>
-      <c r="E97" s="49"/>
-      <c r="F97" s="48"/>
-      <c r="G97" s="50"/>
-      <c r="H97" s="48"/>
-      <c r="I97" s="50"/>
-      <c r="J97" s="48"/>
-    </row>
-    <row r="98" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A98" s="13"/>
-      <c r="B98" s="13"/>
-      <c r="C98" s="13"/>
-      <c r="D98" s="13"/>
-      <c r="E98" s="13"/>
-      <c r="F98" s="13"/>
-      <c r="G98" s="13"/>
-      <c r="H98" s="13"/>
-      <c r="I98" s="13"/>
-      <c r="J98" s="13"/>
-    </row>
-    <row r="99" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A99" s="19"/>
-      <c r="B99" s="40" t="s">
-        <v>192</v>
-      </c>
-      <c r="C99" s="30"/>
-      <c r="D99" s="30"/>
-      <c r="E99" s="30"/>
-      <c r="F99" s="30"/>
-      <c r="G99" s="30"/>
-      <c r="H99" s="30"/>
-      <c r="I99" s="30"/>
-      <c r="J99" s="30"/>
-    </row>
-    <row r="100" spans="1:11" customHeight="1" ht="9">
-      <c r="A100" s="20"/>
-      <c r="B100" s="20"/>
-      <c r="C100" s="20"/>
-      <c r="D100" s="20"/>
-      <c r="E100" s="20"/>
-      <c r="F100" s="20"/>
-      <c r="G100" s="20"/>
-      <c r="H100" s="20"/>
-      <c r="I100" s="20"/>
-      <c r="J100" s="20"/>
-    </row>
-    <row r="101" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A101" s="20"/>
-      <c r="B101" s="43" t="s">
-        <v>193</v>
-      </c>
-      <c r="C101" s="30"/>
-      <c r="D101" s="30"/>
-      <c r="E101" s="30"/>
-      <c r="F101" s="30"/>
-      <c r="G101" s="30"/>
-      <c r="H101" s="30"/>
-      <c r="I101" s="30"/>
-      <c r="J101" s="30"/>
-    </row>
-    <row r="102" spans="1:11" customHeight="1" ht="15">
-      <c r="A102" s="20"/>
-      <c r="B102" s="43" t="s">
-        <v>194</v>
-      </c>
-      <c r="C102" s="30"/>
-      <c r="D102" s="30"/>
-      <c r="E102" s="30"/>
-      <c r="F102" s="30"/>
-      <c r="G102" s="30"/>
-      <c r="H102" s="30"/>
-      <c r="I102" s="30"/>
-      <c r="J102" s="30"/>
-    </row>
-    <row r="103" spans="1:11" customHeight="1" ht="15">
-      <c r="A103" s="20"/>
-      <c r="B103" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="C103" s="30"/>
-      <c r="D103" s="30"/>
-      <c r="E103" s="30"/>
-      <c r="F103" s="30"/>
-      <c r="G103" s="30"/>
-      <c r="H103" s="30"/>
-      <c r="I103" s="30"/>
-      <c r="J103" s="30"/>
-    </row>
-    <row r="104" spans="1:11" customHeight="1" ht="15">
-      <c r="A104" s="20"/>
-      <c r="B104" s="43" t="s">
-        <v>196</v>
-      </c>
-      <c r="C104" s="30"/>
-      <c r="D104" s="30"/>
-      <c r="E104" s="30"/>
-      <c r="F104" s="30"/>
-      <c r="G104" s="30"/>
-      <c r="H104" s="30"/>
-      <c r="I104" s="30"/>
-      <c r="J104" s="30"/>
-    </row>
-    <row r="105" spans="1:11" customHeight="1" ht="15">
-      <c r="A105" s="20"/>
-      <c r="B105" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="C105" s="30"/>
-      <c r="D105" s="30"/>
-      <c r="E105" s="30"/>
-      <c r="F105" s="30"/>
-      <c r="G105" s="30"/>
-      <c r="H105" s="30"/>
-      <c r="I105" s="30"/>
-      <c r="J105" s="30"/>
-    </row>
-    <row r="106" spans="1:11" customHeight="1" ht="12">
-      <c r="A106" s="21"/>
-      <c r="B106" s="44"/>
-      <c r="C106" s="30"/>
-      <c r="D106" s="30"/>
-      <c r="E106" s="30"/>
-      <c r="F106" s="30"/>
-      <c r="G106" s="30"/>
-      <c r="H106" s="30"/>
-      <c r="I106" s="30"/>
-      <c r="J106" s="30"/>
-    </row>
-    <row r="107" spans="1:11" customHeight="1" ht="27.75">
-      <c r="A107" s="17"/>
-      <c r="B107" s="45" t="s">
-        <v>198</v>
-      </c>
-      <c r="C107" s="30"/>
-      <c r="D107" s="30"/>
-      <c r="E107" s="30"/>
-      <c r="F107" s="30"/>
-      <c r="G107" s="30"/>
-      <c r="H107" s="30"/>
-      <c r="I107" s="30"/>
-      <c r="J107" s="30"/>
-    </row>
-    <row r="108" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A108" s="22"/>
-      <c r="B108" s="22"/>
-      <c r="C108" s="22"/>
-      <c r="D108" s="22"/>
-      <c r="E108" s="22"/>
-      <c r="H108" s="15"/>
-      <c r="I108" s="15"/>
-      <c r="J108" s="15"/>
-    </row>
-    <row r="109" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C109" s="22"/>
-      <c r="D109" s="22"/>
-      <c r="E109" s="22"/>
-      <c r="I109" s="15"/>
-      <c r="J109" s="15"/>
-    </row>
-    <row r="110" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A110" s="22"/>
-      <c r="B110" s="22"/>
-      <c r="C110" s="41" t="s">
-        <v>199</v>
-      </c>
-      <c r="D110" s="30"/>
-      <c r="E110" s="30"/>
-      <c r="H110" s="42" t="s">
-        <v>200</v>
-      </c>
-      <c r="I110" s="30"/>
-      <c r="J110" s="30"/>
-    </row>
-    <row r="111" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="112" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C112" s="23"/>
-      <c r="D112" s="23"/>
-      <c r="E112" s="23"/>
-      <c r="H112" s="23"/>
-      <c r="I112" s="23"/>
-      <c r="J112" s="23"/>
-    </row>
-    <row r="113" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="114" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C114" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="D114" s="30"/>
-      <c r="E114" s="30"/>
-      <c r="H114" s="41" t="str">
+      <c r="D107" s="26"/>
+      <c r="E107" s="26"/>
+      <c r="H107" s="25" t="str">
         <f>C8</f>
         <v>Alejandro Cancino Arguello</v>
       </c>
-      <c r="I114" s="30"/>
-      <c r="J114" s="30"/>
-    </row>
-    <row r="115" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C115" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="D115" s="30"/>
-      <c r="E115" s="30"/>
-      <c r="H115" s="41" t="str">
-        <f>C10</f>
-        <v>Coordinador de TI</v>
-      </c>
-      <c r="I115" s="30"/>
-      <c r="J115" s="30"/>
-    </row>
-    <row r="116" spans="1:11" customHeight="1" ht="15.75">
-      <c r="H116" s="22"/>
-      <c r="I116" s="22"/>
-      <c r="J116" s="22"/>
-    </row>
-    <row r="117" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="118" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A118" s="22"/>
-      <c r="B118" s="22"/>
-      <c r="C118" s="22"/>
-      <c r="D118" s="22"/>
-      <c r="E118" s="22"/>
+      <c r="I107" s="26"/>
+      <c r="J107" s="26"/>
+    </row>
+    <row r="108" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C108" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="D108" s="26"/>
+      <c r="E108" s="26"/>
+      <c r="H108" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="I108" s="26"/>
+      <c r="J108" s="26"/>
+    </row>
+    <row r="109" spans="1:11" customHeight="1" ht="15.75">
+      <c r="H109" s="22"/>
+      <c r="I109" s="22"/>
+      <c r="J109" s="22"/>
+    </row>
+    <row r="110" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="111" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A111" s="22"/>
+      <c r="B111" s="22"/>
+      <c r="C111" s="22"/>
+      <c r="D111" s="22"/>
+      <c r="E111" s="22"/>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="C114:E114"/>
-    <mergeCell ref="H114:J114"/>
-    <mergeCell ref="C115:E115"/>
-    <mergeCell ref="H115:J115"/>
-    <mergeCell ref="B101:J101"/>
-    <mergeCell ref="B102:J102"/>
-    <mergeCell ref="B103:J103"/>
-    <mergeCell ref="B104:J104"/>
-    <mergeCell ref="B105:J105"/>
-    <mergeCell ref="B106:J106"/>
-    <mergeCell ref="B107:J107"/>
-    <mergeCell ref="E97:F97"/>
-    <mergeCell ref="G97:H97"/>
-    <mergeCell ref="I97:J97"/>
-    <mergeCell ref="B99:J99"/>
-    <mergeCell ref="C110:E110"/>
-    <mergeCell ref="H110:J110"/>
-    <mergeCell ref="E96:F96"/>
-    <mergeCell ref="G96:H96"/>
-    <mergeCell ref="I96:J96"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="B12:J14"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="C2:H4"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="C5:J6"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="B12:J14"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="G89:H89"/>
+    <mergeCell ref="I89:J89"/>
+    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="G90:H90"/>
+    <mergeCell ref="I90:J90"/>
+    <mergeCell ref="B92:J92"/>
+    <mergeCell ref="C103:E103"/>
+    <mergeCell ref="H103:J103"/>
+    <mergeCell ref="C107:E107"/>
+    <mergeCell ref="H107:J107"/>
+    <mergeCell ref="C108:E108"/>
+    <mergeCell ref="H108:J108"/>
+    <mergeCell ref="B94:J94"/>
+    <mergeCell ref="B95:J95"/>
+    <mergeCell ref="B96:J96"/>
+    <mergeCell ref="B97:J97"/>
+    <mergeCell ref="B98:J98"/>
+    <mergeCell ref="B99:J99"/>
+    <mergeCell ref="B100:J100"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I17:J17"/>
@@ -3801,28 +3587,7 @@
     <mergeCell ref="E88:F88"/>
     <mergeCell ref="G88:H88"/>
     <mergeCell ref="I88:J88"/>
-    <mergeCell ref="E89:F89"/>
-    <mergeCell ref="G89:H89"/>
-    <mergeCell ref="I89:J89"/>
-    <mergeCell ref="E90:F90"/>
-    <mergeCell ref="G90:H90"/>
-    <mergeCell ref="I90:J90"/>
-    <mergeCell ref="E91:F91"/>
-    <mergeCell ref="G91:H91"/>
-    <mergeCell ref="I91:J91"/>
-    <mergeCell ref="E92:F92"/>
-    <mergeCell ref="G92:H92"/>
-    <mergeCell ref="I92:J92"/>
-    <mergeCell ref="E93:F93"/>
-    <mergeCell ref="G93:H93"/>
-    <mergeCell ref="I93:J93"/>
-    <mergeCell ref="E94:F94"/>
-    <mergeCell ref="G94:H94"/>
-    <mergeCell ref="I94:J94"/>
-    <mergeCell ref="E95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="I95:J95"/>
-    <mergeCell ref="I17:J95"/>
+    <mergeCell ref="I17:J88"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>

--- a/database/controller_excel/Resguardo_Alejandro_Cancino_Arguello.xlsx
+++ b/database/controller_excel/Resguardo_Alejandro_Cancino_Arguello.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="157">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,21 +41,27 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>01/07/2025</t>
+    <t>02/07/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
+    <t>TI</t>
+  </si>
+  <si>
     <t>Región:</t>
   </si>
   <si>
-    <t>Norte</t>
+    <t>Sur</t>
   </si>
   <si>
     <t>Ubicación:</t>
   </si>
   <si>
+    <t>Base Operativa</t>
+  </si>
+  <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
   </si>
   <si>
@@ -149,111 +155,60 @@
     <t>BRNFSL1</t>
   </si>
   <si>
-    <t>SERVIDOR 18</t>
-  </si>
-  <si>
-    <t>POWEREDGE R720</t>
-  </si>
-  <si>
-    <t>B3X7RV1</t>
-  </si>
-  <si>
-    <t>SAN</t>
-  </si>
-  <si>
-    <t>POWERVAULT MD3200i</t>
-  </si>
-  <si>
-    <t>48DT7V1</t>
-  </si>
-  <si>
-    <t>Monitor</t>
+    <t>UNIDAD DE CINTAS 19</t>
+  </si>
+  <si>
+    <t>POWER VAULT 114 X</t>
+  </si>
+  <si>
+    <t>YN106813H628</t>
+  </si>
+  <si>
+    <t>SERVIDOR 27</t>
+  </si>
+  <si>
+    <t>POWEREDGE 2950</t>
+  </si>
+  <si>
+    <t>DPBP6K1</t>
+  </si>
+  <si>
+    <t>SERVIDOR 29</t>
+  </si>
+  <si>
+    <t>POWEREDGE R320</t>
+  </si>
+  <si>
+    <t>D64MW12</t>
+  </si>
+  <si>
+    <t>DVR HIKVISION</t>
+  </si>
+  <si>
+    <t>HIKVISION</t>
+  </si>
+  <si>
+    <t>DS-7716NI-I4/16P</t>
+  </si>
+  <si>
+    <t>Switch 8 Puertos</t>
+  </si>
+  <si>
+    <t>Planet</t>
+  </si>
+  <si>
+    <t>GSD-804P</t>
+  </si>
+  <si>
+    <t>A350106300034</t>
+  </si>
+  <si>
+    <t>Access PRO</t>
   </si>
   <si>
     <t>NA</t>
   </si>
   <si>
-    <t>UNIDAD DE CINTAS 19</t>
-  </si>
-  <si>
-    <t>POWER VAULT 114 X</t>
-  </si>
-  <si>
-    <t>YN106813H628</t>
-  </si>
-  <si>
-    <t>SERVIDOR 27</t>
-  </si>
-  <si>
-    <t>POWEREDGE 2950</t>
-  </si>
-  <si>
-    <t>DPBP6K1</t>
-  </si>
-  <si>
-    <t>SERVIDOR 29</t>
-  </si>
-  <si>
-    <t>POWEREDGE R320</t>
-  </si>
-  <si>
-    <t>D64MW12</t>
-  </si>
-  <si>
-    <t>UNIDAD DE CINTAS</t>
-  </si>
-  <si>
-    <t>POWER VAULT 124 T</t>
-  </si>
-  <si>
-    <t>8DDB6K1</t>
-  </si>
-  <si>
-    <t>Switch Linksys Cisco SD216</t>
-  </si>
-  <si>
-    <t>SD216</t>
-  </si>
-  <si>
-    <t>NVR</t>
-  </si>
-  <si>
-    <t>HIKVISION</t>
-  </si>
-  <si>
-    <t>DS-7616NI-K2/16P</t>
-  </si>
-  <si>
-    <t>L48074542</t>
-  </si>
-  <si>
-    <t>DVR HIKVISION</t>
-  </si>
-  <si>
-    <t>DS-7716NI-I4/16P</t>
-  </si>
-  <si>
-    <t>Mouse</t>
-  </si>
-  <si>
-    <t>3D Optical</t>
-  </si>
-  <si>
-    <t>Switch 8 Puertos</t>
-  </si>
-  <si>
-    <t>Planet</t>
-  </si>
-  <si>
-    <t>GSD-804P</t>
-  </si>
-  <si>
-    <t>A350106300034</t>
-  </si>
-  <si>
-    <t>Access PRO</t>
-  </si>
-  <si>
     <t>AP233</t>
   </si>
   <si>
@@ -293,66 +248,33 @@
     <t>F0C1514X0EZ</t>
   </si>
   <si>
-    <t>FOC1903S1ME</t>
-  </si>
-  <si>
-    <t>Catalyst 3750X-24T-E</t>
-  </si>
-  <si>
-    <t>FD01816Z3AU</t>
-  </si>
-  <si>
-    <t>FIREWALL</t>
+    <t>ROUTER</t>
+  </si>
+  <si>
+    <t>CISCO 1900 SERIES</t>
+  </si>
+  <si>
+    <t>FTX174386AU</t>
+  </si>
+  <si>
+    <t>UPS</t>
+  </si>
+  <si>
+    <t>APC</t>
+  </si>
+  <si>
+    <t>APC Galaxy 3500</t>
+  </si>
+  <si>
+    <t>G35TF30KB4F</t>
+  </si>
+  <si>
+    <t>ACCESSPOINT</t>
   </si>
   <si>
     <t>FORTINET</t>
   </si>
   <si>
-    <t>FG100D3G14827870</t>
-  </si>
-  <si>
-    <t>FG100D3G14827806 MASTER</t>
-  </si>
-  <si>
-    <t>FG100D3G14827806</t>
-  </si>
-  <si>
-    <t>FG100D3G14827870 SLAVE</t>
-  </si>
-  <si>
-    <t>CALL MANAGER</t>
-  </si>
-  <si>
-    <t>FTX1328AHLG</t>
-  </si>
-  <si>
-    <t>ROUTER</t>
-  </si>
-  <si>
-    <t>CISCO 1900 SERIES</t>
-  </si>
-  <si>
-    <t>CFTX1614857Q</t>
-  </si>
-  <si>
-    <t>FTX174386AU</t>
-  </si>
-  <si>
-    <t>UPS</t>
-  </si>
-  <si>
-    <t>APC</t>
-  </si>
-  <si>
-    <t>APC Galaxy 3500</t>
-  </si>
-  <si>
-    <t>G35TF30KB4F</t>
-  </si>
-  <si>
-    <t>ACCESSPOINT</t>
-  </si>
-  <si>
     <t>221E</t>
   </si>
   <si>
@@ -434,6 +356,15 @@
     <t>I520150207CCWR502802497</t>
   </si>
   <si>
+    <t>DS-2CD2422FWD-IW</t>
+  </si>
+  <si>
+    <t>IW20170808AAWR808998451</t>
+  </si>
+  <si>
+    <t>I20140922CCWR480540755</t>
+  </si>
+  <si>
     <t>Docking Station</t>
   </si>
   <si>
@@ -443,51 +374,42 @@
     <t>F9WQSB3</t>
   </si>
   <si>
-    <t>I20140922CCWR480540755</t>
+    <t>DS-2CD2T42WD-I5</t>
+  </si>
+  <si>
+    <t>I520160810BBWR633078836</t>
+  </si>
+  <si>
+    <t>I520160810BBWR633078735</t>
+  </si>
+  <si>
+    <t>I520160810BBWR633078506</t>
+  </si>
+  <si>
+    <t>A20150122CCWR500502035</t>
+  </si>
+  <si>
+    <t>KOBLENZ</t>
+  </si>
+  <si>
+    <t>4816 R</t>
+  </si>
+  <si>
+    <t>16-09-17766</t>
+  </si>
+  <si>
+    <t>Lector Biometrico</t>
+  </si>
+  <si>
+    <t>BioEntry W2</t>
+  </si>
+  <si>
+    <t>BEW2-0DP</t>
   </si>
   <si>
     <t>I20140922CCWR480540785</t>
   </si>
   <si>
-    <t>DS-2CD2T42WD-I5</t>
-  </si>
-  <si>
-    <t>I520160810BBWR633078836</t>
-  </si>
-  <si>
-    <t>I520160810BBWR633078735</t>
-  </si>
-  <si>
-    <t>I520160810BBWR633078506</t>
-  </si>
-  <si>
-    <t>A20150122CCWR500502035</t>
-  </si>
-  <si>
-    <t>KOBLENZ</t>
-  </si>
-  <si>
-    <t>4816 R</t>
-  </si>
-  <si>
-    <t>16-09-17766</t>
-  </si>
-  <si>
-    <t>DS-2CD2422FWD-IW</t>
-  </si>
-  <si>
-    <t>IW20170808AAWR808998451</t>
-  </si>
-  <si>
-    <t>Lector Biometrico</t>
-  </si>
-  <si>
-    <t>BioEntry W2</t>
-  </si>
-  <si>
-    <t>BEW2-0DP</t>
-  </si>
-  <si>
     <t>Equipo de Videoconferencia</t>
   </si>
   <si>
@@ -561,12 +483,6 @@
   </si>
   <si>
     <t>ACEPTA Y RECIBE:</t>
-  </si>
-  <si>
-    <t>Cristobal Soto Escalante</t>
-  </si>
-  <si>
-    <t>Coordinador de Proyectos</t>
   </si>
   <si>
     <t>Coordinador de TI</t>
@@ -1236,7 +1152,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K111"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="12.5546875" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="true" style="0"/>
@@ -1362,20 +1278,20 @@
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>11</v>
-      </c>
       <c r="I10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J10" s="6">
-        <v>95</v>
+        <v>13</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:11" customHeight="1" ht="15.75">
@@ -1384,7 +1300,7 @@
     <row r="12" spans="1:11" customHeight="1" ht="15.75">
       <c r="A12" s="13"/>
       <c r="B12" s="38" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C12" s="26"/>
       <c r="D12" s="26"/>
@@ -1433,24 +1349,24 @@
     <row r="16" spans="1:11" customHeight="1" ht="15.75">
       <c r="A16" s="15"/>
       <c r="B16" s="16" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E16" s="39" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="39" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H16" s="40"/>
       <c r="I16" s="39" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J16" s="40"/>
       <c r="K16" s="17"/>
@@ -1461,17 +1377,17 @@
         <v>1</v>
       </c>
       <c r="C17" s="53" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D17" s="53" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E17" s="53" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F17" s="53"/>
       <c r="G17" s="53" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H17" s="53"/>
       <c r="I17" s="53"/>
@@ -1484,7 +1400,7 @@
       <c r="C18" s="53"/>
       <c r="D18" s="53"/>
       <c r="E18" s="51" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F18" s="53"/>
       <c r="G18" s="53"/>
@@ -1499,17 +1415,17 @@
         <v>2</v>
       </c>
       <c r="C19" s="53" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D19" s="53" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E19" s="53" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F19" s="53"/>
       <c r="G19" s="53" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H19" s="53"/>
       <c r="I19" s="53"/>
@@ -1522,13 +1438,13 @@
         <v>3</v>
       </c>
       <c r="C20" s="53" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D20" s="53" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E20" s="53" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F20" s="53"/>
       <c r="G20" s="53">
@@ -1545,17 +1461,17 @@
         <v>4</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D21" s="53" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E21" s="53" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F21" s="53"/>
       <c r="G21" s="53" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H21" s="53"/>
       <c r="I21" s="53"/>
@@ -1568,17 +1484,17 @@
         <v>5</v>
       </c>
       <c r="C22" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="53" t="s">
         <v>35</v>
-      </c>
-      <c r="D22" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="53" t="s">
-        <v>33</v>
       </c>
       <c r="F22" s="53"/>
       <c r="G22" s="53" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H22" s="53"/>
       <c r="I22" s="53"/>
@@ -1591,17 +1507,17 @@
         <v>6</v>
       </c>
       <c r="C23" s="53" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D23" s="53" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E23" s="53" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F23" s="53"/>
       <c r="G23" s="53" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H23" s="53"/>
       <c r="I23" s="53"/>
@@ -1614,17 +1530,17 @@
         <v>7</v>
       </c>
       <c r="C24" s="53" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D24" s="53" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E24" s="53" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F24" s="53"/>
       <c r="G24" s="53" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H24" s="53"/>
       <c r="I24" s="53"/>
@@ -1637,17 +1553,17 @@
         <v>8</v>
       </c>
       <c r="C25" s="53" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D25" s="53" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E25" s="53" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F25" s="53"/>
       <c r="G25" s="53" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H25" s="53"/>
       <c r="I25" s="53"/>
@@ -1660,17 +1576,17 @@
         <v>9</v>
       </c>
       <c r="C26" s="53" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D26" s="53" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E26" s="53" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="53" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H26" s="53"/>
       <c r="I26" s="53"/>
@@ -1683,17 +1599,17 @@
         <v>10</v>
       </c>
       <c r="C27" s="53" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D27" s="53" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E27" s="53" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F27" s="53"/>
       <c r="G27" s="53" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H27" s="53"/>
       <c r="I27" s="53"/>
@@ -1706,17 +1622,17 @@
         <v>11</v>
       </c>
       <c r="C28" s="53" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D28" s="53" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="E28" s="53" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F28" s="53"/>
-      <c r="G28" s="53" t="s">
-        <v>54</v>
+      <c r="G28" s="53">
+        <v>647235228</v>
       </c>
       <c r="H28" s="53"/>
       <c r="I28" s="53"/>
@@ -1729,17 +1645,17 @@
         <v>12</v>
       </c>
       <c r="C29" s="53" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D29" s="53" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="E29" s="53" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F29" s="53"/>
       <c r="G29" s="53" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H29" s="53"/>
       <c r="I29" s="53"/>
@@ -1752,17 +1668,17 @@
         <v>13</v>
       </c>
       <c r="C30" s="53" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D30" s="53" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E30" s="53" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F30" s="53"/>
       <c r="G30" s="53" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H30" s="53"/>
       <c r="I30" s="53"/>
@@ -1775,17 +1691,17 @@
         <v>14</v>
       </c>
       <c r="C31" s="53" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D31" s="53" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E31" s="53" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F31" s="53"/>
       <c r="G31" s="53" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H31" s="53"/>
       <c r="I31" s="53"/>
@@ -1798,17 +1714,17 @@
         <v>15</v>
       </c>
       <c r="C32" s="53" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D32" s="53" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E32" s="53" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F32" s="53"/>
       <c r="G32" s="53" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="H32" s="53"/>
       <c r="I32" s="53"/>
@@ -1824,10 +1740,10 @@
         <v>66</v>
       </c>
       <c r="D33" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="E33" s="53" t="s">
         <v>67</v>
-      </c>
-      <c r="E33" s="53" t="s">
-        <v>68</v>
       </c>
       <c r="F33" s="53"/>
       <c r="G33" s="53" t="s">
@@ -1844,17 +1760,17 @@
         <v>17</v>
       </c>
       <c r="C34" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="D34" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="E34" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53" t="s">
         <v>70</v>
-      </c>
-      <c r="D34" s="53" t="s">
-        <v>67</v>
-      </c>
-      <c r="E34" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="F34" s="53"/>
-      <c r="G34" s="53">
-        <v>647235228</v>
       </c>
       <c r="H34" s="53"/>
       <c r="I34" s="53"/>
@@ -1867,17 +1783,17 @@
         <v>18</v>
       </c>
       <c r="C35" s="53" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D35" s="53" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="E35" s="53" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="F35" s="53"/>
       <c r="G35" s="53" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="H35" s="53"/>
       <c r="I35" s="53"/>
@@ -1890,17 +1806,17 @@
         <v>19</v>
       </c>
       <c r="C36" s="53" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D36" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="E36" s="53" t="s">
         <v>73</v>
-      </c>
-      <c r="E36" s="53" t="s">
-        <v>51</v>
       </c>
       <c r="F36" s="53"/>
       <c r="G36" s="53" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="H36" s="53"/>
       <c r="I36" s="53"/>
@@ -1913,17 +1829,17 @@
         <v>20</v>
       </c>
       <c r="C37" s="53" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D37" s="53" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="E37" s="53" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F37" s="53"/>
       <c r="G37" s="53" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H37" s="53"/>
       <c r="I37" s="53"/>
@@ -1936,17 +1852,17 @@
         <v>21</v>
       </c>
       <c r="C38" s="53" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D38" s="53" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="E38" s="53" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="F38" s="53"/>
       <c r="G38" s="53" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H38" s="53"/>
       <c r="I38" s="53"/>
@@ -1959,17 +1875,17 @@
         <v>22</v>
       </c>
       <c r="C39" s="53" t="s">
+        <v>77</v>
+      </c>
+      <c r="D39" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="E39" s="53" t="s">
         <v>78</v>
-      </c>
-      <c r="D39" s="53" t="s">
-        <v>78</v>
-      </c>
-      <c r="E39" s="53" t="s">
-        <v>51</v>
       </c>
       <c r="F39" s="53"/>
       <c r="G39" s="53" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H39" s="53"/>
       <c r="I39" s="53"/>
@@ -1982,10 +1898,10 @@
         <v>23</v>
       </c>
       <c r="C40" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="53" t="s">
         <v>81</v>
-      </c>
-      <c r="D40" s="53" t="s">
-        <v>38</v>
       </c>
       <c r="E40" s="53" t="s">
         <v>82</v>
@@ -2005,17 +1921,17 @@
         <v>24</v>
       </c>
       <c r="C41" s="53" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D41" s="53" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="E41" s="53" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F41" s="53"/>
       <c r="G41" s="53" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H41" s="53"/>
       <c r="I41" s="53"/>
@@ -2028,17 +1944,17 @@
         <v>25</v>
       </c>
       <c r="C42" s="53" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D42" s="53" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="E42" s="53" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F42" s="53"/>
       <c r="G42" s="53" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H42" s="53"/>
       <c r="I42" s="53"/>
@@ -2051,17 +1967,17 @@
         <v>26</v>
       </c>
       <c r="C43" s="53" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D43" s="53" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="E43" s="53" t="s">
         <v>86</v>
       </c>
       <c r="F43" s="53"/>
       <c r="G43" s="53" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H43" s="53"/>
       <c r="I43" s="53"/>
@@ -2074,17 +1990,17 @@
         <v>27</v>
       </c>
       <c r="C44" s="53" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D44" s="53" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="E44" s="53" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F44" s="53"/>
       <c r="G44" s="53" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H44" s="53"/>
       <c r="I44" s="53"/>
@@ -2097,17 +2013,17 @@
         <v>28</v>
       </c>
       <c r="C45" s="53" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D45" s="53" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="E45" s="53" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F45" s="53"/>
       <c r="G45" s="53" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H45" s="53"/>
       <c r="I45" s="53"/>
@@ -2120,17 +2036,17 @@
         <v>29</v>
       </c>
       <c r="C46" s="53" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D46" s="53" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E46" s="53" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="F46" s="53"/>
       <c r="G46" s="53" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="H46" s="53"/>
       <c r="I46" s="53"/>
@@ -2143,17 +2059,17 @@
         <v>30</v>
       </c>
       <c r="C47" s="53" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D47" s="53" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E47" s="53" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="F47" s="53"/>
       <c r="G47" s="53" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H47" s="53"/>
       <c r="I47" s="53"/>
@@ -2166,17 +2082,17 @@
         <v>31</v>
       </c>
       <c r="C48" s="53" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="D48" s="53" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E48" s="53" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F48" s="53"/>
       <c r="G48" s="53" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="H48" s="53"/>
       <c r="I48" s="53"/>
@@ -2189,17 +2105,17 @@
         <v>32</v>
       </c>
       <c r="C49" s="53" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D49" s="53" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="E49" s="53" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F49" s="53"/>
       <c r="G49" s="53" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H49" s="53"/>
       <c r="I49" s="53"/>
@@ -2212,17 +2128,17 @@
         <v>33</v>
       </c>
       <c r="C50" s="53" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D50" s="53" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="E50" s="53" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F50" s="53"/>
       <c r="G50" s="53" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H50" s="53"/>
       <c r="I50" s="53"/>
@@ -2235,15 +2151,17 @@
         <v>34</v>
       </c>
       <c r="C51" s="53" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D51" s="53" t="s">
-        <v>38</v>
-      </c>
-      <c r="E51" s="53"/>
+        <v>56</v>
+      </c>
+      <c r="E51" s="53" t="s">
+        <v>105</v>
+      </c>
       <c r="F51" s="53"/>
       <c r="G51" s="53" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H51" s="53"/>
       <c r="I51" s="53"/>
@@ -2256,17 +2174,17 @@
         <v>35</v>
       </c>
       <c r="C52" s="53" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D52" s="53" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E52" s="53" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F52" s="53"/>
       <c r="G52" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H52" s="53"/>
       <c r="I52" s="53"/>
@@ -2279,17 +2197,17 @@
         <v>36</v>
       </c>
       <c r="C53" s="53" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D53" s="53" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E53" s="53" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F53" s="53"/>
       <c r="G53" s="53" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H53" s="53"/>
       <c r="I53" s="53"/>
@@ -2302,17 +2220,17 @@
         <v>37</v>
       </c>
       <c r="C54" s="53" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="D54" s="53" t="s">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="E54" s="53" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F54" s="53"/>
       <c r="G54" s="53" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H54" s="53"/>
       <c r="I54" s="53"/>
@@ -2325,17 +2243,17 @@
         <v>38</v>
       </c>
       <c r="C55" s="53" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="D55" s="53" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="E55" s="53" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="F55" s="53"/>
       <c r="G55" s="53" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H55" s="53"/>
       <c r="I55" s="53"/>
@@ -2348,17 +2266,17 @@
         <v>39</v>
       </c>
       <c r="C56" s="53" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="D56" s="53" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="E56" s="53" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="F56" s="53"/>
       <c r="G56" s="53" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H56" s="53"/>
       <c r="I56" s="53"/>
@@ -2371,17 +2289,17 @@
         <v>40</v>
       </c>
       <c r="C57" s="53" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="D57" s="53" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="E57" s="53" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="F57" s="53"/>
       <c r="G57" s="53" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H57" s="53"/>
       <c r="I57" s="53"/>
@@ -2394,17 +2312,17 @@
         <v>41</v>
       </c>
       <c r="C58" s="53" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="D58" s="53" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="E58" s="53" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F58" s="53"/>
       <c r="G58" s="53" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H58" s="53"/>
       <c r="I58" s="53"/>
@@ -2417,17 +2335,17 @@
         <v>42</v>
       </c>
       <c r="C59" s="53" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="D59" s="53" t="s">
-        <v>118</v>
+        <v>56</v>
       </c>
       <c r="E59" s="53" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="F59" s="53"/>
       <c r="G59" s="53" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H59" s="53"/>
       <c r="I59" s="53"/>
@@ -2440,17 +2358,17 @@
         <v>43</v>
       </c>
       <c r="C60" s="53" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D60" s="53" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="E60" s="53" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F60" s="53"/>
       <c r="G60" s="53" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H60" s="53"/>
       <c r="I60" s="53"/>
@@ -2463,17 +2381,17 @@
         <v>44</v>
       </c>
       <c r="C61" s="53" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="D61" s="53" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E61" s="53" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F61" s="53"/>
       <c r="G61" s="53" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H61" s="53"/>
       <c r="I61" s="53"/>
@@ -2486,17 +2404,17 @@
         <v>45</v>
       </c>
       <c r="C62" s="53" t="s">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="D62" s="53" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E62" s="53" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F62" s="53"/>
       <c r="G62" s="53" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="H62" s="53"/>
       <c r="I62" s="53"/>
@@ -2509,17 +2427,17 @@
         <v>46</v>
       </c>
       <c r="C63" s="53" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="D63" s="53" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E63" s="53" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="F63" s="53"/>
       <c r="G63" s="53" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="H63" s="53"/>
       <c r="I63" s="53"/>
@@ -2532,17 +2450,17 @@
         <v>47</v>
       </c>
       <c r="C64" s="53" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="D64" s="53" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E64" s="53" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="F64" s="53"/>
       <c r="G64" s="53" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H64" s="53"/>
       <c r="I64" s="53"/>
@@ -2555,17 +2473,17 @@
         <v>48</v>
       </c>
       <c r="C65" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="D65" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="E65" s="53" t="s">
         <v>125</v>
-      </c>
-      <c r="D65" s="53" t="s">
-        <v>67</v>
-      </c>
-      <c r="E65" s="53" t="s">
-        <v>131</v>
       </c>
       <c r="F65" s="53"/>
       <c r="G65" s="53" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H65" s="53"/>
       <c r="I65" s="53"/>
@@ -2578,17 +2496,17 @@
         <v>49</v>
       </c>
       <c r="C66" s="53" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="D66" s="53" t="s">
-        <v>67</v>
+        <v>128</v>
       </c>
       <c r="E66" s="53" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F66" s="53"/>
-      <c r="G66" s="53" t="s">
-        <v>133</v>
+      <c r="G66" s="53">
+        <v>544161389</v>
       </c>
       <c r="H66" s="53"/>
       <c r="I66" s="53"/>
@@ -2601,17 +2519,17 @@
         <v>50</v>
       </c>
       <c r="C67" s="53" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="D67" s="53" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E67" s="53" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="F67" s="53"/>
       <c r="G67" s="53" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H67" s="53"/>
       <c r="I67" s="53"/>
@@ -2624,17 +2542,17 @@
         <v>51</v>
       </c>
       <c r="C68" s="53" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D68" s="53" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="E68" s="53" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F68" s="53"/>
       <c r="G68" s="53" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H68" s="53"/>
       <c r="I68" s="53"/>
@@ -2647,17 +2565,17 @@
         <v>52</v>
       </c>
       <c r="C69" s="53" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="D69" s="53" t="s">
-        <v>67</v>
+        <v>136</v>
       </c>
       <c r="E69" s="53" t="s">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="F69" s="53"/>
       <c r="G69" s="53" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H69" s="53"/>
       <c r="I69" s="53"/>
@@ -2670,17 +2588,17 @@
         <v>53</v>
       </c>
       <c r="C70" s="53" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="D70" s="53" t="s">
-        <v>67</v>
+        <v>139</v>
       </c>
       <c r="E70" s="53" t="s">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="F70" s="53"/>
       <c r="G70" s="53" t="s">
-        <v>137</v>
+        <v>63</v>
       </c>
       <c r="H70" s="53"/>
       <c r="I70" s="53"/>
@@ -2693,17 +2611,17 @@
         <v>54</v>
       </c>
       <c r="C71" s="53" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="D71" s="53" t="s">
-        <v>67</v>
+        <v>136</v>
       </c>
       <c r="E71" s="53" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="F71" s="53"/>
       <c r="G71" s="53" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H71" s="53"/>
       <c r="I71" s="53"/>
@@ -2716,17 +2634,17 @@
         <v>55</v>
       </c>
       <c r="C72" s="53" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D72" s="53" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="E72" s="53" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F72" s="53"/>
       <c r="G72" s="53" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H72" s="53"/>
       <c r="I72" s="53"/>
@@ -2739,17 +2657,17 @@
         <v>56</v>
       </c>
       <c r="C73" s="53" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="D73" s="53" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E73" s="53" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="F73" s="53"/>
       <c r="G73" s="53" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="H73" s="53"/>
       <c r="I73" s="53"/>
@@ -2762,581 +2680,259 @@
         <v>57</v>
       </c>
       <c r="C74" s="53" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="D74" s="53" t="s">
-        <v>67</v>
+        <v>128</v>
       </c>
       <c r="E74" s="53" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="F74" s="53"/>
-      <c r="G74" s="53" t="s">
-        <v>143</v>
+      <c r="G74" s="53">
+        <v>544161388</v>
       </c>
       <c r="H74" s="53"/>
       <c r="I74" s="53"/>
       <c r="J74" s="53"/>
       <c r="K74" s="17"/>
     </row>
-    <row r="75" spans="1:11">
-      <c r="A75" s="52"/>
-      <c r="B75" s="53">
-        <v>58</v>
-      </c>
-      <c r="C75" s="53" t="s">
-        <v>120</v>
-      </c>
-      <c r="D75" s="53" t="s">
-        <v>67</v>
-      </c>
-      <c r="E75" s="53" t="s">
-        <v>144</v>
-      </c>
-      <c r="F75" s="53"/>
-      <c r="G75" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="H75" s="53"/>
-      <c r="I75" s="53"/>
-      <c r="J75" s="53"/>
-      <c r="K75" s="17"/>
-    </row>
-    <row r="76" spans="1:11">
-      <c r="A76" s="52"/>
-      <c r="B76" s="53">
-        <v>59</v>
-      </c>
-      <c r="C76" s="53" t="s">
-        <v>120</v>
-      </c>
-      <c r="D76" s="53" t="s">
-        <v>67</v>
-      </c>
-      <c r="E76" s="53" t="s">
-        <v>144</v>
-      </c>
-      <c r="F76" s="53"/>
-      <c r="G76" s="53" t="s">
-        <v>146</v>
-      </c>
-      <c r="H76" s="53"/>
-      <c r="I76" s="53"/>
-      <c r="J76" s="53"/>
-      <c r="K76" s="17"/>
-    </row>
-    <row r="77" spans="1:11">
-      <c r="A77" s="52"/>
-      <c r="B77" s="53">
-        <v>60</v>
-      </c>
-      <c r="C77" s="53" t="s">
-        <v>120</v>
-      </c>
-      <c r="D77" s="53" t="s">
-        <v>67</v>
-      </c>
-      <c r="E77" s="53" t="s">
-        <v>144</v>
-      </c>
-      <c r="F77" s="53"/>
-      <c r="G77" s="53" t="s">
+    <row r="75" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A75" s="18"/>
+      <c r="B75" s="24"/>
+      <c r="C75" s="24"/>
+      <c r="D75" s="24"/>
+      <c r="E75" s="35"/>
+      <c r="F75" s="31"/>
+      <c r="G75" s="35"/>
+      <c r="H75" s="31"/>
+      <c r="I75" s="35"/>
+      <c r="J75" s="31"/>
+    </row>
+    <row r="76" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A76" s="18"/>
+      <c r="B76" s="24"/>
+      <c r="C76" s="24"/>
+      <c r="D76" s="24"/>
+      <c r="E76" s="30"/>
+      <c r="F76" s="31"/>
+      <c r="G76" s="32"/>
+      <c r="H76" s="31"/>
+      <c r="I76" s="32"/>
+      <c r="J76" s="31"/>
+    </row>
+    <row r="77" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A77" s="13"/>
+      <c r="B77" s="13"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="13"/>
+      <c r="E77" s="13"/>
+      <c r="F77" s="13"/>
+      <c r="G77" s="13"/>
+      <c r="H77" s="13"/>
+      <c r="I77" s="13"/>
+      <c r="J77" s="13"/>
+    </row>
+    <row r="78" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A78" s="19"/>
+      <c r="B78" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="H77" s="53"/>
-      <c r="I77" s="53"/>
-      <c r="J77" s="53"/>
-      <c r="K77" s="17"/>
-    </row>
-    <row r="78" spans="1:11">
-      <c r="A78" s="52"/>
-      <c r="B78" s="53">
-        <v>61</v>
-      </c>
-      <c r="C78" s="53" t="s">
-        <v>125</v>
-      </c>
-      <c r="D78" s="53" t="s">
-        <v>67</v>
-      </c>
-      <c r="E78" s="53" t="s">
-        <v>131</v>
-      </c>
-      <c r="F78" s="53"/>
-      <c r="G78" s="53" t="s">
+      <c r="C78" s="26"/>
+      <c r="D78" s="26"/>
+      <c r="E78" s="26"/>
+      <c r="F78" s="26"/>
+      <c r="G78" s="26"/>
+      <c r="H78" s="26"/>
+      <c r="I78" s="26"/>
+      <c r="J78" s="26"/>
+    </row>
+    <row r="79" spans="1:11" customHeight="1" ht="9">
+      <c r="A79" s="20"/>
+      <c r="B79" s="20"/>
+      <c r="C79" s="20"/>
+      <c r="D79" s="20"/>
+      <c r="E79" s="20"/>
+      <c r="F79" s="20"/>
+      <c r="G79" s="20"/>
+      <c r="H79" s="20"/>
+      <c r="I79" s="20"/>
+      <c r="J79" s="20"/>
+    </row>
+    <row r="80" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A80" s="20"/>
+      <c r="B80" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="H78" s="53"/>
-      <c r="I78" s="53"/>
-      <c r="J78" s="53"/>
-      <c r="K78" s="17"/>
-    </row>
-    <row r="79" spans="1:11">
-      <c r="A79" s="52"/>
-      <c r="B79" s="53">
-        <v>62</v>
-      </c>
-      <c r="C79" s="53" t="s">
-        <v>107</v>
-      </c>
-      <c r="D79" s="53" t="s">
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
+      <c r="H80" s="26"/>
+      <c r="I80" s="26"/>
+      <c r="J80" s="26"/>
+    </row>
+    <row r="81" spans="1:11" customHeight="1" ht="15">
+      <c r="A81" s="20"/>
+      <c r="B81" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="E79" s="53" t="s">
+      <c r="C81" s="26"/>
+      <c r="D81" s="26"/>
+      <c r="E81" s="26"/>
+      <c r="F81" s="26"/>
+      <c r="G81" s="26"/>
+      <c r="H81" s="26"/>
+      <c r="I81" s="26"/>
+      <c r="J81" s="26"/>
+    </row>
+    <row r="82" spans="1:11" customHeight="1" ht="15">
+      <c r="A82" s="20"/>
+      <c r="B82" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="F79" s="53"/>
-      <c r="G79" s="53" t="s">
+      <c r="C82" s="26"/>
+      <c r="D82" s="26"/>
+      <c r="E82" s="26"/>
+      <c r="F82" s="26"/>
+      <c r="G82" s="26"/>
+      <c r="H82" s="26"/>
+      <c r="I82" s="26"/>
+      <c r="J82" s="26"/>
+    </row>
+    <row r="83" spans="1:11" customHeight="1" ht="15">
+      <c r="A83" s="20"/>
+      <c r="B83" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="H79" s="53"/>
-      <c r="I79" s="53"/>
-      <c r="J79" s="53"/>
-      <c r="K79" s="17"/>
-    </row>
-    <row r="80" spans="1:11">
-      <c r="A80" s="52"/>
-      <c r="B80" s="53">
-        <v>63</v>
-      </c>
-      <c r="C80" s="53" t="s">
-        <v>120</v>
-      </c>
-      <c r="D80" s="53" t="s">
-        <v>67</v>
-      </c>
-      <c r="E80" s="53" t="s">
+      <c r="C83" s="26"/>
+      <c r="D83" s="26"/>
+      <c r="E83" s="26"/>
+      <c r="F83" s="26"/>
+      <c r="G83" s="26"/>
+      <c r="H83" s="26"/>
+      <c r="I83" s="26"/>
+      <c r="J83" s="26"/>
+    </row>
+    <row r="84" spans="1:11" customHeight="1" ht="15">
+      <c r="A84" s="20"/>
+      <c r="B84" s="27" t="s">
         <v>152</v>
       </c>
-      <c r="F80" s="53"/>
-      <c r="G80" s="53" t="s">
+      <c r="C84" s="26"/>
+      <c r="D84" s="26"/>
+      <c r="E84" s="26"/>
+      <c r="F84" s="26"/>
+      <c r="G84" s="26"/>
+      <c r="H84" s="26"/>
+      <c r="I84" s="26"/>
+      <c r="J84" s="26"/>
+    </row>
+    <row r="85" spans="1:11" customHeight="1" ht="12">
+      <c r="A85" s="21"/>
+      <c r="B85" s="28"/>
+      <c r="C85" s="26"/>
+      <c r="D85" s="26"/>
+      <c r="E85" s="26"/>
+      <c r="F85" s="26"/>
+      <c r="G85" s="26"/>
+      <c r="H85" s="26"/>
+      <c r="I85" s="26"/>
+      <c r="J85" s="26"/>
+    </row>
+    <row r="86" spans="1:11" customHeight="1" ht="27.75">
+      <c r="A86" s="17"/>
+      <c r="B86" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="H80" s="53"/>
-      <c r="I80" s="53"/>
-      <c r="J80" s="53"/>
-      <c r="K80" s="17"/>
-    </row>
-    <row r="81" spans="1:11">
-      <c r="A81" s="52"/>
-      <c r="B81" s="53">
-        <v>64</v>
-      </c>
-      <c r="C81" s="53" t="s">
+      <c r="C86" s="26"/>
+      <c r="D86" s="26"/>
+      <c r="E86" s="26"/>
+      <c r="F86" s="26"/>
+      <c r="G86" s="26"/>
+      <c r="H86" s="26"/>
+      <c r="I86" s="26"/>
+      <c r="J86" s="26"/>
+    </row>
+    <row r="87" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A87" s="22"/>
+      <c r="B87" s="22"/>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="H87" s="15"/>
+      <c r="I87" s="15"/>
+      <c r="J87" s="15"/>
+    </row>
+    <row r="88" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="I88" s="15"/>
+      <c r="J88" s="15"/>
+    </row>
+    <row r="89" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A89" s="22"/>
+      <c r="B89" s="22"/>
+      <c r="C89" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="D81" s="53" t="s">
+      <c r="D89" s="26"/>
+      <c r="E89" s="26"/>
+      <c r="H89" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="E81" s="53" t="s">
+      <c r="I89" s="26"/>
+      <c r="J89" s="26"/>
+    </row>
+    <row r="90" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="91" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C91" s="23"/>
+      <c r="D91" s="23"/>
+      <c r="E91" s="23"/>
+      <c r="H91" s="23"/>
+      <c r="I91" s="23"/>
+      <c r="J91" s="23"/>
+    </row>
+    <row r="92" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="93" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C93" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D93" s="26"/>
+      <c r="E93" s="26"/>
+      <c r="H93" s="25" t="str">
+        <f>C8</f>
+        <v>Alejandro Cancino Arguello</v>
+      </c>
+      <c r="I93" s="26"/>
+      <c r="J93" s="26"/>
+    </row>
+    <row r="94" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C94" s="25" t="s">
         <v>156</v>
       </c>
-      <c r="F81" s="53"/>
-      <c r="G81" s="53">
-        <v>544161388</v>
-      </c>
-      <c r="H81" s="53"/>
-      <c r="I81" s="53"/>
-      <c r="J81" s="53"/>
-      <c r="K81" s="17"/>
-    </row>
-    <row r="82" spans="1:11">
-      <c r="A82" s="52"/>
-      <c r="B82" s="53">
-        <v>65</v>
-      </c>
-      <c r="C82" s="53" t="s">
-        <v>157</v>
-      </c>
-      <c r="D82" s="53" t="s">
-        <v>158</v>
-      </c>
-      <c r="E82" s="53" t="s">
-        <v>159</v>
-      </c>
-      <c r="F82" s="53"/>
-      <c r="G82" s="53" t="s">
-        <v>160</v>
-      </c>
-      <c r="H82" s="53"/>
-      <c r="I82" s="53"/>
-      <c r="J82" s="53"/>
-      <c r="K82" s="17"/>
-    </row>
-    <row r="83" spans="1:11">
-      <c r="A83" s="52"/>
-      <c r="B83" s="53">
-        <v>66</v>
-      </c>
-      <c r="C83" s="53" t="s">
-        <v>161</v>
-      </c>
-      <c r="D83" s="53" t="s">
-        <v>162</v>
-      </c>
-      <c r="E83" s="53" t="s">
-        <v>51</v>
-      </c>
-      <c r="F83" s="53"/>
-      <c r="G83" s="53" t="s">
-        <v>163</v>
-      </c>
-      <c r="H83" s="53"/>
-      <c r="I83" s="53"/>
-      <c r="J83" s="53"/>
-      <c r="K83" s="17"/>
-    </row>
-    <row r="84" spans="1:11">
-      <c r="A84" s="52"/>
-      <c r="B84" s="53">
-        <v>67</v>
-      </c>
-      <c r="C84" s="53" t="s">
-        <v>164</v>
-      </c>
-      <c r="D84" s="53" t="s">
-        <v>165</v>
-      </c>
-      <c r="E84" s="53" t="s">
-        <v>51</v>
-      </c>
-      <c r="F84" s="53"/>
-      <c r="G84" s="53" t="s">
-        <v>51</v>
-      </c>
-      <c r="H84" s="53"/>
-      <c r="I84" s="53"/>
-      <c r="J84" s="53"/>
-      <c r="K84" s="17"/>
-    </row>
-    <row r="85" spans="1:11">
-      <c r="A85" s="52"/>
-      <c r="B85" s="53">
-        <v>68</v>
-      </c>
-      <c r="C85" s="53" t="s">
-        <v>166</v>
-      </c>
-      <c r="D85" s="53" t="s">
-        <v>162</v>
-      </c>
-      <c r="E85" s="53" t="s">
-        <v>167</v>
-      </c>
-      <c r="F85" s="53"/>
-      <c r="G85" s="53" t="s">
-        <v>163</v>
-      </c>
-      <c r="H85" s="53"/>
-      <c r="I85" s="53"/>
-      <c r="J85" s="53"/>
-      <c r="K85" s="17"/>
-    </row>
-    <row r="86" spans="1:11">
-      <c r="A86" s="52"/>
-      <c r="B86" s="53">
-        <v>69</v>
-      </c>
-      <c r="C86" s="53" t="s">
-        <v>168</v>
-      </c>
-      <c r="D86" s="53" t="s">
-        <v>38</v>
-      </c>
-      <c r="E86" s="53" t="s">
-        <v>169</v>
-      </c>
-      <c r="F86" s="53"/>
-      <c r="G86" s="53" t="s">
-        <v>170</v>
-      </c>
-      <c r="H86" s="53"/>
-      <c r="I86" s="53"/>
-      <c r="J86" s="53"/>
-      <c r="K86" s="17"/>
-    </row>
-    <row r="87" spans="1:11">
-      <c r="A87" s="52"/>
-      <c r="B87" s="53">
-        <v>70</v>
-      </c>
-      <c r="C87" s="53" t="s">
-        <v>171</v>
-      </c>
-      <c r="D87" s="53" t="s">
-        <v>38</v>
-      </c>
-      <c r="E87" s="53" t="s">
-        <v>169</v>
-      </c>
-      <c r="F87" s="53"/>
-      <c r="G87" s="53" t="s">
-        <v>172</v>
-      </c>
-      <c r="H87" s="53"/>
-      <c r="I87" s="53"/>
-      <c r="J87" s="53"/>
-      <c r="K87" s="17"/>
-    </row>
-    <row r="88" spans="1:11">
-      <c r="A88" s="52"/>
-      <c r="B88" s="53">
-        <v>71</v>
-      </c>
-      <c r="C88" s="53" t="s">
-        <v>154</v>
-      </c>
-      <c r="D88" s="53" t="s">
-        <v>155</v>
-      </c>
-      <c r="E88" s="53" t="s">
-        <v>156</v>
-      </c>
-      <c r="F88" s="53"/>
-      <c r="G88" s="53">
-        <v>544161389</v>
-      </c>
-      <c r="H88" s="53"/>
-      <c r="I88" s="53"/>
-      <c r="J88" s="53"/>
-      <c r="K88" s="17"/>
-    </row>
-    <row r="89" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A89" s="18"/>
-      <c r="B89" s="24"/>
-      <c r="C89" s="24"/>
-      <c r="D89" s="24"/>
-      <c r="E89" s="35"/>
-      <c r="F89" s="31"/>
-      <c r="G89" s="35"/>
-      <c r="H89" s="31"/>
-      <c r="I89" s="35"/>
-      <c r="J89" s="31"/>
-    </row>
-    <row r="90" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A90" s="18"/>
-      <c r="B90" s="24"/>
-      <c r="C90" s="24"/>
-      <c r="D90" s="24"/>
-      <c r="E90" s="30"/>
-      <c r="F90" s="31"/>
-      <c r="G90" s="32"/>
-      <c r="H90" s="31"/>
-      <c r="I90" s="32"/>
-      <c r="J90" s="31"/>
-    </row>
-    <row r="91" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A91" s="13"/>
-      <c r="B91" s="13"/>
-      <c r="C91" s="13"/>
-      <c r="D91" s="13"/>
-      <c r="E91" s="13"/>
-      <c r="F91" s="13"/>
-      <c r="G91" s="13"/>
-      <c r="H91" s="13"/>
-      <c r="I91" s="13"/>
-      <c r="J91" s="13"/>
-    </row>
-    <row r="92" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A92" s="19"/>
-      <c r="B92" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="C92" s="26"/>
-      <c r="D92" s="26"/>
-      <c r="E92" s="26"/>
-      <c r="F92" s="26"/>
-      <c r="G92" s="26"/>
-      <c r="H92" s="26"/>
-      <c r="I92" s="26"/>
-      <c r="J92" s="26"/>
-    </row>
-    <row r="93" spans="1:11" customHeight="1" ht="9">
-      <c r="A93" s="20"/>
-      <c r="B93" s="20"/>
-      <c r="C93" s="20"/>
-      <c r="D93" s="20"/>
-      <c r="E93" s="20"/>
-      <c r="F93" s="20"/>
-      <c r="G93" s="20"/>
-      <c r="H93" s="20"/>
-      <c r="I93" s="20"/>
-      <c r="J93" s="20"/>
-    </row>
-    <row r="94" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A94" s="20"/>
-      <c r="B94" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="C94" s="26"/>
       <c r="D94" s="26"/>
       <c r="E94" s="26"/>
-      <c r="F94" s="26"/>
-      <c r="G94" s="26"/>
-      <c r="H94" s="26"/>
+      <c r="H94" s="25" t="s">
+        <v>156</v>
+      </c>
       <c r="I94" s="26"/>
       <c r="J94" s="26"/>
     </row>
-    <row r="95" spans="1:11" customHeight="1" ht="15">
-      <c r="A95" s="20"/>
-      <c r="B95" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="C95" s="26"/>
-      <c r="D95" s="26"/>
-      <c r="E95" s="26"/>
-      <c r="F95" s="26"/>
-      <c r="G95" s="26"/>
-      <c r="H95" s="26"/>
-      <c r="I95" s="26"/>
-      <c r="J95" s="26"/>
-    </row>
-    <row r="96" spans="1:11" customHeight="1" ht="15">
-      <c r="A96" s="20"/>
-      <c r="B96" s="27" t="s">
-        <v>176</v>
-      </c>
-      <c r="C96" s="26"/>
-      <c r="D96" s="26"/>
-      <c r="E96" s="26"/>
-      <c r="F96" s="26"/>
-      <c r="G96" s="26"/>
-      <c r="H96" s="26"/>
-      <c r="I96" s="26"/>
-      <c r="J96" s="26"/>
-    </row>
-    <row r="97" spans="1:11" customHeight="1" ht="15">
-      <c r="A97" s="20"/>
-      <c r="B97" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="C97" s="26"/>
-      <c r="D97" s="26"/>
-      <c r="E97" s="26"/>
-      <c r="F97" s="26"/>
-      <c r="G97" s="26"/>
-      <c r="H97" s="26"/>
-      <c r="I97" s="26"/>
-      <c r="J97" s="26"/>
-    </row>
-    <row r="98" spans="1:11" customHeight="1" ht="15">
-      <c r="A98" s="20"/>
-      <c r="B98" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="C98" s="26"/>
-      <c r="D98" s="26"/>
-      <c r="E98" s="26"/>
-      <c r="F98" s="26"/>
-      <c r="G98" s="26"/>
-      <c r="H98" s="26"/>
-      <c r="I98" s="26"/>
-      <c r="J98" s="26"/>
-    </row>
-    <row r="99" spans="1:11" customHeight="1" ht="12">
-      <c r="A99" s="21"/>
-      <c r="B99" s="28"/>
-      <c r="C99" s="26"/>
-      <c r="D99" s="26"/>
-      <c r="E99" s="26"/>
-      <c r="F99" s="26"/>
-      <c r="G99" s="26"/>
-      <c r="H99" s="26"/>
-      <c r="I99" s="26"/>
-      <c r="J99" s="26"/>
-    </row>
-    <row r="100" spans="1:11" customHeight="1" ht="27.75">
-      <c r="A100" s="17"/>
-      <c r="B100" s="29" t="s">
-        <v>179</v>
-      </c>
-      <c r="C100" s="26"/>
-      <c r="D100" s="26"/>
-      <c r="E100" s="26"/>
-      <c r="F100" s="26"/>
-      <c r="G100" s="26"/>
-      <c r="H100" s="26"/>
-      <c r="I100" s="26"/>
-      <c r="J100" s="26"/>
-    </row>
-    <row r="101" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A101" s="22"/>
-      <c r="B101" s="22"/>
-      <c r="C101" s="22"/>
-      <c r="D101" s="22"/>
-      <c r="E101" s="22"/>
-      <c r="H101" s="15"/>
-      <c r="I101" s="15"/>
-      <c r="J101" s="15"/>
-    </row>
-    <row r="102" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C102" s="22"/>
-      <c r="D102" s="22"/>
-      <c r="E102" s="22"/>
-      <c r="I102" s="15"/>
-      <c r="J102" s="15"/>
-    </row>
-    <row r="103" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A103" s="22"/>
-      <c r="B103" s="22"/>
-      <c r="C103" s="25" t="s">
-        <v>180</v>
-      </c>
-      <c r="D103" s="26"/>
-      <c r="E103" s="26"/>
-      <c r="H103" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="I103" s="26"/>
-      <c r="J103" s="26"/>
-    </row>
-    <row r="104" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="105" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C105" s="23"/>
-      <c r="D105" s="23"/>
-      <c r="E105" s="23"/>
-      <c r="H105" s="23"/>
-      <c r="I105" s="23"/>
-      <c r="J105" s="23"/>
-    </row>
-    <row r="106" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="107" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C107" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="D107" s="26"/>
-      <c r="E107" s="26"/>
-      <c r="H107" s="25" t="str">
-        <f>C8</f>
-        <v>Alejandro Cancino Arguello</v>
-      </c>
-      <c r="I107" s="26"/>
-      <c r="J107" s="26"/>
-    </row>
-    <row r="108" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C108" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="D108" s="26"/>
-      <c r="E108" s="26"/>
-      <c r="H108" s="25" t="s">
-        <v>184</v>
-      </c>
-      <c r="I108" s="26"/>
-      <c r="J108" s="26"/>
-    </row>
-    <row r="109" spans="1:11" customHeight="1" ht="15.75">
-      <c r="H109" s="22"/>
-      <c r="I109" s="22"/>
-      <c r="J109" s="22"/>
-    </row>
-    <row r="110" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="111" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A111" s="22"/>
-      <c r="B111" s="22"/>
-      <c r="C111" s="22"/>
-      <c r="D111" s="22"/>
-      <c r="E111" s="22"/>
+    <row r="95" spans="1:11" customHeight="1" ht="15.75">
+      <c r="H95" s="22"/>
+      <c r="I95" s="22"/>
+      <c r="J95" s="22"/>
+    </row>
+    <row r="96" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="97" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A97" s="22"/>
+      <c r="B97" s="22"/>
+      <c r="C97" s="22"/>
+      <c r="D97" s="22"/>
+      <c r="E97" s="22"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -3351,26 +2947,26 @@
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="I16:J16"/>
-    <mergeCell ref="E89:F89"/>
-    <mergeCell ref="G89:H89"/>
-    <mergeCell ref="I89:J89"/>
-    <mergeCell ref="E90:F90"/>
-    <mergeCell ref="G90:H90"/>
-    <mergeCell ref="I90:J90"/>
-    <mergeCell ref="B92:J92"/>
-    <mergeCell ref="C103:E103"/>
-    <mergeCell ref="H103:J103"/>
-    <mergeCell ref="C107:E107"/>
-    <mergeCell ref="H107:J107"/>
-    <mergeCell ref="C108:E108"/>
-    <mergeCell ref="H108:J108"/>
-    <mergeCell ref="B94:J94"/>
-    <mergeCell ref="B95:J95"/>
-    <mergeCell ref="B96:J96"/>
-    <mergeCell ref="B97:J97"/>
-    <mergeCell ref="B98:J98"/>
-    <mergeCell ref="B99:J99"/>
-    <mergeCell ref="B100:J100"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="G76:H76"/>
+    <mergeCell ref="I76:J76"/>
+    <mergeCell ref="B78:J78"/>
+    <mergeCell ref="C89:E89"/>
+    <mergeCell ref="H89:J89"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="H93:J93"/>
+    <mergeCell ref="C94:E94"/>
+    <mergeCell ref="H94:J94"/>
+    <mergeCell ref="B80:J80"/>
+    <mergeCell ref="B81:J81"/>
+    <mergeCell ref="B82:J82"/>
+    <mergeCell ref="B83:J83"/>
+    <mergeCell ref="B84:J84"/>
+    <mergeCell ref="B85:J85"/>
+    <mergeCell ref="B86:J86"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I17:J17"/>
@@ -3545,49 +3141,7 @@
     <mergeCell ref="E74:F74"/>
     <mergeCell ref="G74:H74"/>
     <mergeCell ref="I74:J74"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="G75:H75"/>
-    <mergeCell ref="I75:J75"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="G76:H76"/>
-    <mergeCell ref="I76:J76"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="G77:H77"/>
-    <mergeCell ref="I77:J77"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="G78:H78"/>
-    <mergeCell ref="I78:J78"/>
-    <mergeCell ref="E79:F79"/>
-    <mergeCell ref="G79:H79"/>
-    <mergeCell ref="I79:J79"/>
-    <mergeCell ref="E80:F80"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="I80:J80"/>
-    <mergeCell ref="E81:F81"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="I81:J81"/>
-    <mergeCell ref="E82:F82"/>
-    <mergeCell ref="G82:H82"/>
-    <mergeCell ref="I82:J82"/>
-    <mergeCell ref="E83:F83"/>
-    <mergeCell ref="G83:H83"/>
-    <mergeCell ref="I83:J83"/>
-    <mergeCell ref="E84:F84"/>
-    <mergeCell ref="G84:H84"/>
-    <mergeCell ref="I84:J84"/>
-    <mergeCell ref="E85:F85"/>
-    <mergeCell ref="G85:H85"/>
-    <mergeCell ref="I85:J85"/>
-    <mergeCell ref="E86:F86"/>
-    <mergeCell ref="G86:H86"/>
-    <mergeCell ref="I86:J86"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="G87:H87"/>
-    <mergeCell ref="I87:J87"/>
-    <mergeCell ref="E88:F88"/>
-    <mergeCell ref="G88:H88"/>
-    <mergeCell ref="I88:J88"/>
-    <mergeCell ref="I17:J88"/>
+    <mergeCell ref="I17:J74"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>

--- a/database/controller_excel/Resguardo_Alejandro_Cancino_Arguello.xlsx
+++ b/database/controller_excel/Resguardo_Alejandro_Cancino_Arguello.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="159">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,13 +41,13 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>15/07/2025</t>
+    <t>04/08/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>fd</t>
+    <t>t</t>
   </si>
   <si>
     <t>Región:</t>
@@ -80,19 +80,388 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
-    <t>Teléfono Celular</t>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>Latitude 5520</t>
+  </si>
+  <si>
+    <t>1446MG00C698</t>
+  </si>
+  <si>
+    <t>Y8GS78BY8</t>
+  </si>
+  <si>
+    <t>C3Y9FG3</t>
+  </si>
+  <si>
+    <t>DVZ-TP-TI-00027</t>
+  </si>
+  <si>
+    <t>Teclado</t>
+  </si>
+  <si>
+    <t>Logitech</t>
+  </si>
+  <si>
+    <t>K120</t>
+  </si>
+  <si>
+    <t>1446MG0C698O</t>
+  </si>
+  <si>
+    <t>Diadema</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>108DB1</t>
+  </si>
+  <si>
+    <t>2032CW</t>
+  </si>
+  <si>
+    <t>Camara Intrinsicamente segura</t>
+  </si>
+  <si>
+    <t>SONIM</t>
+  </si>
+  <si>
+    <t>XP7700</t>
+  </si>
+  <si>
+    <t>SWITCH SAN 1</t>
+  </si>
+  <si>
+    <t>POWERCONNECT 6224</t>
+  </si>
+  <si>
+    <t>D50KTS1</t>
+  </si>
+  <si>
+    <t>SWITCH SAN 2</t>
+  </si>
+  <si>
+    <t>J50KTS1</t>
+  </si>
+  <si>
+    <t>CALL MANAGER NUEVO</t>
   </si>
   <si>
     <t>CISCO</t>
   </si>
   <si>
+    <t>UCS C220M3BE</t>
+  </si>
+  <si>
+    <t>220M3222</t>
+  </si>
+  <si>
+    <t>SERVIDOR 19</t>
+  </si>
+  <si>
+    <t>POWEREDGE R710</t>
+  </si>
+  <si>
+    <t>BRNFSL1</t>
+  </si>
+  <si>
+    <t>UNIDAD DE CINTAS 19</t>
+  </si>
+  <si>
+    <t>POWER VAULT 114 X</t>
+  </si>
+  <si>
+    <t>YN106813H628</t>
+  </si>
+  <si>
+    <t>SERVIDOR 27</t>
+  </si>
+  <si>
+    <t>POWEREDGE 2950</t>
+  </si>
+  <si>
+    <t>DPBP6K1</t>
+  </si>
+  <si>
+    <t>SERVIDOR 29</t>
+  </si>
+  <si>
+    <t>POWEREDGE R320</t>
+  </si>
+  <si>
+    <t>D64MW12</t>
+  </si>
+  <si>
+    <t>DVR HIKVISION</t>
+  </si>
+  <si>
+    <t>HIKVISION</t>
+  </si>
+  <si>
+    <t>DS-7716NI-I4/16P</t>
+  </si>
+  <si>
+    <t>Switch 8 Puertos</t>
+  </si>
+  <si>
+    <t>Planet</t>
+  </si>
+  <si>
+    <t>GSD-804P</t>
+  </si>
+  <si>
+    <t>A350106300034</t>
+  </si>
+  <si>
+    <t>Access PRO</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>AP233</t>
+  </si>
+  <si>
+    <t>AP234</t>
+  </si>
+  <si>
+    <t>Switch</t>
+  </si>
+  <si>
+    <t>CATALYST 2960-X SERIES</t>
+  </si>
+  <si>
+    <t>FCW1906B1MY</t>
+  </si>
+  <si>
+    <t>FCW1906B1LJ</t>
+  </si>
+  <si>
+    <t>FCW1906B1MM</t>
+  </si>
+  <si>
+    <t>CATALYST 2960-X SERIES POE+</t>
+  </si>
+  <si>
+    <t>FOC1710Y1FV</t>
+  </si>
+  <si>
+    <t>CATALYST 3560</t>
+  </si>
+  <si>
+    <t>CAT0948R334</t>
+  </si>
+  <si>
+    <t>F0C1503Z3QP</t>
+  </si>
+  <si>
+    <t>F0C1514X0EZ</t>
+  </si>
+  <si>
+    <t>ROUTER</t>
+  </si>
+  <si>
+    <t>CISCO 1900 SERIES</t>
+  </si>
+  <si>
+    <t>FTX174386AU</t>
+  </si>
+  <si>
+    <t>UPS</t>
+  </si>
+  <si>
+    <t>APC</t>
+  </si>
+  <si>
+    <t>APC Galaxy 3500</t>
+  </si>
+  <si>
+    <t>G35TF30KB4F</t>
+  </si>
+  <si>
+    <t>ACCESSPOINT</t>
+  </si>
+  <si>
+    <t>FORTINET</t>
+  </si>
+  <si>
+    <t>221E</t>
+  </si>
+  <si>
+    <t>FP221ETF22083298</t>
+  </si>
+  <si>
+    <t>FP221ETF22083291</t>
+  </si>
+  <si>
+    <t>FP221ETF22083300</t>
+  </si>
+  <si>
+    <t>FP221ETF22083299</t>
+  </si>
+  <si>
+    <t>Amplificador celular</t>
+  </si>
+  <si>
+    <t>EPCOM</t>
+  </si>
+  <si>
+    <t>G08W27160502</t>
+  </si>
+  <si>
+    <t>Camara Fija</t>
+  </si>
+  <si>
+    <t>DS-2CD2432F-I</t>
+  </si>
+  <si>
+    <t>I20140922CCWR480540694</t>
+  </si>
+  <si>
+    <t>DS-2CD1043G0-I</t>
+  </si>
+  <si>
+    <t>I20220824AAWRK47327687</t>
+  </si>
+  <si>
+    <t>Camara PTZ</t>
+  </si>
+  <si>
+    <t>DS-2DE4215IW-DE</t>
+  </si>
+  <si>
+    <t>DE20190506CCWRD16875921W</t>
+  </si>
+  <si>
+    <t>DS-2CD2232-I5</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802490</t>
+  </si>
+  <si>
+    <t>I20200824AAWRK47327674</t>
+  </si>
+  <si>
+    <t>DS-2DE7174-A</t>
+  </si>
+  <si>
+    <t>A20150122CCWR500502005</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802472</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802475</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802494</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802491</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802480</t>
+  </si>
+  <si>
+    <t>I520150207CCWR502802497</t>
+  </si>
+  <si>
+    <t>DS-2CD2422FWD-IW</t>
+  </si>
+  <si>
+    <t>IW20170808AAWR808998451</t>
+  </si>
+  <si>
+    <t>I20140922CCWR480540755</t>
+  </si>
+  <si>
+    <t>Cargador de Laptop</t>
+  </si>
+  <si>
+    <t>LA65NM190</t>
+  </si>
+  <si>
+    <t>CN-0VT148-LOC00-18C-3AF4-A02</t>
+  </si>
+  <si>
+    <t>DS-2CD2T42WD-I5</t>
+  </si>
+  <si>
+    <t>I520160810BBWR633078836</t>
+  </si>
+  <si>
+    <t>I520160810BBWR633078735</t>
+  </si>
+  <si>
+    <t>I520160810BBWR633078506</t>
+  </si>
+  <si>
+    <t>A20150122CCWR500502035</t>
+  </si>
+  <si>
+    <t>KOBLENZ</t>
+  </si>
+  <si>
+    <t>4816 R</t>
+  </si>
+  <si>
+    <t>16-09-17766</t>
+  </si>
+  <si>
+    <t>Lector Biometrico</t>
+  </si>
+  <si>
+    <t>BioEntry W2</t>
+  </si>
+  <si>
+    <t>BEW2-0DP</t>
+  </si>
+  <si>
+    <t>I20140922CCWR480540785</t>
+  </si>
+  <si>
+    <t>Equipo de Videoconferencia</t>
+  </si>
+  <si>
+    <t>Chromebox</t>
+  </si>
+  <si>
+    <t>Asus</t>
+  </si>
+  <si>
+    <t>H6MSCX001323</t>
+  </si>
+  <si>
+    <t>Camara Videoconferencia</t>
+  </si>
+  <si>
+    <t>1742LZ106AB8</t>
+  </si>
+  <si>
+    <t>Conectores Videoconferencia</t>
+  </si>
+  <si>
+    <t>Conectores</t>
+  </si>
+  <si>
+    <t>Estrella Bocinas Videoconferencia</t>
+  </si>
+  <si>
+    <t>886-000056</t>
+  </si>
+  <si>
+    <t>Estrella</t>
+  </si>
+  <si>
     <t>Cisco UC Phone CP-8831</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Linea: NA</t>
+    <t>FCH19052AQZ</t>
   </si>
   <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
@@ -395,7 +764,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="54">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
@@ -513,9 +882,6 @@
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="2" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -792,7 +1158,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K99"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="12.5546875" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="true" style="0"/>
@@ -1034,244 +1400,1583 @@
       <c r="J17" s="51"/>
       <c r="K17" s="17"/>
     </row>
-    <row r="18" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A18" s="18"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="54" t="s">
+    <row r="18" spans="1:11">
+      <c r="A18" s="52"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="F18" s="31"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="31"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="31"/>
-    </row>
-    <row r="19" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A19" s="18"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="31"/>
-    </row>
-    <row r="20" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A20" s="13"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-    </row>
-    <row r="21" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A21" s="19"/>
-      <c r="B21" s="33" t="s">
+      <c r="F18" s="53"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="53"/>
+      <c r="K18" s="17"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="52"/>
+      <c r="B19" s="53">
+        <v>2</v>
+      </c>
+      <c r="C19" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="53"/>
+      <c r="G19" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
-    </row>
-    <row r="22" spans="1:11" customHeight="1" ht="9">
-      <c r="A22" s="20"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-    </row>
-    <row r="23" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A23" s="20"/>
-      <c r="B23" s="27" t="s">
+      <c r="H19" s="53"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="17"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="52"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-    </row>
-    <row r="24" spans="1:11" customHeight="1" ht="15">
-      <c r="A24" s="20"/>
-      <c r="B24" s="27" t="s">
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="17"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="52"/>
+      <c r="B21" s="53">
+        <v>3</v>
+      </c>
+      <c r="C21" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
-    </row>
-    <row r="25" spans="1:11" customHeight="1" ht="15">
-      <c r="A25" s="20"/>
-      <c r="B25" s="27" t="s">
+      <c r="D21" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
-    </row>
-    <row r="26" spans="1:11" customHeight="1" ht="15">
-      <c r="A26" s="20"/>
-      <c r="B26" s="27" t="s">
+      <c r="E21" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
-    </row>
-    <row r="27" spans="1:11" customHeight="1" ht="15">
-      <c r="A27" s="20"/>
-      <c r="B27" s="27" t="s">
+      <c r="F21" s="53"/>
+      <c r="G21" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-    </row>
-    <row r="28" spans="1:11" customHeight="1" ht="12">
-      <c r="A28" s="21"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-    </row>
-    <row r="29" spans="1:11" customHeight="1" ht="27.75">
-      <c r="A29" s="17"/>
-      <c r="B29" s="29" t="s">
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="17"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="52"/>
+      <c r="B22" s="53">
+        <v>4</v>
+      </c>
+      <c r="C22" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-    </row>
-    <row r="30" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A30" s="22"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-    </row>
-    <row r="31" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-    </row>
-    <row r="32" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="25" t="s">
+      <c r="D22" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="H32" s="34" t="s">
+      <c r="E22" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
-    </row>
-    <row r="33" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="34" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="23"/>
-      <c r="J34" s="23"/>
-    </row>
-    <row r="35" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="36" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C36" s="25" t="s">
+      <c r="F22" s="53"/>
+      <c r="G22" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="17"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="52"/>
+      <c r="B23" s="53">
+        <v>5</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53">
+        <v>14187000333707</v>
+      </c>
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="17"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="52"/>
+      <c r="B24" s="53">
         <v>6</v>
       </c>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
-      <c r="H36" s="25" t="str">
+      <c r="C24" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="53"/>
+      <c r="K24" s="17"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="52"/>
+      <c r="B25" s="53">
+        <v>7</v>
+      </c>
+      <c r="C25" s="53" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="17"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="52"/>
+      <c r="B26" s="53">
+        <v>8</v>
+      </c>
+      <c r="C26" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="17"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="52"/>
+      <c r="B27" s="53">
+        <v>9</v>
+      </c>
+      <c r="C27" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="17"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="52"/>
+      <c r="B28" s="53">
+        <v>10</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="17"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="52"/>
+      <c r="B29" s="53">
+        <v>11</v>
+      </c>
+      <c r="C29" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="17"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="52"/>
+      <c r="B30" s="53">
+        <v>12</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="H30" s="53"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="17"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="52"/>
+      <c r="B31" s="53">
+        <v>13</v>
+      </c>
+      <c r="C31" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="E31" s="53" t="s">
+        <v>62</v>
+      </c>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53">
+        <v>647235228</v>
+      </c>
+      <c r="H31" s="53"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="17"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="52"/>
+      <c r="B32" s="53">
+        <v>14</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="53" t="s">
+        <v>64</v>
+      </c>
+      <c r="E32" s="53" t="s">
+        <v>65</v>
+      </c>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="17"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="52"/>
+      <c r="B33" s="53">
+        <v>15</v>
+      </c>
+      <c r="C33" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="E33" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="F33" s="53"/>
+      <c r="G33" s="53" t="s">
+        <v>69</v>
+      </c>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="17"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="52"/>
+      <c r="B34" s="53">
+        <v>16</v>
+      </c>
+      <c r="C34" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="E34" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="H34" s="53"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="17"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="52"/>
+      <c r="B35" s="53">
+        <v>17</v>
+      </c>
+      <c r="C35" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="F35" s="53"/>
+      <c r="G35" s="53" t="s">
+        <v>73</v>
+      </c>
+      <c r="H35" s="53"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="17"/>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="52"/>
+      <c r="B36" s="53">
+        <v>18</v>
+      </c>
+      <c r="C36" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53" t="s">
+        <v>74</v>
+      </c>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="17"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="52"/>
+      <c r="B37" s="53">
+        <v>19</v>
+      </c>
+      <c r="C37" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="D37" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53" t="s">
+        <v>75</v>
+      </c>
+      <c r="H37" s="53"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="17"/>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="52"/>
+      <c r="B38" s="53">
+        <v>20</v>
+      </c>
+      <c r="C38" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="D38" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E38" s="53" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53" t="s">
+        <v>77</v>
+      </c>
+      <c r="H38" s="53"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="17"/>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="52"/>
+      <c r="B39" s="53">
+        <v>21</v>
+      </c>
+      <c r="C39" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="D39" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E39" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="F39" s="53"/>
+      <c r="G39" s="53" t="s">
+        <v>79</v>
+      </c>
+      <c r="H39" s="53"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="17"/>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="52"/>
+      <c r="B40" s="53">
+        <v>22</v>
+      </c>
+      <c r="C40" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="D40" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E40" s="53" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" s="53"/>
+      <c r="G40" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="H40" s="53"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="17"/>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="52"/>
+      <c r="B41" s="53">
+        <v>23</v>
+      </c>
+      <c r="C41" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="D41" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E41" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="F41" s="53"/>
+      <c r="G41" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="H41" s="53"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="17"/>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="52"/>
+      <c r="B42" s="53">
+        <v>24</v>
+      </c>
+      <c r="C42" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="D42" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E42" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="F42" s="53"/>
+      <c r="G42" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="H42" s="53"/>
+      <c r="I42" s="53"/>
+      <c r="J42" s="53"/>
+      <c r="K42" s="17"/>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="52"/>
+      <c r="B43" s="53">
+        <v>25</v>
+      </c>
+      <c r="C43" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="D43" s="53" t="s">
+        <v>86</v>
+      </c>
+      <c r="E43" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="F43" s="53"/>
+      <c r="G43" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="H43" s="53"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="17"/>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="52"/>
+      <c r="B44" s="53">
+        <v>26</v>
+      </c>
+      <c r="C44" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="D44" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="E44" s="53" t="s">
+        <v>91</v>
+      </c>
+      <c r="F44" s="53"/>
+      <c r="G44" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="H44" s="53"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="53"/>
+      <c r="K44" s="17"/>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="52"/>
+      <c r="B45" s="53">
+        <v>27</v>
+      </c>
+      <c r="C45" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="D45" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="E45" s="53" t="s">
+        <v>91</v>
+      </c>
+      <c r="F45" s="53"/>
+      <c r="G45" s="53" t="s">
+        <v>93</v>
+      </c>
+      <c r="H45" s="53"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="17"/>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="52"/>
+      <c r="B46" s="53">
+        <v>28</v>
+      </c>
+      <c r="C46" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="D46" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="E46" s="53" t="s">
+        <v>91</v>
+      </c>
+      <c r="F46" s="53"/>
+      <c r="G46" s="53" t="s">
+        <v>94</v>
+      </c>
+      <c r="H46" s="53"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="17"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="52"/>
+      <c r="B47" s="53">
+        <v>29</v>
+      </c>
+      <c r="C47" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="D47" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="E47" s="53" t="s">
+        <v>91</v>
+      </c>
+      <c r="F47" s="53"/>
+      <c r="G47" s="53" t="s">
+        <v>95</v>
+      </c>
+      <c r="H47" s="53"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="17"/>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="52"/>
+      <c r="B48" s="53">
+        <v>30</v>
+      </c>
+      <c r="C48" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="D48" s="53" t="s">
+        <v>97</v>
+      </c>
+      <c r="E48" s="53" t="s">
+        <v>97</v>
+      </c>
+      <c r="F48" s="53"/>
+      <c r="G48" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="H48" s="53"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="17"/>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="52"/>
+      <c r="B49" s="53">
+        <v>31</v>
+      </c>
+      <c r="C49" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="D49" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="E49" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="F49" s="53"/>
+      <c r="G49" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="H49" s="53"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="17"/>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="52"/>
+      <c r="B50" s="53">
+        <v>32</v>
+      </c>
+      <c r="C50" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="D50" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="E50" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="F50" s="53"/>
+      <c r="G50" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="H50" s="53"/>
+      <c r="I50" s="53"/>
+      <c r="J50" s="53"/>
+      <c r="K50" s="17"/>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="52"/>
+      <c r="B51" s="53">
+        <v>33</v>
+      </c>
+      <c r="C51" s="53" t="s">
+        <v>104</v>
+      </c>
+      <c r="D51" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="E51" s="53" t="s">
+        <v>105</v>
+      </c>
+      <c r="F51" s="53"/>
+      <c r="G51" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="H51" s="53"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="17"/>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" s="52"/>
+      <c r="B52" s="53">
+        <v>34</v>
+      </c>
+      <c r="C52" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="D52" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="E52" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="F52" s="53"/>
+      <c r="G52" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="H52" s="53"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="53"/>
+      <c r="K52" s="17"/>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" s="52"/>
+      <c r="B53" s="53">
+        <v>35</v>
+      </c>
+      <c r="C53" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="D53" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="E53" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="F53" s="53"/>
+      <c r="G53" s="53" t="s">
+        <v>109</v>
+      </c>
+      <c r="H53" s="53"/>
+      <c r="I53" s="53"/>
+      <c r="J53" s="53"/>
+      <c r="K53" s="17"/>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" s="52"/>
+      <c r="B54" s="53">
+        <v>36</v>
+      </c>
+      <c r="C54" s="53" t="s">
+        <v>104</v>
+      </c>
+      <c r="D54" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="E54" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="F54" s="53"/>
+      <c r="G54" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="H54" s="53"/>
+      <c r="I54" s="53"/>
+      <c r="J54" s="53"/>
+      <c r="K54" s="17"/>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" s="52"/>
+      <c r="B55" s="53">
+        <v>37</v>
+      </c>
+      <c r="C55" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="D55" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="E55" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="F55" s="53"/>
+      <c r="G55" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="H55" s="53"/>
+      <c r="I55" s="53"/>
+      <c r="J55" s="53"/>
+      <c r="K55" s="17"/>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" s="52"/>
+      <c r="B56" s="53">
+        <v>38</v>
+      </c>
+      <c r="C56" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="D56" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="E56" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="F56" s="53"/>
+      <c r="G56" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="H56" s="53"/>
+      <c r="I56" s="53"/>
+      <c r="J56" s="53"/>
+      <c r="K56" s="17"/>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" s="52"/>
+      <c r="B57" s="53">
+        <v>39</v>
+      </c>
+      <c r="C57" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="D57" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="E57" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="F57" s="53"/>
+      <c r="G57" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="H57" s="53"/>
+      <c r="I57" s="53"/>
+      <c r="J57" s="53"/>
+      <c r="K57" s="17"/>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58" s="52"/>
+      <c r="B58" s="53">
+        <v>40</v>
+      </c>
+      <c r="C58" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="D58" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="E58" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="F58" s="53"/>
+      <c r="G58" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="H58" s="53"/>
+      <c r="I58" s="53"/>
+      <c r="J58" s="53"/>
+      <c r="K58" s="17"/>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" s="52"/>
+      <c r="B59" s="53">
+        <v>41</v>
+      </c>
+      <c r="C59" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="D59" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="E59" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="F59" s="53"/>
+      <c r="G59" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="H59" s="53"/>
+      <c r="I59" s="53"/>
+      <c r="J59" s="53"/>
+      <c r="K59" s="17"/>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60" s="52"/>
+      <c r="B60" s="53">
+        <v>42</v>
+      </c>
+      <c r="C60" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="D60" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="E60" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="F60" s="53"/>
+      <c r="G60" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="H60" s="53"/>
+      <c r="I60" s="53"/>
+      <c r="J60" s="53"/>
+      <c r="K60" s="17"/>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61" s="52"/>
+      <c r="B61" s="53">
+        <v>43</v>
+      </c>
+      <c r="C61" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="D61" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="E61" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="F61" s="53"/>
+      <c r="G61" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="H61" s="53"/>
+      <c r="I61" s="53"/>
+      <c r="J61" s="53"/>
+      <c r="K61" s="17"/>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" s="52"/>
+      <c r="B62" s="53">
+        <v>44</v>
+      </c>
+      <c r="C62" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="D62" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="E62" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="F62" s="53"/>
+      <c r="G62" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="H62" s="53"/>
+      <c r="I62" s="53"/>
+      <c r="J62" s="53"/>
+      <c r="K62" s="17"/>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" s="52"/>
+      <c r="B63" s="53">
+        <v>45</v>
+      </c>
+      <c r="C63" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="D63" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="E63" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="F63" s="53"/>
+      <c r="G63" s="53" t="s">
+        <v>123</v>
+      </c>
+      <c r="H63" s="53"/>
+      <c r="I63" s="53"/>
+      <c r="J63" s="53"/>
+      <c r="K63" s="17"/>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" s="52"/>
+      <c r="B64" s="53">
+        <v>46</v>
+      </c>
+      <c r="C64" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="D64" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="E64" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="F64" s="53"/>
+      <c r="G64" s="53" t="s">
+        <v>125</v>
+      </c>
+      <c r="H64" s="53"/>
+      <c r="I64" s="53"/>
+      <c r="J64" s="53"/>
+      <c r="K64" s="17"/>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" s="52"/>
+      <c r="B65" s="53">
+        <v>47</v>
+      </c>
+      <c r="C65" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="D65" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="E65" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="F65" s="53"/>
+      <c r="G65" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="H65" s="53"/>
+      <c r="I65" s="53"/>
+      <c r="J65" s="53"/>
+      <c r="K65" s="17"/>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" s="52"/>
+      <c r="B66" s="53">
+        <v>48</v>
+      </c>
+      <c r="C66" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="D66" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="E66" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="F66" s="53"/>
+      <c r="G66" s="53" t="s">
+        <v>127</v>
+      </c>
+      <c r="H66" s="53"/>
+      <c r="I66" s="53"/>
+      <c r="J66" s="53"/>
+      <c r="K66" s="17"/>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67" s="52"/>
+      <c r="B67" s="53">
+        <v>49</v>
+      </c>
+      <c r="C67" s="53" t="s">
+        <v>104</v>
+      </c>
+      <c r="D67" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="E67" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="F67" s="53"/>
+      <c r="G67" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="H67" s="53"/>
+      <c r="I67" s="53"/>
+      <c r="J67" s="53"/>
+      <c r="K67" s="17"/>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68" s="52"/>
+      <c r="B68" s="53">
+        <v>50</v>
+      </c>
+      <c r="C68" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="D68" s="53" t="s">
+        <v>129</v>
+      </c>
+      <c r="E68" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="F68" s="53"/>
+      <c r="G68" s="53" t="s">
+        <v>131</v>
+      </c>
+      <c r="H68" s="53"/>
+      <c r="I68" s="53"/>
+      <c r="J68" s="53"/>
+      <c r="K68" s="17"/>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" s="52"/>
+      <c r="B69" s="53">
+        <v>51</v>
+      </c>
+      <c r="C69" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="D69" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="E69" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="F69" s="53"/>
+      <c r="G69" s="53">
+        <v>544161389</v>
+      </c>
+      <c r="H69" s="53"/>
+      <c r="I69" s="53"/>
+      <c r="J69" s="53"/>
+      <c r="K69" s="17"/>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" s="52"/>
+      <c r="B70" s="53">
+        <v>52</v>
+      </c>
+      <c r="C70" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="D70" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="E70" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="F70" s="53"/>
+      <c r="G70" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="H70" s="53"/>
+      <c r="I70" s="53"/>
+      <c r="J70" s="53"/>
+      <c r="K70" s="17"/>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" s="52"/>
+      <c r="B71" s="53">
+        <v>53</v>
+      </c>
+      <c r="C71" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="D71" s="53" t="s">
+        <v>137</v>
+      </c>
+      <c r="E71" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="F71" s="53"/>
+      <c r="G71" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="H71" s="53"/>
+      <c r="I71" s="53"/>
+      <c r="J71" s="53"/>
+      <c r="K71" s="17"/>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" s="52"/>
+      <c r="B72" s="53">
+        <v>54</v>
+      </c>
+      <c r="C72" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="D72" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="E72" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="F72" s="53"/>
+      <c r="G72" s="53" t="s">
+        <v>141</v>
+      </c>
+      <c r="H72" s="53"/>
+      <c r="I72" s="53"/>
+      <c r="J72" s="53"/>
+      <c r="K72" s="17"/>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" s="52"/>
+      <c r="B73" s="53">
+        <v>55</v>
+      </c>
+      <c r="C73" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="D73" s="53" t="s">
+        <v>143</v>
+      </c>
+      <c r="E73" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="F73" s="53"/>
+      <c r="G73" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="H73" s="53"/>
+      <c r="I73" s="53"/>
+      <c r="J73" s="53"/>
+      <c r="K73" s="17"/>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" s="52"/>
+      <c r="B74" s="53">
+        <v>56</v>
+      </c>
+      <c r="C74" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="D74" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="E74" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="F74" s="53"/>
+      <c r="G74" s="53" t="s">
+        <v>141</v>
+      </c>
+      <c r="H74" s="53"/>
+      <c r="I74" s="53"/>
+      <c r="J74" s="53"/>
+      <c r="K74" s="17"/>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75" s="52"/>
+      <c r="B75" s="53">
+        <v>57</v>
+      </c>
+      <c r="C75" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="D75" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E75" s="53" t="s">
+        <v>147</v>
+      </c>
+      <c r="F75" s="53"/>
+      <c r="G75" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="H75" s="53"/>
+      <c r="I75" s="53"/>
+      <c r="J75" s="53"/>
+      <c r="K75" s="17"/>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76" s="52"/>
+      <c r="B76" s="53">
+        <v>58</v>
+      </c>
+      <c r="C76" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="D76" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="E76" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="F76" s="53"/>
+      <c r="G76" s="53">
+        <v>544161388</v>
+      </c>
+      <c r="H76" s="53"/>
+      <c r="I76" s="53"/>
+      <c r="J76" s="53"/>
+      <c r="K76" s="17"/>
+    </row>
+    <row r="77" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A77" s="18"/>
+      <c r="B77" s="24"/>
+      <c r="C77" s="24"/>
+      <c r="D77" s="24"/>
+      <c r="E77" s="35"/>
+      <c r="F77" s="31"/>
+      <c r="G77" s="35"/>
+      <c r="H77" s="31"/>
+      <c r="I77" s="35"/>
+      <c r="J77" s="31"/>
+    </row>
+    <row r="78" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A78" s="18"/>
+      <c r="B78" s="24"/>
+      <c r="C78" s="24"/>
+      <c r="D78" s="24"/>
+      <c r="E78" s="30"/>
+      <c r="F78" s="31"/>
+      <c r="G78" s="32"/>
+      <c r="H78" s="31"/>
+      <c r="I78" s="32"/>
+      <c r="J78" s="31"/>
+    </row>
+    <row r="79" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A79" s="13"/>
+      <c r="B79" s="13"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="13"/>
+      <c r="E79" s="13"/>
+      <c r="F79" s="13"/>
+      <c r="G79" s="13"/>
+      <c r="H79" s="13"/>
+      <c r="I79" s="13"/>
+      <c r="J79" s="13"/>
+    </row>
+    <row r="80" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A80" s="19"/>
+      <c r="B80" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
+      <c r="H80" s="26"/>
+      <c r="I80" s="26"/>
+      <c r="J80" s="26"/>
+    </row>
+    <row r="81" spans="1:11" customHeight="1" ht="9">
+      <c r="A81" s="20"/>
+      <c r="B81" s="20"/>
+      <c r="C81" s="20"/>
+      <c r="D81" s="20"/>
+      <c r="E81" s="20"/>
+      <c r="F81" s="20"/>
+      <c r="G81" s="20"/>
+      <c r="H81" s="20"/>
+      <c r="I81" s="20"/>
+      <c r="J81" s="20"/>
+    </row>
+    <row r="82" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A82" s="20"/>
+      <c r="B82" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C82" s="26"/>
+      <c r="D82" s="26"/>
+      <c r="E82" s="26"/>
+      <c r="F82" s="26"/>
+      <c r="G82" s="26"/>
+      <c r="H82" s="26"/>
+      <c r="I82" s="26"/>
+      <c r="J82" s="26"/>
+    </row>
+    <row r="83" spans="1:11" customHeight="1" ht="15">
+      <c r="A83" s="20"/>
+      <c r="B83" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="C83" s="26"/>
+      <c r="D83" s="26"/>
+      <c r="E83" s="26"/>
+      <c r="F83" s="26"/>
+      <c r="G83" s="26"/>
+      <c r="H83" s="26"/>
+      <c r="I83" s="26"/>
+      <c r="J83" s="26"/>
+    </row>
+    <row r="84" spans="1:11" customHeight="1" ht="15">
+      <c r="A84" s="20"/>
+      <c r="B84" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="C84" s="26"/>
+      <c r="D84" s="26"/>
+      <c r="E84" s="26"/>
+      <c r="F84" s="26"/>
+      <c r="G84" s="26"/>
+      <c r="H84" s="26"/>
+      <c r="I84" s="26"/>
+      <c r="J84" s="26"/>
+    </row>
+    <row r="85" spans="1:11" customHeight="1" ht="15">
+      <c r="A85" s="20"/>
+      <c r="B85" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="C85" s="26"/>
+      <c r="D85" s="26"/>
+      <c r="E85" s="26"/>
+      <c r="F85" s="26"/>
+      <c r="G85" s="26"/>
+      <c r="H85" s="26"/>
+      <c r="I85" s="26"/>
+      <c r="J85" s="26"/>
+    </row>
+    <row r="86" spans="1:11" customHeight="1" ht="15">
+      <c r="A86" s="20"/>
+      <c r="B86" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C86" s="26"/>
+      <c r="D86" s="26"/>
+      <c r="E86" s="26"/>
+      <c r="F86" s="26"/>
+      <c r="G86" s="26"/>
+      <c r="H86" s="26"/>
+      <c r="I86" s="26"/>
+      <c r="J86" s="26"/>
+    </row>
+    <row r="87" spans="1:11" customHeight="1" ht="12">
+      <c r="A87" s="21"/>
+      <c r="B87" s="28"/>
+      <c r="C87" s="26"/>
+      <c r="D87" s="26"/>
+      <c r="E87" s="26"/>
+      <c r="F87" s="26"/>
+      <c r="G87" s="26"/>
+      <c r="H87" s="26"/>
+      <c r="I87" s="26"/>
+      <c r="J87" s="26"/>
+    </row>
+    <row r="88" spans="1:11" customHeight="1" ht="27.75">
+      <c r="A88" s="17"/>
+      <c r="B88" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="C88" s="26"/>
+      <c r="D88" s="26"/>
+      <c r="E88" s="26"/>
+      <c r="F88" s="26"/>
+      <c r="G88" s="26"/>
+      <c r="H88" s="26"/>
+      <c r="I88" s="26"/>
+      <c r="J88" s="26"/>
+    </row>
+    <row r="89" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A89" s="22"/>
+      <c r="B89" s="22"/>
+      <c r="C89" s="22"/>
+      <c r="D89" s="22"/>
+      <c r="E89" s="22"/>
+      <c r="H89" s="15"/>
+      <c r="I89" s="15"/>
+      <c r="J89" s="15"/>
+    </row>
+    <row r="90" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="I90" s="15"/>
+      <c r="J90" s="15"/>
+    </row>
+    <row r="91" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A91" s="22"/>
+      <c r="B91" s="22"/>
+      <c r="C91" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="D91" s="26"/>
+      <c r="E91" s="26"/>
+      <c r="H91" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="I91" s="26"/>
+      <c r="J91" s="26"/>
+    </row>
+    <row r="92" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="93" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C93" s="23"/>
+      <c r="D93" s="23"/>
+      <c r="E93" s="23"/>
+      <c r="H93" s="23"/>
+      <c r="I93" s="23"/>
+      <c r="J93" s="23"/>
+    </row>
+    <row r="94" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="95" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C95" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D95" s="26"/>
+      <c r="E95" s="26"/>
+      <c r="H95" s="25" t="str">
         <f>C8</f>
         <v>Alejandro Cancino Arguello</v>
       </c>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
-    </row>
-    <row r="37" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C37" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="H37" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-    </row>
-    <row r="38" spans="1:11" customHeight="1" ht="15.75">
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
-      <c r="J38" s="22"/>
-    </row>
-    <row r="39" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="40" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A40" s="22"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
+      <c r="I95" s="26"/>
+      <c r="J95" s="26"/>
+    </row>
+    <row r="96" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C96" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="D96" s="26"/>
+      <c r="E96" s="26"/>
+      <c r="H96" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="I96" s="26"/>
+      <c r="J96" s="26"/>
+    </row>
+    <row r="97" spans="1:11" customHeight="1" ht="15.75">
+      <c r="H97" s="22"/>
+      <c r="I97" s="22"/>
+      <c r="J97" s="22"/>
+    </row>
+    <row r="98" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="99" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A99" s="22"/>
+      <c r="B99" s="22"/>
+      <c r="C99" s="22"/>
+      <c r="D99" s="22"/>
+      <c r="E99" s="22"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -1286,29 +2991,207 @@
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="I16:J16"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="G77:H77"/>
+    <mergeCell ref="I77:J77"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="G78:H78"/>
+    <mergeCell ref="I78:J78"/>
+    <mergeCell ref="B80:J80"/>
+    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="H91:J91"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="H95:J95"/>
+    <mergeCell ref="C96:E96"/>
+    <mergeCell ref="H96:J96"/>
+    <mergeCell ref="B82:J82"/>
+    <mergeCell ref="B83:J83"/>
+    <mergeCell ref="B84:J84"/>
+    <mergeCell ref="B85:J85"/>
+    <mergeCell ref="B86:J86"/>
+    <mergeCell ref="B87:J87"/>
+    <mergeCell ref="B88:J88"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="I18:J18"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="I19:J19"/>
-    <mergeCell ref="B21:J21"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="B24:J24"/>
-    <mergeCell ref="B25:J25"/>
-    <mergeCell ref="B26:J26"/>
-    <mergeCell ref="B27:J27"/>
-    <mergeCell ref="B28:J28"/>
-    <mergeCell ref="B29:J29"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="I55:J55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="I59:J59"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="I60:J60"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="G61:H61"/>
+    <mergeCell ref="I61:J61"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="I62:J62"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="G63:H63"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="I67:J67"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="G68:H68"/>
+    <mergeCell ref="I68:J68"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="G69:H69"/>
+    <mergeCell ref="I69:J69"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="I70:J70"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="I71:J71"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="G72:H72"/>
+    <mergeCell ref="I72:J72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="G73:H73"/>
+    <mergeCell ref="I73:J73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="G74:H74"/>
+    <mergeCell ref="I74:J74"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="G76:H76"/>
+    <mergeCell ref="I76:J76"/>
+    <mergeCell ref="I17:J76"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>

--- a/database/controller_excel/Resguardo_Alejandro_Cancino_Arguello.xlsx
+++ b/database/controller_excel/Resguardo_Alejandro_Cancino_Arguello.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="157">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,13 +41,13 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>04/08/2025</t>
+    <t>05/08/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>t</t>
+    <t>g</t>
   </si>
   <si>
     <t>Región:</t>
@@ -87,12 +87,6 @@
   </si>
   <si>
     <t>Latitude 5520</t>
-  </si>
-  <si>
-    <t>1446MG00C698</t>
-  </si>
-  <si>
-    <t>Y8GS78BY8</t>
   </si>
   <si>
     <t>C3Y9FG3</t>
@@ -1158,7 +1152,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K99"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="12.5546875" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="true" style="0"/>
@@ -1421,17 +1415,17 @@
         <v>2</v>
       </c>
       <c r="C19" s="53" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D19" s="53" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E19" s="53" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F19" s="53"/>
       <c r="G19" s="53" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H19" s="53"/>
       <c r="I19" s="53"/>
@@ -1440,14 +1434,22 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="52"/>
-      <c r="B20" s="53"/>
-      <c r="C20" s="53"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="51" t="s">
-        <v>27</v>
+      <c r="B20" s="53">
+        <v>3</v>
+      </c>
+      <c r="C20" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="53" t="s">
+        <v>32</v>
       </c>
       <c r="F20" s="53"/>
-      <c r="G20" s="53"/>
+      <c r="G20" s="53" t="s">
+        <v>33</v>
+      </c>
       <c r="H20" s="53"/>
       <c r="I20" s="53"/>
       <c r="J20" s="53"/>
@@ -1456,20 +1458,20 @@
     <row r="21" spans="1:11">
       <c r="A21" s="52"/>
       <c r="B21" s="53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D21" s="53" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E21" s="53" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F21" s="53"/>
-      <c r="G21" s="53" t="s">
-        <v>31</v>
+      <c r="G21" s="53">
+        <v>14187000333707</v>
       </c>
       <c r="H21" s="53"/>
       <c r="I21" s="53"/>
@@ -1479,20 +1481,20 @@
     <row r="22" spans="1:11">
       <c r="A22" s="52"/>
       <c r="B22" s="53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" s="53" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D22" s="53" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E22" s="53" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F22" s="53"/>
       <c r="G22" s="53" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H22" s="53"/>
       <c r="I22" s="53"/>
@@ -1502,20 +1504,20 @@
     <row r="23" spans="1:11">
       <c r="A23" s="52"/>
       <c r="B23" s="53">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23" s="53" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D23" s="53" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E23" s="53" t="s">
         <v>38</v>
       </c>
       <c r="F23" s="53"/>
-      <c r="G23" s="53">
-        <v>14187000333707</v>
+      <c r="G23" s="53" t="s">
+        <v>41</v>
       </c>
       <c r="H23" s="53"/>
       <c r="I23" s="53"/>
@@ -1525,20 +1527,20 @@
     <row r="24" spans="1:11">
       <c r="A24" s="52"/>
       <c r="B24" s="53">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C24" s="53" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D24" s="53" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="E24" s="53" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F24" s="53"/>
       <c r="G24" s="53" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H24" s="53"/>
       <c r="I24" s="53"/>
@@ -1548,20 +1550,20 @@
     <row r="25" spans="1:11">
       <c r="A25" s="52"/>
       <c r="B25" s="53">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C25" s="53" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D25" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E25" s="53" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F25" s="53"/>
       <c r="G25" s="53" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="H25" s="53"/>
       <c r="I25" s="53"/>
@@ -1571,20 +1573,20 @@
     <row r="26" spans="1:11">
       <c r="A26" s="52"/>
       <c r="B26" s="53">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C26" s="53" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D26" s="53" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="E26" s="53" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="53" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H26" s="53"/>
       <c r="I26" s="53"/>
@@ -1594,20 +1596,20 @@
     <row r="27" spans="1:11">
       <c r="A27" s="52"/>
       <c r="B27" s="53">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C27" s="53" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D27" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E27" s="53" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F27" s="53"/>
       <c r="G27" s="53" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H27" s="53"/>
       <c r="I27" s="53"/>
@@ -1617,20 +1619,20 @@
     <row r="28" spans="1:11">
       <c r="A28" s="52"/>
       <c r="B28" s="53">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C28" s="53" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D28" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E28" s="53" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F28" s="53"/>
       <c r="G28" s="53" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H28" s="53"/>
       <c r="I28" s="53"/>
@@ -1640,20 +1642,20 @@
     <row r="29" spans="1:11">
       <c r="A29" s="52"/>
       <c r="B29" s="53">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C29" s="53" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D29" s="53" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="E29" s="53" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F29" s="53"/>
-      <c r="G29" s="53" t="s">
-        <v>56</v>
+      <c r="G29" s="53">
+        <v>647235228</v>
       </c>
       <c r="H29" s="53"/>
       <c r="I29" s="53"/>
@@ -1663,20 +1665,20 @@
     <row r="30" spans="1:11">
       <c r="A30" s="52"/>
       <c r="B30" s="53">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C30" s="53" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D30" s="53" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="E30" s="53" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F30" s="53"/>
       <c r="G30" s="53" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H30" s="53"/>
       <c r="I30" s="53"/>
@@ -1686,20 +1688,20 @@
     <row r="31" spans="1:11">
       <c r="A31" s="52"/>
       <c r="B31" s="53">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C31" s="53" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D31" s="53" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E31" s="53" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F31" s="53"/>
-      <c r="G31" s="53">
-        <v>647235228</v>
+      <c r="G31" s="53" t="s">
+        <v>67</v>
       </c>
       <c r="H31" s="53"/>
       <c r="I31" s="53"/>
@@ -1709,20 +1711,20 @@
     <row r="32" spans="1:11">
       <c r="A32" s="52"/>
       <c r="B32" s="53">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C32" s="53" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D32" s="53" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E32" s="53" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F32" s="53"/>
       <c r="G32" s="53" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H32" s="53"/>
       <c r="I32" s="53"/>
@@ -1732,20 +1734,20 @@
     <row r="33" spans="1:11">
       <c r="A33" s="52"/>
       <c r="B33" s="53">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C33" s="53" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D33" s="53" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="E33" s="53" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F33" s="53"/>
       <c r="G33" s="53" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H33" s="53"/>
       <c r="I33" s="53"/>
@@ -1755,20 +1757,20 @@
     <row r="34" spans="1:11">
       <c r="A34" s="52"/>
       <c r="B34" s="53">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C34" s="53" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D34" s="53" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="E34" s="53" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F34" s="53"/>
       <c r="G34" s="53" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H34" s="53"/>
       <c r="I34" s="53"/>
@@ -1778,16 +1780,16 @@
     <row r="35" spans="1:11">
       <c r="A35" s="52"/>
       <c r="B35" s="53">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C35" s="53" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D35" s="53" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E35" s="53" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F35" s="53"/>
       <c r="G35" s="53" t="s">
@@ -1801,20 +1803,20 @@
     <row r="36" spans="1:11">
       <c r="A36" s="52"/>
       <c r="B36" s="53">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C36" s="53" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D36" s="53" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E36" s="53" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F36" s="53"/>
       <c r="G36" s="53" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H36" s="53"/>
       <c r="I36" s="53"/>
@@ -1824,20 +1826,20 @@
     <row r="37" spans="1:11">
       <c r="A37" s="52"/>
       <c r="B37" s="53">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C37" s="53" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D37" s="53" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E37" s="53" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F37" s="53"/>
       <c r="G37" s="53" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H37" s="53"/>
       <c r="I37" s="53"/>
@@ -1847,20 +1849,20 @@
     <row r="38" spans="1:11">
       <c r="A38" s="52"/>
       <c r="B38" s="53">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C38" s="53" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D38" s="53" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E38" s="53" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F38" s="53"/>
       <c r="G38" s="53" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H38" s="53"/>
       <c r="I38" s="53"/>
@@ -1870,16 +1872,16 @@
     <row r="39" spans="1:11">
       <c r="A39" s="52"/>
       <c r="B39" s="53">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C39" s="53" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D39" s="53" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E39" s="53" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F39" s="53"/>
       <c r="G39" s="53" t="s">
@@ -1893,20 +1895,20 @@
     <row r="40" spans="1:11">
       <c r="A40" s="52"/>
       <c r="B40" s="53">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C40" s="53" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D40" s="53" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E40" s="53" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F40" s="53"/>
       <c r="G40" s="53" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H40" s="53"/>
       <c r="I40" s="53"/>
@@ -1916,20 +1918,20 @@
     <row r="41" spans="1:11">
       <c r="A41" s="52"/>
       <c r="B41" s="53">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C41" s="53" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D41" s="53" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="E41" s="53" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="F41" s="53"/>
       <c r="G41" s="53" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H41" s="53"/>
       <c r="I41" s="53"/>
@@ -1939,20 +1941,20 @@
     <row r="42" spans="1:11">
       <c r="A42" s="52"/>
       <c r="B42" s="53">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C42" s="53" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D42" s="53" t="s">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="E42" s="53" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F42" s="53"/>
       <c r="G42" s="53" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="H42" s="53"/>
       <c r="I42" s="53"/>
@@ -1962,20 +1964,20 @@
     <row r="43" spans="1:11">
       <c r="A43" s="52"/>
       <c r="B43" s="53">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C43" s="53" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D43" s="53" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E43" s="53" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F43" s="53"/>
       <c r="G43" s="53" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H43" s="53"/>
       <c r="I43" s="53"/>
@@ -1985,16 +1987,16 @@
     <row r="44" spans="1:11">
       <c r="A44" s="52"/>
       <c r="B44" s="53">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C44" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="D44" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="E44" s="53" t="s">
         <v>89</v>
-      </c>
-      <c r="D44" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="E44" s="53" t="s">
-        <v>91</v>
       </c>
       <c r="F44" s="53"/>
       <c r="G44" s="53" t="s">
@@ -2008,16 +2010,16 @@
     <row r="45" spans="1:11">
       <c r="A45" s="52"/>
       <c r="B45" s="53">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C45" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="D45" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="E45" s="53" t="s">
         <v>89</v>
-      </c>
-      <c r="D45" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="E45" s="53" t="s">
-        <v>91</v>
       </c>
       <c r="F45" s="53"/>
       <c r="G45" s="53" t="s">
@@ -2031,20 +2033,20 @@
     <row r="46" spans="1:11">
       <c r="A46" s="52"/>
       <c r="B46" s="53">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C46" s="53" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D46" s="53" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E46" s="53" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F46" s="53"/>
       <c r="G46" s="53" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H46" s="53"/>
       <c r="I46" s="53"/>
@@ -2054,20 +2056,20 @@
     <row r="47" spans="1:11">
       <c r="A47" s="52"/>
       <c r="B47" s="53">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C47" s="53" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D47" s="53" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="E47" s="53" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F47" s="53"/>
       <c r="G47" s="53" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H47" s="53"/>
       <c r="I47" s="53"/>
@@ -2077,20 +2079,20 @@
     <row r="48" spans="1:11">
       <c r="A48" s="52"/>
       <c r="B48" s="53">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C48" s="53" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D48" s="53" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="E48" s="53" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F48" s="53"/>
       <c r="G48" s="53" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H48" s="53"/>
       <c r="I48" s="53"/>
@@ -2100,20 +2102,20 @@
     <row r="49" spans="1:11">
       <c r="A49" s="52"/>
       <c r="B49" s="53">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C49" s="53" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D49" s="53" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E49" s="53" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F49" s="53"/>
       <c r="G49" s="53" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H49" s="53"/>
       <c r="I49" s="53"/>
@@ -2123,20 +2125,20 @@
     <row r="50" spans="1:11">
       <c r="A50" s="52"/>
       <c r="B50" s="53">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C50" s="53" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D50" s="53" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E50" s="53" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F50" s="53"/>
       <c r="G50" s="53" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H50" s="53"/>
       <c r="I50" s="53"/>
@@ -2146,20 +2148,20 @@
     <row r="51" spans="1:11">
       <c r="A51" s="52"/>
       <c r="B51" s="53">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C51" s="53" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D51" s="53" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E51" s="53" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F51" s="53"/>
       <c r="G51" s="53" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H51" s="53"/>
       <c r="I51" s="53"/>
@@ -2169,20 +2171,20 @@
     <row r="52" spans="1:11">
       <c r="A52" s="52"/>
       <c r="B52" s="53">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C52" s="53" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D52" s="53" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E52" s="53" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F52" s="53"/>
       <c r="G52" s="53" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H52" s="53"/>
       <c r="I52" s="53"/>
@@ -2192,20 +2194,20 @@
     <row r="53" spans="1:11">
       <c r="A53" s="52"/>
       <c r="B53" s="53">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C53" s="53" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D53" s="53" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E53" s="53" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F53" s="53"/>
       <c r="G53" s="53" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H53" s="53"/>
       <c r="I53" s="53"/>
@@ -2215,16 +2217,16 @@
     <row r="54" spans="1:11">
       <c r="A54" s="52"/>
       <c r="B54" s="53">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C54" s="53" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D54" s="53" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E54" s="53" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F54" s="53"/>
       <c r="G54" s="53" t="s">
@@ -2238,16 +2240,16 @@
     <row r="55" spans="1:11">
       <c r="A55" s="52"/>
       <c r="B55" s="53">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C55" s="53" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D55" s="53" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E55" s="53" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F55" s="53"/>
       <c r="G55" s="53" t="s">
@@ -2261,16 +2263,16 @@
     <row r="56" spans="1:11">
       <c r="A56" s="52"/>
       <c r="B56" s="53">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C56" s="53" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D56" s="53" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E56" s="53" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F56" s="53"/>
       <c r="G56" s="53" t="s">
@@ -2284,16 +2286,16 @@
     <row r="57" spans="1:11">
       <c r="A57" s="52"/>
       <c r="B57" s="53">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C57" s="53" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D57" s="53" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E57" s="53" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F57" s="53"/>
       <c r="G57" s="53" t="s">
@@ -2307,16 +2309,16 @@
     <row r="58" spans="1:11">
       <c r="A58" s="52"/>
       <c r="B58" s="53">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C58" s="53" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D58" s="53" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E58" s="53" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F58" s="53"/>
       <c r="G58" s="53" t="s">
@@ -2330,20 +2332,20 @@
     <row r="59" spans="1:11">
       <c r="A59" s="52"/>
       <c r="B59" s="53">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C59" s="53" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D59" s="53" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E59" s="53" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="F59" s="53"/>
       <c r="G59" s="53" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H59" s="53"/>
       <c r="I59" s="53"/>
@@ -2353,20 +2355,20 @@
     <row r="60" spans="1:11">
       <c r="A60" s="52"/>
       <c r="B60" s="53">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C60" s="53" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D60" s="53" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E60" s="53" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="F60" s="53"/>
       <c r="G60" s="53" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H60" s="53"/>
       <c r="I60" s="53"/>
@@ -2376,20 +2378,20 @@
     <row r="61" spans="1:11">
       <c r="A61" s="52"/>
       <c r="B61" s="53">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C61" s="53" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="D61" s="53" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="E61" s="53" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F61" s="53"/>
       <c r="G61" s="53" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H61" s="53"/>
       <c r="I61" s="53"/>
@@ -2399,20 +2401,20 @@
     <row r="62" spans="1:11">
       <c r="A62" s="52"/>
       <c r="B62" s="53">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C62" s="53" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D62" s="53" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E62" s="53" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="F62" s="53"/>
       <c r="G62" s="53" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H62" s="53"/>
       <c r="I62" s="53"/>
@@ -2422,20 +2424,20 @@
     <row r="63" spans="1:11">
       <c r="A63" s="52"/>
       <c r="B63" s="53">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C63" s="53" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="D63" s="53" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="E63" s="53" t="s">
         <v>122</v>
       </c>
       <c r="F63" s="53"/>
       <c r="G63" s="53" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H63" s="53"/>
       <c r="I63" s="53"/>
@@ -2445,16 +2447,16 @@
     <row r="64" spans="1:11">
       <c r="A64" s="52"/>
       <c r="B64" s="53">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C64" s="53" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D64" s="53" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E64" s="53" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F64" s="53"/>
       <c r="G64" s="53" t="s">
@@ -2468,16 +2470,16 @@
     <row r="65" spans="1:11">
       <c r="A65" s="52"/>
       <c r="B65" s="53">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C65" s="53" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D65" s="53" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E65" s="53" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="F65" s="53"/>
       <c r="G65" s="53" t="s">
@@ -2491,20 +2493,20 @@
     <row r="66" spans="1:11">
       <c r="A66" s="52"/>
       <c r="B66" s="53">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C66" s="53" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="D66" s="53" t="s">
-        <v>61</v>
+        <v>127</v>
       </c>
       <c r="E66" s="53" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F66" s="53"/>
       <c r="G66" s="53" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H66" s="53"/>
       <c r="I66" s="53"/>
@@ -2514,20 +2516,20 @@
     <row r="67" spans="1:11">
       <c r="A67" s="52"/>
       <c r="B67" s="53">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C67" s="53" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="D67" s="53" t="s">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="E67" s="53" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="F67" s="53"/>
-      <c r="G67" s="53" t="s">
-        <v>128</v>
+      <c r="G67" s="53">
+        <v>544161389</v>
       </c>
       <c r="H67" s="53"/>
       <c r="I67" s="53"/>
@@ -2537,20 +2539,20 @@
     <row r="68" spans="1:11">
       <c r="A68" s="52"/>
       <c r="B68" s="53">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C68" s="53" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="D68" s="53" t="s">
-        <v>129</v>
+        <v>59</v>
       </c>
       <c r="E68" s="53" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="F68" s="53"/>
       <c r="G68" s="53" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H68" s="53"/>
       <c r="I68" s="53"/>
@@ -2560,20 +2562,20 @@
     <row r="69" spans="1:11">
       <c r="A69" s="52"/>
       <c r="B69" s="53">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C69" s="53" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D69" s="53" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E69" s="53" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F69" s="53"/>
-      <c r="G69" s="53">
-        <v>544161389</v>
+      <c r="G69" s="53" t="s">
+        <v>137</v>
       </c>
       <c r="H69" s="53"/>
       <c r="I69" s="53"/>
@@ -2583,20 +2585,20 @@
     <row r="70" spans="1:11">
       <c r="A70" s="52"/>
       <c r="B70" s="53">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C70" s="53" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="D70" s="53" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E70" s="53" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="F70" s="53"/>
       <c r="G70" s="53" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H70" s="53"/>
       <c r="I70" s="53"/>
@@ -2606,20 +2608,20 @@
     <row r="71" spans="1:11">
       <c r="A71" s="52"/>
       <c r="B71" s="53">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C71" s="53" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D71" s="53" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E71" s="53" t="s">
-        <v>138</v>
+        <v>66</v>
       </c>
       <c r="F71" s="53"/>
       <c r="G71" s="53" t="s">
-        <v>139</v>
+        <v>66</v>
       </c>
       <c r="H71" s="53"/>
       <c r="I71" s="53"/>
@@ -2629,20 +2631,20 @@
     <row r="72" spans="1:11">
       <c r="A72" s="52"/>
       <c r="B72" s="53">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C72" s="53" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D72" s="53" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E72" s="53" t="s">
-        <v>68</v>
+        <v>143</v>
       </c>
       <c r="F72" s="53"/>
       <c r="G72" s="53" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H72" s="53"/>
       <c r="I72" s="53"/>
@@ -2652,20 +2654,20 @@
     <row r="73" spans="1:11">
       <c r="A73" s="52"/>
       <c r="B73" s="53">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C73" s="53" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D73" s="53" t="s">
-        <v>143</v>
+        <v>43</v>
       </c>
       <c r="E73" s="53" t="s">
-        <v>68</v>
+        <v>145</v>
       </c>
       <c r="F73" s="53"/>
       <c r="G73" s="53" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="H73" s="53"/>
       <c r="I73" s="53"/>
@@ -2675,112 +2677,92 @@
     <row r="74" spans="1:11">
       <c r="A74" s="52"/>
       <c r="B74" s="53">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C74" s="53" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="D74" s="53" t="s">
-        <v>29</v>
+        <v>131</v>
       </c>
       <c r="E74" s="53" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="F74" s="53"/>
-      <c r="G74" s="53" t="s">
-        <v>141</v>
+      <c r="G74" s="53">
+        <v>544161388</v>
       </c>
       <c r="H74" s="53"/>
       <c r="I74" s="53"/>
       <c r="J74" s="53"/>
       <c r="K74" s="17"/>
     </row>
-    <row r="75" spans="1:11">
-      <c r="A75" s="52"/>
-      <c r="B75" s="53">
-        <v>57</v>
-      </c>
-      <c r="C75" s="53" t="s">
-        <v>146</v>
-      </c>
-      <c r="D75" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="E75" s="53" t="s">
+    <row r="75" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A75" s="18"/>
+      <c r="B75" s="24"/>
+      <c r="C75" s="24"/>
+      <c r="D75" s="24"/>
+      <c r="E75" s="35"/>
+      <c r="F75" s="31"/>
+      <c r="G75" s="35"/>
+      <c r="H75" s="31"/>
+      <c r="I75" s="35"/>
+      <c r="J75" s="31"/>
+    </row>
+    <row r="76" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A76" s="18"/>
+      <c r="B76" s="24"/>
+      <c r="C76" s="24"/>
+      <c r="D76" s="24"/>
+      <c r="E76" s="30"/>
+      <c r="F76" s="31"/>
+      <c r="G76" s="32"/>
+      <c r="H76" s="31"/>
+      <c r="I76" s="32"/>
+      <c r="J76" s="31"/>
+    </row>
+    <row r="77" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A77" s="13"/>
+      <c r="B77" s="13"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="13"/>
+      <c r="E77" s="13"/>
+      <c r="F77" s="13"/>
+      <c r="G77" s="13"/>
+      <c r="H77" s="13"/>
+      <c r="I77" s="13"/>
+      <c r="J77" s="13"/>
+    </row>
+    <row r="78" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A78" s="19"/>
+      <c r="B78" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="F75" s="53"/>
-      <c r="G75" s="53" t="s">
+      <c r="C78" s="26"/>
+      <c r="D78" s="26"/>
+      <c r="E78" s="26"/>
+      <c r="F78" s="26"/>
+      <c r="G78" s="26"/>
+      <c r="H78" s="26"/>
+      <c r="I78" s="26"/>
+      <c r="J78" s="26"/>
+    </row>
+    <row r="79" spans="1:11" customHeight="1" ht="9">
+      <c r="A79" s="20"/>
+      <c r="B79" s="20"/>
+      <c r="C79" s="20"/>
+      <c r="D79" s="20"/>
+      <c r="E79" s="20"/>
+      <c r="F79" s="20"/>
+      <c r="G79" s="20"/>
+      <c r="H79" s="20"/>
+      <c r="I79" s="20"/>
+      <c r="J79" s="20"/>
+    </row>
+    <row r="80" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A80" s="20"/>
+      <c r="B80" s="27" t="s">
         <v>148</v>
-      </c>
-      <c r="H75" s="53"/>
-      <c r="I75" s="53"/>
-      <c r="J75" s="53"/>
-      <c r="K75" s="17"/>
-    </row>
-    <row r="76" spans="1:11">
-      <c r="A76" s="52"/>
-      <c r="B76" s="53">
-        <v>58</v>
-      </c>
-      <c r="C76" s="53" t="s">
-        <v>132</v>
-      </c>
-      <c r="D76" s="53" t="s">
-        <v>133</v>
-      </c>
-      <c r="E76" s="53" t="s">
-        <v>134</v>
-      </c>
-      <c r="F76" s="53"/>
-      <c r="G76" s="53">
-        <v>544161388</v>
-      </c>
-      <c r="H76" s="53"/>
-      <c r="I76" s="53"/>
-      <c r="J76" s="53"/>
-      <c r="K76" s="17"/>
-    </row>
-    <row r="77" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A77" s="18"/>
-      <c r="B77" s="24"/>
-      <c r="C77" s="24"/>
-      <c r="D77" s="24"/>
-      <c r="E77" s="35"/>
-      <c r="F77" s="31"/>
-      <c r="G77" s="35"/>
-      <c r="H77" s="31"/>
-      <c r="I77" s="35"/>
-      <c r="J77" s="31"/>
-    </row>
-    <row r="78" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A78" s="18"/>
-      <c r="B78" s="24"/>
-      <c r="C78" s="24"/>
-      <c r="D78" s="24"/>
-      <c r="E78" s="30"/>
-      <c r="F78" s="31"/>
-      <c r="G78" s="32"/>
-      <c r="H78" s="31"/>
-      <c r="I78" s="32"/>
-      <c r="J78" s="31"/>
-    </row>
-    <row r="79" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A79" s="13"/>
-      <c r="B79" s="13"/>
-      <c r="C79" s="13"/>
-      <c r="D79" s="13"/>
-      <c r="E79" s="13"/>
-      <c r="F79" s="13"/>
-      <c r="G79" s="13"/>
-      <c r="H79" s="13"/>
-      <c r="I79" s="13"/>
-      <c r="J79" s="13"/>
-    </row>
-    <row r="80" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A80" s="19"/>
-      <c r="B80" s="33" t="s">
-        <v>149</v>
       </c>
       <c r="C80" s="26"/>
       <c r="D80" s="26"/>
@@ -2791,19 +2773,21 @@
       <c r="I80" s="26"/>
       <c r="J80" s="26"/>
     </row>
-    <row r="81" spans="1:11" customHeight="1" ht="9">
+    <row r="81" spans="1:11" customHeight="1" ht="15">
       <c r="A81" s="20"/>
-      <c r="B81" s="20"/>
-      <c r="C81" s="20"/>
-      <c r="D81" s="20"/>
-      <c r="E81" s="20"/>
-      <c r="F81" s="20"/>
-      <c r="G81" s="20"/>
-      <c r="H81" s="20"/>
-      <c r="I81" s="20"/>
-      <c r="J81" s="20"/>
-    </row>
-    <row r="82" spans="1:11" customHeight="1" ht="15.75">
+      <c r="B81" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C81" s="26"/>
+      <c r="D81" s="26"/>
+      <c r="E81" s="26"/>
+      <c r="F81" s="26"/>
+      <c r="G81" s="26"/>
+      <c r="H81" s="26"/>
+      <c r="I81" s="26"/>
+      <c r="J81" s="26"/>
+    </row>
+    <row r="82" spans="1:11" customHeight="1" ht="15">
       <c r="A82" s="20"/>
       <c r="B82" s="27" t="s">
         <v>150</v>
@@ -2845,11 +2829,9 @@
       <c r="I84" s="26"/>
       <c r="J84" s="26"/>
     </row>
-    <row r="85" spans="1:11" customHeight="1" ht="15">
-      <c r="A85" s="20"/>
-      <c r="B85" s="27" t="s">
-        <v>153</v>
-      </c>
+    <row r="85" spans="1:11" customHeight="1" ht="12">
+      <c r="A85" s="21"/>
+      <c r="B85" s="28"/>
       <c r="C85" s="26"/>
       <c r="D85" s="26"/>
       <c r="E85" s="26"/>
@@ -2859,10 +2841,10 @@
       <c r="I85" s="26"/>
       <c r="J85" s="26"/>
     </row>
-    <row r="86" spans="1:11" customHeight="1" ht="15">
-      <c r="A86" s="20"/>
-      <c r="B86" s="27" t="s">
-        <v>154</v>
+    <row r="86" spans="1:11" customHeight="1" ht="27.75">
+      <c r="A86" s="17"/>
+      <c r="B86" s="29" t="s">
+        <v>153</v>
       </c>
       <c r="C86" s="26"/>
       <c r="D86" s="26"/>
@@ -2873,110 +2855,84 @@
       <c r="I86" s="26"/>
       <c r="J86" s="26"/>
     </row>
-    <row r="87" spans="1:11" customHeight="1" ht="12">
-      <c r="A87" s="21"/>
-      <c r="B87" s="28"/>
-      <c r="C87" s="26"/>
-      <c r="D87" s="26"/>
-      <c r="E87" s="26"/>
-      <c r="F87" s="26"/>
-      <c r="G87" s="26"/>
-      <c r="H87" s="26"/>
-      <c r="I87" s="26"/>
-      <c r="J87" s="26"/>
-    </row>
-    <row r="88" spans="1:11" customHeight="1" ht="27.75">
-      <c r="A88" s="17"/>
-      <c r="B88" s="29" t="s">
-        <v>155</v>
-      </c>
-      <c r="C88" s="26"/>
-      <c r="D88" s="26"/>
-      <c r="E88" s="26"/>
-      <c r="F88" s="26"/>
-      <c r="G88" s="26"/>
-      <c r="H88" s="26"/>
-      <c r="I88" s="26"/>
-      <c r="J88" s="26"/>
+    <row r="87" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A87" s="22"/>
+      <c r="B87" s="22"/>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="H87" s="15"/>
+      <c r="I87" s="15"/>
+      <c r="J87" s="15"/>
+    </row>
+    <row r="88" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="I88" s="15"/>
+      <c r="J88" s="15"/>
     </row>
     <row r="89" spans="1:11" customHeight="1" ht="15.75">
       <c r="A89" s="22"/>
       <c r="B89" s="22"/>
-      <c r="C89" s="22"/>
-      <c r="D89" s="22"/>
-      <c r="E89" s="22"/>
-      <c r="H89" s="15"/>
-      <c r="I89" s="15"/>
-      <c r="J89" s="15"/>
-    </row>
-    <row r="90" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C90" s="22"/>
-      <c r="D90" s="22"/>
-      <c r="E90" s="22"/>
-      <c r="I90" s="15"/>
-      <c r="J90" s="15"/>
-    </row>
+      <c r="C89" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="D89" s="26"/>
+      <c r="E89" s="26"/>
+      <c r="H89" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="I89" s="26"/>
+      <c r="J89" s="26"/>
+    </row>
+    <row r="90" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="91" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A91" s="22"/>
-      <c r="B91" s="22"/>
-      <c r="C91" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="D91" s="26"/>
-      <c r="E91" s="26"/>
-      <c r="H91" s="34" t="s">
-        <v>157</v>
-      </c>
-      <c r="I91" s="26"/>
-      <c r="J91" s="26"/>
+      <c r="C91" s="23"/>
+      <c r="D91" s="23"/>
+      <c r="E91" s="23"/>
+      <c r="H91" s="23"/>
+      <c r="I91" s="23"/>
+      <c r="J91" s="23"/>
     </row>
     <row r="92" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="93" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C93" s="23"/>
-      <c r="D93" s="23"/>
-      <c r="E93" s="23"/>
-      <c r="H93" s="23"/>
-      <c r="I93" s="23"/>
-      <c r="J93" s="23"/>
-    </row>
-    <row r="94" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="95" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C95" s="25" t="s">
+      <c r="C93" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="D95" s="26"/>
-      <c r="E95" s="26"/>
-      <c r="H95" s="25" t="str">
+      <c r="D93" s="26"/>
+      <c r="E93" s="26"/>
+      <c r="H93" s="25" t="str">
         <f>C8</f>
         <v>Alejandro Cancino Arguello</v>
       </c>
-      <c r="I95" s="26"/>
-      <c r="J95" s="26"/>
-    </row>
-    <row r="96" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C96" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="D96" s="26"/>
-      <c r="E96" s="26"/>
-      <c r="H96" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="I96" s="26"/>
-      <c r="J96" s="26"/>
-    </row>
+      <c r="I93" s="26"/>
+      <c r="J93" s="26"/>
+    </row>
+    <row r="94" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C94" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="D94" s="26"/>
+      <c r="E94" s="26"/>
+      <c r="H94" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="I94" s="26"/>
+      <c r="J94" s="26"/>
+    </row>
+    <row r="95" spans="1:11" customHeight="1" ht="15.75">
+      <c r="H95" s="22"/>
+      <c r="I95" s="22"/>
+      <c r="J95" s="22"/>
+    </row>
+    <row r="96" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="97" spans="1:11" customHeight="1" ht="15.75">
-      <c r="H97" s="22"/>
-      <c r="I97" s="22"/>
-      <c r="J97" s="22"/>
-    </row>
-    <row r="98" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="99" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A99" s="22"/>
-      <c r="B99" s="22"/>
-      <c r="C99" s="22"/>
-      <c r="D99" s="22"/>
-      <c r="E99" s="22"/>
+      <c r="A97" s="22"/>
+      <c r="B97" s="22"/>
+      <c r="C97" s="22"/>
+      <c r="D97" s="22"/>
+      <c r="E97" s="22"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -2991,26 +2947,26 @@
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="I16:J16"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="G77:H77"/>
-    <mergeCell ref="I77:J77"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="G78:H78"/>
-    <mergeCell ref="I78:J78"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="G76:H76"/>
+    <mergeCell ref="I76:J76"/>
+    <mergeCell ref="B78:J78"/>
+    <mergeCell ref="C89:E89"/>
+    <mergeCell ref="H89:J89"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="H93:J93"/>
+    <mergeCell ref="C94:E94"/>
+    <mergeCell ref="H94:J94"/>
     <mergeCell ref="B80:J80"/>
-    <mergeCell ref="C91:E91"/>
-    <mergeCell ref="H91:J91"/>
-    <mergeCell ref="C95:E95"/>
-    <mergeCell ref="H95:J95"/>
-    <mergeCell ref="C96:E96"/>
-    <mergeCell ref="H96:J96"/>
+    <mergeCell ref="B81:J81"/>
     <mergeCell ref="B82:J82"/>
     <mergeCell ref="B83:J83"/>
     <mergeCell ref="B84:J84"/>
     <mergeCell ref="B85:J85"/>
     <mergeCell ref="B86:J86"/>
-    <mergeCell ref="B87:J87"/>
-    <mergeCell ref="B88:J88"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I17:J17"/>
@@ -3185,13 +3141,7 @@
     <mergeCell ref="E74:F74"/>
     <mergeCell ref="G74:H74"/>
     <mergeCell ref="I74:J74"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="G75:H75"/>
-    <mergeCell ref="I75:J75"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="G76:H76"/>
-    <mergeCell ref="I76:J76"/>
-    <mergeCell ref="I17:J76"/>
+    <mergeCell ref="I17:J74"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>
